--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -1498,13 +1498,13 @@
     <t>2021-04-14</t>
   </si>
   <si>
-    <t>2021-07-29</t>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2021-04-12</t>
   </si>
   <si>
-    <t>2021-05-13</t>
+    <t>2021-05-14</t>
   </si>
   <si>
     <t>2021-06-29</t>
@@ -90015,7 +90015,7 @@
         <v>494</v>
       </c>
       <c r="E1757">
-        <v>0.8031297453282145</v>
+        <v>0.7022223778705436</v>
       </c>
       <c r="F1757">
         <v>-1</v>
@@ -90024,10 +90024,10 @@
         <v>0.01121005687389684</v>
       </c>
       <c r="H1757">
-        <v>0.01041687025467179</v>
+        <v>0.009997777622129455</v>
       </c>
       <c r="I1757">
-        <v>-0.09318661922505811</v>
+        <v>0.007720748232612706</v>
       </c>
       <c r="J1757">
         <v>1.136375946730918</v>
@@ -90039,10 +90039,10 @@
         <v>5.96</v>
       </c>
       <c r="M1757">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="N1757">
-        <v>5.61</v>
+        <v>5.35</v>
       </c>
       <c r="O1757">
         <v>1</v>
@@ -90315,7 +90315,7 @@
         <v>494</v>
       </c>
       <c r="E1763">
-        <v>0.7367055826788347</v>
+        <v>0.6379966508644053</v>
       </c>
       <c r="F1763">
         <v>-1</v>
@@ -90324,10 +90324,10 @@
         <v>0.01128260525012383</v>
       </c>
       <c r="H1763">
-        <v>0.01048329441732117</v>
+        <v>0.01006200334913559</v>
       </c>
       <c r="I1763">
-        <v>-0.09931083280265973</v>
+        <v>-0.0006019009882303195</v>
       </c>
       <c r="J1763">
         <v>1.15207905846836</v>
@@ -90339,10 +90339,10 @@
         <v>5.96</v>
       </c>
       <c r="M1763">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="N1763">
-        <v>5.61</v>
+        <v>5.35</v>
       </c>
       <c r="O1763">
         <v>1</v>
@@ -90665,7 +90665,7 @@
         <v>494</v>
       </c>
       <c r="E1770">
-        <v>0.5765098542062637</v>
+        <v>0.4831029086769787</v>
       </c>
       <c r="F1770">
         <v>-1</v>
@@ -90674,10 +90674,10 @@
         <v>0.01145757079753358</v>
       </c>
       <c r="H1770">
-        <v>0.01064349014579374</v>
+        <v>0.01021689709132302</v>
       </c>
       <c r="I1770">
-        <v>-0.1140806517398474</v>
+        <v>-0.02067370621056241</v>
       </c>
       <c r="J1770">
         <v>1.189950389076533</v>
@@ -90689,10 +90689,10 @@
         <v>5.96</v>
       </c>
       <c r="M1770">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="N1770">
-        <v>5.61</v>
+        <v>5.35</v>
       </c>
       <c r="O1770">
         <v>1</v>
@@ -90865,7 +90865,7 @@
         <v>496</v>
       </c>
       <c r="E1774">
-        <v>-0.05248472009649507</v>
+        <v>0.01105099382722319</v>
       </c>
       <c r="F1774">
         <v>1</v>
@@ -90874,10 +90874,10 @@
         <v>0.01320773472263048</v>
       </c>
       <c r="H1774">
-        <v>0.0124724847200965</v>
+        <v>0.01270894900617278</v>
       </c>
       <c r="I1774">
-        <v>0.4752500025339801</v>
+        <v>0.5387857164576983</v>
       </c>
       <c r="J1774">
         <v>1.235204086804042</v>
@@ -90889,10 +90889,10 @@
         <v>6.34</v>
       </c>
       <c r="M1774">
-        <v>5.07</v>
+        <v>5.14</v>
       </c>
       <c r="N1774">
-        <v>6.21</v>
+        <v>6.36</v>
       </c>
       <c r="O1774">
         <v>1</v>
@@ -90915,7 +90915,7 @@
         <v>496</v>
       </c>
       <c r="E1775">
-        <v>-0.05248472009649507</v>
+        <v>0.01105099382722319</v>
       </c>
       <c r="F1775">
         <v>1</v>
@@ -90924,10 +90924,10 @@
         <v>0.01325538268176243</v>
       </c>
       <c r="H1775">
-        <v>0.0124724847200965</v>
+        <v>0.01270894900617278</v>
       </c>
       <c r="I1775">
-        <v>0.4028979616659392</v>
+        <v>0.4664336755896574</v>
       </c>
       <c r="J1775">
         <v>1.235204086804042</v>
@@ -90939,10 +90939,10 @@
         <v>6.4</v>
       </c>
       <c r="M1775">
-        <v>5.07</v>
+        <v>5.14</v>
       </c>
       <c r="N1775">
-        <v>6.21</v>
+        <v>6.36</v>
       </c>
       <c r="O1775">
         <v>1</v>
@@ -90965,7 +90965,7 @@
         <v>494</v>
       </c>
       <c r="E1776">
-        <v>0.3850867128189002</v>
+        <v>0.2980152849714663</v>
       </c>
       <c r="F1776">
         <v>-1</v>
@@ -90974,10 +90974,10 @@
         <v>0.01166664288103468</v>
       </c>
       <c r="H1776">
-        <v>0.0108349132871811</v>
+        <v>0.01040198471502853</v>
       </c>
       <c r="I1776">
-        <v>-0.1317295938535761</v>
+        <v>-0.04465816600614225</v>
       </c>
       <c r="J1776">
         <v>1.235204086804042</v>
@@ -90989,10 +90989,10 @@
         <v>5.96</v>
       </c>
       <c r="M1776">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="N1776">
-        <v>5.61</v>
+        <v>5.35</v>
       </c>
       <c r="O1776">
         <v>1</v>
@@ -91165,7 +91165,7 @@
         <v>494</v>
       </c>
       <c r="E1780">
-        <v>1.540985222751717</v>
+        <v>1.415657106632275</v>
       </c>
       <c r="F1780">
         <v>-1</v>
@@ -91174,10 +91174,10 @@
         <v>0.0106018886897215</v>
       </c>
       <c r="H1780">
-        <v>0.009679014777248285</v>
+        <v>0.009284342893367726</v>
       </c>
       <c r="I1780">
-        <v>0.05712608752677895</v>
+        <v>0.1824542036462211</v>
       </c>
       <c r="J1780">
         <v>0.9619420277182702</v>
@@ -91189,10 +91189,10 @@
         <v>6.1</v>
       </c>
       <c r="M1780">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="N1780">
-        <v>5.61</v>
+        <v>5.35</v>
       </c>
       <c r="O1780">
         <v>1</v>
@@ -91415,7 +91415,7 @@
         <v>494</v>
       </c>
       <c r="E1785">
-        <v>1.297858030730952</v>
+        <v>1.180576677467989</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91424,10 +91424,10 @@
         <v>0.0108708804766381</v>
       </c>
       <c r="H1785">
-        <v>0.009922141969269049</v>
+        <v>0.009519423322532011</v>
       </c>
       <c r="I1785">
-        <v>0.03126149263095268</v>
+        <v>0.1485428458939158</v>
       </c>
       <c r="J1785">
         <v>1.01941890526455</v>
@@ -91439,10 +91439,10 @@
         <v>6.1</v>
       </c>
       <c r="M1785">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="N1785">
-        <v>5.61</v>
+        <v>5.35</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91665,7 +91665,7 @@
         <v>494</v>
       </c>
       <c r="E1790">
-        <v>1.060053292195499</v>
+        <v>0.9506425449360734</v>
       </c>
       <c r="F1790">
         <v>-1</v>
@@ -91674,10 +91674,10 @@
         <v>0.01113398359161349</v>
       </c>
       <c r="H1790">
-        <v>0.0101599467078045</v>
+        <v>0.009749357455063926</v>
       </c>
       <c r="I1790">
-        <v>0.005963116191010975</v>
+        <v>0.1153738634504364</v>
       </c>
       <c r="J1790">
         <v>1.075637519575532</v>
@@ -91689,10 +91689,10 @@
         <v>6.1</v>
       </c>
       <c r="M1790">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="N1790">
-        <v>5.61</v>
+        <v>5.35</v>
       </c>
       <c r="O1790">
         <v>1</v>
@@ -91915,7 +91915,7 @@
         <v>494</v>
       </c>
       <c r="E1795">
-        <v>1.002545245251649</v>
+        <v>0.8950378376073855</v>
       </c>
       <c r="F1795">
         <v>-1</v>
@@ -91924,10 +91924,10 @@
         <v>0.01119760951589179</v>
       </c>
       <c r="H1795">
-        <v>0.01021745475474835</v>
+        <v>0.009804962162392614</v>
       </c>
       <c r="I1795">
-        <v>-0.0001547611434418172</v>
+        <v>0.1073526465008214</v>
       </c>
       <c r="J1795">
         <v>1.089232802540981</v>
@@ -91939,10 +91939,10 @@
         <v>6.1</v>
       </c>
       <c r="M1795">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="N1795">
-        <v>5.61</v>
+        <v>5.35</v>
       </c>
       <c r="O1795">
         <v>1</v>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -1051,6 +1051,9 @@
     <t>2021-01-21</t>
   </si>
   <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
     <t>2021-06-02</t>
   </si>
   <si>
@@ -1058,9 +1061,6 @@
   </si>
   <si>
     <t>2021-06-16</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
   </si>
   <si>
     <t>2021-06-01</t>
@@ -1507,7 +1507,7 @@
     <t>2021-04-12</t>
   </si>
   <si>
-    <t>2021-08-04</t>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2021-05-14</t>
@@ -90024,7 +90024,7 @@
         <v>497</v>
       </c>
       <c r="E1757">
-        <v>0.7526787698801813</v>
+        <v>0.7799512509455635</v>
       </c>
       <c r="F1757">
         <v>-1</v>
@@ -90033,10 +90033,10 @@
         <v>0.01121005687389684</v>
       </c>
       <c r="H1757">
-        <v>0.00970732123011982</v>
+        <v>0.009780048749054438</v>
       </c>
       <c r="I1757">
-        <v>-0.04273564377702499</v>
+        <v>-0.07000812484240715</v>
       </c>
       <c r="J1757">
         <v>1.136375946730918</v>
@@ -90048,10 +90048,10 @@
         <v>5.96</v>
       </c>
       <c r="M1757">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1757">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1757">
         <v>1</v>
@@ -90074,7 +90074,7 @@
         <v>497</v>
       </c>
       <c r="E1758">
-        <v>0.7526787698801813</v>
+        <v>0.7799512509455635</v>
       </c>
       <c r="F1758">
         <v>-1</v>
@@ -90083,10 +90083,10 @@
         <v>0.009858231305858292</v>
       </c>
       <c r="H1758">
-        <v>0.00970732123011982</v>
+        <v>0.009780048749054438</v>
       </c>
       <c r="I1758">
-        <v>-0.03091007573847282</v>
+        <v>-0.05818255680385498</v>
       </c>
       <c r="J1758">
         <v>1.136375946730918</v>
@@ -90098,10 +90098,10 @@
         <v>5.29</v>
       </c>
       <c r="M1758">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1758">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1758">
         <v>1</v>
@@ -90374,7 +90374,7 @@
         <v>497</v>
       </c>
       <c r="E1764">
-        <v>0.6908085096346603</v>
+        <v>0.7177669284652932</v>
       </c>
       <c r="F1764">
         <v>-1</v>
@@ -90383,10 +90383,10 @@
         <v>0.01128260525012383</v>
       </c>
       <c r="H1764">
-        <v>0.00976919149036534</v>
+        <v>0.009842233071534708</v>
       </c>
       <c r="I1764">
-        <v>-0.05341375975848539</v>
+        <v>-0.08037217858911827</v>
       </c>
       <c r="J1764">
         <v>1.15207905846836</v>
@@ -90398,10 +90398,10 @@
         <v>5.96</v>
       </c>
       <c r="M1764">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1764">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1764">
         <v>1</v>
@@ -90424,7 +90424,7 @@
         <v>497</v>
       </c>
       <c r="E1765">
-        <v>0.6908085096346603</v>
+        <v>0.7177669284652932</v>
       </c>
       <c r="F1765">
         <v>-1</v>
@@ -90433,10 +90433,10 @@
         <v>0.00992135781504281</v>
       </c>
       <c r="H1765">
-        <v>0.00976919149036534</v>
+        <v>0.009842233071534708</v>
       </c>
       <c r="I1765">
-        <v>-0.03216632467746905</v>
+        <v>-0.05912474350810193</v>
       </c>
       <c r="J1765">
         <v>1.15207905846836</v>
@@ -90448,10 +90448,10 @@
         <v>5.29</v>
       </c>
       <c r="M1765">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1765">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1765">
         <v>1</v>
@@ -90724,7 +90724,7 @@
         <v>497</v>
       </c>
       <c r="E1771">
-        <v>0.5415954670384595</v>
+        <v>0.5677964592569289</v>
       </c>
       <c r="F1771">
         <v>-1</v>
@@ -90733,10 +90733,10 @@
         <v>0.01145757079753358</v>
       </c>
       <c r="H1771">
-        <v>0.009918404532961542</v>
+        <v>0.009992203540743072</v>
       </c>
       <c r="I1771">
-        <v>-0.07916626457204323</v>
+        <v>-0.1053672567905126</v>
       </c>
       <c r="J1771">
         <v>1.189950389076533</v>
@@ -90748,10 +90748,10 @@
         <v>5.96</v>
       </c>
       <c r="M1771">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1771">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1771">
         <v>1</v>
@@ -90774,7 +90774,7 @@
         <v>497</v>
       </c>
       <c r="E1772">
-        <v>0.5415954670384595</v>
+        <v>0.5677964592569289</v>
       </c>
       <c r="F1772">
         <v>-1</v>
@@ -90783,10 +90783,10 @@
         <v>0.01007360056408766</v>
       </c>
       <c r="H1772">
-        <v>0.009918404532961542</v>
+        <v>0.009992203540743072</v>
       </c>
       <c r="I1772">
-        <v>-0.03519603112612302</v>
+        <v>-0.06139702334459241</v>
       </c>
       <c r="J1772">
         <v>1.189950389076533</v>
@@ -90798,10 +90798,10 @@
         <v>5.29</v>
       </c>
       <c r="M1772">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1772">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1772">
         <v>1</v>
@@ -91065,43 +91065,43 @@
         <v>5</v>
       </c>
       <c r="B1778" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C1778">
-        <v>0.2533571189653241</v>
+        <v>0.3192448737570821</v>
       </c>
       <c r="D1778" t="s">
         <v>497</v>
       </c>
       <c r="E1778">
-        <v>0.3632958979920735</v>
+        <v>0.3885918162559925</v>
       </c>
       <c r="F1778">
         <v>-1</v>
       </c>
       <c r="G1778">
-        <v>0.01166664288103468</v>
+        <v>0.01188075512624292</v>
       </c>
       <c r="H1778">
-        <v>0.01009670410200793</v>
+        <v>0.01017140818374401</v>
       </c>
       <c r="I1778">
-        <v>-0.1099387790267494</v>
+        <v>-0.06934694249891038</v>
       </c>
       <c r="J1778">
         <v>1.235204086804042</v>
       </c>
       <c r="K1778">
-        <v>4.62</v>
+        <v>4.68</v>
       </c>
       <c r="L1778">
-        <v>5.96</v>
+        <v>6.1</v>
       </c>
       <c r="M1778">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1778">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1778">
         <v>1</v>
@@ -91124,7 +91124,7 @@
         <v>497</v>
       </c>
       <c r="E1779">
-        <v>0.3632958979920735</v>
+        <v>0.3885918162559925</v>
       </c>
       <c r="F1779">
         <v>-1</v>
@@ -91133,10 +91133,10 @@
         <v>0.01025552042895225</v>
       </c>
       <c r="H1779">
-        <v>0.01009670410200793</v>
+        <v>0.01017140818374401</v>
       </c>
       <c r="I1779">
-        <v>-0.03881632694432291</v>
+        <v>-0.06411224520824188</v>
       </c>
       <c r="J1779">
         <v>1.235204086804042</v>
@@ -91148,10 +91148,10 @@
         <v>5.29</v>
       </c>
       <c r="M1779">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1779">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1779">
         <v>1</v>
@@ -91165,7 +91165,7 @@
         <v>0</v>
       </c>
       <c r="B1780" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C1780">
         <v>1.197796528658245</v>
@@ -91215,7 +91215,7 @@
         <v>1</v>
       </c>
       <c r="B1781" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C1781">
         <v>1.195132470598524</v>
@@ -91265,7 +91265,7 @@
         <v>2</v>
       </c>
       <c r="B1782" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C1782">
         <v>1.176379136973726</v>
@@ -91315,7 +91315,7 @@
         <v>3</v>
       </c>
       <c r="B1783" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C1783">
         <v>1.598111310278496</v>
@@ -91365,10 +91365,10 @@
         <v>0</v>
       </c>
       <c r="B1784" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C1784">
-        <v>0.883972777255555</v>
+        <v>0.9261088568346558</v>
       </c>
       <c r="D1784" t="s">
         <v>499</v>
@@ -91380,22 +91380,22 @@
         <v>1</v>
       </c>
       <c r="G1784">
-        <v>0.01201602722274444</v>
+        <v>0.01183389114316535</v>
       </c>
       <c r="H1784">
         <v>0.01098398750148042</v>
       </c>
       <c r="I1784">
-        <v>0.2320397212640213</v>
+        <v>0.1899036416849205</v>
       </c>
       <c r="J1784">
         <v>1.01941890526455</v>
       </c>
       <c r="K1784">
-        <v>5.46</v>
+        <v>5.35</v>
       </c>
       <c r="L1784">
-        <v>6.45</v>
+        <v>6.38</v>
       </c>
       <c r="M1784">
         <v>4.84</v>
@@ -91415,7 +91415,7 @@
         <v>1</v>
       </c>
       <c r="B1785" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C1785">
         <v>0.8853321006240735</v>
@@ -91465,7 +91465,7 @@
         <v>2</v>
       </c>
       <c r="B1786" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C1786">
         <v>0.8797984488349195</v>
@@ -91515,7 +91515,7 @@
         <v>3</v>
       </c>
       <c r="B1787" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C1787">
         <v>1.329119523361904</v>
@@ -91524,7 +91524,7 @@
         <v>497</v>
       </c>
       <c r="E1787">
-        <v>1.213489513257672</v>
+        <v>1.243101135152381</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91533,10 +91533,10 @@
         <v>0.0108708804766381</v>
       </c>
       <c r="H1787">
-        <v>0.00924651048674233</v>
+        <v>0.009316898864847619</v>
       </c>
       <c r="I1787">
-        <v>0.1156300101042325</v>
+        <v>0.08601838820952334</v>
       </c>
       <c r="J1787">
         <v>1.01941890526455</v>
@@ -91548,10 +91548,10 @@
         <v>6.1</v>
       </c>
       <c r="M1787">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1787">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91615,7 +91615,7 @@
         <v>1</v>
       </c>
       <c r="B1789" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C1789">
         <v>0.5823137694878824</v>
@@ -91665,7 +91665,7 @@
         <v>2</v>
       </c>
       <c r="B1790" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C1790">
         <v>0.5897103989902535</v>
@@ -91765,7 +91765,7 @@
         <v>4</v>
       </c>
       <c r="B1792" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C1792">
         <v>1.06601640838651</v>
@@ -91774,7 +91774,7 @@
         <v>497</v>
       </c>
       <c r="E1792">
-        <v>0.9919881728724036</v>
+        <v>1.020475422480893</v>
       </c>
       <c r="F1792">
         <v>-1</v>
@@ -91783,10 +91783,10 @@
         <v>0.01113398359161349</v>
       </c>
       <c r="H1792">
-        <v>0.009468011827127597</v>
+        <v>0.009539524577519106</v>
       </c>
       <c r="I1792">
-        <v>0.0740282355141062</v>
+        <v>0.04554098590561662</v>
       </c>
       <c r="J1792">
         <v>1.075637519575532</v>
@@ -91798,10 +91798,10 @@
         <v>6.1</v>
       </c>
       <c r="M1792">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1792">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91865,7 +91865,7 @@
         <v>1</v>
       </c>
       <c r="B1794" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C1794">
         <v>0.5090351943041105</v>
@@ -91915,7 +91915,7 @@
         <v>2</v>
       </c>
       <c r="B1795" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C1795">
         <v>0.5195587388885352</v>
@@ -92015,7 +92015,7 @@
         <v>4</v>
       </c>
       <c r="B1797" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C1797">
         <v>1.002390484108207</v>
@@ -92024,7 +92024,7 @@
         <v>497</v>
       </c>
       <c r="E1797">
-        <v>0.9384227579885334</v>
+        <v>0.9666381019377139</v>
       </c>
       <c r="F1797">
         <v>-1</v>
@@ -92033,10 +92033,10 @@
         <v>0.01119760951589179</v>
       </c>
       <c r="H1797">
-        <v>0.009521577242011468</v>
+        <v>0.009593361898062288</v>
       </c>
       <c r="I1797">
-        <v>0.06396772611967361</v>
+        <v>0.03575238217049304</v>
       </c>
       <c r="J1797">
         <v>1.089232802540981</v>
@@ -92048,10 +92048,10 @@
         <v>6.1</v>
       </c>
       <c r="M1797">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="N1797">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="O1797">
         <v>1</v>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5406" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5403" uniqueCount="617">
   <si>
     <t>trade_time</t>
   </si>
@@ -1060,13 +1060,13 @@
     <t>2021-06-07</t>
   </si>
   <si>
-    <t>2021-08-05</t>
-  </si>
-  <si>
     <t>2021-08-09</t>
   </si>
   <si>
     <t>2021-05-28</t>
+  </si>
+  <si>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2016-05-11</t>
@@ -1525,10 +1525,10 @@
     <t>2021-06-29</t>
   </si>
   <si>
-    <t>2021-08-02</t>
+    <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-08-17</t>
+    <t>2021-08-18</t>
   </si>
   <si>
     <t>2016-03-09</t>
@@ -2222,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1798"/>
+  <dimension ref="A1:P1797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -90333,7 +90333,7 @@
         <v>0.7082700063680729</v>
       </c>
       <c r="D1763" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1763">
         <v>0.7171213943725077</v>
@@ -90383,7 +90383,7 @@
         <v>0.6586421849571913</v>
       </c>
       <c r="D1764" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1764">
         <v>0.7171213943725077</v>
@@ -91236,7 +91236,7 @@
         <v>503</v>
       </c>
       <c r="E1781">
-        <v>1.346037686355093</v>
+        <v>1.787560005246361</v>
       </c>
       <c r="F1781">
         <v>-1</v>
@@ -91245,10 +91245,10 @@
         <v>0.0106018886897215</v>
       </c>
       <c r="H1781">
-        <v>0.009233962313644907</v>
+        <v>0.009752439994753639</v>
       </c>
       <c r="I1781">
-        <v>0.2520736239234029</v>
+        <v>-0.1894486949678655</v>
       </c>
       <c r="J1781">
         <v>0.9619420277182702</v>
@@ -91260,10 +91260,10 @@
         <v>6.1</v>
       </c>
       <c r="M1781">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="N1781">
-        <v>5.29</v>
+        <v>5.77</v>
       </c>
       <c r="O1781">
         <v>1</v>
@@ -91436,7 +91436,7 @@
         <v>504</v>
       </c>
       <c r="E1785">
-        <v>1.165527762099206</v>
+        <v>1.20494519494127</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91445,10 +91445,10 @@
         <v>0.0108708804766381</v>
       </c>
       <c r="H1785">
-        <v>0.01003447223790079</v>
+        <v>0.01013505480505873</v>
       </c>
       <c r="I1785">
-        <v>0.1635917612626985</v>
+        <v>0.1241743284206347</v>
       </c>
       <c r="J1785">
         <v>1.01941890526455</v>
@@ -91460,10 +91460,10 @@
         <v>6.1</v>
       </c>
       <c r="M1785">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="N1785">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91636,7 +91636,7 @@
         <v>504</v>
       </c>
       <c r="E1789">
-        <v>0.9209767898464349</v>
+        <v>0.958707664259169</v>
       </c>
       <c r="F1789">
         <v>-1</v>
@@ -91645,10 +91645,10 @@
         <v>0.01113398359161349</v>
       </c>
       <c r="H1789">
-        <v>0.01027902321015356</v>
+        <v>0.01038129233574083</v>
       </c>
       <c r="I1789">
-        <v>0.1450396185400749</v>
+        <v>0.1073087441273408</v>
       </c>
       <c r="J1789">
         <v>1.075637519575532</v>
@@ -91660,10 +91660,10 @@
         <v>6.1</v>
       </c>
       <c r="M1789">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="N1789">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="O1789">
         <v>1</v>
@@ -91680,40 +91680,40 @@
         <v>348</v>
       </c>
       <c r="C1790">
-        <v>1.020475422480893</v>
+        <v>1.025180796110606</v>
       </c>
       <c r="D1790" t="s">
         <v>504</v>
       </c>
       <c r="E1790">
-        <v>0.9209767898464349</v>
+        <v>0.958707664259169</v>
       </c>
       <c r="F1790">
         <v>-1</v>
       </c>
       <c r="G1790">
-        <v>0.009539524577519106</v>
+        <v>0.009694819203889395</v>
       </c>
       <c r="H1790">
-        <v>0.01027902321015356</v>
+        <v>0.01038129233574083</v>
       </c>
       <c r="I1790">
-        <v>0.09949863263445824</v>
+        <v>0.06647313185143666</v>
       </c>
       <c r="J1790">
         <v>1.075637519575532</v>
       </c>
       <c r="K1790">
-        <v>3.96</v>
+        <v>4.03</v>
       </c>
       <c r="L1790">
-        <v>5.28</v>
+        <v>5.36</v>
       </c>
       <c r="M1790">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="N1790">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="O1790">
         <v>1</v>
@@ -91724,63 +91724,63 @@
     </row>
     <row r="1791" spans="1:16">
       <c r="A1791" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1791" t="s">
         <v>349</v>
       </c>
       <c r="C1791">
-        <v>1.025180796110606</v>
+        <v>0.5874349299737824</v>
       </c>
       <c r="D1791" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E1791">
-        <v>0.9209767898464349</v>
+        <v>0.7781132357016496</v>
       </c>
       <c r="F1791">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1791">
-        <v>0.009694819203889395</v>
+        <v>0.01261256507002622</v>
       </c>
       <c r="H1791">
-        <v>0.01027902321015356</v>
+        <v>0.01132188676429835</v>
       </c>
       <c r="I1791">
-        <v>0.1042040062641707</v>
+        <v>0.1906783057278671</v>
       </c>
       <c r="J1791">
-        <v>1.075637519575532</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1791">
-        <v>4.03</v>
+        <v>5.52</v>
       </c>
       <c r="L1791">
-        <v>5.36</v>
+        <v>6.6</v>
       </c>
       <c r="M1791">
-        <v>4.35</v>
+        <v>4.84</v>
       </c>
       <c r="N1791">
-        <v>5.6</v>
+        <v>6.05</v>
       </c>
       <c r="O1791">
         <v>1</v>
       </c>
       <c r="P1791" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1792" spans="1:16">
       <c r="A1792" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1792" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C1792">
-        <v>0.5874349299737824</v>
+        <v>0.5526045064057499</v>
       </c>
       <c r="D1792" t="s">
         <v>502</v>
@@ -91792,22 +91792,22 @@
         <v>1</v>
       </c>
       <c r="G1792">
-        <v>0.01261256507002622</v>
+        <v>0.01220739549359425</v>
       </c>
       <c r="H1792">
         <v>0.01132188676429835</v>
       </c>
       <c r="I1792">
-        <v>0.1906783057278671</v>
+        <v>0.2255087292958997</v>
       </c>
       <c r="J1792">
         <v>1.089232802540981</v>
       </c>
       <c r="K1792">
-        <v>5.52</v>
+        <v>5.35</v>
       </c>
       <c r="L1792">
-        <v>6.6</v>
+        <v>6.38</v>
       </c>
       <c r="M1792">
         <v>4.84</v>
@@ -91824,13 +91824,13 @@
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1793" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C1793">
-        <v>0.5526045064057499</v>
+        <v>0.5779584745582085</v>
       </c>
       <c r="D1793" t="s">
         <v>502</v>
@@ -91842,22 +91842,22 @@
         <v>1</v>
       </c>
       <c r="G1793">
-        <v>0.01220739549359425</v>
+        <v>0.01210204152544179</v>
       </c>
       <c r="H1793">
         <v>0.01132188676429835</v>
       </c>
       <c r="I1793">
-        <v>0.2255087292958997</v>
+        <v>0.2001547611434411</v>
       </c>
       <c r="J1793">
         <v>1.089232802540981</v>
       </c>
       <c r="K1793">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="L1793">
-        <v>6.38</v>
+        <v>6.34</v>
       </c>
       <c r="M1793">
         <v>4.84</v>
@@ -91874,13 +91874,13 @@
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1794" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C1794">
-        <v>0.5779584745582085</v>
+        <v>0.5813433949393554</v>
       </c>
       <c r="D1794" t="s">
         <v>502</v>
@@ -91892,22 +91892,22 @@
         <v>1</v>
       </c>
       <c r="G1794">
-        <v>0.01210204152544179</v>
+        <v>0.01177865660506064</v>
       </c>
       <c r="H1794">
         <v>0.01132188676429835</v>
       </c>
       <c r="I1794">
-        <v>0.2001547611434411</v>
+        <v>0.1967698407622942</v>
       </c>
       <c r="J1794">
         <v>1.089232802540981</v>
       </c>
       <c r="K1794">
-        <v>5.29</v>
+        <v>5.14</v>
       </c>
       <c r="L1794">
-        <v>6.34</v>
+        <v>6.18</v>
       </c>
       <c r="M1794">
         <v>4.84</v>
@@ -91924,46 +91924,46 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1795" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C1795">
-        <v>0.5813433949393554</v>
+        <v>1.002390484108207</v>
       </c>
       <c r="D1795" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E1795">
-        <v>0.7781132357016496</v>
+        <v>0.8991603248705013</v>
       </c>
       <c r="F1795">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1795">
-        <v>0.01177865660506064</v>
+        <v>0.01119760951589179</v>
       </c>
       <c r="H1795">
-        <v>0.01132188676429835</v>
+        <v>0.0104408396751295</v>
       </c>
       <c r="I1795">
-        <v>0.1967698407622942</v>
+        <v>0.1032301592377056</v>
       </c>
       <c r="J1795">
         <v>1.089232802540981</v>
       </c>
       <c r="K1795">
-        <v>5.14</v>
+        <v>4.68</v>
       </c>
       <c r="L1795">
-        <v>6.18</v>
+        <v>6.1</v>
       </c>
       <c r="M1795">
-        <v>4.84</v>
+        <v>4.38</v>
       </c>
       <c r="N1795">
-        <v>6.05</v>
+        <v>5.67</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -91974,46 +91974,46 @@
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1796" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C1796">
-        <v>1.002390484108207</v>
+        <v>0.9666381019377139</v>
       </c>
       <c r="D1796" t="s">
         <v>504</v>
       </c>
       <c r="E1796">
-        <v>0.8618373089467308</v>
+        <v>0.8991603248705013</v>
       </c>
       <c r="F1796">
         <v>-1</v>
       </c>
       <c r="G1796">
-        <v>0.01119760951589179</v>
+        <v>0.009593361898062288</v>
       </c>
       <c r="H1796">
-        <v>0.01033816269105327</v>
+        <v>0.0104408396751295</v>
       </c>
       <c r="I1796">
-        <v>0.1405531751614761</v>
+        <v>0.06747777706721259</v>
       </c>
       <c r="J1796">
         <v>1.089232802540981</v>
       </c>
       <c r="K1796">
-        <v>4.68</v>
+        <v>3.96</v>
       </c>
       <c r="L1796">
-        <v>6.1</v>
+        <v>5.28</v>
       </c>
       <c r="M1796">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="N1796">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92024,101 +92024,51 @@
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1797" t="s">
         <v>348</v>
       </c>
       <c r="C1797">
-        <v>0.9666381019377139</v>
+        <v>0.9703918057598448</v>
       </c>
       <c r="D1797" t="s">
         <v>504</v>
       </c>
       <c r="E1797">
-        <v>0.8618373089467308</v>
+        <v>0.8991603248705013</v>
       </c>
       <c r="F1797">
         <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.009593361898062288</v>
+        <v>0.009749608194240157</v>
       </c>
       <c r="H1797">
-        <v>0.01033816269105327</v>
+        <v>0.0104408396751295</v>
       </c>
       <c r="I1797">
-        <v>0.1048007929909831</v>
+        <v>0.0712314808893435</v>
       </c>
       <c r="J1797">
         <v>1.089232802540981</v>
       </c>
       <c r="K1797">
-        <v>3.96</v>
+        <v>4.03</v>
       </c>
       <c r="L1797">
-        <v>5.28</v>
+        <v>5.36</v>
       </c>
       <c r="M1797">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="N1797">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="O1797">
         <v>1</v>
       </c>
       <c r="P1797" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="1798" spans="1:16">
-      <c r="A1798" s="1">
-        <v>6</v>
-      </c>
-      <c r="B1798" t="s">
-        <v>349</v>
-      </c>
-      <c r="C1798">
-        <v>0.9703918057598448</v>
-      </c>
-      <c r="D1798" t="s">
-        <v>504</v>
-      </c>
-      <c r="E1798">
-        <v>0.8618373089467308</v>
-      </c>
-      <c r="F1798">
-        <v>-1</v>
-      </c>
-      <c r="G1798">
-        <v>0.009749608194240157</v>
-      </c>
-      <c r="H1798">
-        <v>0.01033816269105327</v>
-      </c>
-      <c r="I1798">
-        <v>0.108554496813114</v>
-      </c>
-      <c r="J1798">
-        <v>1.089232802540981</v>
-      </c>
-      <c r="K1798">
-        <v>4.03</v>
-      </c>
-      <c r="L1798">
-        <v>5.36</v>
-      </c>
-      <c r="M1798">
-        <v>4.35</v>
-      </c>
-      <c r="N1798">
-        <v>5.6</v>
-      </c>
-      <c r="O1798">
-        <v>1</v>
-      </c>
-      <c r="P1798" t="s">
         <v>616</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -1525,7 +1525,7 @@
     <t>2021-08-02</t>
   </si>
   <si>
-    <t>2021-08-23</t>
+    <t>2021-08-24</t>
   </si>
   <si>
     <t>2021-07-09</t>
@@ -91286,7 +91286,7 @@
         <v>503</v>
       </c>
       <c r="E1782">
-        <v>1.569843483583266</v>
+        <v>1.445552179425525</v>
       </c>
       <c r="F1782">
         <v>-1</v>
@@ -91295,10 +91295,10 @@
         <v>0.009688634197525466</v>
       </c>
       <c r="H1782">
-        <v>0.009650156516416736</v>
+        <v>0.009814447820574475</v>
       </c>
       <c r="I1782">
-        <v>-0.03847768110873062</v>
+        <v>0.08581362304900964</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
@@ -91310,10 +91310,10 @@
         <v>5.61</v>
       </c>
       <c r="M1782">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="N1782">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91333,10 +91333,10 @@
         <v>0.9261088568346558</v>
       </c>
       <c r="D1783" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E1783">
-        <v>1.116012498519576</v>
+        <v>1.129313712414549</v>
       </c>
       <c r="F1783">
         <v>1</v>
@@ -91345,10 +91345,10 @@
         <v>0.01183389114316535</v>
       </c>
       <c r="H1783">
-        <v>0.01098398750148042</v>
+        <v>0.01065068628758545</v>
       </c>
       <c r="I1783">
-        <v>0.1899036416849205</v>
+        <v>0.2032048555798935</v>
       </c>
       <c r="J1783">
         <v>1.01941890526455</v>
@@ -91360,10 +91360,10 @@
         <v>6.38</v>
       </c>
       <c r="M1783">
-        <v>4.84</v>
+        <v>4.67</v>
       </c>
       <c r="N1783">
-        <v>6.05</v>
+        <v>5.89</v>
       </c>
       <c r="O1783">
         <v>1</v>
@@ -91383,10 +91383,10 @@
         <v>0.9472739911505288</v>
       </c>
       <c r="D1784" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E1784">
-        <v>1.116012498519576</v>
+        <v>1.129313712414549</v>
       </c>
       <c r="F1784">
         <v>1</v>
@@ -91395,10 +91395,10 @@
         <v>0.01173272600884947</v>
       </c>
       <c r="H1784">
-        <v>0.01098398750148042</v>
+        <v>0.01065068628758545</v>
       </c>
       <c r="I1784">
-        <v>0.1687385073690475</v>
+        <v>0.1820397212640206</v>
       </c>
       <c r="J1784">
         <v>1.01941890526455</v>
@@ -91410,10 +91410,10 @@
         <v>6.34</v>
       </c>
       <c r="M1784">
-        <v>4.84</v>
+        <v>4.67</v>
       </c>
       <c r="N1784">
-        <v>6.05</v>
+        <v>5.89</v>
       </c>
       <c r="O1784">
         <v>1</v>
@@ -91433,10 +91433,10 @@
         <v>0.9401868269402112</v>
       </c>
       <c r="D1785" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E1785">
-        <v>1.116012498519576</v>
+        <v>1.129313712414549</v>
       </c>
       <c r="F1785">
         <v>1</v>
@@ -91445,10 +91445,10 @@
         <v>0.01141981317305979</v>
       </c>
       <c r="H1785">
-        <v>0.01098398750148042</v>
+        <v>0.01065068628758545</v>
       </c>
       <c r="I1785">
-        <v>0.1758256715793651</v>
+        <v>0.1891268854743382</v>
       </c>
       <c r="J1785">
         <v>1.01941890526455</v>
@@ -91460,10 +91460,10 @@
         <v>6.18</v>
       </c>
       <c r="M1785">
-        <v>4.84</v>
+        <v>4.67</v>
       </c>
       <c r="N1785">
-        <v>6.05</v>
+        <v>5.89</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91536,7 +91536,7 @@
         <v>503</v>
       </c>
       <c r="E1787">
-        <v>1.328440597888888</v>
+        <v>1.195527762099206</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91545,10 +91545,10 @@
         <v>0.009932336158321693</v>
       </c>
       <c r="H1787">
-        <v>0.009891559402111113</v>
+        <v>0.01006447223790079</v>
       </c>
       <c r="I1787">
-        <v>-0.04077675621058141</v>
+        <v>0.09213607957910064</v>
       </c>
       <c r="J1787">
         <v>1.01941890526455</v>
@@ -91560,10 +91560,10 @@
         <v>5.61</v>
       </c>
       <c r="M1787">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="N1787">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91786,7 +91786,7 @@
         <v>503</v>
       </c>
       <c r="E1792">
-        <v>1.092322417782765</v>
+        <v>0.9509767898464352</v>
       </c>
       <c r="F1792">
         <v>-1</v>
@@ -91795,10 +91795,10 @@
         <v>0.01113398359161349</v>
       </c>
       <c r="H1792">
-        <v>0.01012767758221723</v>
+        <v>0.01030902321015357</v>
       </c>
       <c r="I1792">
-        <v>-0.02630600939625527</v>
+        <v>0.1150396185400746</v>
       </c>
       <c r="J1792">
         <v>1.075637519575532</v>
@@ -91810,10 +91810,10 @@
         <v>6.1</v>
       </c>
       <c r="M1792">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="N1792">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91836,7 +91836,7 @@
         <v>503</v>
       </c>
       <c r="E1793">
-        <v>1.092322417782765</v>
+        <v>0.9509767898464352</v>
       </c>
       <c r="F1793">
         <v>-1</v>
@@ -91845,10 +91845,10 @@
         <v>0.01017070308300026</v>
       </c>
       <c r="H1793">
-        <v>0.01012767758221723</v>
+        <v>0.01030902321015357</v>
       </c>
       <c r="I1793">
-        <v>-0.04302550078302136</v>
+        <v>0.09832012715330851</v>
       </c>
       <c r="J1793">
         <v>1.075637519575532</v>
@@ -91860,10 +91860,10 @@
         <v>5.61</v>
       </c>
       <c r="M1793">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="N1793">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -92086,7 +92086,7 @@
         <v>503</v>
       </c>
       <c r="E1798">
-        <v>1.035222229327879</v>
+        <v>0.8918373089467311</v>
       </c>
       <c r="F1798">
         <v>-1</v>
@@ -92095,10 +92095,10 @@
         <v>0.01119760951589179</v>
       </c>
       <c r="H1798">
-        <v>0.01018477777067212</v>
+        <v>0.01036816269105327</v>
       </c>
       <c r="I1798">
-        <v>-0.03283174521967158</v>
+        <v>0.1105531751614759</v>
       </c>
       <c r="J1798">
         <v>1.089232802540981</v>
@@ -92110,10 +92110,10 @@
         <v>6.1</v>
       </c>
       <c r="M1798">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="N1798">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92136,7 +92136,7 @@
         <v>503</v>
       </c>
       <c r="E1799">
-        <v>1.035222229327879</v>
+        <v>0.8918373089467311</v>
       </c>
       <c r="F1799">
         <v>-1</v>
@@ -92145,10 +92145,10 @@
         <v>0.01022834708277376</v>
       </c>
       <c r="H1799">
-        <v>0.01018477777067212</v>
+        <v>0.01036816269105327</v>
       </c>
       <c r="I1799">
-        <v>-0.04356931210163939</v>
+        <v>0.09981560827950808</v>
       </c>
       <c r="J1799">
         <v>1.089232802540981</v>
@@ -92160,10 +92160,10 @@
         <v>5.61</v>
       </c>
       <c r="M1799">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="N1799">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="O1799">
         <v>1</v>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5409" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5406" uniqueCount="617">
   <si>
     <t>trade_time</t>
   </si>
@@ -1525,7 +1525,7 @@
     <t>2021-08-02</t>
   </si>
   <si>
-    <t>2021-08-24</t>
+    <t>2021-08-25</t>
   </si>
   <si>
     <t>2021-07-09</t>
@@ -2222,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1799"/>
+  <dimension ref="A1:P1798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91286,7 +91286,7 @@
         <v>503</v>
       </c>
       <c r="E1782">
-        <v>1.445552179425525</v>
+        <v>1.460119136099332</v>
       </c>
       <c r="F1782">
         <v>-1</v>
@@ -91295,10 +91295,10 @@
         <v>0.009688634197525466</v>
       </c>
       <c r="H1782">
-        <v>0.009814447820574475</v>
+        <v>0.01005988086390067</v>
       </c>
       <c r="I1782">
-        <v>0.08581362304900964</v>
+        <v>0.07124666637520249</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
@@ -91310,10 +91310,10 @@
         <v>5.61</v>
       </c>
       <c r="M1782">
-        <v>4.35</v>
+        <v>4.47</v>
       </c>
       <c r="N1782">
-        <v>5.63</v>
+        <v>5.76</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91536,7 +91536,7 @@
         <v>503</v>
       </c>
       <c r="E1787">
-        <v>1.195527762099206</v>
+        <v>1.20319749346746</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91545,10 +91545,10 @@
         <v>0.009932336158321693</v>
       </c>
       <c r="H1787">
-        <v>0.01006447223790079</v>
+        <v>0.01031680250653254</v>
       </c>
       <c r="I1787">
-        <v>0.09213607957910064</v>
+        <v>0.08446634821084675</v>
       </c>
       <c r="J1787">
         <v>1.01941890526455</v>
@@ -91560,10 +91560,10 @@
         <v>5.61</v>
       </c>
       <c r="M1787">
-        <v>4.35</v>
+        <v>4.47</v>
       </c>
       <c r="N1787">
-        <v>5.63</v>
+        <v>5.76</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91786,7 +91786,7 @@
         <v>503</v>
       </c>
       <c r="E1792">
-        <v>0.9509767898464352</v>
+        <v>0.9519002874973719</v>
       </c>
       <c r="F1792">
         <v>-1</v>
@@ -91795,10 +91795,10 @@
         <v>0.01113398359161349</v>
       </c>
       <c r="H1792">
-        <v>0.01030902321015357</v>
+        <v>0.01056809971250263</v>
       </c>
       <c r="I1792">
-        <v>0.1150396185400746</v>
+        <v>0.1141161208891379</v>
       </c>
       <c r="J1792">
         <v>1.075637519575532</v>
@@ -91810,10 +91810,10 @@
         <v>6.1</v>
       </c>
       <c r="M1792">
-        <v>4.35</v>
+        <v>4.47</v>
       </c>
       <c r="N1792">
-        <v>5.63</v>
+        <v>5.76</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91836,7 +91836,7 @@
         <v>503</v>
       </c>
       <c r="E1793">
-        <v>0.9509767898464352</v>
+        <v>0.9519002874973719</v>
       </c>
       <c r="F1793">
         <v>-1</v>
@@ -91845,10 +91845,10 @@
         <v>0.01017070308300026</v>
       </c>
       <c r="H1793">
-        <v>0.01030902321015357</v>
+        <v>0.01056809971250263</v>
       </c>
       <c r="I1793">
-        <v>0.09832012715330851</v>
+        <v>0.09739662950237182</v>
       </c>
       <c r="J1793">
         <v>1.075637519575532</v>
@@ -91860,10 +91860,10 @@
         <v>5.61</v>
       </c>
       <c r="M1793">
-        <v>4.35</v>
+        <v>4.47</v>
       </c>
       <c r="N1793">
-        <v>5.63</v>
+        <v>5.76</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -92027,43 +92027,43 @@
         <v>3</v>
       </c>
       <c r="B1797" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C1797">
-        <v>0.5813433949393554</v>
+        <v>1.002390484108207</v>
       </c>
       <c r="D1797" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E1797">
-        <v>0.8032828121336166</v>
+        <v>0.8911293726418128</v>
       </c>
       <c r="F1797">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.01177865660506064</v>
+        <v>0.01119760951589179</v>
       </c>
       <c r="H1797">
-        <v>0.01097671718786638</v>
+        <v>0.01062887062735819</v>
       </c>
       <c r="I1797">
-        <v>0.2219394171942612</v>
+        <v>0.1112611114663942</v>
       </c>
       <c r="J1797">
         <v>1.089232802540981</v>
       </c>
       <c r="K1797">
-        <v>5.14</v>
+        <v>4.68</v>
       </c>
       <c r="L1797">
-        <v>6.18</v>
+        <v>6.1</v>
       </c>
       <c r="M1797">
-        <v>4.67</v>
+        <v>4.47</v>
       </c>
       <c r="N1797">
-        <v>5.89</v>
+        <v>5.76</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92077,98 +92077,48 @@
         <v>4</v>
       </c>
       <c r="B1798" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C1798">
-        <v>1.002390484108207</v>
+        <v>0.9916529172262392</v>
       </c>
       <c r="D1798" t="s">
         <v>503</v>
       </c>
       <c r="E1798">
-        <v>0.8918373089467311</v>
+        <v>0.8911293726418128</v>
       </c>
       <c r="F1798">
         <v>-1</v>
       </c>
       <c r="G1798">
-        <v>0.01119760951589179</v>
+        <v>0.01022834708277376</v>
       </c>
       <c r="H1798">
-        <v>0.01036816269105327</v>
+        <v>0.01062887062735819</v>
       </c>
       <c r="I1798">
-        <v>0.1105531751614759</v>
+        <v>0.1005235445844264</v>
       </c>
       <c r="J1798">
         <v>1.089232802540981</v>
       </c>
       <c r="K1798">
-        <v>4.68</v>
+        <v>4.24</v>
       </c>
       <c r="L1798">
-        <v>6.1</v>
+        <v>5.61</v>
       </c>
       <c r="M1798">
-        <v>4.35</v>
+        <v>4.47</v>
       </c>
       <c r="N1798">
-        <v>5.63</v>
+        <v>5.76</v>
       </c>
       <c r="O1798">
         <v>1</v>
       </c>
       <c r="P1798" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="1799" spans="1:16">
-      <c r="A1799" s="1">
-        <v>5</v>
-      </c>
-      <c r="B1799" t="s">
-        <v>347</v>
-      </c>
-      <c r="C1799">
-        <v>0.9916529172262392</v>
-      </c>
-      <c r="D1799" t="s">
-        <v>503</v>
-      </c>
-      <c r="E1799">
-        <v>0.8918373089467311</v>
-      </c>
-      <c r="F1799">
-        <v>-1</v>
-      </c>
-      <c r="G1799">
-        <v>0.01022834708277376</v>
-      </c>
-      <c r="H1799">
-        <v>0.01036816269105327</v>
-      </c>
-      <c r="I1799">
-        <v>0.09981560827950808</v>
-      </c>
-      <c r="J1799">
-        <v>1.089232802540981</v>
-      </c>
-      <c r="K1799">
-        <v>4.24</v>
-      </c>
-      <c r="L1799">
-        <v>5.61</v>
-      </c>
-      <c r="M1799">
-        <v>4.35</v>
-      </c>
-      <c r="N1799">
-        <v>5.63</v>
-      </c>
-      <c r="O1799">
-        <v>1</v>
-      </c>
-      <c r="P1799" t="s">
         <v>616</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5406" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5403" uniqueCount="617">
   <si>
     <t>trade_time</t>
   </si>
@@ -1525,7 +1525,7 @@
     <t>2021-08-02</t>
   </si>
   <si>
-    <t>2021-08-25</t>
+    <t>2021-08-26</t>
   </si>
   <si>
     <t>2021-07-09</t>
@@ -2222,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1798"/>
+  <dimension ref="A1:P1797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91286,7 +91286,7 @@
         <v>503</v>
       </c>
       <c r="E1782">
-        <v>1.460119136099332</v>
+        <v>1.469357976653697</v>
       </c>
       <c r="F1782">
         <v>-1</v>
@@ -91295,10 +91295,10 @@
         <v>0.009688634197525466</v>
       </c>
       <c r="H1782">
-        <v>0.01005988086390067</v>
+        <v>0.0100306420233463</v>
       </c>
       <c r="I1782">
-        <v>0.07124666637520249</v>
+        <v>0.06200782582083786</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
@@ -91310,10 +91310,10 @@
         <v>5.61</v>
       </c>
       <c r="M1782">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="N1782">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91536,7 +91536,7 @@
         <v>503</v>
       </c>
       <c r="E1787">
-        <v>1.20319749346746</v>
+        <v>1.213585871572751</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91545,10 +91545,10 @@
         <v>0.009932336158321693</v>
       </c>
       <c r="H1787">
-        <v>0.01031680250653254</v>
+        <v>0.01028641412842725</v>
       </c>
       <c r="I1787">
-        <v>0.08446634821084675</v>
+        <v>0.07407797010555583</v>
       </c>
       <c r="J1787">
         <v>1.01941890526455</v>
@@ -91560,10 +91560,10 @@
         <v>5.61</v>
       </c>
       <c r="M1787">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="N1787">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91727,43 +91727,43 @@
         <v>3</v>
       </c>
       <c r="B1791" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C1791">
-        <v>0.6512231493817646</v>
+        <v>1.06601640838651</v>
       </c>
       <c r="D1791" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E1791">
-        <v>0.8667727835822649</v>
+        <v>0.9634130378888823</v>
       </c>
       <c r="F1791">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1791">
-        <v>0.01170877685061824</v>
+        <v>0.01113398359161349</v>
       </c>
       <c r="H1791">
-        <v>0.01091322721641774</v>
+        <v>0.01053658696211112</v>
       </c>
       <c r="I1791">
-        <v>0.2155496342005003</v>
+        <v>0.1026033704976275</v>
       </c>
       <c r="J1791">
         <v>1.075637519575532</v>
       </c>
       <c r="K1791">
-        <v>5.14</v>
+        <v>4.68</v>
       </c>
       <c r="L1791">
-        <v>6.18</v>
+        <v>6.1</v>
       </c>
       <c r="M1791">
-        <v>4.67</v>
+        <v>4.45</v>
       </c>
       <c r="N1791">
-        <v>5.89</v>
+        <v>5.75</v>
       </c>
       <c r="O1791">
         <v>1</v>
@@ -91777,43 +91777,43 @@
         <v>4</v>
       </c>
       <c r="B1792" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C1792">
-        <v>1.06601640838651</v>
+        <v>1.049296916999744</v>
       </c>
       <c r="D1792" t="s">
         <v>503</v>
       </c>
       <c r="E1792">
-        <v>0.9519002874973719</v>
+        <v>0.9634130378888823</v>
       </c>
       <c r="F1792">
         <v>-1</v>
       </c>
       <c r="G1792">
-        <v>0.01113398359161349</v>
+        <v>0.01017070308300026</v>
       </c>
       <c r="H1792">
-        <v>0.01056809971250263</v>
+        <v>0.01053658696211112</v>
       </c>
       <c r="I1792">
-        <v>0.1141161208891379</v>
+        <v>0.08588387911086137</v>
       </c>
       <c r="J1792">
         <v>1.075637519575532</v>
       </c>
       <c r="K1792">
-        <v>4.68</v>
+        <v>4.24</v>
       </c>
       <c r="L1792">
-        <v>6.1</v>
+        <v>5.61</v>
       </c>
       <c r="M1792">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="N1792">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91824,63 +91824,63 @@
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1793" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C1793">
-        <v>1.049296916999744</v>
+        <v>0.5874349299737824</v>
       </c>
       <c r="D1793" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E1793">
-        <v>0.9519002874973719</v>
+        <v>0.8032828121336166</v>
       </c>
       <c r="F1793">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1793">
-        <v>0.01017070308300026</v>
+        <v>0.01261256507002622</v>
       </c>
       <c r="H1793">
-        <v>0.01056809971250263</v>
+        <v>0.01097671718786638</v>
       </c>
       <c r="I1793">
-        <v>0.09739662950237182</v>
+        <v>0.2158478821598342</v>
       </c>
       <c r="J1793">
-        <v>1.075637519575532</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1793">
-        <v>4.24</v>
+        <v>5.52</v>
       </c>
       <c r="L1793">
-        <v>5.61</v>
+        <v>6.6</v>
       </c>
       <c r="M1793">
-        <v>4.47</v>
+        <v>4.67</v>
       </c>
       <c r="N1793">
-        <v>5.76</v>
+        <v>5.89</v>
       </c>
       <c r="O1793">
         <v>1</v>
       </c>
       <c r="P1793" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1794" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C1794">
-        <v>0.5874349299737824</v>
+        <v>0.5526045064057499</v>
       </c>
       <c r="D1794" t="s">
         <v>504</v>
@@ -91892,22 +91892,22 @@
         <v>1</v>
       </c>
       <c r="G1794">
-        <v>0.01261256507002622</v>
+        <v>0.01220739549359425</v>
       </c>
       <c r="H1794">
         <v>0.01097671718786638</v>
       </c>
       <c r="I1794">
-        <v>0.2158478821598342</v>
+        <v>0.2506783057278668</v>
       </c>
       <c r="J1794">
         <v>1.089232802540981</v>
       </c>
       <c r="K1794">
-        <v>5.52</v>
+        <v>5.35</v>
       </c>
       <c r="L1794">
-        <v>6.6</v>
+        <v>6.38</v>
       </c>
       <c r="M1794">
         <v>4.67</v>
@@ -91924,13 +91924,13 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1795" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1795">
-        <v>0.5526045064057499</v>
+        <v>0.5779584745582085</v>
       </c>
       <c r="D1795" t="s">
         <v>504</v>
@@ -91942,22 +91942,22 @@
         <v>1</v>
       </c>
       <c r="G1795">
-        <v>0.01220739549359425</v>
+        <v>0.01210204152544179</v>
       </c>
       <c r="H1795">
         <v>0.01097671718786638</v>
       </c>
       <c r="I1795">
-        <v>0.2506783057278668</v>
+        <v>0.2253243375754082</v>
       </c>
       <c r="J1795">
         <v>1.089232802540981</v>
       </c>
       <c r="K1795">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="L1795">
-        <v>6.38</v>
+        <v>6.34</v>
       </c>
       <c r="M1795">
         <v>4.67</v>
@@ -91974,46 +91974,46 @@
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1796" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C1796">
-        <v>0.5779584745582085</v>
+        <v>1.002390484108207</v>
       </c>
       <c r="D1796" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E1796">
-        <v>0.8032828121336166</v>
+        <v>0.9029140286926323</v>
       </c>
       <c r="F1796">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1796">
-        <v>0.01210204152544179</v>
+        <v>0.01119760951589179</v>
       </c>
       <c r="H1796">
-        <v>0.01097671718786638</v>
+        <v>0.01059708597130737</v>
       </c>
       <c r="I1796">
-        <v>0.2253243375754082</v>
+        <v>0.0994764554155747</v>
       </c>
       <c r="J1796">
         <v>1.089232802540981</v>
       </c>
       <c r="K1796">
-        <v>5.29</v>
+        <v>4.68</v>
       </c>
       <c r="L1796">
-        <v>6.34</v>
+        <v>6.1</v>
       </c>
       <c r="M1796">
-        <v>4.67</v>
+        <v>4.45</v>
       </c>
       <c r="N1796">
-        <v>5.89</v>
+        <v>5.75</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92024,101 +92024,51 @@
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1797" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C1797">
-        <v>1.002390484108207</v>
+        <v>0.9916529172262392</v>
       </c>
       <c r="D1797" t="s">
         <v>503</v>
       </c>
       <c r="E1797">
-        <v>0.8911293726418128</v>
+        <v>0.9029140286926323</v>
       </c>
       <c r="F1797">
         <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.01119760951589179</v>
+        <v>0.01022834708277376</v>
       </c>
       <c r="H1797">
-        <v>0.01062887062735819</v>
+        <v>0.01059708597130737</v>
       </c>
       <c r="I1797">
-        <v>0.1112611114663942</v>
+        <v>0.0887388885336069</v>
       </c>
       <c r="J1797">
         <v>1.089232802540981</v>
       </c>
       <c r="K1797">
-        <v>4.68</v>
+        <v>4.24</v>
       </c>
       <c r="L1797">
-        <v>6.1</v>
+        <v>5.61</v>
       </c>
       <c r="M1797">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="N1797">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="O1797">
         <v>1</v>
       </c>
       <c r="P1797" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="1798" spans="1:16">
-      <c r="A1798" s="1">
-        <v>4</v>
-      </c>
-      <c r="B1798" t="s">
-        <v>347</v>
-      </c>
-      <c r="C1798">
-        <v>0.9916529172262392</v>
-      </c>
-      <c r="D1798" t="s">
-        <v>503</v>
-      </c>
-      <c r="E1798">
-        <v>0.8911293726418128</v>
-      </c>
-      <c r="F1798">
-        <v>-1</v>
-      </c>
-      <c r="G1798">
-        <v>0.01022834708277376</v>
-      </c>
-      <c r="H1798">
-        <v>0.01062887062735819</v>
-      </c>
-      <c r="I1798">
-        <v>0.1005235445844264</v>
-      </c>
-      <c r="J1798">
-        <v>1.089232802540981</v>
-      </c>
-      <c r="K1798">
-        <v>4.24</v>
-      </c>
-      <c r="L1798">
-        <v>5.61</v>
-      </c>
-      <c r="M1798">
-        <v>4.47</v>
-      </c>
-      <c r="N1798">
-        <v>5.76</v>
-      </c>
-      <c r="O1798">
-        <v>1</v>
-      </c>
-      <c r="P1798" t="s">
         <v>616</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -1525,7 +1525,7 @@
     <t>2021-08-02</t>
   </si>
   <si>
-    <t>2021-08-26</t>
+    <t>2021-08-30</t>
   </si>
   <si>
     <t>2021-07-09</t>
@@ -91286,7 +91286,7 @@
         <v>503</v>
       </c>
       <c r="E1782">
-        <v>1.469357976653697</v>
+        <v>1.418216237485246</v>
       </c>
       <c r="F1782">
         <v>-1</v>
@@ -91295,10 +91295,10 @@
         <v>0.009688634197525466</v>
       </c>
       <c r="H1782">
-        <v>0.0100306420233463</v>
+        <v>0.009921783762514753</v>
       </c>
       <c r="I1782">
-        <v>0.06200782582083786</v>
+        <v>0.1131495649892891</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
@@ -91310,10 +91310,10 @@
         <v>5.61</v>
       </c>
       <c r="M1782">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="N1782">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91536,7 +91536,7 @@
         <v>503</v>
       </c>
       <c r="E1787">
-        <v>1.213585871572751</v>
+        <v>1.164168438730687</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91545,10 +91545,10 @@
         <v>0.009932336158321693</v>
       </c>
       <c r="H1787">
-        <v>0.01028641412842725</v>
+        <v>0.01017583156126931</v>
       </c>
       <c r="I1787">
-        <v>0.07407797010555583</v>
+        <v>0.1234954029476194</v>
       </c>
       <c r="J1787">
         <v>1.01941890526455</v>
@@ -91560,10 +91560,10 @@
         <v>5.61</v>
       </c>
       <c r="M1787">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="N1787">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91736,7 +91736,7 @@
         <v>503</v>
       </c>
       <c r="E1791">
-        <v>0.9634130378888823</v>
+        <v>0.9156821634761485</v>
       </c>
       <c r="F1791">
         <v>-1</v>
@@ -91745,10 +91745,10 @@
         <v>0.01113398359161349</v>
       </c>
       <c r="H1791">
-        <v>0.01053658696211112</v>
+        <v>0.01042431783652385</v>
       </c>
       <c r="I1791">
-        <v>0.1026033704976275</v>
+        <v>0.1503342449103613</v>
       </c>
       <c r="J1791">
         <v>1.075637519575532</v>
@@ -91760,10 +91760,10 @@
         <v>6.1</v>
       </c>
       <c r="M1791">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="N1791">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="O1791">
         <v>1</v>
@@ -91786,7 +91786,7 @@
         <v>503</v>
       </c>
       <c r="E1792">
-        <v>0.9634130378888823</v>
+        <v>0.9156821634761485</v>
       </c>
       <c r="F1792">
         <v>-1</v>
@@ -91795,10 +91795,10 @@
         <v>0.01017070308300026</v>
       </c>
       <c r="H1792">
-        <v>0.01053658696211112</v>
+        <v>0.01042431783652385</v>
       </c>
       <c r="I1792">
-        <v>0.08588387911086137</v>
+        <v>0.1336147535235952</v>
       </c>
       <c r="J1792">
         <v>1.075637519575532</v>
@@ -91810,10 +91810,10 @@
         <v>5.61</v>
       </c>
       <c r="M1792">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="N1792">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91986,7 +91986,7 @@
         <v>503</v>
       </c>
       <c r="E1796">
-        <v>0.9029140286926323</v>
+        <v>0.855591012768862</v>
       </c>
       <c r="F1796">
         <v>-1</v>
@@ -91995,10 +91995,10 @@
         <v>0.01119760951589179</v>
       </c>
       <c r="H1796">
-        <v>0.01059708597130737</v>
+        <v>0.01048440898723114</v>
       </c>
       <c r="I1796">
-        <v>0.0994764554155747</v>
+        <v>0.146799471339345</v>
       </c>
       <c r="J1796">
         <v>1.089232802540981</v>
@@ -92010,10 +92010,10 @@
         <v>6.1</v>
       </c>
       <c r="M1796">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="N1796">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92036,7 +92036,7 @@
         <v>503</v>
       </c>
       <c r="E1797">
-        <v>0.9029140286926323</v>
+        <v>0.855591012768862</v>
       </c>
       <c r="F1797">
         <v>-1</v>
@@ -92045,10 +92045,10 @@
         <v>0.01022834708277376</v>
       </c>
       <c r="H1797">
-        <v>0.01059708597130737</v>
+        <v>0.01048440898723114</v>
       </c>
       <c r="I1797">
-        <v>0.0887388885336069</v>
+        <v>0.1360619044573772</v>
       </c>
       <c r="J1797">
         <v>1.089232802540981</v>
@@ -92060,10 +92060,10 @@
         <v>5.61</v>
       </c>
       <c r="M1797">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="N1797">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="O1797">
         <v>1</v>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5403" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5400" uniqueCount="617">
   <si>
     <t>trade_time</t>
   </si>
@@ -1525,7 +1525,7 @@
     <t>2021-08-02</t>
   </si>
   <si>
-    <t>2021-08-30</t>
+    <t>2021-08-31</t>
   </si>
   <si>
     <t>2021-07-09</t>
@@ -2222,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1797"/>
+  <dimension ref="A1:P1796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91286,7 +91286,7 @@
         <v>503</v>
       </c>
       <c r="E1782">
-        <v>1.418216237485246</v>
+        <v>1.402402614436236</v>
       </c>
       <c r="F1782">
         <v>-1</v>
@@ -91295,10 +91295,10 @@
         <v>0.009688634197525466</v>
       </c>
       <c r="H1782">
-        <v>0.009921783762514753</v>
+        <v>0.01011759738556376</v>
       </c>
       <c r="I1782">
-        <v>0.1131495649892891</v>
+        <v>0.1289631880382993</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
@@ -91310,10 +91310,10 @@
         <v>5.61</v>
       </c>
       <c r="M1782">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="N1782">
-        <v>5.67</v>
+        <v>5.76</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91427,43 +91427,43 @@
         <v>2</v>
       </c>
       <c r="B1785" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C1785">
-        <v>0.9401868269402112</v>
+        <v>1.329119523361904</v>
       </c>
       <c r="D1785" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E1785">
-        <v>1.129313712414549</v>
+        <v>1.110382488415344</v>
       </c>
       <c r="F1785">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1785">
-        <v>0.01141981317305979</v>
+        <v>0.0108708804766381</v>
       </c>
       <c r="H1785">
-        <v>0.01065068628758545</v>
+        <v>0.009469617511584654</v>
       </c>
       <c r="I1785">
-        <v>0.1891268854743382</v>
+        <v>0.2187370349465603</v>
       </c>
       <c r="J1785">
         <v>1.01941890526455</v>
       </c>
       <c r="K1785">
-        <v>5.14</v>
+        <v>4.68</v>
       </c>
       <c r="L1785">
-        <v>6.18</v>
+        <v>6.1</v>
       </c>
       <c r="M1785">
-        <v>4.67</v>
+        <v>4.1</v>
       </c>
       <c r="N1785">
-        <v>5.89</v>
+        <v>5.29</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91477,43 +91477,43 @@
         <v>3</v>
       </c>
       <c r="B1786" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C1786">
-        <v>1.329119523361904</v>
+        <v>1.287663841678307</v>
       </c>
       <c r="D1786" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E1786">
-        <v>1.110382488415344</v>
+        <v>1.142032359151586</v>
       </c>
       <c r="F1786">
         <v>-1</v>
       </c>
       <c r="G1786">
-        <v>0.0108708804766381</v>
+        <v>0.009932336158321693</v>
       </c>
       <c r="H1786">
-        <v>0.009469617511584654</v>
+        <v>0.01037796764084841</v>
       </c>
       <c r="I1786">
-        <v>0.2187370349465603</v>
+        <v>0.1456314825267206</v>
       </c>
       <c r="J1786">
         <v>1.01941890526455</v>
       </c>
       <c r="K1786">
-        <v>4.68</v>
+        <v>4.24</v>
       </c>
       <c r="L1786">
-        <v>6.1</v>
+        <v>5.61</v>
       </c>
       <c r="M1786">
-        <v>4.1</v>
+        <v>4.53</v>
       </c>
       <c r="N1786">
-        <v>5.29</v>
+        <v>5.76</v>
       </c>
       <c r="O1786">
         <v>1</v>
@@ -91524,63 +91524,63 @@
     </row>
     <row r="1787" spans="1:16">
       <c r="A1787" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1787" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C1787">
-        <v>1.287663841678307</v>
+        <v>0.6624808919430629</v>
       </c>
       <c r="D1787" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E1787">
-        <v>1.164168438730687</v>
+        <v>0.8667727835822649</v>
       </c>
       <c r="F1787">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1787">
-        <v>0.009932336158321693</v>
+        <v>0.01253751910805694</v>
       </c>
       <c r="H1787">
-        <v>0.01017583156126931</v>
+        <v>0.01091322721641774</v>
       </c>
       <c r="I1787">
-        <v>0.1234954029476194</v>
+        <v>0.204291891639202</v>
       </c>
       <c r="J1787">
-        <v>1.01941890526455</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1787">
-        <v>4.24</v>
+        <v>5.52</v>
       </c>
       <c r="L1787">
-        <v>5.61</v>
+        <v>6.6</v>
       </c>
       <c r="M1787">
-        <v>4.42</v>
+        <v>4.67</v>
       </c>
       <c r="N1787">
-        <v>5.67</v>
+        <v>5.89</v>
       </c>
       <c r="O1787">
         <v>1</v>
       </c>
       <c r="P1787" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="1788" spans="1:16">
       <c r="A1788" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1788" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C1788">
-        <v>0.6624808919430629</v>
+        <v>0.6253392702709037</v>
       </c>
       <c r="D1788" t="s">
         <v>504</v>
@@ -91592,22 +91592,22 @@
         <v>1</v>
       </c>
       <c r="G1788">
-        <v>0.01253751910805694</v>
+        <v>0.0121346607297291</v>
       </c>
       <c r="H1788">
         <v>0.01091322721641774</v>
       </c>
       <c r="I1788">
-        <v>0.204291891639202</v>
+        <v>0.2414335133113612</v>
       </c>
       <c r="J1788">
         <v>1.075637519575532</v>
       </c>
       <c r="K1788">
-        <v>5.52</v>
+        <v>5.35</v>
       </c>
       <c r="L1788">
-        <v>6.6</v>
+        <v>6.38</v>
       </c>
       <c r="M1788">
         <v>4.67</v>
@@ -91624,13 +91624,13 @@
     </row>
     <row r="1789" spans="1:16">
       <c r="A1789" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1789" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1789">
-        <v>0.6253392702709037</v>
+        <v>0.6498775214454353</v>
       </c>
       <c r="D1789" t="s">
         <v>504</v>
@@ -91642,22 +91642,22 @@
         <v>1</v>
       </c>
       <c r="G1789">
-        <v>0.0121346607297291</v>
+        <v>0.01203012247855456</v>
       </c>
       <c r="H1789">
         <v>0.01091322721641774</v>
       </c>
       <c r="I1789">
-        <v>0.2414335133113612</v>
+        <v>0.2168952621368296</v>
       </c>
       <c r="J1789">
         <v>1.075637519575532</v>
       </c>
       <c r="K1789">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="L1789">
-        <v>6.38</v>
+        <v>6.34</v>
       </c>
       <c r="M1789">
         <v>4.67</v>
@@ -91674,46 +91674,46 @@
     </row>
     <row r="1790" spans="1:16">
       <c r="A1790" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1790" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C1790">
-        <v>0.6498775214454353</v>
+        <v>1.06601640838651</v>
       </c>
       <c r="D1790" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E1790">
-        <v>0.8667727835822649</v>
+        <v>0.8873620363228394</v>
       </c>
       <c r="F1790">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1790">
-        <v>0.01203012247855456</v>
+        <v>0.01113398359161349</v>
       </c>
       <c r="H1790">
-        <v>0.01091322721641774</v>
+        <v>0.01063263796367716</v>
       </c>
       <c r="I1790">
-        <v>0.2168952621368296</v>
+        <v>0.1786543720636704</v>
       </c>
       <c r="J1790">
         <v>1.075637519575532</v>
       </c>
       <c r="K1790">
-        <v>5.29</v>
+        <v>4.68</v>
       </c>
       <c r="L1790">
-        <v>6.34</v>
+        <v>6.1</v>
       </c>
       <c r="M1790">
-        <v>4.67</v>
+        <v>4.53</v>
       </c>
       <c r="N1790">
-        <v>5.89</v>
+        <v>5.76</v>
       </c>
       <c r="O1790">
         <v>1</v>
@@ -91724,46 +91724,46 @@
     </row>
     <row r="1791" spans="1:16">
       <c r="A1791" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1791" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C1791">
-        <v>1.06601640838651</v>
+        <v>1.049296916999744</v>
       </c>
       <c r="D1791" t="s">
         <v>503</v>
       </c>
       <c r="E1791">
-        <v>0.9156821634761485</v>
+        <v>0.8873620363228394</v>
       </c>
       <c r="F1791">
         <v>-1</v>
       </c>
       <c r="G1791">
-        <v>0.01113398359161349</v>
+        <v>0.01017070308300026</v>
       </c>
       <c r="H1791">
-        <v>0.01042431783652385</v>
+        <v>0.01063263796367716</v>
       </c>
       <c r="I1791">
-        <v>0.1503342449103613</v>
+        <v>0.1619348806769043</v>
       </c>
       <c r="J1791">
         <v>1.075637519575532</v>
       </c>
       <c r="K1791">
-        <v>4.68</v>
+        <v>4.24</v>
       </c>
       <c r="L1791">
-        <v>6.1</v>
+        <v>5.61</v>
       </c>
       <c r="M1791">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="N1791">
-        <v>5.67</v>
+        <v>5.76</v>
       </c>
       <c r="O1791">
         <v>1</v>
@@ -91774,63 +91774,63 @@
     </row>
     <row r="1792" spans="1:16">
       <c r="A1792" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1792" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C1792">
-        <v>1.049296916999744</v>
+        <v>0.5874349299737824</v>
       </c>
       <c r="D1792" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E1792">
-        <v>0.9156821634761485</v>
+        <v>0.8032828121336166</v>
       </c>
       <c r="F1792">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1792">
-        <v>0.01017070308300026</v>
+        <v>0.01261256507002622</v>
       </c>
       <c r="H1792">
-        <v>0.01042431783652385</v>
+        <v>0.01097671718786638</v>
       </c>
       <c r="I1792">
-        <v>0.1336147535235952</v>
+        <v>0.2158478821598342</v>
       </c>
       <c r="J1792">
-        <v>1.075637519575532</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1792">
-        <v>4.24</v>
+        <v>5.52</v>
       </c>
       <c r="L1792">
-        <v>5.61</v>
+        <v>6.6</v>
       </c>
       <c r="M1792">
-        <v>4.42</v>
+        <v>4.67</v>
       </c>
       <c r="N1792">
-        <v>5.67</v>
+        <v>5.89</v>
       </c>
       <c r="O1792">
         <v>1</v>
       </c>
       <c r="P1792" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1793" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C1793">
-        <v>0.5874349299737824</v>
+        <v>0.5526045064057499</v>
       </c>
       <c r="D1793" t="s">
         <v>504</v>
@@ -91842,22 +91842,22 @@
         <v>1</v>
       </c>
       <c r="G1793">
-        <v>0.01261256507002622</v>
+        <v>0.01220739549359425</v>
       </c>
       <c r="H1793">
         <v>0.01097671718786638</v>
       </c>
       <c r="I1793">
-        <v>0.2158478821598342</v>
+        <v>0.2506783057278668</v>
       </c>
       <c r="J1793">
         <v>1.089232802540981</v>
       </c>
       <c r="K1793">
-        <v>5.52</v>
+        <v>5.35</v>
       </c>
       <c r="L1793">
-        <v>6.6</v>
+        <v>6.38</v>
       </c>
       <c r="M1793">
         <v>4.67</v>
@@ -91874,13 +91874,13 @@
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1794" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1794">
-        <v>0.5526045064057499</v>
+        <v>0.5779584745582085</v>
       </c>
       <c r="D1794" t="s">
         <v>504</v>
@@ -91892,22 +91892,22 @@
         <v>1</v>
       </c>
       <c r="G1794">
-        <v>0.01220739549359425</v>
+        <v>0.01210204152544179</v>
       </c>
       <c r="H1794">
         <v>0.01097671718786638</v>
       </c>
       <c r="I1794">
-        <v>0.2506783057278668</v>
+        <v>0.2253243375754082</v>
       </c>
       <c r="J1794">
         <v>1.089232802540981</v>
       </c>
       <c r="K1794">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="L1794">
-        <v>6.38</v>
+        <v>6.34</v>
       </c>
       <c r="M1794">
         <v>4.67</v>
@@ -91924,46 +91924,46 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1795" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C1795">
-        <v>0.5779584745582085</v>
+        <v>1.002390484108207</v>
       </c>
       <c r="D1795" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E1795">
-        <v>0.8032828121336166</v>
+        <v>0.8257754044893533</v>
       </c>
       <c r="F1795">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1795">
-        <v>0.01210204152544179</v>
+        <v>0.01119760951589179</v>
       </c>
       <c r="H1795">
-        <v>0.01097671718786638</v>
+        <v>0.01069422459551065</v>
       </c>
       <c r="I1795">
-        <v>0.2253243375754082</v>
+        <v>0.1766150796188537</v>
       </c>
       <c r="J1795">
         <v>1.089232802540981</v>
       </c>
       <c r="K1795">
-        <v>5.29</v>
+        <v>4.68</v>
       </c>
       <c r="L1795">
-        <v>6.34</v>
+        <v>6.1</v>
       </c>
       <c r="M1795">
-        <v>4.67</v>
+        <v>4.53</v>
       </c>
       <c r="N1795">
-        <v>5.89</v>
+        <v>5.76</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -91974,101 +91974,51 @@
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1796" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C1796">
-        <v>1.002390484108207</v>
+        <v>0.9916529172262392</v>
       </c>
       <c r="D1796" t="s">
         <v>503</v>
       </c>
       <c r="E1796">
-        <v>0.855591012768862</v>
+        <v>0.8257754044893533</v>
       </c>
       <c r="F1796">
         <v>-1</v>
       </c>
       <c r="G1796">
-        <v>0.01119760951589179</v>
+        <v>0.01022834708277376</v>
       </c>
       <c r="H1796">
-        <v>0.01048440898723114</v>
+        <v>0.01069422459551065</v>
       </c>
       <c r="I1796">
-        <v>0.146799471339345</v>
+        <v>0.1658775127368859</v>
       </c>
       <c r="J1796">
         <v>1.089232802540981</v>
       </c>
       <c r="K1796">
-        <v>4.68</v>
+        <v>4.24</v>
       </c>
       <c r="L1796">
-        <v>6.1</v>
+        <v>5.61</v>
       </c>
       <c r="M1796">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="N1796">
-        <v>5.67</v>
+        <v>5.76</v>
       </c>
       <c r="O1796">
         <v>1</v>
       </c>
       <c r="P1796" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="1797" spans="1:16">
-      <c r="A1797" s="1">
-        <v>4</v>
-      </c>
-      <c r="B1797" t="s">
-        <v>347</v>
-      </c>
-      <c r="C1797">
-        <v>0.9916529172262392</v>
-      </c>
-      <c r="D1797" t="s">
-        <v>503</v>
-      </c>
-      <c r="E1797">
-        <v>0.855591012768862</v>
-      </c>
-      <c r="F1797">
-        <v>-1</v>
-      </c>
-      <c r="G1797">
-        <v>0.01022834708277376</v>
-      </c>
-      <c r="H1797">
-        <v>0.01048440898723114</v>
-      </c>
-      <c r="I1797">
-        <v>0.1360619044573772</v>
-      </c>
-      <c r="J1797">
-        <v>1.089232802540981</v>
-      </c>
-      <c r="K1797">
-        <v>4.24</v>
-      </c>
-      <c r="L1797">
-        <v>5.61</v>
-      </c>
-      <c r="M1797">
-        <v>4.42</v>
-      </c>
-      <c r="N1797">
-        <v>5.67</v>
-      </c>
-      <c r="O1797">
-        <v>1</v>
-      </c>
-      <c r="P1797" t="s">
         <v>616</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5415" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5418" uniqueCount="618">
   <si>
     <t>trade_time</t>
   </si>
@@ -1531,7 +1531,7 @@
     <t>2021-08-31</t>
   </si>
   <si>
-    <t>2021-09-08</t>
+    <t>2021-09-09</t>
   </si>
   <si>
     <t>2016-03-09</t>
@@ -2225,7 +2225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1801"/>
+  <dimension ref="A1:P1802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91289,7 +91289,7 @@
         <v>505</v>
       </c>
       <c r="E1782">
-        <v>1.57735015083286</v>
+        <v>1.66887246972413</v>
       </c>
       <c r="F1782">
         <v>-1</v>
@@ -91298,10 +91298,10 @@
         <v>0.01039645564639531</v>
       </c>
       <c r="H1782">
-        <v>0.01054264984916714</v>
+        <v>0.01071112753027587</v>
       </c>
       <c r="I1782">
-        <v>0.04619420277182762</v>
+        <v>-0.04532811611944254</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
@@ -91313,10 +91313,10 @@
         <v>6.01</v>
       </c>
       <c r="M1782">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="N1782">
-        <v>6.06</v>
+        <v>6.19</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91539,7 +91539,7 @@
         <v>505</v>
       </c>
       <c r="E1787">
-        <v>1.309507901467195</v>
+        <v>1.398731145256614</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91548,10 +91548,10 @@
         <v>0.009891559402111113</v>
       </c>
       <c r="H1787">
-        <v>0.0108104920985328</v>
+        <v>0.01098126885474339</v>
       </c>
       <c r="I1787">
-        <v>0.01893269642169315</v>
+        <v>-0.07029054736772533</v>
       </c>
       <c r="J1787">
         <v>1.01941890526455</v>
@@ -91563,10 +91563,10 @@
         <v>5.61</v>
       </c>
       <c r="M1787">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="N1787">
-        <v>6.06</v>
+        <v>6.19</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91589,7 +91589,7 @@
         <v>505</v>
       </c>
       <c r="E1788">
-        <v>1.309507901467195</v>
+        <v>1.398731145256614</v>
       </c>
       <c r="F1788">
         <v>-1</v>
@@ -91598,10 +91598,10 @@
         <v>0.01065855020800635</v>
       </c>
       <c r="H1788">
-        <v>0.0108104920985328</v>
+        <v>0.01098126885474339</v>
       </c>
       <c r="I1788">
-        <v>0.05194189052645548</v>
+        <v>-0.037281353262963</v>
       </c>
       <c r="J1788">
         <v>1.01941890526455</v>
@@ -91613,10 +91613,10 @@
         <v>6.01</v>
       </c>
       <c r="M1788">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="N1788">
-        <v>6.06</v>
+        <v>6.19</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91789,7 +91789,7 @@
         <v>505</v>
       </c>
       <c r="E1792">
-        <v>1.04752915877802</v>
+        <v>1.134503657994999</v>
       </c>
       <c r="F1792">
         <v>-1</v>
@@ -91798,10 +91798,10 @@
         <v>0.01113398359161349</v>
       </c>
       <c r="H1792">
-        <v>0.01107247084122198</v>
+        <v>0.011245496342005</v>
       </c>
       <c r="I1792">
-        <v>0.0184872496084898</v>
+        <v>-0.06848724960848962</v>
       </c>
       <c r="J1792">
         <v>1.075637519575532</v>
@@ -91813,10 +91813,10 @@
         <v>6.1</v>
       </c>
       <c r="M1792">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="N1792">
-        <v>6.06</v>
+        <v>6.19</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91830,43 +91830,43 @@
         <v>4</v>
       </c>
       <c r="B1793" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C1793">
-        <v>1.092322417782765</v>
+        <v>1.073413037888883</v>
       </c>
       <c r="D1793" t="s">
         <v>505</v>
       </c>
       <c r="E1793">
-        <v>1.04752915877802</v>
+        <v>1.134503657994999</v>
       </c>
       <c r="F1793">
         <v>-1</v>
       </c>
       <c r="G1793">
-        <v>0.01012767758221723</v>
+        <v>0.01064658696211112</v>
       </c>
       <c r="H1793">
-        <v>0.01107247084122198</v>
+        <v>0.011245496342005</v>
       </c>
       <c r="I1793">
-        <v>0.04479325900474507</v>
+        <v>-0.06109062010611677</v>
       </c>
       <c r="J1793">
         <v>1.075637519575532</v>
       </c>
       <c r="K1793">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="L1793">
-        <v>5.61</v>
+        <v>5.86</v>
       </c>
       <c r="M1793">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="N1793">
-        <v>6.06</v>
+        <v>6.19</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -91880,43 +91880,43 @@
         <v>5</v>
       </c>
       <c r="B1794" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C1794">
-        <v>1.105092910735574</v>
+        <v>1.092322417782765</v>
       </c>
       <c r="D1794" t="s">
         <v>505</v>
       </c>
       <c r="E1794">
-        <v>1.04752915877802</v>
+        <v>1.134503657994999</v>
       </c>
       <c r="F1794">
         <v>-1</v>
       </c>
       <c r="G1794">
-        <v>0.01091490708926443</v>
+        <v>0.01012767758221723</v>
       </c>
       <c r="H1794">
-        <v>0.01107247084122198</v>
+        <v>0.011245496342005</v>
       </c>
       <c r="I1794">
-        <v>0.05756375195755403</v>
+        <v>-0.04218124021223435</v>
       </c>
       <c r="J1794">
         <v>1.075637519575532</v>
       </c>
       <c r="K1794">
-        <v>4.56</v>
+        <v>4.2</v>
       </c>
       <c r="L1794">
-        <v>6.01</v>
+        <v>5.61</v>
       </c>
       <c r="M1794">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="N1794">
-        <v>6.06</v>
+        <v>6.19</v>
       </c>
       <c r="O1794">
         <v>1</v>
@@ -91927,63 +91927,63 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1795" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C1795">
-        <v>0.5874349299737824</v>
+        <v>1.105092910735574</v>
       </c>
       <c r="D1795" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E1795">
-        <v>0.8568521242352567</v>
+        <v>1.134503657994999</v>
       </c>
       <c r="F1795">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1795">
-        <v>0.01261256507002622</v>
+        <v>0.01091490708926443</v>
       </c>
       <c r="H1795">
-        <v>0.01094314787576474</v>
+        <v>0.011245496342005</v>
       </c>
       <c r="I1795">
-        <v>0.2694171942614743</v>
+        <v>-0.02941074725942538</v>
       </c>
       <c r="J1795">
-        <v>1.089232802540981</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1795">
-        <v>5.52</v>
+        <v>4.56</v>
       </c>
       <c r="L1795">
-        <v>6.6</v>
+        <v>6.01</v>
       </c>
       <c r="M1795">
-        <v>4.63</v>
+        <v>4.7</v>
       </c>
       <c r="N1795">
-        <v>5.9</v>
+        <v>6.19</v>
       </c>
       <c r="O1795">
         <v>1</v>
       </c>
       <c r="P1795" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1796" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C1796">
-        <v>0.5526045064057499</v>
+        <v>0.5874349299737824</v>
       </c>
       <c r="D1796" t="s">
         <v>502</v>
@@ -91995,22 +91995,22 @@
         <v>1</v>
       </c>
       <c r="G1796">
-        <v>0.01220739549359425</v>
+        <v>0.01261256507002622</v>
       </c>
       <c r="H1796">
         <v>0.01094314787576474</v>
       </c>
       <c r="I1796">
-        <v>0.3042476178295068</v>
+        <v>0.2694171942614743</v>
       </c>
       <c r="J1796">
         <v>1.089232802540981</v>
       </c>
       <c r="K1796">
-        <v>5.35</v>
+        <v>5.52</v>
       </c>
       <c r="L1796">
-        <v>6.38</v>
+        <v>6.6</v>
       </c>
       <c r="M1796">
         <v>4.63</v>
@@ -92027,13 +92027,13 @@
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1797" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C1797">
-        <v>0.5779584745582085</v>
+        <v>0.5526045064057499</v>
       </c>
       <c r="D1797" t="s">
         <v>502</v>
@@ -92045,22 +92045,22 @@
         <v>1</v>
       </c>
       <c r="G1797">
-        <v>0.01210204152544179</v>
+        <v>0.01220739549359425</v>
       </c>
       <c r="H1797">
         <v>0.01094314787576474</v>
       </c>
       <c r="I1797">
-        <v>0.2788936496770482</v>
+        <v>0.3042476178295068</v>
       </c>
       <c r="J1797">
         <v>1.089232802540981</v>
       </c>
       <c r="K1797">
-        <v>5.29</v>
+        <v>5.35</v>
       </c>
       <c r="L1797">
-        <v>6.34</v>
+        <v>6.38</v>
       </c>
       <c r="M1797">
         <v>4.63</v>
@@ -92077,46 +92077,46 @@
     </row>
     <row r="1798" spans="1:16">
       <c r="A1798" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1798" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C1798">
-        <v>1.002390484108207</v>
+        <v>0.5779584745582085</v>
       </c>
       <c r="D1798" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E1798">
-        <v>0.9841751401590262</v>
+        <v>0.8568521242352567</v>
       </c>
       <c r="F1798">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1798">
-        <v>0.01119760951589179</v>
+        <v>0.01210204152544179</v>
       </c>
       <c r="H1798">
-        <v>0.01113582485984097</v>
+        <v>0.01094314787576474</v>
       </c>
       <c r="I1798">
-        <v>0.01821534394918078</v>
+        <v>0.2788936496770482</v>
       </c>
       <c r="J1798">
         <v>1.089232802540981</v>
       </c>
       <c r="K1798">
-        <v>4.68</v>
+        <v>5.29</v>
       </c>
       <c r="L1798">
-        <v>6.1</v>
+        <v>6.34</v>
       </c>
       <c r="M1798">
-        <v>4.66</v>
+        <v>4.63</v>
       </c>
       <c r="N1798">
-        <v>6.06</v>
+        <v>5.9</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92127,46 +92127,46 @@
     </row>
     <row r="1799" spans="1:16">
       <c r="A1799" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1799" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C1799">
-        <v>1.012914028692633</v>
+        <v>1.002390484108207</v>
       </c>
       <c r="D1799" t="s">
         <v>505</v>
       </c>
       <c r="E1799">
-        <v>0.9841751401590262</v>
+        <v>1.070605828057388</v>
       </c>
       <c r="F1799">
         <v>-1</v>
       </c>
       <c r="G1799">
-        <v>0.01070708597130737</v>
+        <v>0.01119760951589179</v>
       </c>
       <c r="H1799">
-        <v>0.01113582485984097</v>
+        <v>0.01130939417194262</v>
       </c>
       <c r="I1799">
-        <v>0.0287388885336064</v>
+        <v>-0.06821534394918061</v>
       </c>
       <c r="J1799">
         <v>1.089232802540981</v>
       </c>
       <c r="K1799">
-        <v>4.45</v>
+        <v>4.68</v>
       </c>
       <c r="L1799">
-        <v>5.86</v>
+        <v>6.1</v>
       </c>
       <c r="M1799">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="N1799">
-        <v>6.06</v>
+        <v>6.19</v>
       </c>
       <c r="O1799">
         <v>1</v>
@@ -92177,46 +92177,46 @@
     </row>
     <row r="1800" spans="1:16">
       <c r="A1800" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1800" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C1800">
-        <v>1.035222229327879</v>
+        <v>1.012914028692633</v>
       </c>
       <c r="D1800" t="s">
         <v>505</v>
       </c>
       <c r="E1800">
-        <v>0.9841751401590262</v>
+        <v>1.070605828057388</v>
       </c>
       <c r="F1800">
         <v>-1</v>
       </c>
       <c r="G1800">
-        <v>0.01018477777067212</v>
+        <v>0.01070708597130737</v>
       </c>
       <c r="H1800">
-        <v>0.01113582485984097</v>
+        <v>0.01130939417194262</v>
       </c>
       <c r="I1800">
-        <v>0.05104708916885237</v>
+        <v>-0.05769179936475499</v>
       </c>
       <c r="J1800">
         <v>1.089232802540981</v>
       </c>
       <c r="K1800">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="L1800">
-        <v>5.61</v>
+        <v>5.86</v>
       </c>
       <c r="M1800">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="N1800">
-        <v>6.06</v>
+        <v>6.19</v>
       </c>
       <c r="O1800">
         <v>1</v>
@@ -92227,51 +92227,101 @@
     </row>
     <row r="1801" spans="1:16">
       <c r="A1801" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1801" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C1801">
-        <v>1.043098420413125</v>
+        <v>1.035222229327879</v>
       </c>
       <c r="D1801" t="s">
         <v>505</v>
       </c>
       <c r="E1801">
-        <v>0.9841751401590262</v>
+        <v>1.070605828057388</v>
       </c>
       <c r="F1801">
         <v>-1</v>
       </c>
       <c r="G1801">
-        <v>0.01097690157958687</v>
+        <v>0.01018477777067212</v>
       </c>
       <c r="H1801">
-        <v>0.01113582485984097</v>
+        <v>0.01130939417194262</v>
       </c>
       <c r="I1801">
-        <v>0.0589232802540991</v>
+        <v>-0.03538359872950902</v>
       </c>
       <c r="J1801">
         <v>1.089232802540981</v>
       </c>
       <c r="K1801">
+        <v>4.2</v>
+      </c>
+      <c r="L1801">
+        <v>5.61</v>
+      </c>
+      <c r="M1801">
+        <v>4.7</v>
+      </c>
+      <c r="N1801">
+        <v>6.19</v>
+      </c>
+      <c r="O1801">
+        <v>1</v>
+      </c>
+      <c r="P1801" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:16">
+      <c r="A1802" s="1">
+        <v>6</v>
+      </c>
+      <c r="B1802" t="s">
+        <v>347</v>
+      </c>
+      <c r="C1802">
+        <v>1.043098420413125</v>
+      </c>
+      <c r="D1802" t="s">
+        <v>505</v>
+      </c>
+      <c r="E1802">
+        <v>1.070605828057388</v>
+      </c>
+      <c r="F1802">
+        <v>-1</v>
+      </c>
+      <c r="G1802">
+        <v>0.01097690157958687</v>
+      </c>
+      <c r="H1802">
+        <v>0.01130939417194262</v>
+      </c>
+      <c r="I1802">
+        <v>-0.02750740764426229</v>
+      </c>
+      <c r="J1802">
+        <v>1.089232802540981</v>
+      </c>
+      <c r="K1802">
         <v>4.56</v>
       </c>
-      <c r="L1801">
+      <c r="L1802">
         <v>6.01</v>
       </c>
-      <c r="M1801">
-        <v>4.66</v>
-      </c>
-      <c r="N1801">
-        <v>6.06</v>
-      </c>
-      <c r="O1801">
-        <v>1</v>
-      </c>
-      <c r="P1801" t="s">
+      <c r="M1802">
+        <v>4.7</v>
+      </c>
+      <c r="N1802">
+        <v>6.19</v>
+      </c>
+      <c r="O1802">
+        <v>1</v>
+      </c>
+      <c r="P1802" t="s">
         <v>617</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5448" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5460" uniqueCount="629">
   <si>
     <t>trade_time</t>
   </si>
@@ -1054,6 +1054,9 @@
     <t>2021-06-07</t>
   </si>
   <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
     <t>2021-09-03</t>
   </si>
   <si>
@@ -1063,22 +1066,19 @@
     <t>2021-06-25</t>
   </si>
   <si>
-    <t>2021-07-23</t>
+    <t>2021-07-26</t>
   </si>
   <si>
     <t>2021-08-23</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
   </si>
   <si>
     <t>2021-09-09</t>
   </si>
   <si>
     <t>2021-07-20</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
   </si>
   <si>
     <t>2021-09-13</t>
@@ -1552,7 +1552,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-09-16</t>
+    <t>2021-09-17</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -1898,6 +1898,9 @@
   </si>
   <si>
     <t>2021-05-27</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
   </si>
 </sst>
 </file>
@@ -2255,7 +2258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1812"/>
+  <dimension ref="A1:P1816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91263,40 +91266,40 @@
         <v>346</v>
       </c>
       <c r="C1781">
-        <v>1.623544353604688</v>
+        <v>1.579357976653697</v>
       </c>
       <c r="D1781" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E1781">
-        <v>1.670224063306082</v>
+        <v>1.415657106632275</v>
       </c>
       <c r="F1781">
         <v>-1</v>
       </c>
       <c r="G1781">
-        <v>0.01039645564639531</v>
+        <v>0.0101406420233463</v>
       </c>
       <c r="H1781">
-        <v>0.009769775936693918</v>
+        <v>0.009284342893367726</v>
       </c>
       <c r="I1781">
-        <v>-0.04667970970139468</v>
+        <v>0.1637008700214229</v>
       </c>
       <c r="J1781">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1781">
-        <v>4.56</v>
+        <v>4.45</v>
       </c>
       <c r="L1781">
-        <v>6.01</v>
+        <v>5.86</v>
       </c>
       <c r="M1781">
-        <v>4.21</v>
+        <v>4.09</v>
       </c>
       <c r="N1781">
-        <v>5.72</v>
+        <v>5.35</v>
       </c>
       <c r="O1781">
         <v>1</v>
@@ -91307,63 +91310,63 @@
     </row>
     <row r="1782" spans="1:16">
       <c r="A1782" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1782" t="s">
         <v>347</v>
       </c>
       <c r="C1782">
-        <v>0.9728076429396824</v>
+        <v>1.623544353604688</v>
       </c>
       <c r="D1782" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E1782">
-        <v>1.180090468625132</v>
+        <v>1.730985222751716</v>
       </c>
       <c r="F1782">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1782">
-        <v>0.01222719235706032</v>
+        <v>0.01039645564639531</v>
       </c>
       <c r="H1782">
-        <v>0.01061990953137487</v>
+        <v>0.009869014777248284</v>
       </c>
       <c r="I1782">
-        <v>0.20728282568545</v>
+        <v>-0.1074408691470286</v>
       </c>
       <c r="J1782">
-        <v>1.01941890526455</v>
+        <v>0.9619420277182702</v>
       </c>
       <c r="K1782">
-        <v>5.52</v>
+        <v>4.56</v>
       </c>
       <c r="L1782">
-        <v>6.6</v>
+        <v>6.01</v>
       </c>
       <c r="M1782">
-        <v>4.63</v>
+        <v>4.23</v>
       </c>
       <c r="N1782">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O1782">
         <v>1</v>
       </c>
       <c r="P1782" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1783" spans="1:16">
       <c r="A1783" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1783" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C1783">
-        <v>0.9261088568346558</v>
+        <v>0.9728076429396824</v>
       </c>
       <c r="D1783" t="s">
         <v>510</v>
@@ -91375,22 +91378,22 @@
         <v>1</v>
       </c>
       <c r="G1783">
-        <v>0.01183389114316535</v>
+        <v>0.01222719235706032</v>
       </c>
       <c r="H1783">
         <v>0.01061990953137487</v>
       </c>
       <c r="I1783">
-        <v>0.2539816117904765</v>
+        <v>0.20728282568545</v>
       </c>
       <c r="J1783">
         <v>1.01941890526455</v>
       </c>
       <c r="K1783">
-        <v>5.35</v>
+        <v>5.52</v>
       </c>
       <c r="L1783">
-        <v>6.38</v>
+        <v>6.6</v>
       </c>
       <c r="M1783">
         <v>4.63</v>
@@ -91407,13 +91410,13 @@
     </row>
     <row r="1784" spans="1:16">
       <c r="A1784" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1784" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C1784">
-        <v>0.9472739911505288</v>
+        <v>0.9261088568346558</v>
       </c>
       <c r="D1784" t="s">
         <v>510</v>
@@ -91425,22 +91428,22 @@
         <v>1</v>
       </c>
       <c r="G1784">
-        <v>0.01173272600884947</v>
+        <v>0.01183389114316535</v>
       </c>
       <c r="H1784">
         <v>0.01061990953137487</v>
       </c>
       <c r="I1784">
-        <v>0.2328164774746035</v>
+        <v>0.2539816117904765</v>
       </c>
       <c r="J1784">
         <v>1.01941890526455</v>
       </c>
       <c r="K1784">
-        <v>5.29</v>
+        <v>5.35</v>
       </c>
       <c r="L1784">
-        <v>6.34</v>
+        <v>6.38</v>
       </c>
       <c r="M1784">
         <v>4.63</v>
@@ -91457,13 +91460,13 @@
     </row>
     <row r="1785" spans="1:16">
       <c r="A1785" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1785" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C1785">
-        <v>0.9915461503087295</v>
+        <v>0.9472739911505288</v>
       </c>
       <c r="D1785" t="s">
         <v>510</v>
@@ -91475,22 +91478,22 @@
         <v>1</v>
       </c>
       <c r="G1785">
-        <v>0.01132845384969127</v>
+        <v>0.01173272600884947</v>
       </c>
       <c r="H1785">
         <v>0.01061990953137487</v>
       </c>
       <c r="I1785">
-        <v>0.1885443183164028</v>
+        <v>0.2328164774746035</v>
       </c>
       <c r="J1785">
         <v>1.01941890526455</v>
       </c>
       <c r="K1785">
-        <v>5.07</v>
+        <v>5.29</v>
       </c>
       <c r="L1785">
-        <v>6.16</v>
+        <v>6.34</v>
       </c>
       <c r="M1785">
         <v>4.63</v>
@@ -91507,46 +91510,46 @@
     </row>
     <row r="1786" spans="1:16">
       <c r="A1786" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1786" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C1786">
-        <v>1.329119523361904</v>
+        <v>0.9915461503087295</v>
       </c>
       <c r="D1786" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E1786">
-        <v>1.110382488415344</v>
+        <v>1.180090468625132</v>
       </c>
       <c r="F1786">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1786">
-        <v>0.0108708804766381</v>
+        <v>0.01132845384969127</v>
       </c>
       <c r="H1786">
-        <v>0.009469617511584654</v>
+        <v>0.01061990953137487</v>
       </c>
       <c r="I1786">
-        <v>0.2187370349465603</v>
+        <v>0.1885443183164028</v>
       </c>
       <c r="J1786">
         <v>1.01941890526455</v>
       </c>
       <c r="K1786">
-        <v>4.68</v>
+        <v>5.07</v>
       </c>
       <c r="L1786">
-        <v>6.1</v>
+        <v>6.16</v>
       </c>
       <c r="M1786">
-        <v>4.1</v>
+        <v>4.63</v>
       </c>
       <c r="N1786">
-        <v>5.29</v>
+        <v>5.9</v>
       </c>
       <c r="O1786">
         <v>1</v>
@@ -91557,13 +91560,13 @@
     </row>
     <row r="1787" spans="1:16">
       <c r="A1787" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1787" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C1787">
-        <v>1.323585871572751</v>
+        <v>1.329119523361904</v>
       </c>
       <c r="D1787" t="s">
         <v>513</v>
@@ -91575,22 +91578,22 @@
         <v>-1</v>
       </c>
       <c r="G1787">
-        <v>0.01039641412842725</v>
+        <v>0.0108708804766381</v>
       </c>
       <c r="H1787">
         <v>0.009469617511584654</v>
       </c>
       <c r="I1787">
-        <v>0.2132033831574072</v>
+        <v>0.2187370349465603</v>
       </c>
       <c r="J1787">
         <v>1.01941890526455</v>
       </c>
       <c r="K1787">
-        <v>4.45</v>
+        <v>4.68</v>
       </c>
       <c r="L1787">
-        <v>5.86</v>
+        <v>6.1</v>
       </c>
       <c r="M1787">
         <v>4.1</v>
@@ -91607,46 +91610,46 @@
     </row>
     <row r="1788" spans="1:16">
       <c r="A1788" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1788" t="s">
         <v>350</v>
       </c>
       <c r="C1788">
-        <v>1.328440597888888</v>
+        <v>1.376887085467724</v>
       </c>
       <c r="D1788" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E1788">
-        <v>1.142032359151586</v>
+        <v>1.110382488415344</v>
       </c>
       <c r="F1788">
         <v>-1</v>
       </c>
       <c r="G1788">
-        <v>0.009891559402111113</v>
+        <v>0.01010311291453228</v>
       </c>
       <c r="H1788">
-        <v>0.01037796764084841</v>
+        <v>0.009469617511584654</v>
       </c>
       <c r="I1788">
-        <v>0.1864082387373021</v>
+        <v>0.2665045970523803</v>
       </c>
       <c r="J1788">
         <v>1.01941890526455</v>
       </c>
       <c r="K1788">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="L1788">
-        <v>5.61</v>
+        <v>5.74</v>
       </c>
       <c r="M1788">
-        <v>4.53</v>
+        <v>4.1</v>
       </c>
       <c r="N1788">
-        <v>5.76</v>
+        <v>5.29</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91657,46 +91660,46 @@
     </row>
     <row r="1789" spans="1:16">
       <c r="A1789" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1789" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C1789">
-        <v>1.361449791993651</v>
+        <v>1.328440597888888</v>
       </c>
       <c r="D1789" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E1789">
-        <v>1.428246408836243</v>
+        <v>1.142032359151586</v>
       </c>
       <c r="F1789">
         <v>-1</v>
       </c>
       <c r="G1789">
-        <v>0.01065855020800635</v>
+        <v>0.009891559402111113</v>
       </c>
       <c r="H1789">
-        <v>0.01001175359116376</v>
+        <v>0.01037796764084841</v>
       </c>
       <c r="I1789">
-        <v>-0.06679661684259219</v>
+        <v>0.1864082387373021</v>
       </c>
       <c r="J1789">
         <v>1.01941890526455</v>
       </c>
       <c r="K1789">
-        <v>4.56</v>
+        <v>4.2</v>
       </c>
       <c r="L1789">
-        <v>6.01</v>
+        <v>5.61</v>
       </c>
       <c r="M1789">
-        <v>4.21</v>
+        <v>4.53</v>
       </c>
       <c r="N1789">
-        <v>5.72</v>
+        <v>5.76</v>
       </c>
       <c r="O1789">
         <v>1</v>
@@ -91707,46 +91710,46 @@
     </row>
     <row r="1790" spans="1:16">
       <c r="A1790" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1790" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C1790">
-        <v>1.398731145256614</v>
+        <v>1.361449791993651</v>
       </c>
       <c r="D1790" t="s">
         <v>512</v>
       </c>
       <c r="E1790">
-        <v>1.428246408836243</v>
+        <v>1.487858030730951</v>
       </c>
       <c r="F1790">
         <v>-1</v>
       </c>
       <c r="G1790">
-        <v>0.01098126885474339</v>
+        <v>0.01065855020800635</v>
       </c>
       <c r="H1790">
-        <v>0.01001175359116376</v>
+        <v>0.01011214196926905</v>
       </c>
       <c r="I1790">
-        <v>-0.02951526357962919</v>
+        <v>-0.1264082387373007</v>
       </c>
       <c r="J1790">
         <v>1.01941890526455</v>
       </c>
       <c r="K1790">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="L1790">
-        <v>6.19</v>
+        <v>6.01</v>
       </c>
       <c r="M1790">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="N1790">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="O1790">
         <v>1</v>
@@ -91757,113 +91760,113 @@
     </row>
     <row r="1791" spans="1:16">
       <c r="A1791" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1791" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C1791">
-        <v>0.6624808919430629</v>
+        <v>1.411643981046296</v>
       </c>
       <c r="D1791" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E1791">
-        <v>0.919798284365287</v>
+        <v>1.487858030730951</v>
       </c>
       <c r="F1791">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1791">
-        <v>0.01253751910805694</v>
+        <v>0.0106883560189537</v>
       </c>
       <c r="H1791">
-        <v>0.01088020171563471</v>
+        <v>0.01011214196926905</v>
       </c>
       <c r="I1791">
-        <v>0.2573173924222241</v>
+        <v>-0.07621404968465573</v>
       </c>
       <c r="J1791">
-        <v>1.075637519575532</v>
+        <v>1.01941890526455</v>
       </c>
       <c r="K1791">
-        <v>5.52</v>
+        <v>4.55</v>
       </c>
       <c r="L1791">
-        <v>6.6</v>
+        <v>6.05</v>
       </c>
       <c r="M1791">
-        <v>4.63</v>
+        <v>4.23</v>
       </c>
       <c r="N1791">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O1791">
         <v>1</v>
       </c>
       <c r="P1791" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1792" spans="1:16">
       <c r="A1792" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B1792" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C1792">
-        <v>0.6253392702709037</v>
+        <v>1.398731145256614</v>
       </c>
       <c r="D1792" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E1792">
-        <v>0.919798284365287</v>
+        <v>1.487858030730951</v>
       </c>
       <c r="F1792">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1792">
-        <v>0.0121346607297291</v>
+        <v>0.01098126885474339</v>
       </c>
       <c r="H1792">
-        <v>0.01088020171563471</v>
+        <v>0.01011214196926905</v>
       </c>
       <c r="I1792">
-        <v>0.2944590140943832</v>
+        <v>-0.08912688547433767</v>
       </c>
       <c r="J1792">
-        <v>1.075637519575532</v>
+        <v>1.01941890526455</v>
       </c>
       <c r="K1792">
-        <v>5.35</v>
+        <v>4.7</v>
       </c>
       <c r="L1792">
-        <v>6.38</v>
+        <v>6.19</v>
       </c>
       <c r="M1792">
-        <v>4.63</v>
+        <v>4.23</v>
       </c>
       <c r="N1792">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O1792">
         <v>1</v>
       </c>
       <c r="P1792" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1793" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C1793">
-        <v>0.6498775214454353</v>
+        <v>0.6624808919430629</v>
       </c>
       <c r="D1793" t="s">
         <v>510</v>
@@ -91875,22 +91878,22 @@
         <v>1</v>
       </c>
       <c r="G1793">
-        <v>0.01203012247855456</v>
+        <v>0.01253751910805694</v>
       </c>
       <c r="H1793">
         <v>0.01088020171563471</v>
       </c>
       <c r="I1793">
-        <v>0.2699207629198517</v>
+        <v>0.2573173924222241</v>
       </c>
       <c r="J1793">
         <v>1.075637519575532</v>
       </c>
       <c r="K1793">
-        <v>5.29</v>
+        <v>5.52</v>
       </c>
       <c r="L1793">
-        <v>6.34</v>
+        <v>6.6</v>
       </c>
       <c r="M1793">
         <v>4.63</v>
@@ -91907,13 +91910,13 @@
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1794" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C1794">
-        <v>0.7065177757520518</v>
+        <v>0.6253392702709037</v>
       </c>
       <c r="D1794" t="s">
         <v>510</v>
@@ -91925,22 +91928,22 @@
         <v>1</v>
       </c>
       <c r="G1794">
-        <v>0.01161348222424795</v>
+        <v>0.0121346607297291</v>
       </c>
       <c r="H1794">
         <v>0.01088020171563471</v>
       </c>
       <c r="I1794">
-        <v>0.2132805086132352</v>
+        <v>0.2944590140943832</v>
       </c>
       <c r="J1794">
         <v>1.075637519575532</v>
       </c>
       <c r="K1794">
-        <v>5.07</v>
+        <v>5.35</v>
       </c>
       <c r="L1794">
-        <v>6.16</v>
+        <v>6.38</v>
       </c>
       <c r="M1794">
         <v>4.63</v>
@@ -91957,46 +91960,46 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1795" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C1795">
-        <v>1.099798284365287</v>
+        <v>0.6498775214454353</v>
       </c>
       <c r="D1795" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E1795">
-        <v>0.8798861697403186</v>
+        <v>0.919798284365287</v>
       </c>
       <c r="F1795">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1795">
-        <v>0.01106020171563471</v>
+        <v>0.01203012247855456</v>
       </c>
       <c r="H1795">
-        <v>0.009700113830259682</v>
+        <v>0.01088020171563471</v>
       </c>
       <c r="I1795">
-        <v>0.2199121146249681</v>
+        <v>0.2699207629198517</v>
       </c>
       <c r="J1795">
         <v>1.075637519575532</v>
       </c>
       <c r="K1795">
+        <v>5.29</v>
+      </c>
+      <c r="L1795">
+        <v>6.34</v>
+      </c>
+      <c r="M1795">
         <v>4.63</v>
       </c>
-      <c r="L1795">
-        <v>6.08</v>
-      </c>
-      <c r="M1795">
-        <v>4.1</v>
-      </c>
       <c r="N1795">
-        <v>5.29</v>
+        <v>5.9</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -92007,46 +92010,46 @@
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1796" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C1796">
-        <v>1.136271416216722</v>
+        <v>0.7065177757520518</v>
       </c>
       <c r="D1796" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E1796">
-        <v>0.8798861697403186</v>
+        <v>0.919798284365287</v>
       </c>
       <c r="F1796">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1796">
-        <v>0.01034372858378328</v>
+        <v>0.01161348222424795</v>
       </c>
       <c r="H1796">
-        <v>0.009700113830259682</v>
+        <v>0.01088020171563471</v>
       </c>
       <c r="I1796">
-        <v>0.2563852464764036</v>
+        <v>0.2132805086132352</v>
       </c>
       <c r="J1796">
         <v>1.075637519575532</v>
       </c>
       <c r="K1796">
-        <v>4.28</v>
+        <v>5.07</v>
       </c>
       <c r="L1796">
-        <v>5.74</v>
+        <v>6.16</v>
       </c>
       <c r="M1796">
-        <v>4.1</v>
+        <v>4.63</v>
       </c>
       <c r="N1796">
-        <v>5.29</v>
+        <v>5.9</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92057,46 +92060,46 @@
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1797" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C1797">
-        <v>1.092322417782765</v>
+        <v>1.099798284365287</v>
       </c>
       <c r="D1797" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E1797">
-        <v>0.8873620363228394</v>
+        <v>0.8798861697403186</v>
       </c>
       <c r="F1797">
         <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.01012767758221723</v>
+        <v>0.01106020171563471</v>
       </c>
       <c r="H1797">
-        <v>0.01063263796367716</v>
+        <v>0.009700113830259682</v>
       </c>
       <c r="I1797">
-        <v>0.2049603814599257</v>
+        <v>0.2199121146249681</v>
       </c>
       <c r="J1797">
         <v>1.075637519575532</v>
       </c>
       <c r="K1797">
-        <v>4.2</v>
+        <v>4.63</v>
       </c>
       <c r="L1797">
-        <v>5.61</v>
+        <v>6.08</v>
       </c>
       <c r="M1797">
-        <v>4.53</v>
+        <v>4.1</v>
       </c>
       <c r="N1797">
-        <v>5.76</v>
+        <v>5.29</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92107,46 +92110,46 @@
     </row>
     <row r="1798" spans="1:16">
       <c r="A1798" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1798" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C1798">
-        <v>1.105092910735574</v>
+        <v>1.136271416216722</v>
       </c>
       <c r="D1798" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E1798">
-        <v>1.191566042587009</v>
+        <v>0.8798861697403186</v>
       </c>
       <c r="F1798">
         <v>-1</v>
       </c>
       <c r="G1798">
-        <v>0.01091490708926443</v>
+        <v>0.01034372858378328</v>
       </c>
       <c r="H1798">
-        <v>0.01024843395741299</v>
+        <v>0.009700113830259682</v>
       </c>
       <c r="I1798">
-        <v>-0.08647313185143535</v>
+        <v>0.2563852464764036</v>
       </c>
       <c r="J1798">
         <v>1.075637519575532</v>
       </c>
       <c r="K1798">
-        <v>4.56</v>
+        <v>4.28</v>
       </c>
       <c r="L1798">
-        <v>6.01</v>
+        <v>5.74</v>
       </c>
       <c r="M1798">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="N1798">
-        <v>5.72</v>
+        <v>5.29</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92157,46 +92160,46 @@
     </row>
     <row r="1799" spans="1:16">
       <c r="A1799" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1799" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C1799">
-        <v>1.155849285931329</v>
+        <v>1.092322417782765</v>
       </c>
       <c r="D1799" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E1799">
-        <v>1.191566042587009</v>
+        <v>0.8873620363228394</v>
       </c>
       <c r="F1799">
         <v>-1</v>
       </c>
       <c r="G1799">
-        <v>0.01094415071406867</v>
+        <v>0.01012767758221723</v>
       </c>
       <c r="H1799">
-        <v>0.01024843395741299</v>
+        <v>0.01063263796367716</v>
       </c>
       <c r="I1799">
-        <v>-0.03571675665568019</v>
+        <v>0.2049603814599257</v>
       </c>
       <c r="J1799">
         <v>1.075637519575532</v>
       </c>
       <c r="K1799">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="L1799">
-        <v>6.05</v>
+        <v>5.61</v>
       </c>
       <c r="M1799">
-        <v>4.21</v>
+        <v>4.53</v>
       </c>
       <c r="N1799">
-        <v>5.72</v>
+        <v>5.76</v>
       </c>
       <c r="O1799">
         <v>1</v>
@@ -92207,46 +92210,46 @@
     </row>
     <row r="1800" spans="1:16">
       <c r="A1800" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1800" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C1800">
-        <v>1.134503657994999</v>
+        <v>1.105092910735574</v>
       </c>
       <c r="D1800" t="s">
         <v>512</v>
       </c>
       <c r="E1800">
-        <v>1.191566042587009</v>
+        <v>1.250053292195498</v>
       </c>
       <c r="F1800">
         <v>-1</v>
       </c>
       <c r="G1800">
-        <v>0.011245496342005</v>
+        <v>0.01091490708926443</v>
       </c>
       <c r="H1800">
-        <v>0.01024843395741299</v>
+        <v>0.0103499467078045</v>
       </c>
       <c r="I1800">
-        <v>-0.05706238459200996</v>
+        <v>-0.1449603814599243</v>
       </c>
       <c r="J1800">
         <v>1.075637519575532</v>
       </c>
       <c r="K1800">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="L1800">
-        <v>6.19</v>
+        <v>6.01</v>
       </c>
       <c r="M1800">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="N1800">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="O1800">
         <v>1</v>
@@ -92257,46 +92260,46 @@
     </row>
     <row r="1801" spans="1:16">
       <c r="A1801" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1801" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C1801">
-        <v>1.120554659561042</v>
+        <v>1.155849285931329</v>
       </c>
       <c r="D1801" t="s">
         <v>512</v>
       </c>
       <c r="E1801">
-        <v>1.191566042587009</v>
+        <v>1.250053292195498</v>
       </c>
       <c r="F1801">
         <v>-1</v>
       </c>
       <c r="G1801">
-        <v>0.01105944534043896</v>
+        <v>0.01094415071406867</v>
       </c>
       <c r="H1801">
-        <v>0.01024843395741299</v>
+        <v>0.0103499467078045</v>
       </c>
       <c r="I1801">
-        <v>-0.07101138302596777</v>
+        <v>-0.09420400626416914</v>
       </c>
       <c r="J1801">
         <v>1.075637519575532</v>
       </c>
       <c r="K1801">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="L1801">
-        <v>6.09</v>
+        <v>6.05</v>
       </c>
       <c r="M1801">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="N1801">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="O1801">
         <v>1</v>
@@ -92307,146 +92310,146 @@
     </row>
     <row r="1802" spans="1:16">
       <c r="A1802" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1802" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C1802">
-        <v>0.5779584745582085</v>
+        <v>1.134503657994999</v>
       </c>
       <c r="D1802" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E1802">
-        <v>0.8568521242352567</v>
+        <v>1.250053292195498</v>
       </c>
       <c r="F1802">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1802">
-        <v>0.01210204152544179</v>
+        <v>0.011245496342005</v>
       </c>
       <c r="H1802">
-        <v>0.01094314787576474</v>
+        <v>0.0103499467078045</v>
       </c>
       <c r="I1802">
-        <v>0.2788936496770482</v>
+        <v>-0.1155496342004989</v>
       </c>
       <c r="J1802">
-        <v>1.089232802540981</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1802">
-        <v>5.29</v>
+        <v>4.7</v>
       </c>
       <c r="L1802">
-        <v>6.34</v>
+        <v>6.19</v>
       </c>
       <c r="M1802">
-        <v>4.63</v>
+        <v>4.23</v>
       </c>
       <c r="N1802">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O1802">
         <v>1</v>
       </c>
       <c r="P1802" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1803" spans="1:16">
       <c r="A1803" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B1803" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C1803">
-        <v>0.6375896911172241</v>
+        <v>1.120554659561042</v>
       </c>
       <c r="D1803" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E1803">
-        <v>0.8568521242352567</v>
+        <v>1.250053292195498</v>
       </c>
       <c r="F1803">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1803">
-        <v>0.01168241030888278</v>
+        <v>0.01105944534043896</v>
       </c>
       <c r="H1803">
-        <v>0.01094314787576474</v>
+        <v>0.0103499467078045</v>
       </c>
       <c r="I1803">
-        <v>0.2192624331180326</v>
+        <v>-0.1294986326344567</v>
       </c>
       <c r="J1803">
-        <v>1.089232802540981</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1803">
-        <v>5.07</v>
+        <v>4.62</v>
       </c>
       <c r="L1803">
-        <v>6.16</v>
+        <v>6.09</v>
       </c>
       <c r="M1803">
-        <v>4.63</v>
+        <v>4.23</v>
       </c>
       <c r="N1803">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O1803">
         <v>1</v>
       </c>
       <c r="P1803" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1804" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C1804">
-        <v>1.036852124235256</v>
+        <v>0.5779584745582085</v>
       </c>
       <c r="D1804" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E1804">
-        <v>0.8241455095819763</v>
+        <v>0.8568521242352567</v>
       </c>
       <c r="F1804">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1804">
-        <v>0.01112314787576474</v>
+        <v>0.01210204152544179</v>
       </c>
       <c r="H1804">
-        <v>0.009755854490418023</v>
+        <v>0.01094314787576474</v>
       </c>
       <c r="I1804">
-        <v>0.2127066146532801</v>
+        <v>0.2788936496770482</v>
       </c>
       <c r="J1804">
         <v>1.089232802540981</v>
       </c>
       <c r="K1804">
+        <v>5.29</v>
+      </c>
+      <c r="L1804">
+        <v>6.34</v>
+      </c>
+      <c r="M1804">
         <v>4.63</v>
       </c>
-      <c r="L1804">
-        <v>6.08</v>
-      </c>
-      <c r="M1804">
-        <v>4.1</v>
-      </c>
       <c r="N1804">
-        <v>5.29</v>
+        <v>5.9</v>
       </c>
       <c r="O1804">
         <v>1</v>
@@ -92457,46 +92460,46 @@
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1805" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C1805">
-        <v>1.0780836051246</v>
+        <v>0.6375896911172241</v>
       </c>
       <c r="D1805" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E1805">
-        <v>0.8241455095819763</v>
+        <v>0.8568521242352567</v>
       </c>
       <c r="F1805">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1805">
-        <v>0.0104019163948754</v>
+        <v>0.01168241030888278</v>
       </c>
       <c r="H1805">
-        <v>0.009755854490418023</v>
+        <v>0.01094314787576474</v>
       </c>
       <c r="I1805">
-        <v>0.2539380955426234</v>
+        <v>0.2192624331180326</v>
       </c>
       <c r="J1805">
         <v>1.089232802540981</v>
       </c>
       <c r="K1805">
-        <v>4.28</v>
+        <v>5.07</v>
       </c>
       <c r="L1805">
-        <v>5.74</v>
+        <v>6.16</v>
       </c>
       <c r="M1805">
-        <v>4.1</v>
+        <v>4.63</v>
       </c>
       <c r="N1805">
-        <v>5.29</v>
+        <v>5.9</v>
       </c>
       <c r="O1805">
         <v>1</v>
@@ -92507,46 +92510,46 @@
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1806" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C1806">
-        <v>1.035222229327879</v>
+        <v>1.036852124235256</v>
       </c>
       <c r="D1806" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E1806">
-        <v>0.8257754044893533</v>
+        <v>0.8241455095819763</v>
       </c>
       <c r="F1806">
         <v>-1</v>
       </c>
       <c r="G1806">
-        <v>0.01018477777067212</v>
+        <v>0.01112314787576474</v>
       </c>
       <c r="H1806">
-        <v>0.01069422459551065</v>
+        <v>0.009755854490418023</v>
       </c>
       <c r="I1806">
-        <v>0.2094468248385253</v>
+        <v>0.2127066146532801</v>
       </c>
       <c r="J1806">
         <v>1.089232802540981</v>
       </c>
       <c r="K1806">
-        <v>4.2</v>
+        <v>4.63</v>
       </c>
       <c r="L1806">
-        <v>5.61</v>
+        <v>6.08</v>
       </c>
       <c r="M1806">
-        <v>4.53</v>
+        <v>4.1</v>
       </c>
       <c r="N1806">
-        <v>5.76</v>
+        <v>5.29</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92557,46 +92560,46 @@
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1807" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C1807">
-        <v>1.043098420413125</v>
+        <v>1.0780836051246</v>
       </c>
       <c r="D1807" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E1807">
-        <v>1.134329901302468</v>
+        <v>0.8241455095819763</v>
       </c>
       <c r="F1807">
         <v>-1</v>
       </c>
       <c r="G1807">
-        <v>0.01097690157958687</v>
+        <v>0.0104019163948754</v>
       </c>
       <c r="H1807">
-        <v>0.01030567009869753</v>
+        <v>0.009755854490418023</v>
       </c>
       <c r="I1807">
-        <v>-0.09123148088934308</v>
+        <v>0.2539380955426234</v>
       </c>
       <c r="J1807">
         <v>1.089232802540981</v>
       </c>
       <c r="K1807">
-        <v>4.56</v>
+        <v>4.28</v>
       </c>
       <c r="L1807">
-        <v>6.01</v>
+        <v>5.74</v>
       </c>
       <c r="M1807">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="N1807">
-        <v>5.72</v>
+        <v>5.29</v>
       </c>
       <c r="O1807">
         <v>1</v>
@@ -92607,46 +92610,46 @@
     </row>
     <row r="1808" spans="1:16">
       <c r="A1808" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1808" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C1808">
-        <v>1.093990748438535</v>
+        <v>1.035222229327879</v>
       </c>
       <c r="D1808" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E1808">
-        <v>1.134329901302468</v>
+        <v>0.8257754044893533</v>
       </c>
       <c r="F1808">
         <v>-1</v>
       </c>
       <c r="G1808">
-        <v>0.01100600925156146</v>
+        <v>0.01018477777067212</v>
       </c>
       <c r="H1808">
-        <v>0.01030567009869753</v>
+        <v>0.01069422459551065</v>
       </c>
       <c r="I1808">
-        <v>-0.04033915286393341</v>
+        <v>0.2094468248385253</v>
       </c>
       <c r="J1808">
         <v>1.089232802540981</v>
       </c>
       <c r="K1808">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="L1808">
-        <v>6.05</v>
+        <v>5.61</v>
       </c>
       <c r="M1808">
-        <v>4.21</v>
+        <v>4.53</v>
       </c>
       <c r="N1808">
-        <v>5.72</v>
+        <v>5.76</v>
       </c>
       <c r="O1808">
         <v>1</v>
@@ -92657,46 +92660,46 @@
     </row>
     <row r="1809" spans="1:16">
       <c r="A1809" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1809" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C1809">
-        <v>1.070605828057388</v>
+        <v>1.043098420413125</v>
       </c>
       <c r="D1809" t="s">
         <v>512</v>
       </c>
       <c r="E1809">
-        <v>1.134329901302468</v>
+        <v>1.192545245251648</v>
       </c>
       <c r="F1809">
         <v>-1</v>
       </c>
       <c r="G1809">
-        <v>0.01130939417194262</v>
+        <v>0.01097690157958687</v>
       </c>
       <c r="H1809">
-        <v>0.01030567009869753</v>
+        <v>0.01040745475474835</v>
       </c>
       <c r="I1809">
-        <v>-0.06372407324508078</v>
+        <v>-0.149446824838523</v>
       </c>
       <c r="J1809">
         <v>1.089232802540981</v>
       </c>
       <c r="K1809">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="L1809">
-        <v>6.19</v>
+        <v>6.01</v>
       </c>
       <c r="M1809">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="N1809">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="O1809">
         <v>1</v>
@@ -92707,46 +92710,46 @@
     </row>
     <row r="1810" spans="1:16">
       <c r="A1810" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1810" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C1810">
-        <v>1.057744452260666</v>
+        <v>1.093990748438535</v>
       </c>
       <c r="D1810" t="s">
         <v>512</v>
       </c>
       <c r="E1810">
-        <v>1.134329901302468</v>
+        <v>1.192545245251648</v>
       </c>
       <c r="F1810">
         <v>-1</v>
       </c>
       <c r="G1810">
-        <v>0.01112225554773933</v>
+        <v>0.01100600925156146</v>
       </c>
       <c r="H1810">
-        <v>0.01030567009869753</v>
+        <v>0.01040745475474835</v>
       </c>
       <c r="I1810">
-        <v>-0.07658544904180253</v>
+        <v>-0.09855449681311335</v>
       </c>
       <c r="J1810">
         <v>1.089232802540981</v>
       </c>
       <c r="K1810">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="L1810">
-        <v>6.09</v>
+        <v>6.05</v>
       </c>
       <c r="M1810">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="N1810">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="O1810">
         <v>1</v>
@@ -92757,102 +92760,302 @@
     </row>
     <row r="1811" spans="1:16">
       <c r="A1811" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1811" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C1811">
-        <v>1.437331032547627</v>
+        <v>1.070605828057388</v>
       </c>
       <c r="D1811" t="s">
-        <v>354</v>
+        <v>512</v>
       </c>
       <c r="E1811">
-        <v>1.527152008316966</v>
+        <v>1.192545245251648</v>
       </c>
       <c r="F1811">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1811">
-        <v>0.01054266896745237</v>
+        <v>0.01130939417194262</v>
       </c>
       <c r="H1811">
-        <v>0.01057284799168303</v>
+        <v>0.01040745475474835</v>
       </c>
       <c r="I1811">
-        <v>0.08982097576933867</v>
+        <v>-0.1219394171942607</v>
       </c>
       <c r="J1811">
-        <v>0.994032525644623</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1811">
-        <v>4.58</v>
+        <v>4.7</v>
       </c>
       <c r="L1811">
-        <v>5.99</v>
+        <v>6.19</v>
       </c>
       <c r="M1811">
-        <v>4.55</v>
+        <v>4.23</v>
       </c>
       <c r="N1811">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="O1811">
         <v>1</v>
       </c>
       <c r="P1811" t="s">
-        <v>346</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1812" spans="1:16">
       <c r="A1812" s="1">
+        <v>8</v>
+      </c>
+      <c r="B1812" t="s">
+        <v>355</v>
+      </c>
+      <c r="C1812">
+        <v>1.057744452260666</v>
+      </c>
+      <c r="D1812" t="s">
+        <v>512</v>
+      </c>
+      <c r="E1812">
+        <v>1.192545245251648</v>
+      </c>
+      <c r="F1812">
+        <v>-1</v>
+      </c>
+      <c r="G1812">
+        <v>0.01112225554773933</v>
+      </c>
+      <c r="H1812">
+        <v>0.01040745475474835</v>
+      </c>
+      <c r="I1812">
+        <v>-0.1348007929909825</v>
+      </c>
+      <c r="J1812">
+        <v>1.089232802540981</v>
+      </c>
+      <c r="K1812">
+        <v>4.62</v>
+      </c>
+      <c r="L1812">
+        <v>6.09</v>
+      </c>
+      <c r="M1812">
+        <v>4.23</v>
+      </c>
+      <c r="N1812">
+        <v>5.8</v>
+      </c>
+      <c r="O1812">
+        <v>1</v>
+      </c>
+      <c r="P1812" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:16">
+      <c r="A1813" s="1">
         <v>0</v>
       </c>
-      <c r="B1812" t="s">
+      <c r="B1813" t="s">
+        <v>356</v>
+      </c>
+      <c r="C1813">
+        <v>1.437331032547627</v>
+      </c>
+      <c r="D1813" t="s">
+        <v>352</v>
+      </c>
+      <c r="E1813">
+        <v>1.527152008316966</v>
+      </c>
+      <c r="F1813">
+        <v>1</v>
+      </c>
+      <c r="G1813">
+        <v>0.01054266896745237</v>
+      </c>
+      <c r="H1813">
+        <v>0.01057284799168303</v>
+      </c>
+      <c r="I1813">
+        <v>0.08982097576933867</v>
+      </c>
+      <c r="J1813">
+        <v>0.994032525644623</v>
+      </c>
+      <c r="K1813">
+        <v>4.58</v>
+      </c>
+      <c r="L1813">
+        <v>5.99</v>
+      </c>
+      <c r="M1813">
+        <v>4.55</v>
+      </c>
+      <c r="N1813">
+        <v>6.05</v>
+      </c>
+      <c r="O1813">
+        <v>1</v>
+      </c>
+      <c r="P1813" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:16">
+      <c r="A1814" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1814" t="s">
         <v>357</v>
       </c>
-      <c r="C1812">
+      <c r="C1814">
+        <v>1.106278882193859</v>
+      </c>
+      <c r="D1814" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1814">
+        <v>1.203415097025192</v>
+      </c>
+      <c r="F1814">
+        <v>1</v>
+      </c>
+      <c r="G1814">
+        <v>0.01121372111780614</v>
+      </c>
+      <c r="H1814">
+        <v>0.01043658490297481</v>
+      </c>
+      <c r="I1814">
+        <v>0.09713621483133306</v>
+      </c>
+      <c r="J1814">
+        <v>1.066185889832519</v>
+      </c>
+      <c r="K1814">
+        <v>4.74</v>
+      </c>
+      <c r="L1814">
+        <v>6.16</v>
+      </c>
+      <c r="M1814">
+        <v>4.33</v>
+      </c>
+      <c r="N1814">
+        <v>5.82</v>
+      </c>
+      <c r="O1814">
+        <v>1</v>
+      </c>
+      <c r="P1814" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:16">
+      <c r="A1815" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1815" t="s">
+        <v>357</v>
+      </c>
+      <c r="C1815">
+        <v>0.9527648456254667</v>
+      </c>
+      <c r="D1815" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1815">
+        <v>1.06317970075069</v>
+      </c>
+      <c r="F1815">
+        <v>1</v>
+      </c>
+      <c r="G1815">
+        <v>0.01136723515437453</v>
+      </c>
+      <c r="H1815">
+        <v>0.01057682029924931</v>
+      </c>
+      <c r="I1815">
+        <v>0.1104148551252235</v>
+      </c>
+      <c r="J1815">
+        <v>1.098572817378594</v>
+      </c>
+      <c r="K1815">
+        <v>4.74</v>
+      </c>
+      <c r="L1815">
+        <v>6.16</v>
+      </c>
+      <c r="M1815">
+        <v>4.33</v>
+      </c>
+      <c r="N1815">
+        <v>5.82</v>
+      </c>
+      <c r="O1815">
+        <v>1</v>
+      </c>
+      <c r="P1815" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:16">
+      <c r="A1816" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1816" t="s">
+        <v>357</v>
+      </c>
+      <c r="C1816">
         <v>0.8652138986958411</v>
       </c>
-      <c r="D1812" t="s">
+      <c r="D1816" t="s">
         <v>515</v>
       </c>
-      <c r="E1812">
+      <c r="E1816">
         <v>0.9832017260238386</v>
       </c>
-      <c r="F1812">
-        <v>1</v>
-      </c>
-      <c r="G1812">
+      <c r="F1816">
+        <v>1</v>
+      </c>
+      <c r="G1816">
         <v>0.01145478610130416</v>
       </c>
-      <c r="H1812">
+      <c r="H1816">
         <v>0.01065679827397616</v>
       </c>
-      <c r="I1812">
+      <c r="I1816">
         <v>0.1179878273279975</v>
       </c>
-      <c r="J1812">
+      <c r="J1816">
         <v>1.117043481287797</v>
       </c>
-      <c r="K1812">
+      <c r="K1816">
         <v>4.74</v>
       </c>
-      <c r="L1812">
+      <c r="L1816">
         <v>6.16</v>
       </c>
-      <c r="M1812">
+      <c r="M1816">
         <v>4.33</v>
       </c>
-      <c r="N1812">
+      <c r="N1816">
         <v>5.82</v>
       </c>
-      <c r="O1812">
-        <v>1</v>
-      </c>
-      <c r="P1812" t="s">
-        <v>351</v>
+      <c r="O1816">
+        <v>1</v>
+      </c>
+      <c r="P1816" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5472" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5469" uniqueCount="629">
   <si>
     <t>trade_time</t>
   </si>
@@ -1558,7 +1558,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-09-27</t>
+    <t>2021-09-28</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -2258,7 +2258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1820"/>
+  <dimension ref="A1:P1819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91372,7 +91372,7 @@
         <v>514</v>
       </c>
       <c r="E1783">
-        <v>1.6606046430289</v>
+        <v>1.665171599702707</v>
       </c>
       <c r="F1783">
         <v>-1</v>
@@ -91381,10 +91381,10 @@
         <v>0.01039645564639531</v>
       </c>
       <c r="H1783">
-        <v>0.009779395356971102</v>
+        <v>0.01001482840029729</v>
       </c>
       <c r="I1783">
-        <v>-0.03706028942421202</v>
+        <v>-0.04162724609801938</v>
       </c>
       <c r="J1783">
         <v>0.9619420277182702</v>
@@ -91396,10 +91396,10 @@
         <v>6.01</v>
       </c>
       <c r="M1783">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1783">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1783">
         <v>1</v>
@@ -91422,7 +91422,7 @@
         <v>514</v>
       </c>
       <c r="E1784">
-        <v>1.6606046430289</v>
+        <v>1.665171599702707</v>
       </c>
       <c r="F1784">
         <v>-1</v>
@@ -91431,10 +91431,10 @@
         <v>0.01042683622611813</v>
       </c>
       <c r="H1784">
-        <v>0.009779395356971102</v>
+        <v>0.01001482840029729</v>
       </c>
       <c r="I1784">
-        <v>0.01255913085297067</v>
+        <v>0.007992174179163314</v>
       </c>
       <c r="J1784">
         <v>0.9619420277182702</v>
@@ -91446,10 +91446,10 @@
         <v>6.05</v>
       </c>
       <c r="M1784">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1784">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1784">
         <v>1</v>
@@ -91472,7 +91472,7 @@
         <v>514</v>
       </c>
       <c r="E1785">
-        <v>1.6606046430289</v>
+        <v>1.665171599702707</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91481,10 +91481,10 @@
         <v>0.01071112753027587</v>
       </c>
       <c r="H1785">
-        <v>0.009779395356971102</v>
+        <v>0.01001482840029729</v>
       </c>
       <c r="I1785">
-        <v>0.008267826695230518</v>
+        <v>0.003700870021423164</v>
       </c>
       <c r="J1785">
         <v>0.9619420277182702</v>
@@ -91496,10 +91496,10 @@
         <v>6.19</v>
       </c>
       <c r="M1785">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1785">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91822,7 +91822,7 @@
         <v>514</v>
       </c>
       <c r="E1792">
-        <v>1.418052219783598</v>
+        <v>1.415721951151851</v>
       </c>
       <c r="F1792">
         <v>-1</v>
@@ -91831,10 +91831,10 @@
         <v>0.01065855020800635</v>
       </c>
       <c r="H1792">
-        <v>0.0100219477802164</v>
+        <v>0.01026427804884815</v>
       </c>
       <c r="I1792">
-        <v>-0.05660242778994728</v>
+        <v>-0.05427215915820049</v>
       </c>
       <c r="J1792">
         <v>1.01941890526455</v>
@@ -91846,10 +91846,10 @@
         <v>6.01</v>
       </c>
       <c r="M1792">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1792">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91872,7 +91872,7 @@
         <v>514</v>
       </c>
       <c r="E1793">
-        <v>1.418052219783598</v>
+        <v>1.415721951151851</v>
       </c>
       <c r="F1793">
         <v>-1</v>
@@ -91881,10 +91881,10 @@
         <v>0.0106883560189537</v>
       </c>
       <c r="H1793">
-        <v>0.0100219477802164</v>
+        <v>0.01026427804884815</v>
       </c>
       <c r="I1793">
-        <v>-0.006408238737302341</v>
+        <v>-0.004077970105555551</v>
       </c>
       <c r="J1793">
         <v>1.01941890526455</v>
@@ -91896,10 +91896,10 @@
         <v>6.05</v>
       </c>
       <c r="M1793">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1793">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -91922,7 +91922,7 @@
         <v>514</v>
       </c>
       <c r="E1794">
-        <v>1.418052219783598</v>
+        <v>1.415721951151851</v>
       </c>
       <c r="F1794">
         <v>-1</v>
@@ -91931,10 +91931,10 @@
         <v>0.01098126885474339</v>
       </c>
       <c r="H1794">
-        <v>0.0100219477802164</v>
+        <v>0.01026427804884815</v>
       </c>
       <c r="I1794">
-        <v>-0.01932107452698428</v>
+        <v>-0.01699080589523749</v>
       </c>
       <c r="J1794">
         <v>1.01941890526455</v>
@@ -91946,10 +91946,10 @@
         <v>6.19</v>
       </c>
       <c r="M1794">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1794">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1794">
         <v>1</v>
@@ -91972,7 +91972,7 @@
         <v>514</v>
       </c>
       <c r="E1795">
-        <v>1.418052219783598</v>
+        <v>1.415721951151851</v>
       </c>
       <c r="F1795">
         <v>-1</v>
@@ -91981,10 +91981,10 @@
         <v>0.01079971534232222</v>
       </c>
       <c r="H1795">
-        <v>0.0100219477802164</v>
+        <v>0.01026427804884815</v>
       </c>
       <c r="I1795">
-        <v>-0.03776756210582111</v>
+        <v>-0.03543729347407432</v>
       </c>
       <c r="J1795">
         <v>1.01941890526455</v>
@@ -91996,10 +91996,10 @@
         <v>6.09</v>
       </c>
       <c r="M1795">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1795">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -92263,43 +92263,43 @@
         <v>5</v>
       </c>
       <c r="B1801" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C1801">
-        <v>1.105092910735574</v>
+        <v>1.155849285931329</v>
       </c>
       <c r="D1801" t="s">
         <v>514</v>
       </c>
       <c r="E1801">
-        <v>1.180809667391254</v>
+        <v>1.17173316504219</v>
       </c>
       <c r="F1801">
         <v>-1</v>
       </c>
       <c r="G1801">
-        <v>0.01091490708926443</v>
+        <v>0.01094415071406867</v>
       </c>
       <c r="H1801">
-        <v>0.01025919033260875</v>
+        <v>0.01050826683495781</v>
       </c>
       <c r="I1801">
-        <v>-0.07571675665568023</v>
+        <v>-0.01588387911086109</v>
       </c>
       <c r="J1801">
         <v>1.075637519575532</v>
       </c>
       <c r="K1801">
-        <v>4.56</v>
+        <v>4.55</v>
       </c>
       <c r="L1801">
-        <v>6.01</v>
+        <v>6.05</v>
       </c>
       <c r="M1801">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1801">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1801">
         <v>1</v>
@@ -92313,43 +92313,43 @@
         <v>6</v>
       </c>
       <c r="B1802" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C1802">
-        <v>1.155849285931329</v>
+        <v>1.134503657994999</v>
       </c>
       <c r="D1802" t="s">
         <v>514</v>
       </c>
       <c r="E1802">
-        <v>1.180809667391254</v>
+        <v>1.17173316504219</v>
       </c>
       <c r="F1802">
         <v>-1</v>
       </c>
       <c r="G1802">
-        <v>0.01094415071406867</v>
+        <v>0.011245496342005</v>
       </c>
       <c r="H1802">
-        <v>0.01025919033260875</v>
+        <v>0.01050826683495781</v>
       </c>
       <c r="I1802">
-        <v>-0.02496038145992507</v>
+        <v>-0.03722950704719086</v>
       </c>
       <c r="J1802">
         <v>1.075637519575532</v>
       </c>
       <c r="K1802">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="L1802">
-        <v>6.05</v>
+        <v>6.19</v>
       </c>
       <c r="M1802">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1802">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1802">
         <v>1</v>
@@ -92363,43 +92363,43 @@
         <v>7</v>
       </c>
       <c r="B1803" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C1803">
-        <v>1.134503657994999</v>
+        <v>1.120554659561042</v>
       </c>
       <c r="D1803" t="s">
         <v>514</v>
       </c>
       <c r="E1803">
-        <v>1.180809667391254</v>
+        <v>1.17173316504219</v>
       </c>
       <c r="F1803">
         <v>-1</v>
       </c>
       <c r="G1803">
-        <v>0.011245496342005</v>
+        <v>0.01105944534043896</v>
       </c>
       <c r="H1803">
-        <v>0.01025919033260875</v>
+        <v>0.01050826683495781</v>
       </c>
       <c r="I1803">
-        <v>-0.04630600939625484</v>
+        <v>-0.05117850548114866</v>
       </c>
       <c r="J1803">
         <v>1.075637519575532</v>
       </c>
       <c r="K1803">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="L1803">
-        <v>6.19</v>
+        <v>6.09</v>
       </c>
       <c r="M1803">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1803">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1803">
         <v>1</v>
@@ -92410,63 +92410,63 @@
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1804" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C1804">
-        <v>1.120554659561042</v>
+        <v>0.5779584745582085</v>
       </c>
       <c r="D1804" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E1804">
-        <v>1.180809667391254</v>
+        <v>0.8568521242352567</v>
       </c>
       <c r="F1804">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1804">
-        <v>0.01105944534043896</v>
+        <v>0.01210204152544179</v>
       </c>
       <c r="H1804">
-        <v>0.01025919033260875</v>
+        <v>0.01094314787576474</v>
       </c>
       <c r="I1804">
-        <v>-0.06025500783021265</v>
+        <v>0.2788936496770482</v>
       </c>
       <c r="J1804">
-        <v>1.075637519575532</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1804">
-        <v>4.62</v>
+        <v>5.29</v>
       </c>
       <c r="L1804">
-        <v>6.09</v>
+        <v>6.34</v>
       </c>
       <c r="M1804">
-        <v>4.22</v>
+        <v>4.63</v>
       </c>
       <c r="N1804">
-        <v>5.72</v>
+        <v>5.9</v>
       </c>
       <c r="O1804">
         <v>1</v>
       </c>
       <c r="P1804" t="s">
-        <v>628</v>
+        <v>354</v>
       </c>
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1805" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C1805">
-        <v>0.5779584745582085</v>
+        <v>0.6375896911172241</v>
       </c>
       <c r="D1805" t="s">
         <v>512</v>
@@ -92478,22 +92478,22 @@
         <v>1</v>
       </c>
       <c r="G1805">
-        <v>0.01210204152544179</v>
+        <v>0.01168241030888278</v>
       </c>
       <c r="H1805">
         <v>0.01094314787576474</v>
       </c>
       <c r="I1805">
-        <v>0.2788936496770482</v>
+        <v>0.2192624331180326</v>
       </c>
       <c r="J1805">
         <v>1.089232802540981</v>
       </c>
       <c r="K1805">
-        <v>5.29</v>
+        <v>5.07</v>
       </c>
       <c r="L1805">
-        <v>6.34</v>
+        <v>6.16</v>
       </c>
       <c r="M1805">
         <v>4.63</v>
@@ -92510,46 +92510,46 @@
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1806" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C1806">
-        <v>0.6375896911172241</v>
+        <v>1.088452388565583</v>
       </c>
       <c r="D1806" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E1806">
-        <v>0.8568521242352567</v>
+        <v>0.8241455095819763</v>
       </c>
       <c r="F1806">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1806">
-        <v>0.01168241030888278</v>
+        <v>0.01089154761143442</v>
       </c>
       <c r="H1806">
-        <v>0.01094314787576474</v>
+        <v>0.009755854490418023</v>
       </c>
       <c r="I1806">
-        <v>0.2192624331180326</v>
+        <v>0.2643068789836072</v>
       </c>
       <c r="J1806">
         <v>1.089232802540981</v>
       </c>
       <c r="K1806">
-        <v>5.07</v>
+        <v>4.5</v>
       </c>
       <c r="L1806">
-        <v>6.16</v>
+        <v>5.99</v>
       </c>
       <c r="M1806">
-        <v>4.63</v>
+        <v>4.1</v>
       </c>
       <c r="N1806">
-        <v>5.9</v>
+        <v>5.29</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92560,13 +92560,13 @@
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1807" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C1807">
-        <v>1.088452388565583</v>
+        <v>1.0780836051246</v>
       </c>
       <c r="D1807" t="s">
         <v>515</v>
@@ -92578,22 +92578,22 @@
         <v>-1</v>
       </c>
       <c r="G1807">
-        <v>0.01089154761143442</v>
+        <v>0.0104019163948754</v>
       </c>
       <c r="H1807">
         <v>0.009755854490418023</v>
       </c>
       <c r="I1807">
-        <v>0.2643068789836072</v>
+        <v>0.2539380955426234</v>
       </c>
       <c r="J1807">
         <v>1.089232802540981</v>
       </c>
       <c r="K1807">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="L1807">
-        <v>5.99</v>
+        <v>5.74</v>
       </c>
       <c r="M1807">
         <v>4.1</v>
@@ -92610,46 +92610,46 @@
     </row>
     <row r="1808" spans="1:16">
       <c r="A1808" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1808" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C1808">
-        <v>1.0780836051246</v>
+        <v>1.093990748438535</v>
       </c>
       <c r="D1808" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E1808">
-        <v>0.8241455095819763</v>
+        <v>1.112729636972141</v>
       </c>
       <c r="F1808">
         <v>-1</v>
       </c>
       <c r="G1808">
-        <v>0.0104019163948754</v>
+        <v>0.01100600925156146</v>
       </c>
       <c r="H1808">
-        <v>0.009755854490418023</v>
+        <v>0.01056727036302786</v>
       </c>
       <c r="I1808">
-        <v>0.2539380955426234</v>
+        <v>-0.01873888853360572</v>
       </c>
       <c r="J1808">
         <v>1.089232802540981</v>
       </c>
       <c r="K1808">
-        <v>4.28</v>
+        <v>4.55</v>
       </c>
       <c r="L1808">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="M1808">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="N1808">
-        <v>5.29</v>
+        <v>5.84</v>
       </c>
       <c r="O1808">
         <v>1</v>
@@ -92660,46 +92660,46 @@
     </row>
     <row r="1809" spans="1:16">
       <c r="A1809" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1809" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C1809">
-        <v>1.093990748438535</v>
+        <v>1.070605828057388</v>
       </c>
       <c r="D1809" t="s">
         <v>514</v>
       </c>
       <c r="E1809">
-        <v>1.123437573277059</v>
+        <v>1.112729636972141</v>
       </c>
       <c r="F1809">
         <v>-1</v>
       </c>
       <c r="G1809">
-        <v>0.01100600925156146</v>
+        <v>0.01130939417194262</v>
       </c>
       <c r="H1809">
-        <v>0.01031656242672294</v>
+        <v>0.01056727036302786</v>
       </c>
       <c r="I1809">
-        <v>-0.02944682483852379</v>
+        <v>-0.04212380891475309</v>
       </c>
       <c r="J1809">
         <v>1.089232802540981</v>
       </c>
       <c r="K1809">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="L1809">
-        <v>6.05</v>
+        <v>6.19</v>
       </c>
       <c r="M1809">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1809">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1809">
         <v>1</v>
@@ -92710,46 +92710,46 @@
     </row>
     <row r="1810" spans="1:16">
       <c r="A1810" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1810" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C1810">
-        <v>1.070605828057388</v>
+        <v>1.057744452260666</v>
       </c>
       <c r="D1810" t="s">
         <v>514</v>
       </c>
       <c r="E1810">
-        <v>1.123437573277059</v>
+        <v>1.112729636972141</v>
       </c>
       <c r="F1810">
         <v>-1</v>
       </c>
       <c r="G1810">
-        <v>0.01130939417194262</v>
+        <v>0.01112225554773933</v>
       </c>
       <c r="H1810">
-        <v>0.01031656242672294</v>
+        <v>0.01056727036302786</v>
       </c>
       <c r="I1810">
-        <v>-0.05283174521967116</v>
+        <v>-0.05498518471147484</v>
       </c>
       <c r="J1810">
         <v>1.089232802540981</v>
       </c>
       <c r="K1810">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="L1810">
-        <v>6.19</v>
+        <v>6.09</v>
       </c>
       <c r="M1810">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="N1810">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1810">
         <v>1</v>
@@ -92760,96 +92760,96 @@
     </row>
     <row r="1811" spans="1:16">
       <c r="A1811" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1811" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C1811">
-        <v>1.057744452260666</v>
+        <v>1.437331032547627</v>
       </c>
       <c r="D1811" t="s">
-        <v>514</v>
+        <v>349</v>
       </c>
       <c r="E1811">
-        <v>1.123437573277059</v>
+        <v>1.527152008316966</v>
       </c>
       <c r="F1811">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1811">
-        <v>0.01112225554773933</v>
+        <v>0.01054266896745237</v>
       </c>
       <c r="H1811">
-        <v>0.01031656242672294</v>
+        <v>0.01057284799168303</v>
       </c>
       <c r="I1811">
-        <v>-0.06569312101639291</v>
+        <v>0.08982097576933867</v>
       </c>
       <c r="J1811">
-        <v>1.089232802540981</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1811">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="L1811">
-        <v>6.09</v>
+        <v>5.99</v>
       </c>
       <c r="M1811">
-        <v>4.22</v>
+        <v>4.55</v>
       </c>
       <c r="N1811">
-        <v>5.72</v>
+        <v>6.05</v>
       </c>
       <c r="O1811">
         <v>1</v>
       </c>
       <c r="P1811" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1812" spans="1:16">
       <c r="A1812" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1812" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1812">
-        <v>1.437331032547627</v>
+        <v>1.595242416523244</v>
       </c>
       <c r="D1812" t="s">
-        <v>349</v>
+        <v>514</v>
       </c>
       <c r="E1812">
-        <v>1.527152008316966</v>
+        <v>1.525898838702337</v>
       </c>
       <c r="F1812">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1812">
-        <v>0.01054266896745237</v>
+        <v>0.01000475758347676</v>
       </c>
       <c r="H1812">
-        <v>0.01057284799168303</v>
+        <v>0.01015410116129766</v>
       </c>
       <c r="I1812">
-        <v>0.08982097576933867</v>
+        <v>0.0693435778209075</v>
       </c>
       <c r="J1812">
         <v>0.994032525644623</v>
       </c>
       <c r="K1812">
-        <v>4.58</v>
+        <v>4.23</v>
       </c>
       <c r="L1812">
-        <v>5.99</v>
+        <v>5.8</v>
       </c>
       <c r="M1812">
-        <v>4.55</v>
+        <v>4.34</v>
       </c>
       <c r="N1812">
-        <v>6.05</v>
+        <v>5.84</v>
       </c>
       <c r="O1812">
         <v>1</v>
@@ -92860,63 +92860,63 @@
     </row>
     <row r="1813" spans="1:16">
       <c r="A1813" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1813" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C1813">
-        <v>1.595242416523244</v>
+        <v>1.091573753380461</v>
       </c>
       <c r="D1813" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E1813">
-        <v>1.525182741779691</v>
+        <v>1.203415097025192</v>
       </c>
       <c r="F1813">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1813">
-        <v>0.01000475758347676</v>
+        <v>0.01102842624661954</v>
       </c>
       <c r="H1813">
-        <v>0.009914817258220309</v>
+        <v>0.01043658490297481</v>
       </c>
       <c r="I1813">
-        <v>0.07005967474355312</v>
+        <v>0.1118413436447314</v>
       </c>
       <c r="J1813">
-        <v>0.994032525644623</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1813">
-        <v>4.23</v>
+        <v>4.66</v>
       </c>
       <c r="L1813">
-        <v>5.8</v>
+        <v>6.06</v>
       </c>
       <c r="M1813">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="N1813">
-        <v>5.72</v>
+        <v>5.82</v>
       </c>
       <c r="O1813">
         <v>1</v>
       </c>
       <c r="P1813" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1814" spans="1:16">
       <c r="A1814" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1814" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C1814">
-        <v>1.091573753380461</v>
+        <v>1.106278882193859</v>
       </c>
       <c r="D1814" t="s">
         <v>516</v>
@@ -92928,22 +92928,22 @@
         <v>1</v>
       </c>
       <c r="G1814">
-        <v>0.01102842624661954</v>
+        <v>0.01121372111780614</v>
       </c>
       <c r="H1814">
         <v>0.01043658490297481</v>
       </c>
       <c r="I1814">
-        <v>0.1118413436447314</v>
+        <v>0.09713621483133306</v>
       </c>
       <c r="J1814">
         <v>1.066185889832519</v>
       </c>
       <c r="K1814">
-        <v>4.66</v>
+        <v>4.74</v>
       </c>
       <c r="L1814">
-        <v>6.06</v>
+        <v>6.16</v>
       </c>
       <c r="M1814">
         <v>4.33</v>
@@ -92960,46 +92960,46 @@
     </row>
     <row r="1815" spans="1:16">
       <c r="A1815" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1815" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C1815">
-        <v>1.106278882193859</v>
+        <v>1.290033686008443</v>
       </c>
       <c r="D1815" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E1815">
-        <v>1.203415097025192</v>
+        <v>1.212753238126867</v>
       </c>
       <c r="F1815">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1815">
-        <v>0.01121372111780614</v>
+        <v>0.01030996631399156</v>
       </c>
       <c r="H1815">
-        <v>0.01043658490297481</v>
+        <v>0.01046724676187313</v>
       </c>
       <c r="I1815">
-        <v>0.09713621483133306</v>
+        <v>0.07728044788157629</v>
       </c>
       <c r="J1815">
         <v>1.066185889832519</v>
       </c>
       <c r="K1815">
-        <v>4.74</v>
+        <v>4.23</v>
       </c>
       <c r="L1815">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="M1815">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="N1815">
-        <v>5.82</v>
+        <v>5.84</v>
       </c>
       <c r="O1815">
         <v>1</v>
@@ -93010,96 +93010,96 @@
     </row>
     <row r="1816" spans="1:16">
       <c r="A1816" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1816" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C1816">
-        <v>1.290033686008443</v>
+        <v>0.9527648456254667</v>
       </c>
       <c r="D1816" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E1816">
-        <v>1.22069554490677</v>
+        <v>1.06317970075069</v>
       </c>
       <c r="F1816">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1816">
-        <v>0.01030996631399156</v>
+        <v>0.01136723515437453</v>
       </c>
       <c r="H1816">
-        <v>0.01021930445509323</v>
+        <v>0.01057682029924931</v>
       </c>
       <c r="I1816">
-        <v>0.06933814110167358</v>
+        <v>0.1104148551252235</v>
       </c>
       <c r="J1816">
-        <v>1.066185889832519</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1816">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="L1816">
-        <v>5.8</v>
+        <v>6.16</v>
       </c>
       <c r="M1816">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="N1816">
-        <v>5.72</v>
+        <v>5.82</v>
       </c>
       <c r="O1816">
         <v>1</v>
       </c>
       <c r="P1816" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="1817" spans="1:16">
       <c r="A1817" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1817" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C1817">
-        <v>0.9527648456254667</v>
+        <v>1.153036982488548</v>
       </c>
       <c r="D1817" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E1817">
-        <v>1.06317970075069</v>
+        <v>1.072193972576904</v>
       </c>
       <c r="F1817">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1817">
-        <v>0.01136723515437453</v>
+        <v>0.01044696301751145</v>
       </c>
       <c r="H1817">
-        <v>0.01057682029924931</v>
+        <v>0.0106078060274231</v>
       </c>
       <c r="I1817">
-        <v>0.1104148551252235</v>
+        <v>0.08084300991164461</v>
       </c>
       <c r="J1817">
         <v>1.098572817378594</v>
       </c>
       <c r="K1817">
-        <v>4.74</v>
+        <v>4.23</v>
       </c>
       <c r="L1817">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="M1817">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="N1817">
-        <v>5.82</v>
+        <v>5.84</v>
       </c>
       <c r="O1817">
         <v>1</v>
@@ -93110,43 +93110,43 @@
     </row>
     <row r="1818" spans="1:16">
       <c r="A1818" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1818" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C1818">
-        <v>1.153036982488548</v>
+        <v>0.8652138986958411</v>
       </c>
       <c r="D1818" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E1818">
-        <v>1.084022710662335</v>
+        <v>1.017246943778374</v>
       </c>
       <c r="F1818">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1818">
-        <v>0.01044696301751145</v>
+        <v>0.01145478610130416</v>
       </c>
       <c r="H1818">
-        <v>0.01035597728933766</v>
+        <v>0.01042275305622163</v>
       </c>
       <c r="I1818">
-        <v>0.06901427182621322</v>
+        <v>0.1520330450825327</v>
       </c>
       <c r="J1818">
-        <v>1.098572817378594</v>
+        <v>1.117043481287797</v>
       </c>
       <c r="K1818">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="L1818">
-        <v>5.8</v>
+        <v>6.16</v>
       </c>
       <c r="M1818">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="N1818">
         <v>5.72</v>
@@ -93155,106 +93155,56 @@
         <v>1</v>
       </c>
       <c r="P1818" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1819" spans="1:16">
       <c r="A1819" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1819" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C1819">
-        <v>0.8652138986958411</v>
+        <v>1.074906074152617</v>
       </c>
       <c r="D1819" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E1819">
-        <v>1.017246943778374</v>
+        <v>0.9920312912109601</v>
       </c>
       <c r="F1819">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1819">
-        <v>0.01145478610130416</v>
+        <v>0.01052509392584738</v>
       </c>
       <c r="H1819">
-        <v>0.01042275305622163</v>
+        <v>0.01068796870878904</v>
       </c>
       <c r="I1819">
-        <v>0.1520330450825327</v>
+        <v>0.08287478294165673</v>
       </c>
       <c r="J1819">
         <v>1.117043481287797</v>
       </c>
       <c r="K1819">
-        <v>4.74</v>
+        <v>4.23</v>
       </c>
       <c r="L1819">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="M1819">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="N1819">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="O1819">
         <v>1</v>
       </c>
       <c r="P1819" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="1820" spans="1:16">
-      <c r="A1820" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1820" t="s">
-        <v>357</v>
-      </c>
-      <c r="C1820">
-        <v>1.074906074152617</v>
-      </c>
-      <c r="D1820" t="s">
-        <v>514</v>
-      </c>
-      <c r="E1820">
-        <v>1.006076508965496</v>
-      </c>
-      <c r="F1820">
-        <v>-1</v>
-      </c>
-      <c r="G1820">
-        <v>0.01052509392584738</v>
-      </c>
-      <c r="H1820">
-        <v>0.0104339234910345</v>
-      </c>
-      <c r="I1820">
-        <v>0.06882956518712113</v>
-      </c>
-      <c r="J1820">
-        <v>1.117043481287797</v>
-      </c>
-      <c r="K1820">
-        <v>4.23</v>
-      </c>
-      <c r="L1820">
-        <v>5.8</v>
-      </c>
-      <c r="M1820">
-        <v>4.22</v>
-      </c>
-      <c r="N1820">
-        <v>5.72</v>
-      </c>
-      <c r="O1820">
-        <v>1</v>
-      </c>
-      <c r="P1820" t="s">
         <v>350</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5466" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5472" uniqueCount="630">
   <si>
     <t>trade_time</t>
   </si>
@@ -1048,6 +1048,9 @@
     <t>2021-03-03</t>
   </si>
   <si>
+    <t>2021-05-28</t>
+  </si>
+  <si>
     <t>2021-06-01</t>
   </si>
   <si>
@@ -1055,6 +1058,9 @@
   </si>
   <si>
     <t>2021-06-25</t>
+  </si>
+  <si>
+    <t>2021-07-20</t>
   </si>
   <si>
     <t>2021-07-26</t>
@@ -1069,34 +1075,28 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-05-28</t>
-  </si>
-  <si>
-    <t>2021-07-20</t>
-  </si>
-  <si>
     <t>2021-09-13</t>
   </si>
   <si>
     <t>2021-05-27</t>
   </si>
   <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
     <t>2021-07-21</t>
   </si>
   <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
     <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
   </si>
   <si>
     <t>2021-09-17</t>
   </si>
   <si>
     <t>2021-09-10</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
   </si>
   <si>
     <t>2016-05-11</t>
@@ -1555,13 +1555,13 @@
     <t>2021-08-11</t>
   </si>
   <si>
-    <t>2021-07-13</t>
+    <t>2021-07-16</t>
   </si>
   <si>
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-09-30</t>
+    <t>2021-10-11</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -2261,7 +2261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1818"/>
+  <dimension ref="A1:P1820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91119,40 +91119,40 @@
         <v>344</v>
       </c>
       <c r="C1778">
-        <v>1.233610151707254</v>
+        <v>1.290080006995148</v>
       </c>
       <c r="D1778" t="s">
         <v>513</v>
       </c>
       <c r="E1778">
-        <v>1.44620841166441</v>
+        <v>1.515827831941592</v>
       </c>
       <c r="F1778">
         <v>1</v>
       </c>
       <c r="G1778">
-        <v>0.01152638984829274</v>
+        <v>0.01190991999300485</v>
       </c>
       <c r="H1778">
-        <v>0.01035379158833559</v>
+        <v>0.01040417216805841</v>
       </c>
       <c r="I1778">
-        <v>0.2125982599571552</v>
+        <v>0.2257478249464437</v>
       </c>
       <c r="J1778">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1778">
-        <v>5.35</v>
+        <v>5.52</v>
       </c>
       <c r="L1778">
-        <v>6.38</v>
+        <v>6.6</v>
       </c>
       <c r="M1778">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="N1778">
-        <v>5.9</v>
+        <v>5.96</v>
       </c>
       <c r="O1778">
         <v>1</v>
@@ -91169,40 +91169,40 @@
         <v>345</v>
       </c>
       <c r="C1779">
-        <v>1.25132667337035</v>
+        <v>1.233610151707254</v>
       </c>
       <c r="D1779" t="s">
         <v>513</v>
       </c>
       <c r="E1779">
-        <v>1.44620841166441</v>
+        <v>1.515827831941592</v>
       </c>
       <c r="F1779">
         <v>1</v>
       </c>
       <c r="G1779">
-        <v>0.01142867332662965</v>
+        <v>0.01152638984829274</v>
       </c>
       <c r="H1779">
-        <v>0.01035379158833559</v>
+        <v>0.01040417216805841</v>
       </c>
       <c r="I1779">
-        <v>0.1948817382940593</v>
+        <v>0.2822176802343375</v>
       </c>
       <c r="J1779">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1779">
-        <v>5.29</v>
+        <v>5.35</v>
       </c>
       <c r="L1779">
-        <v>6.34</v>
+        <v>6.38</v>
       </c>
       <c r="M1779">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="N1779">
-        <v>5.9</v>
+        <v>5.96</v>
       </c>
       <c r="O1779">
         <v>1</v>
@@ -91219,40 +91219,40 @@
         <v>346</v>
       </c>
       <c r="C1780">
-        <v>1.28295391946837</v>
+        <v>1.25132667337035</v>
       </c>
       <c r="D1780" t="s">
         <v>513</v>
       </c>
       <c r="E1780">
-        <v>1.44620841166441</v>
+        <v>1.515827831941592</v>
       </c>
       <c r="F1780">
         <v>1</v>
       </c>
       <c r="G1780">
-        <v>0.01103704608053163</v>
+        <v>0.01142867332662965</v>
       </c>
       <c r="H1780">
-        <v>0.01035379158833559</v>
+        <v>0.01040417216805841</v>
       </c>
       <c r="I1780">
-        <v>0.1632544921960397</v>
+        <v>0.2645011585712416</v>
       </c>
       <c r="J1780">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1780">
-        <v>5.07</v>
+        <v>5.29</v>
       </c>
       <c r="L1780">
-        <v>6.16</v>
+        <v>6.34</v>
       </c>
       <c r="M1780">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="N1780">
-        <v>5.9</v>
+        <v>5.96</v>
       </c>
       <c r="O1780">
         <v>1</v>
@@ -91266,43 +91266,43 @@
         <v>3</v>
       </c>
       <c r="B1781" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C1781">
-        <v>1.598111310278496</v>
+        <v>1.28295391946837</v>
       </c>
       <c r="D1781" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E1781">
-        <v>1.415657106632275</v>
+        <v>1.515827831941592</v>
       </c>
       <c r="F1781">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1781">
-        <v>0.0106018886897215</v>
+        <v>0.01103704608053163</v>
       </c>
       <c r="H1781">
-        <v>0.009284342893367726</v>
+        <v>0.01040417216805841</v>
       </c>
       <c r="I1781">
-        <v>0.1824542036462211</v>
+        <v>0.232873912473222</v>
       </c>
       <c r="J1781">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1781">
-        <v>4.68</v>
+        <v>5.07</v>
       </c>
       <c r="L1781">
-        <v>6.1</v>
+        <v>6.16</v>
       </c>
       <c r="M1781">
-        <v>4.09</v>
+        <v>4.62</v>
       </c>
       <c r="N1781">
-        <v>5.35</v>
+        <v>5.96</v>
       </c>
       <c r="O1781">
         <v>1</v>
@@ -91316,10 +91316,10 @@
         <v>4</v>
       </c>
       <c r="B1782" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C1782">
-        <v>1.622888121365803</v>
+        <v>1.626208411664409</v>
       </c>
       <c r="D1782" t="s">
         <v>514</v>
@@ -91331,22 +91331,22 @@
         <v>-1</v>
       </c>
       <c r="G1782">
-        <v>0.009857111878634197</v>
+        <v>0.01053379158833559</v>
       </c>
       <c r="H1782">
         <v>0.009284342893367726</v>
       </c>
       <c r="I1782">
-        <v>0.2072310147335288</v>
+        <v>0.2105513050321348</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1782">
-        <v>4.28</v>
+        <v>4.63</v>
       </c>
       <c r="L1782">
-        <v>5.74</v>
+        <v>6.08</v>
       </c>
       <c r="M1782">
         <v>4.09</v>
@@ -91366,43 +91366,43 @@
         <v>5</v>
       </c>
       <c r="B1783" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C1783">
-        <v>1.623544353604688</v>
+        <v>1.622888121365803</v>
       </c>
       <c r="D1783" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E1783">
-        <v>1.547455078039611</v>
+        <v>1.415657106632275</v>
       </c>
       <c r="F1783">
         <v>-1</v>
       </c>
       <c r="G1783">
-        <v>0.01039645564639531</v>
+        <v>0.009857111878634197</v>
       </c>
       <c r="H1783">
-        <v>0.01001254492196039</v>
+        <v>0.009284342893367726</v>
       </c>
       <c r="I1783">
-        <v>0.07608927556507616</v>
+        <v>0.2072310147335288</v>
       </c>
       <c r="J1783">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1783">
-        <v>4.56</v>
+        <v>4.28</v>
       </c>
       <c r="L1783">
-        <v>6.01</v>
+        <v>5.74</v>
       </c>
       <c r="M1783">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="N1783">
-        <v>5.78</v>
+        <v>5.35</v>
       </c>
       <c r="O1783">
         <v>1</v>
@@ -91416,43 +91416,43 @@
         <v>6</v>
       </c>
       <c r="B1784" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C1784">
-        <v>1.67316377388187</v>
+        <v>1.623544353604688</v>
       </c>
       <c r="D1784" t="s">
         <v>515</v>
       </c>
       <c r="E1784">
-        <v>1.547455078039611</v>
+        <v>1.728491890001313</v>
       </c>
       <c r="F1784">
         <v>-1</v>
       </c>
       <c r="G1784">
-        <v>0.01042683622611813</v>
+        <v>0.01039645564639531</v>
       </c>
       <c r="H1784">
-        <v>0.01001254492196039</v>
+        <v>0.01075150810999869</v>
       </c>
       <c r="I1784">
-        <v>0.1257086958422589</v>
+        <v>-0.104947536396625</v>
       </c>
       <c r="J1784">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1784">
-        <v>4.55</v>
+        <v>4.56</v>
       </c>
       <c r="L1784">
-        <v>6.05</v>
+        <v>6.01</v>
       </c>
       <c r="M1784">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="N1784">
-        <v>5.78</v>
+        <v>6.24</v>
       </c>
       <c r="O1784">
         <v>1</v>
@@ -91466,43 +91466,43 @@
         <v>7</v>
       </c>
       <c r="B1785" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C1785">
-        <v>1.66887246972413</v>
+        <v>1.67316377388187</v>
       </c>
       <c r="D1785" t="s">
         <v>515</v>
       </c>
       <c r="E1785">
-        <v>1.547455078039611</v>
+        <v>1.728491890001313</v>
       </c>
       <c r="F1785">
         <v>-1</v>
       </c>
       <c r="G1785">
-        <v>0.01071112753027587</v>
+        <v>0.01042683622611813</v>
       </c>
       <c r="H1785">
-        <v>0.01001254492196039</v>
+        <v>0.01075150810999869</v>
       </c>
       <c r="I1785">
-        <v>0.1214173916845187</v>
+        <v>-0.05532811611944233</v>
       </c>
       <c r="J1785">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1785">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="L1785">
-        <v>6.19</v>
+        <v>6.05</v>
       </c>
       <c r="M1785">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="N1785">
-        <v>5.78</v>
+        <v>6.24</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91513,146 +91513,146 @@
     </row>
     <row r="1786" spans="1:16">
       <c r="A1786" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1786" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C1786">
-        <v>0.9728076429396824</v>
+        <v>1.66887246972413</v>
       </c>
       <c r="D1786" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1786">
-        <v>1.180090468625132</v>
+        <v>1.728491890001313</v>
       </c>
       <c r="F1786">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1786">
-        <v>0.01222719235706032</v>
+        <v>0.01071112753027587</v>
       </c>
       <c r="H1786">
-        <v>0.01061990953137487</v>
+        <v>0.01075150810999869</v>
       </c>
       <c r="I1786">
-        <v>0.20728282568545</v>
+        <v>-0.05961942027718248</v>
       </c>
       <c r="J1786">
-        <v>1.01941890526455</v>
+        <v>0.9619420277182702</v>
       </c>
       <c r="K1786">
-        <v>5.52</v>
+        <v>4.7</v>
       </c>
       <c r="L1786">
-        <v>6.6</v>
+        <v>6.19</v>
       </c>
       <c r="M1786">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="N1786">
-        <v>5.9</v>
+        <v>6.24</v>
       </c>
       <c r="O1786">
         <v>1</v>
       </c>
       <c r="P1786" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1787" spans="1:16">
       <c r="A1787" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B1787" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C1787">
-        <v>0.9261088568346558</v>
+        <v>1.645827831941592</v>
       </c>
       <c r="D1787" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1787">
-        <v>1.180090468625132</v>
+        <v>1.728491890001313</v>
       </c>
       <c r="F1787">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1787">
-        <v>0.01183389114316535</v>
+        <v>0.01053417216805841</v>
       </c>
       <c r="H1787">
-        <v>0.01061990953137487</v>
+        <v>0.01075150810999869</v>
       </c>
       <c r="I1787">
-        <v>0.2539816117904765</v>
+        <v>-0.08266405805972088</v>
       </c>
       <c r="J1787">
-        <v>1.01941890526455</v>
+        <v>0.9619420277182702</v>
       </c>
       <c r="K1787">
-        <v>5.35</v>
+        <v>4.62</v>
       </c>
       <c r="L1787">
-        <v>6.38</v>
+        <v>6.09</v>
       </c>
       <c r="M1787">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="N1787">
-        <v>5.9</v>
+        <v>6.24</v>
       </c>
       <c r="O1787">
         <v>1</v>
       </c>
       <c r="P1787" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1788" spans="1:16">
       <c r="A1788" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1788" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C1788">
-        <v>0.9472739911505288</v>
+        <v>0.9728076429396824</v>
       </c>
       <c r="D1788" t="s">
         <v>513</v>
       </c>
       <c r="E1788">
-        <v>1.180090468625132</v>
+        <v>1.250284657677777</v>
       </c>
       <c r="F1788">
         <v>1</v>
       </c>
       <c r="G1788">
-        <v>0.01173272600884947</v>
+        <v>0.01222719235706032</v>
       </c>
       <c r="H1788">
-        <v>0.01061990953137487</v>
+        <v>0.01066971534232222</v>
       </c>
       <c r="I1788">
-        <v>0.2328164774746035</v>
+        <v>0.2774770147380945</v>
       </c>
       <c r="J1788">
         <v>1.01941890526455</v>
       </c>
       <c r="K1788">
-        <v>5.29</v>
+        <v>5.52</v>
       </c>
       <c r="L1788">
-        <v>6.34</v>
+        <v>6.6</v>
       </c>
       <c r="M1788">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="N1788">
-        <v>5.9</v>
+        <v>5.96</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91663,46 +91663,46 @@
     </row>
     <row r="1789" spans="1:16">
       <c r="A1789" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1789" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1789">
-        <v>0.9915461503087295</v>
+        <v>0.9261088568346558</v>
       </c>
       <c r="D1789" t="s">
         <v>513</v>
       </c>
       <c r="E1789">
-        <v>1.180090468625132</v>
+        <v>1.250284657677777</v>
       </c>
       <c r="F1789">
         <v>1</v>
       </c>
       <c r="G1789">
-        <v>0.01132845384969127</v>
+        <v>0.01183389114316535</v>
       </c>
       <c r="H1789">
-        <v>0.01061990953137487</v>
+        <v>0.01066971534232222</v>
       </c>
       <c r="I1789">
-        <v>0.1885443183164028</v>
+        <v>0.324175800843121</v>
       </c>
       <c r="J1789">
         <v>1.01941890526455</v>
       </c>
       <c r="K1789">
-        <v>5.07</v>
+        <v>5.35</v>
       </c>
       <c r="L1789">
-        <v>6.16</v>
+        <v>6.38</v>
       </c>
       <c r="M1789">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="N1789">
-        <v>5.9</v>
+        <v>5.96</v>
       </c>
       <c r="O1789">
         <v>1</v>
@@ -91713,46 +91713,46 @@
     </row>
     <row r="1790" spans="1:16">
       <c r="A1790" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1790" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C1790">
-        <v>1.360090468625132</v>
+        <v>0.9472739911505288</v>
       </c>
       <c r="D1790" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E1790">
-        <v>1.110382488415344</v>
+        <v>1.250284657677777</v>
       </c>
       <c r="F1790">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1790">
-        <v>0.01079990953137487</v>
+        <v>0.01173272600884947</v>
       </c>
       <c r="H1790">
-        <v>0.009469617511584654</v>
+        <v>0.01066971534232222</v>
       </c>
       <c r="I1790">
-        <v>0.2497079802097879</v>
+        <v>0.3030106665272481</v>
       </c>
       <c r="J1790">
         <v>1.01941890526455</v>
       </c>
       <c r="K1790">
-        <v>4.63</v>
+        <v>5.29</v>
       </c>
       <c r="L1790">
-        <v>6.08</v>
+        <v>6.34</v>
       </c>
       <c r="M1790">
-        <v>4.1</v>
+        <v>4.62</v>
       </c>
       <c r="N1790">
-        <v>5.29</v>
+        <v>5.96</v>
       </c>
       <c r="O1790">
         <v>1</v>
@@ -91763,46 +91763,46 @@
     </row>
     <row r="1791" spans="1:16">
       <c r="A1791" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1791" t="s">
         <v>347</v>
       </c>
       <c r="C1791">
-        <v>1.376887085467724</v>
+        <v>0.9915461503087295</v>
       </c>
       <c r="D1791" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E1791">
-        <v>1.110382488415344</v>
+        <v>1.250284657677777</v>
       </c>
       <c r="F1791">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1791">
-        <v>0.01010311291453228</v>
+        <v>0.01132845384969127</v>
       </c>
       <c r="H1791">
-        <v>0.009469617511584654</v>
+        <v>0.01066971534232222</v>
       </c>
       <c r="I1791">
-        <v>0.2665045970523803</v>
+        <v>0.2587385073690474</v>
       </c>
       <c r="J1791">
         <v>1.01941890526455</v>
       </c>
       <c r="K1791">
-        <v>4.28</v>
+        <v>5.07</v>
       </c>
       <c r="L1791">
-        <v>5.74</v>
+        <v>6.16</v>
       </c>
       <c r="M1791">
-        <v>4.1</v>
+        <v>4.62</v>
       </c>
       <c r="N1791">
-        <v>5.29</v>
+        <v>5.96</v>
       </c>
       <c r="O1791">
         <v>1</v>
@@ -91813,46 +91813,46 @@
     </row>
     <row r="1792" spans="1:16">
       <c r="A1792" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1792" t="s">
         <v>348</v>
       </c>
       <c r="C1792">
-        <v>1.361449791993651</v>
+        <v>1.360090468625132</v>
       </c>
       <c r="D1792" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E1792">
-        <v>1.294556816835978</v>
+        <v>1.110382488415344</v>
       </c>
       <c r="F1792">
         <v>-1</v>
       </c>
       <c r="G1792">
-        <v>0.01065855020800635</v>
+        <v>0.01079990953137487</v>
       </c>
       <c r="H1792">
-        <v>0.01026544318316402</v>
+        <v>0.009469617511584654</v>
       </c>
       <c r="I1792">
-        <v>0.06689297515767212</v>
+        <v>0.2497079802097879</v>
       </c>
       <c r="J1792">
         <v>1.01941890526455</v>
       </c>
       <c r="K1792">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="L1792">
-        <v>6.01</v>
+        <v>6.08</v>
       </c>
       <c r="M1792">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N1792">
-        <v>5.78</v>
+        <v>5.29</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91863,46 +91863,46 @@
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1793" t="s">
         <v>349</v>
       </c>
       <c r="C1793">
-        <v>1.411643981046296</v>
+        <v>1.376887085467724</v>
       </c>
       <c r="D1793" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E1793">
-        <v>1.294556816835978</v>
+        <v>1.110382488415344</v>
       </c>
       <c r="F1793">
         <v>-1</v>
       </c>
       <c r="G1793">
-        <v>0.0106883560189537</v>
+        <v>0.01010311291453228</v>
       </c>
       <c r="H1793">
-        <v>0.01026544318316402</v>
+        <v>0.009469617511584654</v>
       </c>
       <c r="I1793">
-        <v>0.1170871642103171</v>
+        <v>0.2665045970523803</v>
       </c>
       <c r="J1793">
         <v>1.01941890526455</v>
       </c>
       <c r="K1793">
-        <v>4.55</v>
+        <v>4.28</v>
       </c>
       <c r="L1793">
-        <v>6.05</v>
+        <v>5.74</v>
       </c>
       <c r="M1793">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N1793">
-        <v>5.78</v>
+        <v>5.29</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -91913,46 +91913,46 @@
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1794" t="s">
         <v>350</v>
       </c>
       <c r="C1794">
-        <v>1.398731145256614</v>
+        <v>1.361449791993651</v>
       </c>
       <c r="D1794" t="s">
         <v>515</v>
       </c>
       <c r="E1794">
-        <v>1.294556816835978</v>
+        <v>1.458925334309258</v>
       </c>
       <c r="F1794">
         <v>-1</v>
       </c>
       <c r="G1794">
-        <v>0.01098126885474339</v>
+        <v>0.01065855020800635</v>
       </c>
       <c r="H1794">
-        <v>0.01026544318316402</v>
+        <v>0.01102107466569074</v>
       </c>
       <c r="I1794">
-        <v>0.1041743284206351</v>
+        <v>-0.09747554231560773</v>
       </c>
       <c r="J1794">
         <v>1.01941890526455</v>
       </c>
       <c r="K1794">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="L1794">
-        <v>6.19</v>
+        <v>6.01</v>
       </c>
       <c r="M1794">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="N1794">
-        <v>5.78</v>
+        <v>6.24</v>
       </c>
       <c r="O1794">
         <v>1</v>
@@ -91963,46 +91963,46 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1795" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C1795">
-        <v>1.380284657677777</v>
+        <v>1.411643981046296</v>
       </c>
       <c r="D1795" t="s">
         <v>515</v>
       </c>
       <c r="E1795">
-        <v>1.294556816835978</v>
+        <v>1.458925334309258</v>
       </c>
       <c r="F1795">
         <v>-1</v>
       </c>
       <c r="G1795">
-        <v>0.01079971534232222</v>
+        <v>0.0106883560189537</v>
       </c>
       <c r="H1795">
-        <v>0.01026544318316402</v>
+        <v>0.01102107466569074</v>
       </c>
       <c r="I1795">
-        <v>0.0857278408417983</v>
+        <v>-0.04728135326296279</v>
       </c>
       <c r="J1795">
         <v>1.01941890526455</v>
       </c>
       <c r="K1795">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="L1795">
-        <v>6.09</v>
+        <v>6.05</v>
       </c>
       <c r="M1795">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="N1795">
-        <v>5.78</v>
+        <v>6.24</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -92013,146 +92013,146 @@
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1796" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C1796">
-        <v>0.7149171399855092</v>
+        <v>1.398731145256614</v>
       </c>
       <c r="D1796" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1796">
-        <v>0.919798284365287</v>
+        <v>1.458925334309258</v>
       </c>
       <c r="F1796">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1796">
-        <v>0.01280508286001449</v>
+        <v>0.01098126885474339</v>
       </c>
       <c r="H1796">
-        <v>0.01088020171563471</v>
+        <v>0.01102107466569074</v>
       </c>
       <c r="I1796">
-        <v>0.2048811443797778</v>
+        <v>-0.06019418905264473</v>
       </c>
       <c r="J1796">
-        <v>1.075637519575532</v>
+        <v>1.01941890526455</v>
       </c>
       <c r="K1796">
-        <v>5.62</v>
+        <v>4.7</v>
       </c>
       <c r="L1796">
-        <v>6.76</v>
+        <v>6.19</v>
       </c>
       <c r="M1796">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="N1796">
-        <v>5.9</v>
+        <v>6.24</v>
       </c>
       <c r="O1796">
         <v>1</v>
       </c>
       <c r="P1796" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B1797" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C1797">
-        <v>0.6498775214454353</v>
+        <v>1.380284657677777</v>
       </c>
       <c r="D1797" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1797">
-        <v>0.919798284365287</v>
+        <v>1.458925334309258</v>
       </c>
       <c r="F1797">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.01203012247855456</v>
+        <v>0.01079971534232222</v>
       </c>
       <c r="H1797">
-        <v>0.01088020171563471</v>
+        <v>0.01102107466569074</v>
       </c>
       <c r="I1797">
-        <v>0.2699207629198517</v>
+        <v>-0.07864067663148155</v>
       </c>
       <c r="J1797">
-        <v>1.075637519575532</v>
+        <v>1.01941890526455</v>
       </c>
       <c r="K1797">
-        <v>5.29</v>
+        <v>4.62</v>
       </c>
       <c r="L1797">
-        <v>6.34</v>
+        <v>6.09</v>
       </c>
       <c r="M1797">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="N1797">
-        <v>5.9</v>
+        <v>6.24</v>
       </c>
       <c r="O1797">
         <v>1</v>
       </c>
       <c r="P1797" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1798" spans="1:16">
       <c r="A1798" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1798" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C1798">
-        <v>0.7065177757520518</v>
+        <v>0.7149171399855092</v>
       </c>
       <c r="D1798" t="s">
         <v>513</v>
       </c>
       <c r="E1798">
-        <v>0.919798284365287</v>
+        <v>0.9905546595610417</v>
       </c>
       <c r="F1798">
         <v>1</v>
       </c>
       <c r="G1798">
-        <v>0.01161348222424795</v>
+        <v>0.01280508286001449</v>
       </c>
       <c r="H1798">
-        <v>0.01088020171563471</v>
+        <v>0.01092944534043896</v>
       </c>
       <c r="I1798">
-        <v>0.2132805086132352</v>
+        <v>0.2756375195755325</v>
       </c>
       <c r="J1798">
         <v>1.075637519575532</v>
       </c>
       <c r="K1798">
-        <v>5.07</v>
+        <v>5.62</v>
       </c>
       <c r="L1798">
-        <v>6.16</v>
+        <v>6.76</v>
       </c>
       <c r="M1798">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="N1798">
-        <v>5.9</v>
+        <v>5.96</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92163,46 +92163,46 @@
     </row>
     <row r="1799" spans="1:16">
       <c r="A1799" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1799" t="s">
         <v>355</v>
       </c>
       <c r="C1799">
-        <v>1.149631161910106</v>
+        <v>0.7250050253605416</v>
       </c>
       <c r="D1799" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E1799">
-        <v>0.8798861697403186</v>
+        <v>0.9905546595610417</v>
       </c>
       <c r="F1799">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1799">
-        <v>0.01083036883808989</v>
+        <v>0.01167499497463946</v>
       </c>
       <c r="H1799">
-        <v>0.009700113830259682</v>
+        <v>0.01092944534043896</v>
       </c>
       <c r="I1799">
-        <v>0.2697449921697874</v>
+        <v>0.2655496342005002</v>
       </c>
       <c r="J1799">
         <v>1.075637519575532</v>
       </c>
       <c r="K1799">
-        <v>4.5</v>
+        <v>5.09</v>
       </c>
       <c r="L1799">
-        <v>5.99</v>
+        <v>6.2</v>
       </c>
       <c r="M1799">
-        <v>4.1</v>
+        <v>4.62</v>
       </c>
       <c r="N1799">
-        <v>5.29</v>
+        <v>5.96</v>
       </c>
       <c r="O1799">
         <v>1</v>
@@ -92213,13 +92213,13 @@
     </row>
     <row r="1800" spans="1:16">
       <c r="A1800" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1800" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C1800">
-        <v>1.136271416216722</v>
+        <v>1.149631161910106</v>
       </c>
       <c r="D1800" t="s">
         <v>516</v>
@@ -92231,22 +92231,22 @@
         <v>-1</v>
       </c>
       <c r="G1800">
-        <v>0.01034372858378328</v>
+        <v>0.01083036883808989</v>
       </c>
       <c r="H1800">
         <v>0.009700113830259682</v>
       </c>
       <c r="I1800">
-        <v>0.2563852464764036</v>
+        <v>0.2697449921697874</v>
       </c>
       <c r="J1800">
         <v>1.075637519575532</v>
       </c>
       <c r="K1800">
-        <v>4.28</v>
+        <v>4.5</v>
       </c>
       <c r="L1800">
-        <v>5.74</v>
+        <v>5.99</v>
       </c>
       <c r="M1800">
         <v>4.1</v>
@@ -92263,46 +92263,46 @@
     </row>
     <row r="1801" spans="1:16">
       <c r="A1801" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1801" t="s">
         <v>349</v>
       </c>
       <c r="C1801">
-        <v>1.155849285931329</v>
+        <v>1.136271416216722</v>
       </c>
       <c r="D1801" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E1801">
-        <v>1.047194913867658</v>
+        <v>0.8798861697403186</v>
       </c>
       <c r="F1801">
         <v>-1</v>
       </c>
       <c r="G1801">
-        <v>0.01094415071406867</v>
+        <v>0.01034372858378328</v>
       </c>
       <c r="H1801">
-        <v>0.01051280508613234</v>
+        <v>0.009700113830259682</v>
       </c>
       <c r="I1801">
-        <v>0.108654372063671</v>
+        <v>0.2563852464764036</v>
       </c>
       <c r="J1801">
         <v>1.075637519575532</v>
       </c>
       <c r="K1801">
-        <v>4.55</v>
+        <v>4.28</v>
       </c>
       <c r="L1801">
-        <v>6.05</v>
+        <v>5.74</v>
       </c>
       <c r="M1801">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N1801">
-        <v>5.78</v>
+        <v>5.29</v>
       </c>
       <c r="O1801">
         <v>1</v>
@@ -92313,46 +92313,46 @@
     </row>
     <row r="1802" spans="1:16">
       <c r="A1802" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1802" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C1802">
-        <v>1.134503657994999</v>
+        <v>1.155849285931329</v>
       </c>
       <c r="D1802" t="s">
         <v>515</v>
       </c>
       <c r="E1802">
-        <v>1.047194913867658</v>
+        <v>1.195260033190754</v>
       </c>
       <c r="F1802">
         <v>-1</v>
       </c>
       <c r="G1802">
-        <v>0.011245496342005</v>
+        <v>0.01094415071406867</v>
       </c>
       <c r="H1802">
-        <v>0.01051280508613234</v>
+        <v>0.01128473996680925</v>
       </c>
       <c r="I1802">
-        <v>0.08730874412734124</v>
+        <v>-0.03941074725942517</v>
       </c>
       <c r="J1802">
         <v>1.075637519575532</v>
       </c>
       <c r="K1802">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="L1802">
-        <v>6.19</v>
+        <v>6.05</v>
       </c>
       <c r="M1802">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="N1802">
-        <v>5.78</v>
+        <v>6.24</v>
       </c>
       <c r="O1802">
         <v>1</v>
@@ -92363,46 +92363,46 @@
     </row>
     <row r="1803" spans="1:16">
       <c r="A1803" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1803" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C1803">
-        <v>1.120554659561042</v>
+        <v>1.134503657994999</v>
       </c>
       <c r="D1803" t="s">
         <v>515</v>
       </c>
       <c r="E1803">
-        <v>1.047194913867658</v>
+        <v>1.195260033190754</v>
       </c>
       <c r="F1803">
         <v>-1</v>
       </c>
       <c r="G1803">
-        <v>0.01105944534043896</v>
+        <v>0.011245496342005</v>
       </c>
       <c r="H1803">
-        <v>0.01051280508613234</v>
+        <v>0.01128473996680925</v>
       </c>
       <c r="I1803">
-        <v>0.07335974569338344</v>
+        <v>-0.06075637519575494</v>
       </c>
       <c r="J1803">
         <v>1.075637519575532</v>
       </c>
       <c r="K1803">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="L1803">
-        <v>6.09</v>
+        <v>6.19</v>
       </c>
       <c r="M1803">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="N1803">
-        <v>5.78</v>
+        <v>6.24</v>
       </c>
       <c r="O1803">
         <v>1</v>
@@ -92413,113 +92413,113 @@
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1804" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C1804">
-        <v>0.6558050350664049</v>
+        <v>1.120554659561042</v>
       </c>
       <c r="D1804" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1804">
-        <v>0.8568521242352567</v>
+        <v>1.195260033190754</v>
       </c>
       <c r="F1804">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1804">
-        <v>0.01174419496493359</v>
+        <v>0.01105944534043896</v>
       </c>
       <c r="H1804">
-        <v>0.01094314787576474</v>
+        <v>0.01128473996680925</v>
       </c>
       <c r="I1804">
-        <v>0.2010470891688518</v>
+        <v>-0.07470537362971275</v>
       </c>
       <c r="J1804">
-        <v>1.089232802540981</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1804">
-        <v>5.09</v>
+        <v>4.62</v>
       </c>
       <c r="L1804">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
       <c r="M1804">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="N1804">
-        <v>5.9</v>
+        <v>6.24</v>
       </c>
       <c r="O1804">
         <v>1</v>
       </c>
       <c r="P1804" t="s">
-        <v>354</v>
+        <v>628</v>
       </c>
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B1805" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C1805">
-        <v>1.088452388565583</v>
+        <v>1.162489540237946</v>
       </c>
       <c r="D1805" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E1805">
-        <v>0.8241455095819763</v>
+        <v>1.195260033190754</v>
       </c>
       <c r="F1805">
         <v>-1</v>
       </c>
       <c r="G1805">
-        <v>0.01089154761143442</v>
+        <v>0.01047751045976206</v>
       </c>
       <c r="H1805">
-        <v>0.009755854490418023</v>
+        <v>0.01128473996680925</v>
       </c>
       <c r="I1805">
-        <v>0.2643068789836072</v>
+        <v>-0.03277049295280854</v>
       </c>
       <c r="J1805">
-        <v>1.089232802540981</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1805">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L1805">
-        <v>5.99</v>
+        <v>5.82</v>
       </c>
       <c r="M1805">
-        <v>4.1</v>
+        <v>4.69</v>
       </c>
       <c r="N1805">
-        <v>5.29</v>
+        <v>6.24</v>
       </c>
       <c r="O1805">
         <v>1</v>
       </c>
       <c r="P1805" t="s">
-        <v>354</v>
+        <v>628</v>
       </c>
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1806" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C1806">
-        <v>1.0780836051246</v>
+        <v>1.088452388565583</v>
       </c>
       <c r="D1806" t="s">
         <v>516</v>
@@ -92531,22 +92531,22 @@
         <v>-1</v>
       </c>
       <c r="G1806">
-        <v>0.0104019163948754</v>
+        <v>0.01089154761143442</v>
       </c>
       <c r="H1806">
         <v>0.009755854490418023</v>
       </c>
       <c r="I1806">
-        <v>0.2539380955426234</v>
+        <v>0.2643068789836072</v>
       </c>
       <c r="J1806">
         <v>1.089232802540981</v>
       </c>
       <c r="K1806">
-        <v>4.28</v>
+        <v>4.5</v>
       </c>
       <c r="L1806">
-        <v>5.74</v>
+        <v>5.99</v>
       </c>
       <c r="M1806">
         <v>4.1</v>
@@ -92563,46 +92563,46 @@
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1807" t="s">
         <v>349</v>
       </c>
       <c r="C1807">
-        <v>1.093990748438535</v>
+        <v>1.0780836051246</v>
       </c>
       <c r="D1807" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E1807">
-        <v>0.9873756688196815</v>
+        <v>0.8241455095819763</v>
       </c>
       <c r="F1807">
         <v>-1</v>
       </c>
       <c r="G1807">
-        <v>0.01100600925156146</v>
+        <v>0.0104019163948754</v>
       </c>
       <c r="H1807">
-        <v>0.01057262433118032</v>
+        <v>0.009755854490418023</v>
       </c>
       <c r="I1807">
-        <v>0.1066150796188534</v>
+        <v>0.2539380955426234</v>
       </c>
       <c r="J1807">
         <v>1.089232802540981</v>
       </c>
       <c r="K1807">
-        <v>4.55</v>
+        <v>4.28</v>
       </c>
       <c r="L1807">
-        <v>6.05</v>
+        <v>5.74</v>
       </c>
       <c r="M1807">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N1807">
-        <v>5.78</v>
+        <v>5.29</v>
       </c>
       <c r="O1807">
         <v>1</v>
@@ -92613,46 +92613,46 @@
     </row>
     <row r="1808" spans="1:16">
       <c r="A1808" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1808" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C1808">
-        <v>1.070605828057388</v>
+        <v>1.093990748438535</v>
       </c>
       <c r="D1808" t="s">
         <v>515</v>
       </c>
       <c r="E1808">
-        <v>0.9873756688196815</v>
+        <v>1.131498156082797</v>
       </c>
       <c r="F1808">
         <v>-1</v>
       </c>
       <c r="G1808">
-        <v>0.01130939417194262</v>
+        <v>0.01100600925156146</v>
       </c>
       <c r="H1808">
-        <v>0.01057262433118032</v>
+        <v>0.0113485018439172</v>
       </c>
       <c r="I1808">
-        <v>0.08323015923770605</v>
+        <v>-0.03750740764426208</v>
       </c>
       <c r="J1808">
         <v>1.089232802540981</v>
       </c>
       <c r="K1808">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="L1808">
-        <v>6.19</v>
+        <v>6.05</v>
       </c>
       <c r="M1808">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="N1808">
-        <v>5.78</v>
+        <v>6.24</v>
       </c>
       <c r="O1808">
         <v>1</v>
@@ -92663,46 +92663,46 @@
     </row>
     <row r="1809" spans="1:16">
       <c r="A1809" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1809" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C1809">
-        <v>1.057744452260666</v>
+        <v>1.070605828057388</v>
       </c>
       <c r="D1809" t="s">
         <v>515</v>
       </c>
       <c r="E1809">
-        <v>0.9873756688196815</v>
+        <v>1.131498156082797</v>
       </c>
       <c r="F1809">
         <v>-1</v>
       </c>
       <c r="G1809">
-        <v>0.01112225554773933</v>
+        <v>0.01130939417194262</v>
       </c>
       <c r="H1809">
-        <v>0.01057262433118032</v>
+        <v>0.0113485018439172</v>
       </c>
       <c r="I1809">
-        <v>0.07036878344098429</v>
+        <v>-0.06089232802540945</v>
       </c>
       <c r="J1809">
         <v>1.089232802540981</v>
       </c>
       <c r="K1809">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="L1809">
-        <v>6.09</v>
+        <v>6.19</v>
       </c>
       <c r="M1809">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="N1809">
-        <v>5.78</v>
+        <v>6.24</v>
       </c>
       <c r="O1809">
         <v>1</v>
@@ -92713,46 +92713,46 @@
     </row>
     <row r="1810" spans="1:16">
       <c r="A1810" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1810" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C1810">
-        <v>1.103621964997551</v>
+        <v>1.057744452260666</v>
       </c>
       <c r="D1810" t="s">
         <v>515</v>
       </c>
       <c r="E1810">
-        <v>0.9873756688196815</v>
+        <v>1.131498156082797</v>
       </c>
       <c r="F1810">
         <v>-1</v>
       </c>
       <c r="G1810">
-        <v>0.01053637803500245</v>
+        <v>0.01112225554773933</v>
       </c>
       <c r="H1810">
-        <v>0.01057262433118032</v>
+        <v>0.0113485018439172</v>
       </c>
       <c r="I1810">
-        <v>0.1162462961778692</v>
+        <v>-0.0737537038221312</v>
       </c>
       <c r="J1810">
         <v>1.089232802540981</v>
       </c>
       <c r="K1810">
-        <v>4.33</v>
+        <v>4.62</v>
       </c>
       <c r="L1810">
-        <v>5.82</v>
+        <v>6.09</v>
       </c>
       <c r="M1810">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="N1810">
-        <v>5.78</v>
+        <v>6.24</v>
       </c>
       <c r="O1810">
         <v>1</v>
@@ -92763,60 +92763,60 @@
     </row>
     <row r="1811" spans="1:16">
       <c r="A1811" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1811" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C1811">
-        <v>1.437331032547627</v>
+        <v>1.103621964997551</v>
       </c>
       <c r="D1811" t="s">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="E1811">
-        <v>1.527152008316966</v>
+        <v>1.131498156082797</v>
       </c>
       <c r="F1811">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1811">
-        <v>0.01054266896745237</v>
+        <v>0.01053637803500245</v>
       </c>
       <c r="H1811">
-        <v>0.01057284799168303</v>
+        <v>0.0113485018439172</v>
       </c>
       <c r="I1811">
-        <v>0.08982097576933867</v>
+        <v>-0.0278761910852463</v>
       </c>
       <c r="J1811">
-        <v>0.994032525644623</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1811">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="L1811">
-        <v>5.99</v>
+        <v>5.82</v>
       </c>
       <c r="M1811">
-        <v>4.55</v>
+        <v>4.69</v>
       </c>
       <c r="N1811">
-        <v>6.05</v>
+        <v>6.24</v>
       </c>
       <c r="O1811">
         <v>1</v>
       </c>
       <c r="P1811" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="1812" spans="1:16">
       <c r="A1812" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1812" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1812">
         <v>1.595242416523244</v>
@@ -92858,7 +92858,7 @@
         <v>1</v>
       </c>
       <c r="P1812" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1813" spans="1:16">
@@ -92866,7 +92866,7 @@
         <v>0</v>
       </c>
       <c r="B1813" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C1813">
         <v>1.106278882193859</v>
@@ -92908,7 +92908,7 @@
         <v>1</v>
       </c>
       <c r="P1813" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="1814" spans="1:16">
@@ -92916,7 +92916,7 @@
         <v>1</v>
       </c>
       <c r="B1814" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1814">
         <v>1.290033686008443</v>
@@ -92958,7 +92958,7 @@
         <v>1</v>
       </c>
       <c r="P1814" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="1815" spans="1:16">
@@ -92966,7 +92966,7 @@
         <v>0</v>
       </c>
       <c r="B1815" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C1815">
         <v>0.9527648456254667</v>
@@ -93016,7 +93016,7 @@
         <v>1</v>
       </c>
       <c r="B1816" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1816">
         <v>1.153036982488548</v>
@@ -93063,102 +93063,202 @@
     </row>
     <row r="1817" spans="1:16">
       <c r="A1817" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1817" t="s">
         <v>360</v>
       </c>
       <c r="C1817">
-        <v>0.8652138986958411</v>
+        <v>0.9462796035341885</v>
       </c>
       <c r="D1817" t="s">
-        <v>357</v>
+        <v>515</v>
       </c>
       <c r="E1817">
-        <v>0.9832017260238386</v>
+        <v>1.087693486494396</v>
       </c>
       <c r="F1817">
         <v>1</v>
       </c>
       <c r="G1817">
-        <v>0.01145478610130416</v>
+        <v>0.01061372039646581</v>
       </c>
       <c r="H1817">
-        <v>0.01065679827397616</v>
+        <v>0.01139230651350561</v>
       </c>
       <c r="I1817">
-        <v>0.1179878273279975</v>
+        <v>0.1414138829602072</v>
       </c>
       <c r="J1817">
-        <v>1.117043481287797</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1817">
-        <v>4.74</v>
+        <v>4.4</v>
       </c>
       <c r="L1817">
-        <v>6.16</v>
+        <v>5.78</v>
       </c>
       <c r="M1817">
-        <v>4.33</v>
+        <v>4.69</v>
       </c>
       <c r="N1817">
-        <v>5.82</v>
+        <v>6.24</v>
       </c>
       <c r="O1817">
         <v>1</v>
       </c>
       <c r="P1817" t="s">
-        <v>350</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1818" spans="1:16">
       <c r="A1818" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1818" t="s">
         <v>359</v>
       </c>
       <c r="C1818">
-        <v>1.074906074152617</v>
+        <v>0.8652138986958411</v>
       </c>
       <c r="D1818" t="s">
-        <v>517</v>
+        <v>357</v>
       </c>
       <c r="E1818">
-        <v>0.8855425956495946</v>
+        <v>0.9832017260238386</v>
       </c>
       <c r="F1818">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1818">
-        <v>0.01052509392584738</v>
+        <v>0.01145478610130416</v>
       </c>
       <c r="H1818">
-        <v>0.01051445740435041</v>
+        <v>0.01065679827397616</v>
       </c>
       <c r="I1818">
-        <v>0.1893634785030223</v>
+        <v>0.1179878273279975</v>
       </c>
       <c r="J1818">
         <v>1.117043481287797</v>
       </c>
       <c r="K1818">
+        <v>4.74</v>
+      </c>
+      <c r="L1818">
+        <v>6.16</v>
+      </c>
+      <c r="M1818">
+        <v>4.33</v>
+      </c>
+      <c r="N1818">
+        <v>5.82</v>
+      </c>
+      <c r="O1818">
+        <v>1</v>
+      </c>
+      <c r="P1818" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:16">
+      <c r="A1819" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1819" t="s">
+        <v>358</v>
+      </c>
+      <c r="C1819">
+        <v>1.074906074152617</v>
+      </c>
+      <c r="D1819" t="s">
+        <v>517</v>
+      </c>
+      <c r="E1819">
+        <v>0.8855425956495946</v>
+      </c>
+      <c r="F1819">
+        <v>-1</v>
+      </c>
+      <c r="G1819">
+        <v>0.01052509392584738</v>
+      </c>
+      <c r="H1819">
+        <v>0.01051445740435041</v>
+      </c>
+      <c r="I1819">
+        <v>0.1893634785030223</v>
+      </c>
+      <c r="J1819">
+        <v>1.117043481287797</v>
+      </c>
+      <c r="K1819">
         <v>4.23</v>
       </c>
-      <c r="L1818">
+      <c r="L1819">
         <v>5.8</v>
       </c>
-      <c r="M1818">
+      <c r="M1819">
         <v>4.31</v>
       </c>
-      <c r="N1818">
+      <c r="N1819">
         <v>5.7</v>
       </c>
-      <c r="O1818">
-        <v>1</v>
-      </c>
-      <c r="P1818" t="s">
-        <v>350</v>
+      <c r="O1819">
+        <v>1</v>
+      </c>
+      <c r="P1819" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:16">
+      <c r="A1820" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1820" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1820">
+        <v>0.8650086823336922</v>
+      </c>
+      <c r="D1820" t="s">
+        <v>515</v>
+      </c>
+      <c r="E1820">
+        <v>1.001066072760231</v>
+      </c>
+      <c r="F1820">
+        <v>1</v>
+      </c>
+      <c r="G1820">
+        <v>0.01069499131766631</v>
+      </c>
+      <c r="H1820">
+        <v>0.01147893392723977</v>
+      </c>
+      <c r="I1820">
+        <v>0.1360573904265392</v>
+      </c>
+      <c r="J1820">
+        <v>1.117043481287797</v>
+      </c>
+      <c r="K1820">
+        <v>4.4</v>
+      </c>
+      <c r="L1820">
+        <v>5.78</v>
+      </c>
+      <c r="M1820">
+        <v>4.69</v>
+      </c>
+      <c r="N1820">
+        <v>6.24</v>
+      </c>
+      <c r="O1820">
+        <v>1</v>
+      </c>
+      <c r="P1820" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5472" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5475" uniqueCount="630">
   <si>
     <t>trade_time</t>
   </si>
@@ -1078,10 +1078,10 @@
     <t>2021-09-13</t>
   </si>
   <si>
-    <t>2021-05-27</t>
+    <t>2021-10-11</t>
   </si>
   <si>
-    <t>2021-06-24</t>
+    <t>2021-05-27</t>
   </si>
   <si>
     <t>2021-07-21</t>
@@ -1561,7 +1561,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-10-11</t>
+    <t>2021-10-12</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -2261,7 +2261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1820"/>
+  <dimension ref="A1:P1821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91425,7 +91425,7 @@
         <v>515</v>
       </c>
       <c r="E1784">
-        <v>1.728491890001313</v>
+        <v>1.632297687229486</v>
       </c>
       <c r="F1784">
         <v>-1</v>
@@ -91434,10 +91434,10 @@
         <v>0.01039645564639531</v>
       </c>
       <c r="H1784">
-        <v>0.01075150810999869</v>
+        <v>0.01084770231277052</v>
       </c>
       <c r="I1784">
-        <v>-0.104947536396625</v>
+        <v>-0.008753333624798465</v>
       </c>
       <c r="J1784">
         <v>0.9619420277182702</v>
@@ -91449,7 +91449,7 @@
         <v>6.01</v>
       </c>
       <c r="M1784">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1784">
         <v>6.24</v>
@@ -91475,7 +91475,7 @@
         <v>515</v>
       </c>
       <c r="E1785">
-        <v>1.728491890001313</v>
+        <v>1.632297687229486</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91484,10 +91484,10 @@
         <v>0.01042683622611813</v>
       </c>
       <c r="H1785">
-        <v>0.01075150810999869</v>
+        <v>0.01084770231277052</v>
       </c>
       <c r="I1785">
-        <v>-0.05532811611944233</v>
+        <v>0.04086608665238423</v>
       </c>
       <c r="J1785">
         <v>0.9619420277182702</v>
@@ -91499,7 +91499,7 @@
         <v>6.05</v>
       </c>
       <c r="M1785">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1785">
         <v>6.24</v>
@@ -91525,7 +91525,7 @@
         <v>515</v>
       </c>
       <c r="E1786">
-        <v>1.728491890001313</v>
+        <v>1.632297687229486</v>
       </c>
       <c r="F1786">
         <v>-1</v>
@@ -91534,10 +91534,10 @@
         <v>0.01071112753027587</v>
       </c>
       <c r="H1786">
-        <v>0.01075150810999869</v>
+        <v>0.01084770231277052</v>
       </c>
       <c r="I1786">
-        <v>-0.05961942027718248</v>
+        <v>0.03657478249464408</v>
       </c>
       <c r="J1786">
         <v>0.9619420277182702</v>
@@ -91549,7 +91549,7 @@
         <v>6.19</v>
       </c>
       <c r="M1786">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1786">
         <v>6.24</v>
@@ -91575,7 +91575,7 @@
         <v>515</v>
       </c>
       <c r="E1787">
-        <v>1.728491890001313</v>
+        <v>1.632297687229486</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91584,10 +91584,10 @@
         <v>0.01053417216805841</v>
       </c>
       <c r="H1787">
-        <v>0.01075150810999869</v>
+        <v>0.01084770231277052</v>
       </c>
       <c r="I1787">
-        <v>-0.08266405805972088</v>
+        <v>0.01353014471210567</v>
       </c>
       <c r="J1787">
         <v>0.9619420277182702</v>
@@ -91599,7 +91599,7 @@
         <v>6.09</v>
       </c>
       <c r="M1787">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1787">
         <v>6.24</v>
@@ -91613,63 +91613,63 @@
     </row>
     <row r="1788" spans="1:16">
       <c r="A1788" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1788" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="C1788">
-        <v>0.9728076429396824</v>
+        <v>1.728491890001313</v>
       </c>
       <c r="D1788" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1788">
-        <v>1.250284657677777</v>
+        <v>1.632297687229486</v>
       </c>
       <c r="F1788">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1788">
-        <v>0.01222719235706032</v>
+        <v>0.01075150810999869</v>
       </c>
       <c r="H1788">
-        <v>0.01066971534232222</v>
+        <v>0.01084770231277052</v>
       </c>
       <c r="I1788">
-        <v>0.2774770147380945</v>
+        <v>0.09619420277182655</v>
       </c>
       <c r="J1788">
-        <v>1.01941890526455</v>
+        <v>0.9619420277182702</v>
       </c>
       <c r="K1788">
-        <v>5.52</v>
+        <v>4.69</v>
       </c>
       <c r="L1788">
-        <v>6.6</v>
+        <v>6.24</v>
       </c>
       <c r="M1788">
-        <v>4.62</v>
+        <v>4.79</v>
       </c>
       <c r="N1788">
-        <v>5.96</v>
+        <v>6.24</v>
       </c>
       <c r="O1788">
         <v>1</v>
       </c>
       <c r="P1788" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1789" spans="1:16">
       <c r="A1789" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1789" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C1789">
-        <v>0.9261088568346558</v>
+        <v>0.9728076429396824</v>
       </c>
       <c r="D1789" t="s">
         <v>513</v>
@@ -91681,22 +91681,22 @@
         <v>1</v>
       </c>
       <c r="G1789">
-        <v>0.01183389114316535</v>
+        <v>0.01222719235706032</v>
       </c>
       <c r="H1789">
         <v>0.01066971534232222</v>
       </c>
       <c r="I1789">
-        <v>0.324175800843121</v>
+        <v>0.2774770147380945</v>
       </c>
       <c r="J1789">
         <v>1.01941890526455</v>
       </c>
       <c r="K1789">
-        <v>5.35</v>
+        <v>5.52</v>
       </c>
       <c r="L1789">
-        <v>6.38</v>
+        <v>6.6</v>
       </c>
       <c r="M1789">
         <v>4.62</v>
@@ -91713,7 +91713,7 @@
     </row>
     <row r="1790" spans="1:16">
       <c r="A1790" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1790" t="s">
         <v>346</v>
@@ -91763,7 +91763,7 @@
     </row>
     <row r="1791" spans="1:16">
       <c r="A1791" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1791" t="s">
         <v>347</v>
@@ -91813,7 +91813,7 @@
     </row>
     <row r="1792" spans="1:16">
       <c r="A1792" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1792" t="s">
         <v>348</v>
@@ -91822,10 +91822,10 @@
         <v>1.360090468625132</v>
       </c>
       <c r="D1792" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E1792">
-        <v>1.110382488415344</v>
+        <v>1.180576677467989</v>
       </c>
       <c r="F1792">
         <v>-1</v>
@@ -91834,10 +91834,10 @@
         <v>0.01079990953137487</v>
       </c>
       <c r="H1792">
-        <v>0.009469617511584654</v>
+        <v>0.009519423322532011</v>
       </c>
       <c r="I1792">
-        <v>0.2497079802097879</v>
+        <v>0.1795137911571434</v>
       </c>
       <c r="J1792">
         <v>1.01941890526455</v>
@@ -91849,10 +91849,10 @@
         <v>6.08</v>
       </c>
       <c r="M1792">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="N1792">
-        <v>5.29</v>
+        <v>5.35</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91863,7 +91863,7 @@
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1793" t="s">
         <v>349</v>
@@ -91872,10 +91872,10 @@
         <v>1.376887085467724</v>
       </c>
       <c r="D1793" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E1793">
-        <v>1.110382488415344</v>
+        <v>1.180576677467989</v>
       </c>
       <c r="F1793">
         <v>-1</v>
@@ -91884,10 +91884,10 @@
         <v>0.01010311291453228</v>
       </c>
       <c r="H1793">
-        <v>0.009469617511584654</v>
+        <v>0.009519423322532011</v>
       </c>
       <c r="I1793">
-        <v>0.2665045970523803</v>
+        <v>0.1963104079997358</v>
       </c>
       <c r="J1793">
         <v>1.01941890526455</v>
@@ -91899,10 +91899,10 @@
         <v>5.74</v>
       </c>
       <c r="M1793">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="N1793">
-        <v>5.29</v>
+        <v>5.35</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -91913,7 +91913,7 @@
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1794" t="s">
         <v>350</v>
@@ -91925,7 +91925,7 @@
         <v>515</v>
       </c>
       <c r="E1794">
-        <v>1.458925334309258</v>
+        <v>1.356983443782804</v>
       </c>
       <c r="F1794">
         <v>-1</v>
@@ -91934,10 +91934,10 @@
         <v>0.01065855020800635</v>
       </c>
       <c r="H1794">
-        <v>0.01102107466569074</v>
+        <v>0.0111230165562172</v>
       </c>
       <c r="I1794">
-        <v>-0.09747554231560773</v>
+        <v>0.004466348210846682</v>
       </c>
       <c r="J1794">
         <v>1.01941890526455</v>
@@ -91949,7 +91949,7 @@
         <v>6.01</v>
       </c>
       <c r="M1794">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1794">
         <v>6.24</v>
@@ -91963,7 +91963,7 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1795" t="s">
         <v>351</v>
@@ -91975,7 +91975,7 @@
         <v>515</v>
       </c>
       <c r="E1795">
-        <v>1.458925334309258</v>
+        <v>1.356983443782804</v>
       </c>
       <c r="F1795">
         <v>-1</v>
@@ -91984,10 +91984,10 @@
         <v>0.0106883560189537</v>
       </c>
       <c r="H1795">
-        <v>0.01102107466569074</v>
+        <v>0.0111230165562172</v>
       </c>
       <c r="I1795">
-        <v>-0.04728135326296279</v>
+        <v>0.05466053726349163</v>
       </c>
       <c r="J1795">
         <v>1.01941890526455</v>
@@ -91999,7 +91999,7 @@
         <v>6.05</v>
       </c>
       <c r="M1795">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1795">
         <v>6.24</v>
@@ -92013,7 +92013,7 @@
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1796" t="s">
         <v>352</v>
@@ -92025,7 +92025,7 @@
         <v>515</v>
       </c>
       <c r="E1796">
-        <v>1.458925334309258</v>
+        <v>1.356983443782804</v>
       </c>
       <c r="F1796">
         <v>-1</v>
@@ -92034,10 +92034,10 @@
         <v>0.01098126885474339</v>
       </c>
       <c r="H1796">
-        <v>0.01102107466569074</v>
+        <v>0.0111230165562172</v>
       </c>
       <c r="I1796">
-        <v>-0.06019418905264473</v>
+        <v>0.04174770147380968</v>
       </c>
       <c r="J1796">
         <v>1.01941890526455</v>
@@ -92049,7 +92049,7 @@
         <v>6.19</v>
       </c>
       <c r="M1796">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1796">
         <v>6.24</v>
@@ -92063,7 +92063,7 @@
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1797" t="s">
         <v>353</v>
@@ -92075,7 +92075,7 @@
         <v>515</v>
       </c>
       <c r="E1797">
-        <v>1.458925334309258</v>
+        <v>1.356983443782804</v>
       </c>
       <c r="F1797">
         <v>-1</v>
@@ -92084,10 +92084,10 @@
         <v>0.01079971534232222</v>
       </c>
       <c r="H1797">
-        <v>0.01102107466569074</v>
+        <v>0.0111230165562172</v>
       </c>
       <c r="I1797">
-        <v>-0.07864067663148155</v>
+        <v>0.02330121389497286</v>
       </c>
       <c r="J1797">
         <v>1.01941890526455</v>
@@ -92099,7 +92099,7 @@
         <v>6.09</v>
       </c>
       <c r="M1797">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1797">
         <v>6.24</v>
@@ -92113,63 +92113,63 @@
     </row>
     <row r="1798" spans="1:16">
       <c r="A1798" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1798" t="s">
         <v>354</v>
       </c>
       <c r="C1798">
-        <v>0.7149171399855092</v>
+        <v>1.458925334309258</v>
       </c>
       <c r="D1798" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1798">
-        <v>0.9905546595610417</v>
+        <v>1.356983443782804</v>
       </c>
       <c r="F1798">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1798">
-        <v>0.01280508286001449</v>
+        <v>0.01102107466569074</v>
       </c>
       <c r="H1798">
-        <v>0.01092944534043896</v>
+        <v>0.0111230165562172</v>
       </c>
       <c r="I1798">
-        <v>0.2756375195755325</v>
+        <v>0.1019418905264544</v>
       </c>
       <c r="J1798">
-        <v>1.075637519575532</v>
+        <v>1.01941890526455</v>
       </c>
       <c r="K1798">
-        <v>5.62</v>
+        <v>4.69</v>
       </c>
       <c r="L1798">
-        <v>6.76</v>
+        <v>6.24</v>
       </c>
       <c r="M1798">
-        <v>4.62</v>
+        <v>4.79</v>
       </c>
       <c r="N1798">
-        <v>5.96</v>
+        <v>6.24</v>
       </c>
       <c r="O1798">
         <v>1</v>
       </c>
       <c r="P1798" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1799" spans="1:16">
       <c r="A1799" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1799" t="s">
         <v>355</v>
       </c>
       <c r="C1799">
-        <v>0.7250050253605416</v>
+        <v>0.7149171399855092</v>
       </c>
       <c r="D1799" t="s">
         <v>513</v>
@@ -92181,22 +92181,22 @@
         <v>1</v>
       </c>
       <c r="G1799">
-        <v>0.01167499497463946</v>
+        <v>0.01280508286001449</v>
       </c>
       <c r="H1799">
         <v>0.01092944534043896</v>
       </c>
       <c r="I1799">
-        <v>0.2655496342005002</v>
+        <v>0.2756375195755325</v>
       </c>
       <c r="J1799">
         <v>1.075637519575532</v>
       </c>
       <c r="K1799">
-        <v>5.09</v>
+        <v>5.62</v>
       </c>
       <c r="L1799">
-        <v>6.2</v>
+        <v>6.76</v>
       </c>
       <c r="M1799">
         <v>4.62</v>
@@ -92213,7 +92213,7 @@
     </row>
     <row r="1800" spans="1:16">
       <c r="A1800" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1800" t="s">
         <v>356</v>
@@ -92263,7 +92263,7 @@
     </row>
     <row r="1801" spans="1:16">
       <c r="A1801" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1801" t="s">
         <v>349</v>
@@ -92313,7 +92313,7 @@
     </row>
     <row r="1802" spans="1:16">
       <c r="A1802" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1802" t="s">
         <v>351</v>
@@ -92325,7 +92325,7 @@
         <v>515</v>
       </c>
       <c r="E1802">
-        <v>1.195260033190754</v>
+        <v>1.087696281233201</v>
       </c>
       <c r="F1802">
         <v>-1</v>
@@ -92334,10 +92334,10 @@
         <v>0.01094415071406867</v>
       </c>
       <c r="H1802">
-        <v>0.01128473996680925</v>
+        <v>0.0113923037187668</v>
       </c>
       <c r="I1802">
-        <v>-0.03941074725942517</v>
+        <v>0.06815300469812779</v>
       </c>
       <c r="J1802">
         <v>1.075637519575532</v>
@@ -92349,7 +92349,7 @@
         <v>6.05</v>
       </c>
       <c r="M1802">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1802">
         <v>6.24</v>
@@ -92363,7 +92363,7 @@
     </row>
     <row r="1803" spans="1:16">
       <c r="A1803" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1803" t="s">
         <v>352</v>
@@ -92375,7 +92375,7 @@
         <v>515</v>
       </c>
       <c r="E1803">
-        <v>1.195260033190754</v>
+        <v>1.087696281233201</v>
       </c>
       <c r="F1803">
         <v>-1</v>
@@ -92384,10 +92384,10 @@
         <v>0.011245496342005</v>
       </c>
       <c r="H1803">
-        <v>0.01128473996680925</v>
+        <v>0.0113923037187668</v>
       </c>
       <c r="I1803">
-        <v>-0.06075637519575494</v>
+        <v>0.04680737676179803</v>
       </c>
       <c r="J1803">
         <v>1.075637519575532</v>
@@ -92399,7 +92399,7 @@
         <v>6.19</v>
       </c>
       <c r="M1803">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1803">
         <v>6.24</v>
@@ -92413,7 +92413,7 @@
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1804" t="s">
         <v>353</v>
@@ -92425,7 +92425,7 @@
         <v>515</v>
       </c>
       <c r="E1804">
-        <v>1.195260033190754</v>
+        <v>1.087696281233201</v>
       </c>
       <c r="F1804">
         <v>-1</v>
@@ -92434,10 +92434,10 @@
         <v>0.01105944534043896</v>
       </c>
       <c r="H1804">
-        <v>0.01128473996680925</v>
+        <v>0.0113923037187668</v>
       </c>
       <c r="I1804">
-        <v>-0.07470537362971275</v>
+        <v>0.03285837832784022</v>
       </c>
       <c r="J1804">
         <v>1.075637519575532</v>
@@ -92449,7 +92449,7 @@
         <v>6.09</v>
       </c>
       <c r="M1804">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1804">
         <v>6.24</v>
@@ -92463,7 +92463,7 @@
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1805" t="s">
         <v>357</v>
@@ -92475,7 +92475,7 @@
         <v>515</v>
       </c>
       <c r="E1805">
-        <v>1.195260033190754</v>
+        <v>1.087696281233201</v>
       </c>
       <c r="F1805">
         <v>-1</v>
@@ -92484,10 +92484,10 @@
         <v>0.01047751045976206</v>
       </c>
       <c r="H1805">
-        <v>0.01128473996680925</v>
+        <v>0.0113923037187668</v>
       </c>
       <c r="I1805">
-        <v>-0.03277049295280854</v>
+        <v>0.07479325900474443</v>
       </c>
       <c r="J1805">
         <v>1.075637519575532</v>
@@ -92499,7 +92499,7 @@
         <v>5.82</v>
       </c>
       <c r="M1805">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1805">
         <v>6.24</v>
@@ -92513,63 +92513,63 @@
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1806" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C1806">
-        <v>1.088452388565583</v>
+        <v>1.195260033190754</v>
       </c>
       <c r="D1806" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E1806">
-        <v>0.8241455095819763</v>
+        <v>1.087696281233201</v>
       </c>
       <c r="F1806">
         <v>-1</v>
       </c>
       <c r="G1806">
-        <v>0.01089154761143442</v>
+        <v>0.01128473996680925</v>
       </c>
       <c r="H1806">
-        <v>0.009755854490418023</v>
+        <v>0.0113923037187668</v>
       </c>
       <c r="I1806">
-        <v>0.2643068789836072</v>
+        <v>0.107563751957553</v>
       </c>
       <c r="J1806">
-        <v>1.089232802540981</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1806">
-        <v>4.5</v>
+        <v>4.69</v>
       </c>
       <c r="L1806">
-        <v>5.99</v>
+        <v>6.24</v>
       </c>
       <c r="M1806">
-        <v>4.1</v>
+        <v>4.79</v>
       </c>
       <c r="N1806">
-        <v>5.29</v>
+        <v>6.24</v>
       </c>
       <c r="O1806">
         <v>1</v>
       </c>
       <c r="P1806" t="s">
-        <v>354</v>
+        <v>628</v>
       </c>
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1807" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C1807">
-        <v>1.0780836051246</v>
+        <v>1.088452388565583</v>
       </c>
       <c r="D1807" t="s">
         <v>516</v>
@@ -92581,22 +92581,22 @@
         <v>-1</v>
       </c>
       <c r="G1807">
-        <v>0.0104019163948754</v>
+        <v>0.01089154761143442</v>
       </c>
       <c r="H1807">
         <v>0.009755854490418023</v>
       </c>
       <c r="I1807">
-        <v>0.2539380955426234</v>
+        <v>0.2643068789836072</v>
       </c>
       <c r="J1807">
         <v>1.089232802540981</v>
       </c>
       <c r="K1807">
-        <v>4.28</v>
+        <v>4.5</v>
       </c>
       <c r="L1807">
-        <v>5.74</v>
+        <v>5.99</v>
       </c>
       <c r="M1807">
         <v>4.1</v>
@@ -92608,98 +92608,98 @@
         <v>1</v>
       </c>
       <c r="P1807" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1808" spans="1:16">
       <c r="A1808" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1808" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C1808">
-        <v>1.093990748438535</v>
+        <v>1.0780836051246</v>
       </c>
       <c r="D1808" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E1808">
-        <v>1.131498156082797</v>
+        <v>0.8241455095819763</v>
       </c>
       <c r="F1808">
         <v>-1</v>
       </c>
       <c r="G1808">
-        <v>0.01100600925156146</v>
+        <v>0.0104019163948754</v>
       </c>
       <c r="H1808">
-        <v>0.0113485018439172</v>
+        <v>0.009755854490418023</v>
       </c>
       <c r="I1808">
-        <v>-0.03750740764426208</v>
+        <v>0.2539380955426234</v>
       </c>
       <c r="J1808">
         <v>1.089232802540981</v>
       </c>
       <c r="K1808">
-        <v>4.55</v>
+        <v>4.28</v>
       </c>
       <c r="L1808">
-        <v>6.05</v>
+        <v>5.74</v>
       </c>
       <c r="M1808">
-        <v>4.69</v>
+        <v>4.1</v>
       </c>
       <c r="N1808">
-        <v>6.24</v>
+        <v>5.29</v>
       </c>
       <c r="O1808">
         <v>1</v>
       </c>
       <c r="P1808" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1809" spans="1:16">
       <c r="A1809" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1809" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C1809">
-        <v>1.070605828057388</v>
+        <v>1.093990748438535</v>
       </c>
       <c r="D1809" t="s">
         <v>515</v>
       </c>
       <c r="E1809">
-        <v>1.131498156082797</v>
+        <v>1.022574875828699</v>
       </c>
       <c r="F1809">
         <v>-1</v>
       </c>
       <c r="G1809">
-        <v>0.01130939417194262</v>
+        <v>0.01100600925156146</v>
       </c>
       <c r="H1809">
-        <v>0.0113485018439172</v>
+        <v>0.0114574251241713</v>
       </c>
       <c r="I1809">
-        <v>-0.06089232802540945</v>
+        <v>0.07141587260983595</v>
       </c>
       <c r="J1809">
         <v>1.089232802540981</v>
       </c>
       <c r="K1809">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="L1809">
-        <v>6.19</v>
+        <v>6.05</v>
       </c>
       <c r="M1809">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1809">
         <v>6.24</v>
@@ -92708,48 +92708,48 @@
         <v>1</v>
       </c>
       <c r="P1809" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1810" spans="1:16">
       <c r="A1810" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1810" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C1810">
-        <v>1.057744452260666</v>
+        <v>1.070605828057388</v>
       </c>
       <c r="D1810" t="s">
         <v>515</v>
       </c>
       <c r="E1810">
-        <v>1.131498156082797</v>
+        <v>1.022574875828699</v>
       </c>
       <c r="F1810">
         <v>-1</v>
       </c>
       <c r="G1810">
-        <v>0.01112225554773933</v>
+        <v>0.01130939417194262</v>
       </c>
       <c r="H1810">
-        <v>0.0113485018439172</v>
+        <v>0.0114574251241713</v>
       </c>
       <c r="I1810">
-        <v>-0.0737537038221312</v>
+        <v>0.04803095222868858</v>
       </c>
       <c r="J1810">
         <v>1.089232802540981</v>
       </c>
       <c r="K1810">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="L1810">
-        <v>6.09</v>
+        <v>6.19</v>
       </c>
       <c r="M1810">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1810">
         <v>6.24</v>
@@ -92758,12 +92758,12 @@
         <v>1</v>
       </c>
       <c r="P1810" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1811" spans="1:16">
       <c r="A1811" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1811" t="s">
         <v>357</v>
@@ -92775,7 +92775,7 @@
         <v>515</v>
       </c>
       <c r="E1811">
-        <v>1.131498156082797</v>
+        <v>1.022574875828699</v>
       </c>
       <c r="F1811">
         <v>-1</v>
@@ -92784,10 +92784,10 @@
         <v>0.01053637803500245</v>
       </c>
       <c r="H1811">
-        <v>0.0113485018439172</v>
+        <v>0.0114574251241713</v>
       </c>
       <c r="I1811">
-        <v>-0.0278761910852463</v>
+        <v>0.08104708916885173</v>
       </c>
       <c r="J1811">
         <v>1.089232802540981</v>
@@ -92799,7 +92799,7 @@
         <v>5.82</v>
       </c>
       <c r="M1811">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="N1811">
         <v>6.24</v>
@@ -92808,57 +92808,57 @@
         <v>1</v>
       </c>
       <c r="P1811" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1812" spans="1:16">
       <c r="A1812" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1812" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C1812">
-        <v>1.595242416523244</v>
+        <v>1.131498156082797</v>
       </c>
       <c r="D1812" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E1812">
-        <v>1.415719814471675</v>
+        <v>1.022574875828699</v>
       </c>
       <c r="F1812">
         <v>-1</v>
       </c>
       <c r="G1812">
-        <v>0.01000475758347676</v>
+        <v>0.0113485018439172</v>
       </c>
       <c r="H1812">
-        <v>0.009984280185528325</v>
+        <v>0.0114574251241713</v>
       </c>
       <c r="I1812">
-        <v>0.179522602051569</v>
+        <v>0.108923280254098</v>
       </c>
       <c r="J1812">
-        <v>0.994032525644623</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1812">
-        <v>4.23</v>
+        <v>4.69</v>
       </c>
       <c r="L1812">
-        <v>5.8</v>
+        <v>6.24</v>
       </c>
       <c r="M1812">
-        <v>4.31</v>
+        <v>4.79</v>
       </c>
       <c r="N1812">
-        <v>5.7</v>
+        <v>6.24</v>
       </c>
       <c r="O1812">
         <v>1</v>
       </c>
       <c r="P1812" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1813" spans="1:16">
@@ -92866,93 +92866,93 @@
         <v>0</v>
       </c>
       <c r="B1813" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1813">
-        <v>1.106278882193859</v>
+        <v>1.595242416523244</v>
       </c>
       <c r="D1813" t="s">
-        <v>357</v>
+        <v>517</v>
       </c>
       <c r="E1813">
-        <v>1.203415097025192</v>
+        <v>1.415719814471675</v>
       </c>
       <c r="F1813">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1813">
-        <v>0.01121372111780614</v>
+        <v>0.01000475758347676</v>
       </c>
       <c r="H1813">
-        <v>0.01043658490297481</v>
+        <v>0.009984280185528325</v>
       </c>
       <c r="I1813">
-        <v>0.09713621483133306</v>
+        <v>0.179522602051569</v>
       </c>
       <c r="J1813">
-        <v>1.066185889832519</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1813">
-        <v>4.74</v>
+        <v>4.23</v>
       </c>
       <c r="L1813">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="M1813">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="N1813">
-        <v>5.82</v>
+        <v>5.7</v>
       </c>
       <c r="O1813">
         <v>1</v>
       </c>
       <c r="P1813" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1814" spans="1:16">
       <c r="A1814" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1814" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C1814">
-        <v>1.290033686008443</v>
+        <v>1.106278882193859</v>
       </c>
       <c r="D1814" t="s">
-        <v>517</v>
+        <v>357</v>
       </c>
       <c r="E1814">
-        <v>1.104738814821843</v>
+        <v>1.203415097025192</v>
       </c>
       <c r="F1814">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1814">
-        <v>0.01030996631399156</v>
+        <v>0.01121372111780614</v>
       </c>
       <c r="H1814">
-        <v>0.01029526118517816</v>
+        <v>0.01043658490297481</v>
       </c>
       <c r="I1814">
-        <v>0.1852948711866</v>
+        <v>0.09713621483133306</v>
       </c>
       <c r="J1814">
         <v>1.066185889832519</v>
       </c>
       <c r="K1814">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="L1814">
-        <v>5.8</v>
+        <v>6.16</v>
       </c>
       <c r="M1814">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1814">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="O1814">
         <v>1</v>
@@ -92963,96 +92963,96 @@
     </row>
     <row r="1815" spans="1:16">
       <c r="A1815" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1815" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1815">
-        <v>0.9527648456254667</v>
+        <v>1.290033686008443</v>
       </c>
       <c r="D1815" t="s">
-        <v>357</v>
+        <v>517</v>
       </c>
       <c r="E1815">
-        <v>1.06317970075069</v>
+        <v>1.104738814821843</v>
       </c>
       <c r="F1815">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1815">
-        <v>0.01136723515437453</v>
+        <v>0.01030996631399156</v>
       </c>
       <c r="H1815">
-        <v>0.01057682029924931</v>
+        <v>0.01029526118517816</v>
       </c>
       <c r="I1815">
-        <v>0.1104148551252235</v>
+        <v>0.1852948711866</v>
       </c>
       <c r="J1815">
-        <v>1.098572817378594</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1815">
-        <v>4.74</v>
+        <v>4.23</v>
       </c>
       <c r="L1815">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="M1815">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="N1815">
-        <v>5.82</v>
+        <v>5.7</v>
       </c>
       <c r="O1815">
         <v>1</v>
       </c>
       <c r="P1815" t="s">
-        <v>629</v>
+        <v>351</v>
       </c>
     </row>
     <row r="1816" spans="1:16">
       <c r="A1816" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1816" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C1816">
-        <v>1.153036982488548</v>
+        <v>0.9527648456254667</v>
       </c>
       <c r="D1816" t="s">
-        <v>517</v>
+        <v>357</v>
       </c>
       <c r="E1816">
-        <v>0.965151157098262</v>
+        <v>1.06317970075069</v>
       </c>
       <c r="F1816">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1816">
-        <v>0.01044696301751145</v>
+        <v>0.01136723515437453</v>
       </c>
       <c r="H1816">
-        <v>0.01043484884290174</v>
+        <v>0.01057682029924931</v>
       </c>
       <c r="I1816">
-        <v>0.1878858253902864</v>
+        <v>0.1104148551252235</v>
       </c>
       <c r="J1816">
         <v>1.098572817378594</v>
       </c>
       <c r="K1816">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="L1816">
-        <v>5.8</v>
+        <v>6.16</v>
       </c>
       <c r="M1816">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1816">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="O1816">
         <v>1</v>
@@ -93063,46 +93063,46 @@
     </row>
     <row r="1817" spans="1:16">
       <c r="A1817" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1817" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C1817">
-        <v>0.9462796035341885</v>
+        <v>1.153036982488548</v>
       </c>
       <c r="D1817" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E1817">
-        <v>1.087693486494396</v>
+        <v>0.965151157098262</v>
       </c>
       <c r="F1817">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1817">
-        <v>0.01061372039646581</v>
+        <v>0.01044696301751145</v>
       </c>
       <c r="H1817">
-        <v>0.01139230651350561</v>
+        <v>0.01043484884290174</v>
       </c>
       <c r="I1817">
-        <v>0.1414138829602072</v>
+        <v>0.1878858253902864</v>
       </c>
       <c r="J1817">
         <v>1.098572817378594</v>
       </c>
       <c r="K1817">
-        <v>4.4</v>
+        <v>4.23</v>
       </c>
       <c r="L1817">
-        <v>5.78</v>
+        <v>5.8</v>
       </c>
       <c r="M1817">
-        <v>4.69</v>
+        <v>4.31</v>
       </c>
       <c r="N1817">
-        <v>6.24</v>
+        <v>5.7</v>
       </c>
       <c r="O1817">
         <v>1</v>
@@ -93113,96 +93113,96 @@
     </row>
     <row r="1818" spans="1:16">
       <c r="A1818" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1818" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C1818">
-        <v>0.8652138986958411</v>
+        <v>0.9462796035341885</v>
       </c>
       <c r="D1818" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E1818">
-        <v>0.9832017260238386</v>
+        <v>1.087693486494396</v>
       </c>
       <c r="F1818">
         <v>1</v>
       </c>
       <c r="G1818">
-        <v>0.01145478610130416</v>
+        <v>0.01061372039646581</v>
       </c>
       <c r="H1818">
-        <v>0.01065679827397616</v>
+        <v>0.01139230651350561</v>
       </c>
       <c r="I1818">
-        <v>0.1179878273279975</v>
+        <v>0.1414138829602072</v>
       </c>
       <c r="J1818">
-        <v>1.117043481287797</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1818">
-        <v>4.74</v>
+        <v>4.4</v>
       </c>
       <c r="L1818">
-        <v>6.16</v>
+        <v>5.78</v>
       </c>
       <c r="M1818">
-        <v>4.33</v>
+        <v>4.69</v>
       </c>
       <c r="N1818">
-        <v>5.82</v>
+        <v>6.24</v>
       </c>
       <c r="O1818">
         <v>1</v>
       </c>
       <c r="P1818" t="s">
-        <v>352</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1819" spans="1:16">
       <c r="A1819" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1819" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C1819">
-        <v>1.074906074152617</v>
+        <v>0.8652138986958411</v>
       </c>
       <c r="D1819" t="s">
-        <v>517</v>
+        <v>357</v>
       </c>
       <c r="E1819">
-        <v>0.8855425956495946</v>
+        <v>0.9832017260238386</v>
       </c>
       <c r="F1819">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1819">
-        <v>0.01052509392584738</v>
+        <v>0.01145478610130416</v>
       </c>
       <c r="H1819">
-        <v>0.01051445740435041</v>
+        <v>0.01065679827397616</v>
       </c>
       <c r="I1819">
-        <v>0.1893634785030223</v>
+        <v>0.1179878273279975</v>
       </c>
       <c r="J1819">
         <v>1.117043481287797</v>
       </c>
       <c r="K1819">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="L1819">
-        <v>5.8</v>
+        <v>6.16</v>
       </c>
       <c r="M1819">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1819">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="O1819">
         <v>1</v>
@@ -93213,51 +93213,101 @@
     </row>
     <row r="1820" spans="1:16">
       <c r="A1820" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1820" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C1820">
-        <v>0.8650086823336922</v>
+        <v>1.074906074152617</v>
       </c>
       <c r="D1820" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E1820">
-        <v>1.001066072760231</v>
+        <v>0.8855425956495946</v>
       </c>
       <c r="F1820">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1820">
-        <v>0.01069499131766631</v>
+        <v>0.01052509392584738</v>
       </c>
       <c r="H1820">
-        <v>0.01147893392723977</v>
+        <v>0.01051445740435041</v>
       </c>
       <c r="I1820">
-        <v>0.1360573904265392</v>
+        <v>0.1893634785030223</v>
       </c>
       <c r="J1820">
         <v>1.117043481287797</v>
       </c>
       <c r="K1820">
+        <v>4.23</v>
+      </c>
+      <c r="L1820">
+        <v>5.8</v>
+      </c>
+      <c r="M1820">
+        <v>4.31</v>
+      </c>
+      <c r="N1820">
+        <v>5.7</v>
+      </c>
+      <c r="O1820">
+        <v>1</v>
+      </c>
+      <c r="P1820" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:16">
+      <c r="A1821" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1821" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1821">
+        <v>0.8650086823336922</v>
+      </c>
+      <c r="D1821" t="s">
+        <v>354</v>
+      </c>
+      <c r="E1821">
+        <v>1.001066072760231</v>
+      </c>
+      <c r="F1821">
+        <v>1</v>
+      </c>
+      <c r="G1821">
+        <v>0.01069499131766631</v>
+      </c>
+      <c r="H1821">
+        <v>0.01147893392723977</v>
+      </c>
+      <c r="I1821">
+        <v>0.1360573904265392</v>
+      </c>
+      <c r="J1821">
+        <v>1.117043481287797</v>
+      </c>
+      <c r="K1821">
         <v>4.4</v>
       </c>
-      <c r="L1820">
+      <c r="L1821">
         <v>5.78</v>
       </c>
-      <c r="M1820">
+      <c r="M1821">
         <v>4.69</v>
       </c>
-      <c r="N1820">
+      <c r="N1821">
         <v>6.24</v>
       </c>
-      <c r="O1820">
-        <v>1</v>
-      </c>
-      <c r="P1820" t="s">
+      <c r="O1821">
+        <v>1</v>
+      </c>
+      <c r="P1821" t="s">
         <v>352</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5478" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5472" uniqueCount="632">
   <si>
     <t>trade_time</t>
   </si>
@@ -1063,10 +1063,7 @@
     <t>2021-07-20</t>
   </si>
   <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
+    <t>2021-07-27</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -1085,6 +1082,9 @@
   </si>
   <si>
     <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
   </si>
   <si>
     <t>2021-10-15</t>
@@ -1564,7 +1564,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-10-19</t>
+    <t>2021-10-20</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -1904,6 +1904,9 @@
   </si>
   <si>
     <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
   </si>
   <si>
     <t>2021-09-08</t>
@@ -2264,7 +2267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1822"/>
+  <dimension ref="A1:P1820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91372,7 +91375,7 @@
         <v>349</v>
       </c>
       <c r="C1783">
-        <v>1.622888121365803</v>
+        <v>1.787560005246361</v>
       </c>
       <c r="D1783" t="s">
         <v>515</v>
@@ -91384,22 +91387,22 @@
         <v>-1</v>
       </c>
       <c r="G1783">
-        <v>0.009857111878634197</v>
+        <v>0.009752439994753639</v>
       </c>
       <c r="H1783">
         <v>0.009284342893367726</v>
       </c>
       <c r="I1783">
-        <v>0.2072310147335288</v>
+        <v>0.3719028986140867</v>
       </c>
       <c r="J1783">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1783">
-        <v>4.28</v>
+        <v>4.14</v>
       </c>
       <c r="L1783">
-        <v>5.74</v>
+        <v>5.77</v>
       </c>
       <c r="M1783">
         <v>4.09</v>
@@ -91422,40 +91425,40 @@
         <v>350</v>
       </c>
       <c r="C1784">
-        <v>1.623544353604688</v>
+        <v>1.67316377388187</v>
       </c>
       <c r="D1784" t="s">
         <v>516</v>
       </c>
       <c r="E1784">
-        <v>1.683820006120755</v>
+        <v>1.69458116556639</v>
       </c>
       <c r="F1784">
         <v>-1</v>
       </c>
       <c r="G1784">
-        <v>0.01039645564639531</v>
+        <v>0.01042683622611813</v>
       </c>
       <c r="H1784">
-        <v>0.01097617999387925</v>
+        <v>0.01102541883443361</v>
       </c>
       <c r="I1784">
-        <v>-0.0602756525160677</v>
+        <v>-0.02141739168451995</v>
       </c>
       <c r="J1784">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1784">
-        <v>4.56</v>
+        <v>4.55</v>
       </c>
       <c r="L1784">
-        <v>6.01</v>
+        <v>6.05</v>
       </c>
       <c r="M1784">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1784">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1784">
         <v>1</v>
@@ -91472,40 +91475,40 @@
         <v>351</v>
       </c>
       <c r="C1785">
-        <v>1.67316377388187</v>
+        <v>1.66887246972413</v>
       </c>
       <c r="D1785" t="s">
         <v>516</v>
       </c>
       <c r="E1785">
-        <v>1.683820006120755</v>
+        <v>1.69458116556639</v>
       </c>
       <c r="F1785">
         <v>-1</v>
       </c>
       <c r="G1785">
-        <v>0.01042683622611813</v>
+        <v>0.01071112753027587</v>
       </c>
       <c r="H1785">
-        <v>0.01097617999387925</v>
+        <v>0.01102541883443361</v>
       </c>
       <c r="I1785">
-        <v>-0.01065623223888501</v>
+        <v>-0.0257086958422601</v>
       </c>
       <c r="J1785">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1785">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="L1785">
-        <v>6.05</v>
+        <v>6.19</v>
       </c>
       <c r="M1785">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1785">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91522,40 +91525,40 @@
         <v>352</v>
       </c>
       <c r="C1786">
-        <v>1.66887246972413</v>
+        <v>1.645827831941592</v>
       </c>
       <c r="D1786" t="s">
         <v>516</v>
       </c>
       <c r="E1786">
-        <v>1.683820006120755</v>
+        <v>1.69458116556639</v>
       </c>
       <c r="F1786">
         <v>-1</v>
       </c>
       <c r="G1786">
-        <v>0.01071112753027587</v>
+        <v>0.01053417216805841</v>
       </c>
       <c r="H1786">
-        <v>0.01097617999387925</v>
+        <v>0.01102541883443361</v>
       </c>
       <c r="I1786">
-        <v>-0.01494753639662516</v>
+        <v>-0.0487533336247985</v>
       </c>
       <c r="J1786">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1786">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="L1786">
-        <v>6.19</v>
+        <v>6.09</v>
       </c>
       <c r="M1786">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1786">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1786">
         <v>1</v>
@@ -91572,40 +91575,40 @@
         <v>353</v>
       </c>
       <c r="C1787">
-        <v>1.645827831941592</v>
+        <v>1.65479101997989</v>
       </c>
       <c r="D1787" t="s">
         <v>516</v>
       </c>
       <c r="E1787">
-        <v>1.683820006120755</v>
+        <v>1.69458116556639</v>
       </c>
       <c r="F1787">
         <v>-1</v>
       </c>
       <c r="G1787">
-        <v>0.01053417216805841</v>
+        <v>0.009985208980020111</v>
       </c>
       <c r="H1787">
-        <v>0.01097617999387925</v>
+        <v>0.01102541883443361</v>
       </c>
       <c r="I1787">
-        <v>-0.03799217417916356</v>
+        <v>-0.03979014558650018</v>
       </c>
       <c r="J1787">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1787">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="L1787">
-        <v>6.09</v>
+        <v>5.82</v>
       </c>
       <c r="M1787">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1787">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91622,40 +91625,40 @@
         <v>354</v>
       </c>
       <c r="C1788">
-        <v>1.65479101997989</v>
+        <v>1.728491890001313</v>
       </c>
       <c r="D1788" t="s">
         <v>516</v>
       </c>
       <c r="E1788">
-        <v>1.683820006120755</v>
+        <v>1.69458116556639</v>
       </c>
       <c r="F1788">
         <v>-1</v>
       </c>
       <c r="G1788">
-        <v>0.009985208980020111</v>
+        <v>0.01075150810999869</v>
       </c>
       <c r="H1788">
-        <v>0.01097617999387925</v>
+        <v>0.01102541883443361</v>
       </c>
       <c r="I1788">
-        <v>-0.02902898614086524</v>
+        <v>0.03391072443492238</v>
       </c>
       <c r="J1788">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1788">
-        <v>4.33</v>
+        <v>4.69</v>
       </c>
       <c r="L1788">
-        <v>5.82</v>
+        <v>6.24</v>
       </c>
       <c r="M1788">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1788">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91666,63 +91669,63 @@
     </row>
     <row r="1789" spans="1:16">
       <c r="A1789" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B1789" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="C1789">
-        <v>1.728491890001313</v>
+        <v>0.9728076429396824</v>
       </c>
       <c r="D1789" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E1789">
-        <v>1.683820006120755</v>
+        <v>1.250284657677777</v>
       </c>
       <c r="F1789">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1789">
-        <v>0.01075150810999869</v>
+        <v>0.01222719235706032</v>
       </c>
       <c r="H1789">
-        <v>0.01097617999387925</v>
+        <v>0.01066971534232222</v>
       </c>
       <c r="I1789">
-        <v>0.04467188388055732</v>
+        <v>0.2774770147380945</v>
       </c>
       <c r="J1789">
-        <v>0.9619420277182702</v>
+        <v>1.01941890526455</v>
       </c>
       <c r="K1789">
-        <v>4.69</v>
+        <v>5.52</v>
       </c>
       <c r="L1789">
-        <v>6.24</v>
+        <v>6.6</v>
       </c>
       <c r="M1789">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="N1789">
-        <v>6.33</v>
+        <v>5.96</v>
       </c>
       <c r="O1789">
         <v>1</v>
       </c>
       <c r="P1789" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="1790" spans="1:16">
       <c r="A1790" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1790" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1790">
-        <v>0.9728076429396824</v>
+        <v>0.9472739911505288</v>
       </c>
       <c r="D1790" t="s">
         <v>514</v>
@@ -91734,22 +91737,22 @@
         <v>1</v>
       </c>
       <c r="G1790">
-        <v>0.01222719235706032</v>
+        <v>0.01173272600884947</v>
       </c>
       <c r="H1790">
         <v>0.01066971534232222</v>
       </c>
       <c r="I1790">
-        <v>0.2774770147380945</v>
+        <v>0.3030106665272481</v>
       </c>
       <c r="J1790">
         <v>1.01941890526455</v>
       </c>
       <c r="K1790">
-        <v>5.52</v>
+        <v>5.29</v>
       </c>
       <c r="L1790">
-        <v>6.6</v>
+        <v>6.34</v>
       </c>
       <c r="M1790">
         <v>4.62</v>
@@ -91766,46 +91769,46 @@
     </row>
     <row r="1791" spans="1:16">
       <c r="A1791" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1791" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C1791">
-        <v>0.9472739911505288</v>
+        <v>1.402614926309523</v>
       </c>
       <c r="D1791" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E1791">
-        <v>1.250284657677777</v>
+        <v>1.180576677467989</v>
       </c>
       <c r="F1791">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1791">
-        <v>0.01173272600884947</v>
+        <v>0.01057738507369048</v>
       </c>
       <c r="H1791">
-        <v>0.01066971534232222</v>
+        <v>0.009519423322532011</v>
       </c>
       <c r="I1791">
-        <v>0.3030106665272481</v>
+        <v>0.2220382488415344</v>
       </c>
       <c r="J1791">
         <v>1.01941890526455</v>
       </c>
       <c r="K1791">
-        <v>5.29</v>
+        <v>4.5</v>
       </c>
       <c r="L1791">
-        <v>6.34</v>
+        <v>5.99</v>
       </c>
       <c r="M1791">
-        <v>4.62</v>
+        <v>4.09</v>
       </c>
       <c r="N1791">
-        <v>5.96</v>
+        <v>5.35</v>
       </c>
       <c r="O1791">
         <v>1</v>
@@ -91816,13 +91819,13 @@
     </row>
     <row r="1792" spans="1:16">
       <c r="A1792" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1792" t="s">
         <v>356</v>
       </c>
       <c r="C1792">
-        <v>1.402614926309523</v>
+        <v>1.376887085467724</v>
       </c>
       <c r="D1792" t="s">
         <v>515</v>
@@ -91834,22 +91837,22 @@
         <v>-1</v>
       </c>
       <c r="G1792">
-        <v>0.01057738507369048</v>
+        <v>0.01010311291453228</v>
       </c>
       <c r="H1792">
         <v>0.009519423322532011</v>
       </c>
       <c r="I1792">
-        <v>0.2220382488415344</v>
+        <v>0.1963104079997358</v>
       </c>
       <c r="J1792">
         <v>1.01941890526455</v>
       </c>
       <c r="K1792">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="L1792">
-        <v>5.99</v>
+        <v>5.74</v>
       </c>
       <c r="M1792">
         <v>4.09</v>
@@ -91866,46 +91869,46 @@
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1793" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C1793">
-        <v>1.376887085467724</v>
+        <v>1.411643981046296</v>
       </c>
       <c r="D1793" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E1793">
-        <v>1.180576677467989</v>
+        <v>1.415818309466931</v>
       </c>
       <c r="F1793">
         <v>-1</v>
       </c>
       <c r="G1793">
-        <v>0.01010311291453228</v>
+        <v>0.0106883560189537</v>
       </c>
       <c r="H1793">
-        <v>0.009519423322532011</v>
+        <v>0.01130418169053307</v>
       </c>
       <c r="I1793">
-        <v>0.1963104079997358</v>
+        <v>-0.004174328420635476</v>
       </c>
       <c r="J1793">
         <v>1.01941890526455</v>
       </c>
       <c r="K1793">
-        <v>4.28</v>
+        <v>4.55</v>
       </c>
       <c r="L1793">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="M1793">
-        <v>4.09</v>
+        <v>4.85</v>
       </c>
       <c r="N1793">
-        <v>5.35</v>
+        <v>6.36</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -91916,46 +91919,46 @@
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1794" t="s">
         <v>351</v>
       </c>
       <c r="C1794">
-        <v>1.411643981046296</v>
+        <v>1.398731145256614</v>
       </c>
       <c r="D1794" t="s">
         <v>516</v>
       </c>
       <c r="E1794">
-        <v>1.406206687572221</v>
+        <v>1.415818309466931</v>
       </c>
       <c r="F1794">
         <v>-1</v>
       </c>
       <c r="G1794">
-        <v>0.0106883560189537</v>
+        <v>0.01098126885474339</v>
       </c>
       <c r="H1794">
-        <v>0.01125379331242778</v>
+        <v>0.01130418169053307</v>
       </c>
       <c r="I1794">
-        <v>0.005437293474074067</v>
+        <v>-0.01708716421031742</v>
       </c>
       <c r="J1794">
         <v>1.01941890526455</v>
       </c>
       <c r="K1794">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="L1794">
-        <v>6.05</v>
+        <v>6.19</v>
       </c>
       <c r="M1794">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1794">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1794">
         <v>1</v>
@@ -91966,46 +91969,46 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1795" t="s">
         <v>352</v>
       </c>
       <c r="C1795">
-        <v>1.398731145256614</v>
+        <v>1.380284657677777</v>
       </c>
       <c r="D1795" t="s">
         <v>516</v>
       </c>
       <c r="E1795">
-        <v>1.406206687572221</v>
+        <v>1.415818309466931</v>
       </c>
       <c r="F1795">
         <v>-1</v>
       </c>
       <c r="G1795">
-        <v>0.01098126885474339</v>
+        <v>0.01079971534232222</v>
       </c>
       <c r="H1795">
-        <v>0.01125379331242778</v>
+        <v>0.01130418169053307</v>
       </c>
       <c r="I1795">
-        <v>-0.007475542315607875</v>
+        <v>-0.03553365178915424</v>
       </c>
       <c r="J1795">
         <v>1.01941890526455</v>
       </c>
       <c r="K1795">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="L1795">
-        <v>6.19</v>
+        <v>6.09</v>
       </c>
       <c r="M1795">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1795">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -92016,46 +92019,46 @@
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1796" t="s">
         <v>353</v>
       </c>
       <c r="C1796">
-        <v>1.380284657677777</v>
+        <v>1.405916140204497</v>
       </c>
       <c r="D1796" t="s">
         <v>516</v>
       </c>
       <c r="E1796">
-        <v>1.406206687572221</v>
+        <v>1.415818309466931</v>
       </c>
       <c r="F1796">
         <v>-1</v>
       </c>
       <c r="G1796">
-        <v>0.01079971534232222</v>
+        <v>0.0102340838597955</v>
       </c>
       <c r="H1796">
-        <v>0.01125379331242778</v>
+        <v>0.01130418169053307</v>
       </c>
       <c r="I1796">
-        <v>-0.0259220298944447</v>
+        <v>-0.009902169262433702</v>
       </c>
       <c r="J1796">
         <v>1.01941890526455</v>
       </c>
       <c r="K1796">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="L1796">
-        <v>6.09</v>
+        <v>5.82</v>
       </c>
       <c r="M1796">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1796">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92066,46 +92069,46 @@
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1797" t="s">
         <v>354</v>
       </c>
       <c r="C1797">
-        <v>1.405916140204497</v>
+        <v>1.458925334309258</v>
       </c>
       <c r="D1797" t="s">
         <v>516</v>
       </c>
       <c r="E1797">
-        <v>1.406206687572221</v>
+        <v>1.415818309466931</v>
       </c>
       <c r="F1797">
         <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.0102340838597955</v>
+        <v>0.01102107466569074</v>
       </c>
       <c r="H1797">
-        <v>0.01125379331242778</v>
+        <v>0.01130418169053307</v>
       </c>
       <c r="I1797">
-        <v>-0.0002905473677241588</v>
+        <v>0.04310702484232731</v>
       </c>
       <c r="J1797">
         <v>1.01941890526455</v>
       </c>
       <c r="K1797">
-        <v>4.33</v>
+        <v>4.69</v>
       </c>
       <c r="L1797">
-        <v>5.82</v>
+        <v>6.24</v>
       </c>
       <c r="M1797">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1797">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92116,46 +92119,46 @@
     </row>
     <row r="1798" spans="1:16">
       <c r="A1798" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1798" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C1798">
-        <v>1.458925334309258</v>
+        <v>1.506206687572221</v>
       </c>
       <c r="D1798" t="s">
         <v>516</v>
       </c>
       <c r="E1798">
-        <v>1.406206687572221</v>
+        <v>1.415818309466931</v>
       </c>
       <c r="F1798">
         <v>-1</v>
       </c>
       <c r="G1798">
-        <v>0.01102107466569074</v>
+        <v>0.01135379331242778</v>
       </c>
       <c r="H1798">
-        <v>0.01125379331242778</v>
+        <v>0.01130418169053307</v>
       </c>
       <c r="I1798">
-        <v>0.05271864673703686</v>
+        <v>0.0903883781052901</v>
       </c>
       <c r="J1798">
         <v>1.01941890526455</v>
       </c>
       <c r="K1798">
-        <v>4.69</v>
+        <v>4.83</v>
       </c>
       <c r="L1798">
-        <v>6.24</v>
+        <v>6.43</v>
       </c>
       <c r="M1798">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1798">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92166,96 +92169,96 @@
     </row>
     <row r="1799" spans="1:16">
       <c r="A1799" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B1799" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C1799">
-        <v>1.506206687572221</v>
+        <v>0.7149171399855092</v>
       </c>
       <c r="D1799" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E1799">
-        <v>1.406206687572221</v>
+        <v>0.9905546595610417</v>
       </c>
       <c r="F1799">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1799">
-        <v>0.01135379331242778</v>
+        <v>0.01280508286001449</v>
       </c>
       <c r="H1799">
-        <v>0.01125379331242778</v>
+        <v>0.01092944534043896</v>
       </c>
       <c r="I1799">
-        <v>0.09999999999999964</v>
+        <v>0.2756375195755325</v>
       </c>
       <c r="J1799">
-        <v>1.01941890526455</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1799">
-        <v>4.83</v>
+        <v>5.62</v>
       </c>
       <c r="L1799">
-        <v>6.43</v>
+        <v>6.76</v>
       </c>
       <c r="M1799">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="N1799">
-        <v>6.33</v>
+        <v>5.96</v>
       </c>
       <c r="O1799">
         <v>1</v>
       </c>
       <c r="P1799" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1800" spans="1:16">
       <c r="A1800" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1800" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C1800">
-        <v>0.7149171399855092</v>
+        <v>1.149631161910106</v>
       </c>
       <c r="D1800" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E1800">
-        <v>0.9905546595610417</v>
+        <v>0.8798861697403186</v>
       </c>
       <c r="F1800">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1800">
-        <v>0.01280508286001449</v>
+        <v>0.01083036883808989</v>
       </c>
       <c r="H1800">
-        <v>0.01092944534043896</v>
+        <v>0.009700113830259682</v>
       </c>
       <c r="I1800">
-        <v>0.2756375195755325</v>
+        <v>0.2697449921697874</v>
       </c>
       <c r="J1800">
         <v>1.075637519575532</v>
       </c>
       <c r="K1800">
-        <v>5.62</v>
+        <v>4.5</v>
       </c>
       <c r="L1800">
-        <v>6.76</v>
+        <v>5.99</v>
       </c>
       <c r="M1800">
-        <v>4.62</v>
+        <v>4.1</v>
       </c>
       <c r="N1800">
-        <v>5.96</v>
+        <v>5.29</v>
       </c>
       <c r="O1800">
         <v>1</v>
@@ -92266,13 +92269,13 @@
     </row>
     <row r="1801" spans="1:16">
       <c r="A1801" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1801" t="s">
         <v>356</v>
       </c>
       <c r="C1801">
-        <v>1.149631161910106</v>
+        <v>1.136271416216722</v>
       </c>
       <c r="D1801" t="s">
         <v>517</v>
@@ -92284,22 +92287,22 @@
         <v>-1</v>
       </c>
       <c r="G1801">
-        <v>0.01083036883808989</v>
+        <v>0.01034372858378328</v>
       </c>
       <c r="H1801">
         <v>0.009700113830259682</v>
       </c>
       <c r="I1801">
-        <v>0.2697449921697874</v>
+        <v>0.2563852464764036</v>
       </c>
       <c r="J1801">
         <v>1.075637519575532</v>
       </c>
       <c r="K1801">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="L1801">
-        <v>5.99</v>
+        <v>5.74</v>
       </c>
       <c r="M1801">
         <v>4.1</v>
@@ -92316,46 +92319,46 @@
     </row>
     <row r="1802" spans="1:16">
       <c r="A1802" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1802" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C1802">
-        <v>1.136271416216722</v>
+        <v>1.155849285931329</v>
       </c>
       <c r="D1802" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1802">
-        <v>0.8798861697403186</v>
+        <v>1.14315803005867</v>
       </c>
       <c r="F1802">
         <v>-1</v>
       </c>
       <c r="G1802">
-        <v>0.01034372858378328</v>
+        <v>0.01094415071406867</v>
       </c>
       <c r="H1802">
-        <v>0.009700113830259682</v>
+        <v>0.01157684196994133</v>
       </c>
       <c r="I1802">
-        <v>0.2563852464764036</v>
+        <v>0.01269125587265929</v>
       </c>
       <c r="J1802">
         <v>1.075637519575532</v>
       </c>
       <c r="K1802">
-        <v>4.28</v>
+        <v>4.55</v>
       </c>
       <c r="L1802">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="M1802">
-        <v>4.1</v>
+        <v>4.85</v>
       </c>
       <c r="N1802">
-        <v>5.29</v>
+        <v>6.36</v>
       </c>
       <c r="O1802">
         <v>1</v>
@@ -92366,46 +92369,46 @@
     </row>
     <row r="1803" spans="1:16">
       <c r="A1803" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1803" t="s">
         <v>351</v>
       </c>
       <c r="C1803">
-        <v>1.155849285931329</v>
+        <v>1.134503657994999</v>
       </c>
       <c r="D1803" t="s">
         <v>516</v>
       </c>
       <c r="E1803">
-        <v>1.13467078045018</v>
+        <v>1.14315803005867</v>
       </c>
       <c r="F1803">
         <v>-1</v>
       </c>
       <c r="G1803">
-        <v>0.01094415071406867</v>
+        <v>0.011245496342005</v>
       </c>
       <c r="H1803">
-        <v>0.01152532921954982</v>
+        <v>0.01157684196994133</v>
       </c>
       <c r="I1803">
-        <v>0.0211785054811493</v>
+        <v>-0.008654372063670479</v>
       </c>
       <c r="J1803">
         <v>1.075637519575532</v>
       </c>
       <c r="K1803">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="L1803">
-        <v>6.05</v>
+        <v>6.19</v>
       </c>
       <c r="M1803">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1803">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1803">
         <v>1</v>
@@ -92416,46 +92419,46 @@
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1804" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C1804">
-        <v>1.134503657994999</v>
+        <v>1.162489540237946</v>
       </c>
       <c r="D1804" t="s">
         <v>516</v>
       </c>
       <c r="E1804">
-        <v>1.13467078045018</v>
+        <v>1.14315803005867</v>
       </c>
       <c r="F1804">
         <v>-1</v>
       </c>
       <c r="G1804">
-        <v>0.011245496342005</v>
+        <v>0.01047751045976206</v>
       </c>
       <c r="H1804">
-        <v>0.01152532921954982</v>
+        <v>0.01157684196994133</v>
       </c>
       <c r="I1804">
-        <v>-0.0001671224551804684</v>
+        <v>0.01933151017927592</v>
       </c>
       <c r="J1804">
         <v>1.075637519575532</v>
       </c>
       <c r="K1804">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="L1804">
-        <v>6.19</v>
+        <v>5.82</v>
       </c>
       <c r="M1804">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1804">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1804">
         <v>1</v>
@@ -92466,46 +92469,46 @@
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1805" t="s">
         <v>354</v>
       </c>
       <c r="C1805">
-        <v>1.162489540237946</v>
+        <v>1.195260033190754</v>
       </c>
       <c r="D1805" t="s">
         <v>516</v>
       </c>
       <c r="E1805">
-        <v>1.13467078045018</v>
+        <v>1.14315803005867</v>
       </c>
       <c r="F1805">
         <v>-1</v>
       </c>
       <c r="G1805">
-        <v>0.01047751045976206</v>
+        <v>0.01128473996680925</v>
       </c>
       <c r="H1805">
-        <v>0.01152532921954982</v>
+        <v>0.01157684196994133</v>
       </c>
       <c r="I1805">
-        <v>0.02781875978776593</v>
+        <v>0.05210200313208446</v>
       </c>
       <c r="J1805">
         <v>1.075637519575532</v>
       </c>
       <c r="K1805">
-        <v>4.33</v>
+        <v>4.69</v>
       </c>
       <c r="L1805">
-        <v>5.82</v>
+        <v>6.24</v>
       </c>
       <c r="M1805">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1805">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1805">
         <v>1</v>
@@ -92516,46 +92519,46 @@
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1806" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C1806">
-        <v>1.195260033190754</v>
+        <v>1.23467078045018</v>
       </c>
       <c r="D1806" t="s">
         <v>516</v>
       </c>
       <c r="E1806">
-        <v>1.13467078045018</v>
+        <v>1.14315803005867</v>
       </c>
       <c r="F1806">
         <v>-1</v>
       </c>
       <c r="G1806">
-        <v>0.01128473996680925</v>
+        <v>0.01162532921954982</v>
       </c>
       <c r="H1806">
-        <v>0.01152532921954982</v>
+        <v>0.01157684196994133</v>
       </c>
       <c r="I1806">
-        <v>0.06058925274057447</v>
+        <v>0.09151275039150963</v>
       </c>
       <c r="J1806">
         <v>1.075637519575532</v>
       </c>
       <c r="K1806">
-        <v>4.69</v>
+        <v>4.83</v>
       </c>
       <c r="L1806">
-        <v>6.24</v>
+        <v>6.43</v>
       </c>
       <c r="M1806">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1806">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92566,63 +92569,63 @@
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1807" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C1807">
-        <v>1.23467078045018</v>
+        <v>1.088452388565583</v>
       </c>
       <c r="D1807" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E1807">
-        <v>1.13467078045018</v>
+        <v>0.8241455095819763</v>
       </c>
       <c r="F1807">
         <v>-1</v>
       </c>
       <c r="G1807">
-        <v>0.01162532921954982</v>
+        <v>0.01089154761143442</v>
       </c>
       <c r="H1807">
-        <v>0.01152532921954982</v>
+        <v>0.009755854490418023</v>
       </c>
       <c r="I1807">
-        <v>0.09999999999999964</v>
+        <v>0.2643068789836072</v>
       </c>
       <c r="J1807">
-        <v>1.075637519575532</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1807">
-        <v>4.83</v>
+        <v>4.5</v>
       </c>
       <c r="L1807">
-        <v>6.43</v>
+        <v>5.99</v>
       </c>
       <c r="M1807">
-        <v>4.83</v>
+        <v>4.1</v>
       </c>
       <c r="N1807">
-        <v>6.33</v>
+        <v>5.29</v>
       </c>
       <c r="O1807">
         <v>1</v>
       </c>
       <c r="P1807" t="s">
-        <v>629</v>
+        <v>358</v>
       </c>
     </row>
     <row r="1808" spans="1:16">
       <c r="A1808" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1808" t="s">
         <v>356</v>
       </c>
       <c r="C1808">
-        <v>1.088452388565583</v>
+        <v>1.0780836051246</v>
       </c>
       <c r="D1808" t="s">
         <v>517</v>
@@ -92634,22 +92637,22 @@
         <v>-1</v>
       </c>
       <c r="G1808">
-        <v>0.01089154761143442</v>
+        <v>0.0104019163948754</v>
       </c>
       <c r="H1808">
         <v>0.009755854490418023</v>
       </c>
       <c r="I1808">
-        <v>0.2643068789836072</v>
+        <v>0.2539380955426234</v>
       </c>
       <c r="J1808">
         <v>1.089232802540981</v>
       </c>
       <c r="K1808">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="L1808">
-        <v>5.99</v>
+        <v>5.74</v>
       </c>
       <c r="M1808">
         <v>4.1</v>
@@ -92666,46 +92669,46 @@
     </row>
     <row r="1809" spans="1:16">
       <c r="A1809" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1809" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C1809">
-        <v>1.0780836051246</v>
+        <v>1.093990748438535</v>
       </c>
       <c r="D1809" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1809">
-        <v>0.8241455095819763</v>
+        <v>1.07722090767624</v>
       </c>
       <c r="F1809">
         <v>-1</v>
       </c>
       <c r="G1809">
-        <v>0.0104019163948754</v>
+        <v>0.01100600925156146</v>
       </c>
       <c r="H1809">
-        <v>0.009755854490418023</v>
+        <v>0.01164277909232376</v>
       </c>
       <c r="I1809">
-        <v>0.2539380955426234</v>
+        <v>0.01676984076229449</v>
       </c>
       <c r="J1809">
         <v>1.089232802540981</v>
       </c>
       <c r="K1809">
-        <v>4.28</v>
+        <v>4.55</v>
       </c>
       <c r="L1809">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="M1809">
-        <v>4.1</v>
+        <v>4.85</v>
       </c>
       <c r="N1809">
-        <v>5.29</v>
+        <v>6.36</v>
       </c>
       <c r="O1809">
         <v>1</v>
@@ -92716,46 +92719,46 @@
     </row>
     <row r="1810" spans="1:16">
       <c r="A1810" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1810" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C1810">
-        <v>1.093990748438535</v>
+        <v>1.103621964997551</v>
       </c>
       <c r="D1810" t="s">
         <v>516</v>
       </c>
       <c r="E1810">
-        <v>1.069005563727059</v>
+        <v>1.07722090767624</v>
       </c>
       <c r="F1810">
         <v>-1</v>
       </c>
       <c r="G1810">
-        <v>0.01100600925156146</v>
+        <v>0.01053637803500245</v>
       </c>
       <c r="H1810">
-        <v>0.01159099443627294</v>
+        <v>0.01164277909232376</v>
       </c>
       <c r="I1810">
-        <v>0.02498518471147548</v>
+        <v>0.02640105732131026</v>
       </c>
       <c r="J1810">
         <v>1.089232802540981</v>
       </c>
       <c r="K1810">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="L1810">
-        <v>6.05</v>
+        <v>5.82</v>
       </c>
       <c r="M1810">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1810">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1810">
         <v>1</v>
@@ -92766,46 +92769,46 @@
     </row>
     <row r="1811" spans="1:16">
       <c r="A1811" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1811" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C1811">
-        <v>1.070605828057388</v>
+        <v>1.131498156082797</v>
       </c>
       <c r="D1811" t="s">
         <v>516</v>
       </c>
       <c r="E1811">
-        <v>1.069005563727059</v>
+        <v>1.07722090767624</v>
       </c>
       <c r="F1811">
         <v>-1</v>
       </c>
       <c r="G1811">
-        <v>0.01130939417194262</v>
+        <v>0.0113485018439172</v>
       </c>
       <c r="H1811">
-        <v>0.01159099443627294</v>
+        <v>0.01164277909232376</v>
       </c>
       <c r="I1811">
-        <v>0.001600264330328116</v>
+        <v>0.05427724840655657</v>
       </c>
       <c r="J1811">
         <v>1.089232802540981</v>
       </c>
       <c r="K1811">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="L1811">
-        <v>6.19</v>
+        <v>6.24</v>
       </c>
       <c r="M1811">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1811">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1811">
         <v>1</v>
@@ -92816,46 +92819,46 @@
     </row>
     <row r="1812" spans="1:16">
       <c r="A1812" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1812" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C1812">
-        <v>1.103621964997551</v>
+        <v>1.169005563727059</v>
       </c>
       <c r="D1812" t="s">
         <v>516</v>
       </c>
       <c r="E1812">
-        <v>1.069005563727059</v>
+        <v>1.07722090767624</v>
       </c>
       <c r="F1812">
         <v>-1</v>
       </c>
       <c r="G1812">
-        <v>0.01053637803500245</v>
+        <v>0.01169099443627294</v>
       </c>
       <c r="H1812">
-        <v>0.01159099443627294</v>
+        <v>0.01164277909232376</v>
       </c>
       <c r="I1812">
-        <v>0.03461640127049126</v>
+        <v>0.09178465605081865</v>
       </c>
       <c r="J1812">
         <v>1.089232802540981</v>
       </c>
       <c r="K1812">
-        <v>4.33</v>
+        <v>4.83</v>
       </c>
       <c r="L1812">
-        <v>5.82</v>
+        <v>6.43</v>
       </c>
       <c r="M1812">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="N1812">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="O1812">
         <v>1</v>
@@ -92866,102 +92869,102 @@
     </row>
     <row r="1813" spans="1:16">
       <c r="A1813" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1813" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C1813">
-        <v>1.131498156082797</v>
+        <v>1.437331032547627</v>
       </c>
       <c r="D1813" t="s">
-        <v>516</v>
+        <v>350</v>
       </c>
       <c r="E1813">
-        <v>1.069005563727059</v>
+        <v>1.527152008316966</v>
       </c>
       <c r="F1813">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1813">
-        <v>0.0113485018439172</v>
+        <v>0.01054266896745237</v>
       </c>
       <c r="H1813">
-        <v>0.01159099443627294</v>
+        <v>0.01057284799168303</v>
       </c>
       <c r="I1813">
-        <v>0.06249259235573756</v>
+        <v>0.08982097576933867</v>
       </c>
       <c r="J1813">
-        <v>1.089232802540981</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1813">
-        <v>4.69</v>
+        <v>4.58</v>
       </c>
       <c r="L1813">
-        <v>6.24</v>
+        <v>5.99</v>
       </c>
       <c r="M1813">
-        <v>4.83</v>
+        <v>4.55</v>
       </c>
       <c r="N1813">
-        <v>6.33</v>
+        <v>6.05</v>
       </c>
       <c r="O1813">
         <v>1</v>
       </c>
       <c r="P1813" t="s">
-        <v>358</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1814" spans="1:16">
       <c r="A1814" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B1814" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C1814">
-        <v>1.169005563727059</v>
+        <v>1.595242416523244</v>
       </c>
       <c r="D1814" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E1814">
-        <v>1.069005563727059</v>
+        <v>1.415719814471675</v>
       </c>
       <c r="F1814">
         <v>-1</v>
       </c>
       <c r="G1814">
-        <v>0.01169099443627294</v>
+        <v>0.01000475758347676</v>
       </c>
       <c r="H1814">
-        <v>0.01159099443627294</v>
+        <v>0.009984280185528325</v>
       </c>
       <c r="I1814">
-        <v>0.09999999999999964</v>
+        <v>0.179522602051569</v>
       </c>
       <c r="J1814">
-        <v>1.089232802540981</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1814">
-        <v>4.83</v>
+        <v>4.23</v>
       </c>
       <c r="L1814">
-        <v>6.43</v>
+        <v>5.8</v>
       </c>
       <c r="M1814">
-        <v>4.83</v>
+        <v>4.31</v>
       </c>
       <c r="N1814">
-        <v>6.33</v>
+        <v>5.7</v>
       </c>
       <c r="O1814">
         <v>1</v>
       </c>
       <c r="P1814" t="s">
-        <v>358</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1815" spans="1:16">
@@ -92969,43 +92972,43 @@
         <v>0</v>
       </c>
       <c r="B1815" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C1815">
-        <v>1.437331032547627</v>
+        <v>1.106278882193859</v>
       </c>
       <c r="D1815" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E1815">
-        <v>1.527152008316966</v>
+        <v>1.203415097025192</v>
       </c>
       <c r="F1815">
         <v>1</v>
       </c>
       <c r="G1815">
-        <v>0.01054266896745237</v>
+        <v>0.01121372111780614</v>
       </c>
       <c r="H1815">
-        <v>0.01057284799168303</v>
+        <v>0.01043658490297481</v>
       </c>
       <c r="I1815">
-        <v>0.08982097576933867</v>
+        <v>0.09713621483133306</v>
       </c>
       <c r="J1815">
-        <v>0.994032525644623</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1815">
-        <v>4.58</v>
+        <v>4.74</v>
       </c>
       <c r="L1815">
-        <v>5.99</v>
+        <v>6.16</v>
       </c>
       <c r="M1815">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="N1815">
-        <v>6.05</v>
+        <v>5.82</v>
       </c>
       <c r="O1815">
         <v>1</v>
@@ -93022,28 +93025,28 @@
         <v>360</v>
       </c>
       <c r="C1816">
-        <v>1.595242416523244</v>
+        <v>1.290033686008443</v>
       </c>
       <c r="D1816" t="s">
         <v>518</v>
       </c>
       <c r="E1816">
-        <v>1.415719814471675</v>
+        <v>1.104738814821843</v>
       </c>
       <c r="F1816">
         <v>-1</v>
       </c>
       <c r="G1816">
-        <v>0.01000475758347676</v>
+        <v>0.01030996631399156</v>
       </c>
       <c r="H1816">
-        <v>0.009984280185528325</v>
+        <v>0.01029526118517816</v>
       </c>
       <c r="I1816">
-        <v>0.179522602051569</v>
+        <v>0.1852948711866</v>
       </c>
       <c r="J1816">
-        <v>0.994032525644623</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1816">
         <v>4.23</v>
@@ -93072,28 +93075,28 @@
         <v>361</v>
       </c>
       <c r="C1817">
-        <v>1.106278882193859</v>
+        <v>0.9527648456254667</v>
       </c>
       <c r="D1817" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1817">
-        <v>1.203415097025192</v>
+        <v>1.06317970075069</v>
       </c>
       <c r="F1817">
         <v>1</v>
       </c>
       <c r="G1817">
-        <v>0.01121372111780614</v>
+        <v>0.01136723515437453</v>
       </c>
       <c r="H1817">
-        <v>0.01043658490297481</v>
+        <v>0.01057682029924931</v>
       </c>
       <c r="I1817">
-        <v>0.09713621483133306</v>
+        <v>0.1104148551252235</v>
       </c>
       <c r="J1817">
-        <v>1.066185889832519</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1817">
         <v>4.74</v>
@@ -93111,7 +93114,7 @@
         <v>1</v>
       </c>
       <c r="P1817" t="s">
-        <v>351</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1818" spans="1:16">
@@ -93122,28 +93125,28 @@
         <v>360</v>
       </c>
       <c r="C1818">
-        <v>1.290033686008443</v>
+        <v>1.153036982488548</v>
       </c>
       <c r="D1818" t="s">
         <v>518</v>
       </c>
       <c r="E1818">
-        <v>1.104738814821843</v>
+        <v>0.965151157098262</v>
       </c>
       <c r="F1818">
         <v>-1</v>
       </c>
       <c r="G1818">
-        <v>0.01030996631399156</v>
+        <v>0.01044696301751145</v>
       </c>
       <c r="H1818">
-        <v>0.01029526118517816</v>
+        <v>0.01043484884290174</v>
       </c>
       <c r="I1818">
-        <v>0.1852948711866</v>
+        <v>0.1878858253902864</v>
       </c>
       <c r="J1818">
-        <v>1.066185889832519</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1818">
         <v>4.23</v>
@@ -93161,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="P1818" t="s">
-        <v>351</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1819" spans="1:16">
@@ -93172,28 +93175,28 @@
         <v>361</v>
       </c>
       <c r="C1819">
-        <v>0.9527648456254667</v>
+        <v>0.8652138986958411</v>
       </c>
       <c r="D1819" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1819">
-        <v>1.06317970075069</v>
+        <v>0.9832017260238386</v>
       </c>
       <c r="F1819">
         <v>1</v>
       </c>
       <c r="G1819">
-        <v>0.01136723515437453</v>
+        <v>0.01145478610130416</v>
       </c>
       <c r="H1819">
-        <v>0.01057682029924931</v>
+        <v>0.01065679827397616</v>
       </c>
       <c r="I1819">
-        <v>0.1104148551252235</v>
+        <v>0.1179878273279975</v>
       </c>
       <c r="J1819">
-        <v>1.098572817378594</v>
+        <v>1.117043481287797</v>
       </c>
       <c r="K1819">
         <v>4.74</v>
@@ -93211,7 +93214,7 @@
         <v>1</v>
       </c>
       <c r="P1819" t="s">
-        <v>630</v>
+        <v>351</v>
       </c>
     </row>
     <row r="1820" spans="1:16">
@@ -93222,28 +93225,28 @@
         <v>360</v>
       </c>
       <c r="C1820">
-        <v>1.153036982488548</v>
+        <v>1.074906074152617</v>
       </c>
       <c r="D1820" t="s">
         <v>518</v>
       </c>
       <c r="E1820">
-        <v>0.965151157098262</v>
+        <v>0.8855425956495946</v>
       </c>
       <c r="F1820">
         <v>-1</v>
       </c>
       <c r="G1820">
-        <v>0.01044696301751145</v>
+        <v>0.01052509392584738</v>
       </c>
       <c r="H1820">
-        <v>0.01043484884290174</v>
+        <v>0.01051445740435041</v>
       </c>
       <c r="I1820">
-        <v>0.1878858253902864</v>
+        <v>0.1893634785030223</v>
       </c>
       <c r="J1820">
-        <v>1.098572817378594</v>
+        <v>1.117043481287797</v>
       </c>
       <c r="K1820">
         <v>4.23</v>
@@ -93261,107 +93264,7 @@
         <v>1</v>
       </c>
       <c r="P1820" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="1821" spans="1:16">
-      <c r="A1821" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1821" t="s">
-        <v>361</v>
-      </c>
-      <c r="C1821">
-        <v>0.8652138986958411</v>
-      </c>
-      <c r="D1821" t="s">
-        <v>354</v>
-      </c>
-      <c r="E1821">
-        <v>0.9832017260238386</v>
-      </c>
-      <c r="F1821">
-        <v>1</v>
-      </c>
-      <c r="G1821">
-        <v>0.01145478610130416</v>
-      </c>
-      <c r="H1821">
-        <v>0.01065679827397616</v>
-      </c>
-      <c r="I1821">
-        <v>0.1179878273279975</v>
-      </c>
-      <c r="J1821">
-        <v>1.117043481287797</v>
-      </c>
-      <c r="K1821">
-        <v>4.74</v>
-      </c>
-      <c r="L1821">
-        <v>6.16</v>
-      </c>
-      <c r="M1821">
-        <v>4.33</v>
-      </c>
-      <c r="N1821">
-        <v>5.82</v>
-      </c>
-      <c r="O1821">
-        <v>1</v>
-      </c>
-      <c r="P1821" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="1822" spans="1:16">
-      <c r="A1822" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1822" t="s">
-        <v>360</v>
-      </c>
-      <c r="C1822">
-        <v>1.074906074152617</v>
-      </c>
-      <c r="D1822" t="s">
-        <v>518</v>
-      </c>
-      <c r="E1822">
-        <v>0.8855425956495946</v>
-      </c>
-      <c r="F1822">
-        <v>-1</v>
-      </c>
-      <c r="G1822">
-        <v>0.01052509392584738</v>
-      </c>
-      <c r="H1822">
-        <v>0.01051445740435041</v>
-      </c>
-      <c r="I1822">
-        <v>0.1893634785030223</v>
-      </c>
-      <c r="J1822">
-        <v>1.117043481287797</v>
-      </c>
-      <c r="K1822">
-        <v>4.23</v>
-      </c>
-      <c r="L1822">
-        <v>5.8</v>
-      </c>
-      <c r="M1822">
-        <v>4.31</v>
-      </c>
-      <c r="N1822">
-        <v>5.7</v>
-      </c>
-      <c r="O1822">
-        <v>1</v>
-      </c>
-      <c r="P1822" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5472" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5475" uniqueCount="632">
   <si>
     <t>trade_time</t>
   </si>
@@ -1060,7 +1060,7 @@
     <t>2021-06-25</t>
   </si>
   <si>
-    <t>2021-07-20</t>
+    <t>2021-07-21</t>
   </si>
   <si>
     <t>2021-07-27</t>
@@ -1081,9 +1081,6 @@
     <t>2021-10-11</t>
   </si>
   <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
     <t>2021-07-26</t>
   </si>
   <si>
@@ -1091,6 +1088,9 @@
   </si>
   <si>
     <t>2021-05-27</t>
+  </si>
+  <si>
+    <t>2021-10-20</t>
   </si>
   <si>
     <t>2021-09-06</t>
@@ -1564,7 +1564,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-10-21</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -2267,7 +2267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1820"/>
+  <dimension ref="A1:P1821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91325,7 +91325,7 @@
         <v>348</v>
       </c>
       <c r="C1782">
-        <v>1.626208411664409</v>
+        <v>1.661260875267784</v>
       </c>
       <c r="D1782" t="s">
         <v>515</v>
@@ -91337,22 +91337,22 @@
         <v>-1</v>
       </c>
       <c r="G1782">
-        <v>0.01053379158833559</v>
+        <v>0.01031873912473222</v>
       </c>
       <c r="H1782">
         <v>0.009284342893367726</v>
       </c>
       <c r="I1782">
-        <v>0.2105513050321348</v>
+        <v>0.2456037686355095</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1782">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="L1782">
-        <v>6.08</v>
+        <v>5.99</v>
       </c>
       <c r="M1782">
         <v>4.09</v>
@@ -91431,7 +91431,7 @@
         <v>516</v>
       </c>
       <c r="E1784">
-        <v>1.69458116556639</v>
+        <v>1.682678266952303</v>
       </c>
       <c r="F1784">
         <v>-1</v>
@@ -91440,10 +91440,10 @@
         <v>0.01042683622611813</v>
       </c>
       <c r="H1784">
-        <v>0.01102541883443361</v>
+        <v>0.0109173217330477</v>
       </c>
       <c r="I1784">
-        <v>-0.02141739168451995</v>
+        <v>-0.009514493070432728</v>
       </c>
       <c r="J1784">
         <v>0.9619420277182702</v>
@@ -91455,10 +91455,10 @@
         <v>6.05</v>
       </c>
       <c r="M1784">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1784">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1784">
         <v>1</v>
@@ -91481,7 +91481,7 @@
         <v>516</v>
       </c>
       <c r="E1785">
-        <v>1.69458116556639</v>
+        <v>1.682678266952303</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91490,10 +91490,10 @@
         <v>0.01071112753027587</v>
       </c>
       <c r="H1785">
-        <v>0.01102541883443361</v>
+        <v>0.0109173217330477</v>
       </c>
       <c r="I1785">
-        <v>-0.0257086958422601</v>
+        <v>-0.01380579722817288</v>
       </c>
       <c r="J1785">
         <v>0.9619420277182702</v>
@@ -91505,10 +91505,10 @@
         <v>6.19</v>
       </c>
       <c r="M1785">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1785">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91531,7 +91531,7 @@
         <v>516</v>
       </c>
       <c r="E1786">
-        <v>1.69458116556639</v>
+        <v>1.682678266952303</v>
       </c>
       <c r="F1786">
         <v>-1</v>
@@ -91540,10 +91540,10 @@
         <v>0.01053417216805841</v>
       </c>
       <c r="H1786">
-        <v>0.01102541883443361</v>
+        <v>0.0109173217330477</v>
       </c>
       <c r="I1786">
-        <v>-0.0487533336247985</v>
+        <v>-0.03685043501071128</v>
       </c>
       <c r="J1786">
         <v>0.9619420277182702</v>
@@ -91555,10 +91555,10 @@
         <v>6.09</v>
       </c>
       <c r="M1786">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1786">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1786">
         <v>1</v>
@@ -91581,7 +91581,7 @@
         <v>516</v>
       </c>
       <c r="E1787">
-        <v>1.69458116556639</v>
+        <v>1.682678266952303</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91590,10 +91590,10 @@
         <v>0.009985208980020111</v>
       </c>
       <c r="H1787">
-        <v>0.01102541883443361</v>
+        <v>0.0109173217330477</v>
       </c>
       <c r="I1787">
-        <v>-0.03979014558650018</v>
+        <v>-0.02788724697241296</v>
       </c>
       <c r="J1787">
         <v>0.9619420277182702</v>
@@ -91605,10 +91605,10 @@
         <v>5.82</v>
       </c>
       <c r="M1787">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1787">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91631,7 +91631,7 @@
         <v>516</v>
       </c>
       <c r="E1788">
-        <v>1.69458116556639</v>
+        <v>1.682678266952303</v>
       </c>
       <c r="F1788">
         <v>-1</v>
@@ -91640,10 +91640,10 @@
         <v>0.01075150810999869</v>
       </c>
       <c r="H1788">
-        <v>0.01102541883443361</v>
+        <v>0.0109173217330477</v>
       </c>
       <c r="I1788">
-        <v>0.03391072443492238</v>
+        <v>0.0458136230490096</v>
       </c>
       <c r="J1788">
         <v>0.9619420277182702</v>
@@ -91655,10 +91655,10 @@
         <v>6.24</v>
       </c>
       <c r="M1788">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1788">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91772,7 +91772,7 @@
         <v>2</v>
       </c>
       <c r="B1791" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C1791">
         <v>1.402614926309523</v>
@@ -91822,7 +91822,7 @@
         <v>3</v>
       </c>
       <c r="B1792" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C1792">
         <v>1.376887085467724</v>
@@ -91881,7 +91881,7 @@
         <v>516</v>
       </c>
       <c r="E1793">
-        <v>1.415818309466931</v>
+        <v>1.406789254730159</v>
       </c>
       <c r="F1793">
         <v>-1</v>
@@ -91890,10 +91890,10 @@
         <v>0.0106883560189537</v>
       </c>
       <c r="H1793">
-        <v>0.01130418169053307</v>
+        <v>0.01119321074526984</v>
       </c>
       <c r="I1793">
-        <v>-0.004174328420635476</v>
+        <v>0.004854726316136926</v>
       </c>
       <c r="J1793">
         <v>1.01941890526455</v>
@@ -91905,10 +91905,10 @@
         <v>6.05</v>
       </c>
       <c r="M1793">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1793">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -91931,7 +91931,7 @@
         <v>516</v>
       </c>
       <c r="E1794">
-        <v>1.415818309466931</v>
+        <v>1.406789254730159</v>
       </c>
       <c r="F1794">
         <v>-1</v>
@@ -91940,10 +91940,10 @@
         <v>0.01098126885474339</v>
       </c>
       <c r="H1794">
-        <v>0.01130418169053307</v>
+        <v>0.01119321074526984</v>
       </c>
       <c r="I1794">
-        <v>-0.01708716421031742</v>
+        <v>-0.008058109473545016</v>
       </c>
       <c r="J1794">
         <v>1.01941890526455</v>
@@ -91955,10 +91955,10 @@
         <v>6.19</v>
       </c>
       <c r="M1794">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1794">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1794">
         <v>1</v>
@@ -91981,7 +91981,7 @@
         <v>516</v>
       </c>
       <c r="E1795">
-        <v>1.415818309466931</v>
+        <v>1.406789254730159</v>
       </c>
       <c r="F1795">
         <v>-1</v>
@@ -91990,10 +91990,10 @@
         <v>0.01079971534232222</v>
       </c>
       <c r="H1795">
-        <v>0.01130418169053307</v>
+        <v>0.01119321074526984</v>
       </c>
       <c r="I1795">
-        <v>-0.03553365178915424</v>
+        <v>-0.02650459705238184</v>
       </c>
       <c r="J1795">
         <v>1.01941890526455</v>
@@ -92005,10 +92005,10 @@
         <v>6.09</v>
       </c>
       <c r="M1795">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1795">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -92031,7 +92031,7 @@
         <v>516</v>
       </c>
       <c r="E1796">
-        <v>1.415818309466931</v>
+        <v>1.406789254730159</v>
       </c>
       <c r="F1796">
         <v>-1</v>
@@ -92040,10 +92040,10 @@
         <v>0.0102340838597955</v>
       </c>
       <c r="H1796">
-        <v>0.01130418169053307</v>
+        <v>0.01119321074526984</v>
       </c>
       <c r="I1796">
-        <v>-0.009902169262433702</v>
+        <v>-0.0008731145256613004</v>
       </c>
       <c r="J1796">
         <v>1.01941890526455</v>
@@ -92055,10 +92055,10 @@
         <v>5.82</v>
       </c>
       <c r="M1796">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1796">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92081,7 +92081,7 @@
         <v>516</v>
       </c>
       <c r="E1797">
-        <v>1.415818309466931</v>
+        <v>1.406789254730159</v>
       </c>
       <c r="F1797">
         <v>-1</v>
@@ -92090,10 +92090,10 @@
         <v>0.01102107466569074</v>
       </c>
       <c r="H1797">
-        <v>0.01130418169053307</v>
+        <v>0.01119321074526984</v>
       </c>
       <c r="I1797">
-        <v>0.04310702484232731</v>
+        <v>0.05213607957909971</v>
       </c>
       <c r="J1797">
         <v>1.01941890526455</v>
@@ -92105,10 +92105,10 @@
         <v>6.24</v>
       </c>
       <c r="M1797">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1797">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92122,7 +92122,7 @@
         <v>9</v>
       </c>
       <c r="B1798" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1798">
         <v>1.506206687572221</v>
@@ -92131,7 +92131,7 @@
         <v>516</v>
       </c>
       <c r="E1798">
-        <v>1.415818309466931</v>
+        <v>1.406789254730159</v>
       </c>
       <c r="F1798">
         <v>-1</v>
@@ -92140,10 +92140,10 @@
         <v>0.01135379331242778</v>
       </c>
       <c r="H1798">
-        <v>0.01130418169053307</v>
+        <v>0.01119321074526984</v>
       </c>
       <c r="I1798">
-        <v>0.0903883781052901</v>
+        <v>0.0994174328420625</v>
       </c>
       <c r="J1798">
         <v>1.01941890526455</v>
@@ -92155,10 +92155,10 @@
         <v>6.43</v>
       </c>
       <c r="M1798">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1798">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92172,7 +92172,7 @@
         <v>0</v>
       </c>
       <c r="B1799" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C1799">
         <v>0.7149171399855092</v>
@@ -92222,7 +92222,7 @@
         <v>1</v>
       </c>
       <c r="B1800" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C1800">
         <v>1.149631161910106</v>
@@ -92272,7 +92272,7 @@
         <v>2</v>
       </c>
       <c r="B1801" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C1801">
         <v>1.136271416216722</v>
@@ -92331,7 +92331,7 @@
         <v>516</v>
       </c>
       <c r="E1802">
-        <v>1.14315803005867</v>
+        <v>1.136939906037446</v>
       </c>
       <c r="F1802">
         <v>-1</v>
@@ -92340,10 +92340,10 @@
         <v>0.01094415071406867</v>
       </c>
       <c r="H1802">
-        <v>0.01157684196994133</v>
+        <v>0.01146306009396255</v>
       </c>
       <c r="I1802">
-        <v>0.01269125587265929</v>
+        <v>0.0189093798938833</v>
       </c>
       <c r="J1802">
         <v>1.075637519575532</v>
@@ -92355,10 +92355,10 @@
         <v>6.05</v>
       </c>
       <c r="M1802">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1802">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1802">
         <v>1</v>
@@ -92381,7 +92381,7 @@
         <v>516</v>
       </c>
       <c r="E1803">
-        <v>1.14315803005867</v>
+        <v>1.136939906037446</v>
       </c>
       <c r="F1803">
         <v>-1</v>
@@ -92390,10 +92390,10 @@
         <v>0.011245496342005</v>
       </c>
       <c r="H1803">
-        <v>0.01157684196994133</v>
+        <v>0.01146306009396255</v>
       </c>
       <c r="I1803">
-        <v>-0.008654372063670479</v>
+        <v>-0.002436248042446465</v>
       </c>
       <c r="J1803">
         <v>1.075637519575532</v>
@@ -92405,10 +92405,10 @@
         <v>6.19</v>
       </c>
       <c r="M1803">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1803">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1803">
         <v>1</v>
@@ -92431,7 +92431,7 @@
         <v>516</v>
       </c>
       <c r="E1804">
-        <v>1.14315803005867</v>
+        <v>1.136939906037446</v>
       </c>
       <c r="F1804">
         <v>-1</v>
@@ -92440,10 +92440,10 @@
         <v>0.01047751045976206</v>
       </c>
       <c r="H1804">
-        <v>0.01157684196994133</v>
+        <v>0.01146306009396255</v>
       </c>
       <c r="I1804">
-        <v>0.01933151017927592</v>
+        <v>0.02554963420049994</v>
       </c>
       <c r="J1804">
         <v>1.075637519575532</v>
@@ -92455,10 +92455,10 @@
         <v>5.82</v>
       </c>
       <c r="M1804">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1804">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1804">
         <v>1</v>
@@ -92481,7 +92481,7 @@
         <v>516</v>
       </c>
       <c r="E1805">
-        <v>1.14315803005867</v>
+        <v>1.136939906037446</v>
       </c>
       <c r="F1805">
         <v>-1</v>
@@ -92490,10 +92490,10 @@
         <v>0.01128473996680925</v>
       </c>
       <c r="H1805">
-        <v>0.01157684196994133</v>
+        <v>0.01146306009396255</v>
       </c>
       <c r="I1805">
-        <v>0.05210200313208446</v>
+        <v>0.05832012715330848</v>
       </c>
       <c r="J1805">
         <v>1.075637519575532</v>
@@ -92505,10 +92505,10 @@
         <v>6.24</v>
       </c>
       <c r="M1805">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1805">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1805">
         <v>1</v>
@@ -92522,7 +92522,7 @@
         <v>7</v>
       </c>
       <c r="B1806" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1806">
         <v>1.23467078045018</v>
@@ -92531,7 +92531,7 @@
         <v>516</v>
       </c>
       <c r="E1806">
-        <v>1.14315803005867</v>
+        <v>1.136939906037446</v>
       </c>
       <c r="F1806">
         <v>-1</v>
@@ -92540,10 +92540,10 @@
         <v>0.01162532921954982</v>
       </c>
       <c r="H1806">
-        <v>0.01157684196994133</v>
+        <v>0.01146306009396255</v>
       </c>
       <c r="I1806">
-        <v>0.09151275039150963</v>
+        <v>0.09773087441273365</v>
       </c>
       <c r="J1806">
         <v>1.075637519575532</v>
@@ -92555,10 +92555,10 @@
         <v>6.43</v>
       </c>
       <c r="M1806">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1806">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92572,7 +92572,7 @@
         <v>0</v>
       </c>
       <c r="B1807" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C1807">
         <v>1.088452388565583</v>
@@ -92614,7 +92614,7 @@
         <v>1</v>
       </c>
       <c r="P1807" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1808" spans="1:16">
@@ -92622,7 +92622,7 @@
         <v>1</v>
       </c>
       <c r="B1808" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C1808">
         <v>1.0780836051246</v>
@@ -92664,7 +92664,7 @@
         <v>1</v>
       </c>
       <c r="P1808" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1809" spans="1:16">
@@ -92681,7 +92681,7 @@
         <v>516</v>
       </c>
       <c r="E1809">
-        <v>1.07722090767624</v>
+        <v>1.071682547803289</v>
       </c>
       <c r="F1809">
         <v>-1</v>
@@ -92690,10 +92690,10 @@
         <v>0.01100600925156146</v>
       </c>
       <c r="H1809">
-        <v>0.01164277909232376</v>
+        <v>0.01152831745219671</v>
       </c>
       <c r="I1809">
-        <v>0.01676984076229449</v>
+        <v>0.02230820063524597</v>
       </c>
       <c r="J1809">
         <v>1.089232802540981</v>
@@ -92705,16 +92705,16 @@
         <v>6.05</v>
       </c>
       <c r="M1809">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1809">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1809">
         <v>1</v>
       </c>
       <c r="P1809" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1810" spans="1:16">
@@ -92731,7 +92731,7 @@
         <v>516</v>
       </c>
       <c r="E1810">
-        <v>1.07722090767624</v>
+        <v>1.071682547803289</v>
       </c>
       <c r="F1810">
         <v>-1</v>
@@ -92740,10 +92740,10 @@
         <v>0.01053637803500245</v>
       </c>
       <c r="H1810">
-        <v>0.01164277909232376</v>
+        <v>0.01152831745219671</v>
       </c>
       <c r="I1810">
-        <v>0.02640105732131026</v>
+        <v>0.03193941719426174</v>
       </c>
       <c r="J1810">
         <v>1.089232802540981</v>
@@ -92755,16 +92755,16 @@
         <v>5.82</v>
       </c>
       <c r="M1810">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1810">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1810">
         <v>1</v>
       </c>
       <c r="P1810" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1811" spans="1:16">
@@ -92781,7 +92781,7 @@
         <v>516</v>
       </c>
       <c r="E1811">
-        <v>1.07722090767624</v>
+        <v>1.071682547803289</v>
       </c>
       <c r="F1811">
         <v>-1</v>
@@ -92790,10 +92790,10 @@
         <v>0.0113485018439172</v>
       </c>
       <c r="H1811">
-        <v>0.01164277909232376</v>
+        <v>0.01152831745219671</v>
       </c>
       <c r="I1811">
-        <v>0.05427724840655657</v>
+        <v>0.05981560827950805</v>
       </c>
       <c r="J1811">
         <v>1.089232802540981</v>
@@ -92805,16 +92805,16 @@
         <v>6.24</v>
       </c>
       <c r="M1811">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1811">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1811">
         <v>1</v>
       </c>
       <c r="P1811" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1812" spans="1:16">
@@ -92822,7 +92822,7 @@
         <v>5</v>
       </c>
       <c r="B1812" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1812">
         <v>1.169005563727059</v>
@@ -92831,7 +92831,7 @@
         <v>516</v>
       </c>
       <c r="E1812">
-        <v>1.07722090767624</v>
+        <v>1.071682547803289</v>
       </c>
       <c r="F1812">
         <v>-1</v>
@@ -92840,10 +92840,10 @@
         <v>0.01169099443627294</v>
       </c>
       <c r="H1812">
-        <v>0.01164277909232376</v>
+        <v>0.01152831745219671</v>
       </c>
       <c r="I1812">
-        <v>0.09178465605081865</v>
+        <v>0.09732301592377013</v>
       </c>
       <c r="J1812">
         <v>1.089232802540981</v>
@@ -92855,110 +92855,110 @@
         <v>6.43</v>
       </c>
       <c r="M1812">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="N1812">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="O1812">
         <v>1</v>
       </c>
       <c r="P1812" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1813" spans="1:16">
       <c r="A1813" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1813" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1813">
-        <v>1.437331032547627</v>
+        <v>1.07722090767624</v>
       </c>
       <c r="D1813" t="s">
-        <v>350</v>
+        <v>516</v>
       </c>
       <c r="E1813">
-        <v>1.527152008316966</v>
+        <v>1.071682547803289</v>
       </c>
       <c r="F1813">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1813">
-        <v>0.01054266896745237</v>
+        <v>0.01164277909232376</v>
       </c>
       <c r="H1813">
-        <v>0.01057284799168303</v>
+        <v>0.01152831745219671</v>
       </c>
       <c r="I1813">
-        <v>0.08982097576933867</v>
+        <v>0.005538359872951482</v>
       </c>
       <c r="J1813">
-        <v>0.994032525644623</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1813">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="L1813">
-        <v>5.99</v>
+        <v>6.36</v>
       </c>
       <c r="M1813">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="N1813">
-        <v>6.05</v>
+        <v>6.3</v>
       </c>
       <c r="O1813">
         <v>1</v>
       </c>
       <c r="P1813" t="s">
-        <v>630</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1814" spans="1:16">
       <c r="A1814" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1814" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C1814">
-        <v>1.595242416523244</v>
+        <v>1.437331032547627</v>
       </c>
       <c r="D1814" t="s">
-        <v>518</v>
+        <v>350</v>
       </c>
       <c r="E1814">
-        <v>1.415719814471675</v>
+        <v>1.527152008316966</v>
       </c>
       <c r="F1814">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1814">
-        <v>0.01000475758347676</v>
+        <v>0.01054266896745237</v>
       </c>
       <c r="H1814">
-        <v>0.009984280185528325</v>
+        <v>0.01057284799168303</v>
       </c>
       <c r="I1814">
-        <v>0.179522602051569</v>
+        <v>0.08982097576933867</v>
       </c>
       <c r="J1814">
         <v>0.994032525644623</v>
       </c>
       <c r="K1814">
-        <v>4.23</v>
+        <v>4.58</v>
       </c>
       <c r="L1814">
-        <v>5.8</v>
+        <v>5.99</v>
       </c>
       <c r="M1814">
-        <v>4.31</v>
+        <v>4.55</v>
       </c>
       <c r="N1814">
-        <v>5.7</v>
+        <v>6.05</v>
       </c>
       <c r="O1814">
         <v>1</v>
@@ -92969,96 +92969,96 @@
     </row>
     <row r="1815" spans="1:16">
       <c r="A1815" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1815" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C1815">
-        <v>1.106278882193859</v>
+        <v>1.595242416523244</v>
       </c>
       <c r="D1815" t="s">
-        <v>353</v>
+        <v>518</v>
       </c>
       <c r="E1815">
-        <v>1.203415097025192</v>
+        <v>1.415719814471675</v>
       </c>
       <c r="F1815">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1815">
-        <v>0.01121372111780614</v>
+        <v>0.01000475758347676</v>
       </c>
       <c r="H1815">
-        <v>0.01043658490297481</v>
+        <v>0.009984280185528325</v>
       </c>
       <c r="I1815">
-        <v>0.09713621483133306</v>
+        <v>0.179522602051569</v>
       </c>
       <c r="J1815">
-        <v>1.066185889832519</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1815">
-        <v>4.74</v>
+        <v>4.23</v>
       </c>
       <c r="L1815">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="M1815">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="N1815">
-        <v>5.82</v>
+        <v>5.7</v>
       </c>
       <c r="O1815">
         <v>1</v>
       </c>
       <c r="P1815" t="s">
-        <v>350</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1816" spans="1:16">
       <c r="A1816" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1816" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1816">
-        <v>1.290033686008443</v>
+        <v>1.106278882193859</v>
       </c>
       <c r="D1816" t="s">
-        <v>518</v>
+        <v>353</v>
       </c>
       <c r="E1816">
-        <v>1.104738814821843</v>
+        <v>1.203415097025192</v>
       </c>
       <c r="F1816">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1816">
-        <v>0.01030996631399156</v>
+        <v>0.01121372111780614</v>
       </c>
       <c r="H1816">
-        <v>0.01029526118517816</v>
+        <v>0.01043658490297481</v>
       </c>
       <c r="I1816">
-        <v>0.1852948711866</v>
+        <v>0.09713621483133306</v>
       </c>
       <c r="J1816">
         <v>1.066185889832519</v>
       </c>
       <c r="K1816">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="L1816">
-        <v>5.8</v>
+        <v>6.16</v>
       </c>
       <c r="M1816">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1816">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="O1816">
         <v>1</v>
@@ -93069,96 +93069,96 @@
     </row>
     <row r="1817" spans="1:16">
       <c r="A1817" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1817" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C1817">
-        <v>0.9527648456254667</v>
+        <v>1.290033686008443</v>
       </c>
       <c r="D1817" t="s">
-        <v>353</v>
+        <v>518</v>
       </c>
       <c r="E1817">
-        <v>1.06317970075069</v>
+        <v>1.104738814821843</v>
       </c>
       <c r="F1817">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1817">
-        <v>0.01136723515437453</v>
+        <v>0.01030996631399156</v>
       </c>
       <c r="H1817">
-        <v>0.01057682029924931</v>
+        <v>0.01029526118517816</v>
       </c>
       <c r="I1817">
-        <v>0.1104148551252235</v>
+        <v>0.1852948711866</v>
       </c>
       <c r="J1817">
-        <v>1.098572817378594</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1817">
-        <v>4.74</v>
+        <v>4.23</v>
       </c>
       <c r="L1817">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="M1817">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="N1817">
-        <v>5.82</v>
+        <v>5.7</v>
       </c>
       <c r="O1817">
         <v>1</v>
       </c>
       <c r="P1817" t="s">
-        <v>631</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1818" spans="1:16">
       <c r="A1818" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1818" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1818">
-        <v>1.153036982488548</v>
+        <v>0.9527648456254667</v>
       </c>
       <c r="D1818" t="s">
-        <v>518</v>
+        <v>353</v>
       </c>
       <c r="E1818">
-        <v>0.965151157098262</v>
+        <v>1.06317970075069</v>
       </c>
       <c r="F1818">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1818">
-        <v>0.01044696301751145</v>
+        <v>0.01136723515437453</v>
       </c>
       <c r="H1818">
-        <v>0.01043484884290174</v>
+        <v>0.01057682029924931</v>
       </c>
       <c r="I1818">
-        <v>0.1878858253902864</v>
+        <v>0.1104148551252235</v>
       </c>
       <c r="J1818">
         <v>1.098572817378594</v>
       </c>
       <c r="K1818">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="L1818">
-        <v>5.8</v>
+        <v>6.16</v>
       </c>
       <c r="M1818">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1818">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="O1818">
         <v>1</v>
@@ -93169,101 +93169,151 @@
     </row>
     <row r="1819" spans="1:16">
       <c r="A1819" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1819" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C1819">
-        <v>0.8652138986958411</v>
+        <v>1.153036982488548</v>
       </c>
       <c r="D1819" t="s">
-        <v>353</v>
+        <v>518</v>
       </c>
       <c r="E1819">
-        <v>0.9832017260238386</v>
+        <v>0.965151157098262</v>
       </c>
       <c r="F1819">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1819">
-        <v>0.01145478610130416</v>
+        <v>0.01044696301751145</v>
       </c>
       <c r="H1819">
-        <v>0.01065679827397616</v>
+        <v>0.01043484884290174</v>
       </c>
       <c r="I1819">
-        <v>0.1179878273279975</v>
+        <v>0.1878858253902864</v>
       </c>
       <c r="J1819">
-        <v>1.117043481287797</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1819">
-        <v>4.74</v>
+        <v>4.23</v>
       </c>
       <c r="L1819">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="M1819">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="N1819">
-        <v>5.82</v>
+        <v>5.7</v>
       </c>
       <c r="O1819">
         <v>1</v>
       </c>
       <c r="P1819" t="s">
-        <v>351</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1820" spans="1:16">
       <c r="A1820" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1820" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1820">
-        <v>1.074906074152617</v>
+        <v>0.8652138986958411</v>
       </c>
       <c r="D1820" t="s">
-        <v>518</v>
+        <v>353</v>
       </c>
       <c r="E1820">
-        <v>0.8855425956495946</v>
+        <v>0.9832017260238386</v>
       </c>
       <c r="F1820">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1820">
-        <v>0.01052509392584738</v>
+        <v>0.01145478610130416</v>
       </c>
       <c r="H1820">
-        <v>0.01051445740435041</v>
+        <v>0.01065679827397616</v>
       </c>
       <c r="I1820">
-        <v>0.1893634785030223</v>
+        <v>0.1179878273279975</v>
       </c>
       <c r="J1820">
         <v>1.117043481287797</v>
       </c>
       <c r="K1820">
+        <v>4.74</v>
+      </c>
+      <c r="L1820">
+        <v>6.16</v>
+      </c>
+      <c r="M1820">
+        <v>4.33</v>
+      </c>
+      <c r="N1820">
+        <v>5.82</v>
+      </c>
+      <c r="O1820">
+        <v>1</v>
+      </c>
+      <c r="P1820" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:16">
+      <c r="A1821" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1821" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1821">
+        <v>1.074906074152617</v>
+      </c>
+      <c r="D1821" t="s">
+        <v>518</v>
+      </c>
+      <c r="E1821">
+        <v>0.8855425956495946</v>
+      </c>
+      <c r="F1821">
+        <v>-1</v>
+      </c>
+      <c r="G1821">
+        <v>0.01052509392584738</v>
+      </c>
+      <c r="H1821">
+        <v>0.01051445740435041</v>
+      </c>
+      <c r="I1821">
+        <v>0.1893634785030223</v>
+      </c>
+      <c r="J1821">
+        <v>1.117043481287797</v>
+      </c>
+      <c r="K1821">
         <v>4.23</v>
       </c>
-      <c r="L1820">
+      <c r="L1821">
         <v>5.8</v>
       </c>
-      <c r="M1820">
+      <c r="M1821">
         <v>4.31</v>
       </c>
-      <c r="N1820">
+      <c r="N1821">
         <v>5.7</v>
       </c>
-      <c r="O1820">
-        <v>1</v>
-      </c>
-      <c r="P1820" t="s">
+      <c r="O1821">
+        <v>1</v>
+      </c>
+      <c r="P1821" t="s">
         <v>351</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -1567,7 +1567,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-10-26</t>
+    <t>2021-10-27</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -91434,7 +91434,7 @@
         <v>517</v>
       </c>
       <c r="E1784">
-        <v>1.690775368338216</v>
+        <v>1.667730730555679</v>
       </c>
       <c r="F1784">
         <v>-1</v>
@@ -91443,10 +91443,10 @@
         <v>0.01042683622611813</v>
       </c>
       <c r="H1784">
-        <v>0.01082922463166178</v>
+        <v>0.01065226926944432</v>
       </c>
       <c r="I1784">
-        <v>-0.01761159445634597</v>
+        <v>0.005433043326191545</v>
       </c>
       <c r="J1784">
         <v>0.9619420277182702</v>
@@ -91458,10 +91458,10 @@
         <v>6.05</v>
       </c>
       <c r="M1784">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1784">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1784">
         <v>1</v>
@@ -91484,7 +91484,7 @@
         <v>517</v>
       </c>
       <c r="E1785">
-        <v>1.690775368338216</v>
+        <v>1.667730730555679</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91493,10 +91493,10 @@
         <v>0.01071112753027587</v>
       </c>
       <c r="H1785">
-        <v>0.01082922463166178</v>
+        <v>0.01065226926944432</v>
       </c>
       <c r="I1785">
-        <v>-0.02190289861408612</v>
+        <v>0.001141739168451394</v>
       </c>
       <c r="J1785">
         <v>0.9619420277182702</v>
@@ -91508,10 +91508,10 @@
         <v>6.19</v>
       </c>
       <c r="M1785">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1785">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91534,7 +91534,7 @@
         <v>517</v>
       </c>
       <c r="E1786">
-        <v>1.690775368338216</v>
+        <v>1.667730730555679</v>
       </c>
       <c r="F1786">
         <v>-1</v>
@@ -91543,10 +91543,10 @@
         <v>0.01053417216805841</v>
       </c>
       <c r="H1786">
-        <v>0.01082922463166178</v>
+        <v>0.01065226926944432</v>
       </c>
       <c r="I1786">
-        <v>-0.04494753639662452</v>
+        <v>-0.02190289861408701</v>
       </c>
       <c r="J1786">
         <v>0.9619420277182702</v>
@@ -91558,10 +91558,10 @@
         <v>6.09</v>
       </c>
       <c r="M1786">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1786">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1786">
         <v>1</v>
@@ -91584,7 +91584,7 @@
         <v>517</v>
       </c>
       <c r="E1787">
-        <v>1.690775368338216</v>
+        <v>1.667730730555679</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91593,10 +91593,10 @@
         <v>0.009985208980020111</v>
       </c>
       <c r="H1787">
-        <v>0.01082922463166178</v>
+        <v>0.01065226926944432</v>
       </c>
       <c r="I1787">
-        <v>-0.0359843483583262</v>
+        <v>-0.01293971057578869</v>
       </c>
       <c r="J1787">
         <v>0.9619420277182702</v>
@@ -91608,10 +91608,10 @@
         <v>5.82</v>
       </c>
       <c r="M1787">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1787">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91634,7 +91634,7 @@
         <v>517</v>
       </c>
       <c r="E1788">
-        <v>1.690775368338216</v>
+        <v>1.667730730555679</v>
       </c>
       <c r="F1788">
         <v>-1</v>
@@ -91643,10 +91643,10 @@
         <v>0.01075150810999869</v>
       </c>
       <c r="H1788">
-        <v>0.01082922463166178</v>
+        <v>0.01065226926944432</v>
       </c>
       <c r="I1788">
-        <v>0.03771652166309636</v>
+        <v>0.06076115944563387</v>
       </c>
       <c r="J1788">
         <v>0.9619420277182702</v>
@@ -91658,10 +91658,10 @@
         <v>6.24</v>
       </c>
       <c r="M1788">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1788">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91684,7 +91684,7 @@
         <v>517</v>
       </c>
       <c r="E1789">
-        <v>1.690775368338216</v>
+        <v>1.667730730555679</v>
       </c>
       <c r="F1789">
         <v>-1</v>
@@ -91693,10 +91693,10 @@
         <v>0.01107617999387924</v>
       </c>
       <c r="H1789">
-        <v>0.01082922463166178</v>
+        <v>0.01065226926944432</v>
       </c>
       <c r="I1789">
-        <v>0.09304463778253869</v>
+        <v>0.1160892755650762</v>
       </c>
       <c r="J1789">
         <v>0.9619420277182702</v>
@@ -91708,10 +91708,10 @@
         <v>6.43</v>
       </c>
       <c r="M1789">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1789">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1789">
         <v>1</v>
@@ -91734,7 +91734,7 @@
         <v>517</v>
       </c>
       <c r="E1790">
-        <v>1.690775368338216</v>
+        <v>1.667730730555679</v>
       </c>
       <c r="F1790">
         <v>-1</v>
@@ -91743,10 +91743,10 @@
         <v>0.01065303042888996</v>
       </c>
       <c r="H1790">
-        <v>0.01082922463166178</v>
+        <v>0.01065226926944432</v>
       </c>
       <c r="I1790">
-        <v>0.01619420277182648</v>
+        <v>0.039238840554364</v>
       </c>
       <c r="J1790">
         <v>0.9619420277182702</v>
@@ -91758,10 +91758,10 @@
         <v>6.18</v>
       </c>
       <c r="M1790">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1790">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1790">
         <v>1</v>
@@ -91984,7 +91984,7 @@
         <v>517</v>
       </c>
       <c r="E1795">
-        <v>1.417760199993386</v>
+        <v>1.39931371241455</v>
       </c>
       <c r="F1795">
         <v>-1</v>
@@ -91993,10 +91993,10 @@
         <v>0.0106883560189537</v>
       </c>
       <c r="H1795">
-        <v>0.01110223980000661</v>
+        <v>0.01092068628758545</v>
       </c>
       <c r="I1795">
-        <v>-0.006116218947090246</v>
+        <v>0.01233026863174569</v>
       </c>
       <c r="J1795">
         <v>1.01941890526455</v>
@@ -92008,10 +92008,10 @@
         <v>6.05</v>
       </c>
       <c r="M1795">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1795">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -92034,7 +92034,7 @@
         <v>517</v>
       </c>
       <c r="E1796">
-        <v>1.417760199993386</v>
+        <v>1.39931371241455</v>
       </c>
       <c r="F1796">
         <v>-1</v>
@@ -92043,10 +92043,10 @@
         <v>0.01098126885474339</v>
       </c>
       <c r="H1796">
-        <v>0.01110223980000661</v>
+        <v>0.01092068628758545</v>
       </c>
       <c r="I1796">
-        <v>-0.01902905473677219</v>
+        <v>-0.0005825671579362535</v>
       </c>
       <c r="J1796">
         <v>1.01941890526455</v>
@@ -92058,10 +92058,10 @@
         <v>6.19</v>
       </c>
       <c r="M1796">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1796">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92084,7 +92084,7 @@
         <v>517</v>
       </c>
       <c r="E1797">
-        <v>1.417760199993386</v>
+        <v>1.39931371241455</v>
       </c>
       <c r="F1797">
         <v>-1</v>
@@ -92093,10 +92093,10 @@
         <v>0.0102340838597955</v>
       </c>
       <c r="H1797">
-        <v>0.01110223980000661</v>
+        <v>0.01092068628758545</v>
       </c>
       <c r="I1797">
-        <v>-0.01184405978888847</v>
+        <v>0.006602427789947463</v>
       </c>
       <c r="J1797">
         <v>1.01941890526455</v>
@@ -92108,10 +92108,10 @@
         <v>5.82</v>
       </c>
       <c r="M1797">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1797">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92134,7 +92134,7 @@
         <v>517</v>
       </c>
       <c r="E1798">
-        <v>1.417760199993386</v>
+        <v>1.39931371241455</v>
       </c>
       <c r="F1798">
         <v>-1</v>
@@ -92143,10 +92143,10 @@
         <v>0.01102107466569074</v>
       </c>
       <c r="H1798">
-        <v>0.01110223980000661</v>
+        <v>0.01092068628758545</v>
       </c>
       <c r="I1798">
-        <v>0.04116513431587254</v>
+        <v>0.05961162189470848</v>
       </c>
       <c r="J1798">
         <v>1.01941890526455</v>
@@ -92158,10 +92158,10 @@
         <v>6.24</v>
       </c>
       <c r="M1798">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1798">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92184,7 +92184,7 @@
         <v>517</v>
       </c>
       <c r="E1799">
-        <v>1.417760199993386</v>
+        <v>1.39931371241455</v>
       </c>
       <c r="F1799">
         <v>-1</v>
@@ -92193,10 +92193,10 @@
         <v>0.01135379331242778</v>
       </c>
       <c r="H1799">
-        <v>0.01110223980000661</v>
+        <v>0.01092068628758545</v>
       </c>
       <c r="I1799">
-        <v>0.08844648757883533</v>
+        <v>0.1068929751576713</v>
       </c>
       <c r="J1799">
         <v>1.01941890526455</v>
@@ -92208,10 +92208,10 @@
         <v>6.43</v>
       </c>
       <c r="M1799">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1799">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1799">
         <v>1</v>
@@ -92234,7 +92234,7 @@
         <v>517</v>
       </c>
       <c r="E1800">
-        <v>1.417760199993386</v>
+        <v>1.39931371241455</v>
       </c>
       <c r="F1800">
         <v>-1</v>
@@ -92243,10 +92243,10 @@
         <v>0.01092029790948016</v>
       </c>
       <c r="H1800">
-        <v>0.01110223980000661</v>
+        <v>0.01092068628758545</v>
       </c>
       <c r="I1800">
-        <v>0.02194189052645434</v>
+        <v>0.04038837810529028</v>
       </c>
       <c r="J1800">
         <v>1.01941890526455</v>
@@ -92258,10 +92258,10 @@
         <v>6.18</v>
       </c>
       <c r="M1800">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1800">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1800">
         <v>1</v>
@@ -92434,7 +92434,7 @@
         <v>517</v>
       </c>
       <c r="E1804">
-        <v>1.150721782016222</v>
+        <v>1.136772783582265</v>
       </c>
       <c r="F1804">
         <v>-1</v>
@@ -92443,10 +92443,10 @@
         <v>0.01094415071406867</v>
       </c>
       <c r="H1804">
-        <v>0.01136927821798378</v>
+        <v>0.01118322721641773</v>
       </c>
       <c r="I1804">
-        <v>0.005127503915106857</v>
+        <v>0.01907650234906377</v>
       </c>
       <c r="J1804">
         <v>1.075637519575532</v>
@@ -92458,10 +92458,10 @@
         <v>6.05</v>
       </c>
       <c r="M1804">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1804">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1804">
         <v>1</v>
@@ -92484,7 +92484,7 @@
         <v>517</v>
       </c>
       <c r="E1805">
-        <v>1.150721782016222</v>
+        <v>1.136772783582265</v>
       </c>
       <c r="F1805">
         <v>-1</v>
@@ -92493,10 +92493,10 @@
         <v>0.01047751045976206</v>
       </c>
       <c r="H1805">
-        <v>0.01136927821798378</v>
+        <v>0.01118322721641773</v>
       </c>
       <c r="I1805">
-        <v>0.01176775822172349</v>
+        <v>0.02571675665568041</v>
       </c>
       <c r="J1805">
         <v>1.075637519575532</v>
@@ -92508,10 +92508,10 @@
         <v>5.82</v>
       </c>
       <c r="M1805">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1805">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1805">
         <v>1</v>
@@ -92534,7 +92534,7 @@
         <v>517</v>
       </c>
       <c r="E1806">
-        <v>1.150721782016222</v>
+        <v>1.136772783582265</v>
       </c>
       <c r="F1806">
         <v>-1</v>
@@ -92543,10 +92543,10 @@
         <v>0.01128473996680925</v>
       </c>
       <c r="H1806">
-        <v>0.01136927821798378</v>
+        <v>0.01118322721641773</v>
       </c>
       <c r="I1806">
-        <v>0.04453825117453203</v>
+        <v>0.05848724960848894</v>
       </c>
       <c r="J1806">
         <v>1.075637519575532</v>
@@ -92558,10 +92558,10 @@
         <v>6.24</v>
       </c>
       <c r="M1806">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1806">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92584,7 +92584,7 @@
         <v>517</v>
       </c>
       <c r="E1807">
-        <v>1.150721782016222</v>
+        <v>1.136772783582265</v>
       </c>
       <c r="F1807">
         <v>-1</v>
@@ -92593,10 +92593,10 @@
         <v>0.01162532921954982</v>
       </c>
       <c r="H1807">
-        <v>0.01136927821798378</v>
+        <v>0.01118322721641773</v>
       </c>
       <c r="I1807">
-        <v>0.0839489984339572</v>
+        <v>0.09789799686791412</v>
       </c>
       <c r="J1807">
         <v>1.075637519575532</v>
@@ -92608,10 +92608,10 @@
         <v>6.43</v>
       </c>
       <c r="M1807">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1807">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1807">
         <v>1</v>
@@ -92634,7 +92634,7 @@
         <v>517</v>
       </c>
       <c r="E1808">
-        <v>1.150721782016222</v>
+        <v>1.136772783582265</v>
       </c>
       <c r="F1808">
         <v>-1</v>
@@ -92643,10 +92643,10 @@
         <v>0.01157684196994133</v>
       </c>
       <c r="H1808">
-        <v>0.01136927821798378</v>
+        <v>0.01118322721641773</v>
       </c>
       <c r="I1808">
-        <v>-0.007563751957552434</v>
+        <v>0.006385246476404483</v>
       </c>
       <c r="J1808">
         <v>1.075637519575532</v>
@@ -92658,10 +92658,10 @@
         <v>6.36</v>
       </c>
       <c r="M1808">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1808">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1808">
         <v>1</v>
@@ -92684,7 +92684,7 @@
         <v>517</v>
       </c>
       <c r="E1809">
-        <v>1.150721782016222</v>
+        <v>1.136772783582265</v>
       </c>
       <c r="F1809">
         <v>-1</v>
@@ -92693,10 +92693,10 @@
         <v>0.01118171446602623</v>
       </c>
       <c r="H1809">
-        <v>0.01136927821798378</v>
+        <v>0.01118322721641773</v>
       </c>
       <c r="I1809">
-        <v>0.0275637519575529</v>
+        <v>0.04151275039150981</v>
       </c>
       <c r="J1809">
         <v>1.075637519575532</v>
@@ -92708,10 +92708,10 @@
         <v>6.18</v>
       </c>
       <c r="M1809">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1809">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1809">
         <v>1</v>
@@ -92834,7 +92834,7 @@
         <v>517</v>
       </c>
       <c r="E1812">
-        <v>1.086144187930338</v>
+        <v>1.073282812133617</v>
       </c>
       <c r="F1812">
         <v>-1</v>
@@ -92843,10 +92843,10 @@
         <v>0.01100600925156146</v>
       </c>
       <c r="H1812">
-        <v>0.01143385581206966</v>
+        <v>0.01124671718786638</v>
       </c>
       <c r="I1812">
-        <v>0.007846560508196987</v>
+        <v>0.02070793630491785</v>
       </c>
       <c r="J1812">
         <v>1.089232802540981</v>
@@ -92858,10 +92858,10 @@
         <v>6.05</v>
       </c>
       <c r="M1812">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1812">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1812">
         <v>1</v>
@@ -92884,7 +92884,7 @@
         <v>517</v>
       </c>
       <c r="E1813">
-        <v>1.086144187930338</v>
+        <v>1.073282812133617</v>
       </c>
       <c r="F1813">
         <v>-1</v>
@@ -92893,10 +92893,10 @@
         <v>0.01053637803500245</v>
       </c>
       <c r="H1813">
-        <v>0.01143385581206966</v>
+        <v>0.01124671718786638</v>
       </c>
       <c r="I1813">
-        <v>0.01747777706721276</v>
+        <v>0.03033915286393363</v>
       </c>
       <c r="J1813">
         <v>1.089232802540981</v>
@@ -92908,10 +92908,10 @@
         <v>5.82</v>
       </c>
       <c r="M1813">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1813">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1813">
         <v>1</v>
@@ -92934,7 +92934,7 @@
         <v>517</v>
       </c>
       <c r="E1814">
-        <v>1.086144187930338</v>
+        <v>1.073282812133617</v>
       </c>
       <c r="F1814">
         <v>-1</v>
@@ -92943,10 +92943,10 @@
         <v>0.0113485018439172</v>
       </c>
       <c r="H1814">
-        <v>0.01143385581206966</v>
+        <v>0.01124671718786638</v>
       </c>
       <c r="I1814">
-        <v>0.04535396815245907</v>
+        <v>0.05821534394917993</v>
       </c>
       <c r="J1814">
         <v>1.089232802540981</v>
@@ -92958,10 +92958,10 @@
         <v>6.24</v>
       </c>
       <c r="M1814">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1814">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1814">
         <v>1</v>
@@ -92984,7 +92984,7 @@
         <v>517</v>
       </c>
       <c r="E1815">
-        <v>1.086144187930338</v>
+        <v>1.073282812133617</v>
       </c>
       <c r="F1815">
         <v>-1</v>
@@ -92993,10 +92993,10 @@
         <v>0.01169099443627294</v>
       </c>
       <c r="H1815">
-        <v>0.01143385581206966</v>
+        <v>0.01124671718786638</v>
       </c>
       <c r="I1815">
-        <v>0.08286137579672115</v>
+        <v>0.09572275159344201</v>
       </c>
       <c r="J1815">
         <v>1.089232802540981</v>
@@ -93008,10 +93008,10 @@
         <v>6.43</v>
       </c>
       <c r="M1815">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1815">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1815">
         <v>1</v>
@@ -93034,7 +93034,7 @@
         <v>517</v>
       </c>
       <c r="E1816">
-        <v>1.086144187930338</v>
+        <v>1.073282812133617</v>
       </c>
       <c r="F1816">
         <v>-1</v>
@@ -93043,10 +93043,10 @@
         <v>0.01124493253181556</v>
       </c>
       <c r="H1816">
-        <v>0.01143385581206966</v>
+        <v>0.01124671718786638</v>
       </c>
       <c r="I1816">
-        <v>0.02892328025409796</v>
+        <v>0.04178465605081882</v>
       </c>
       <c r="J1816">
         <v>1.089232802540981</v>
@@ -93058,10 +93058,10 @@
         <v>6.18</v>
       </c>
       <c r="M1816">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="N1816">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="O1816">
         <v>1</v>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -1567,7 +1567,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-10-27</t>
+    <t>2021-10-28</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -91434,7 +91434,7 @@
         <v>517</v>
       </c>
       <c r="E1784">
-        <v>1.667730730555679</v>
+        <v>1.730014208892582</v>
       </c>
       <c r="F1784">
         <v>-1</v>
@@ -91443,10 +91443,10 @@
         <v>0.01042683622611813</v>
       </c>
       <c r="H1784">
-        <v>0.01065226926944432</v>
+        <v>0.01082998579110742</v>
       </c>
       <c r="I1784">
-        <v>0.005433043326191545</v>
+        <v>-0.05685043501071174</v>
       </c>
       <c r="J1784">
         <v>0.9619420277182702</v>
@@ -91458,10 +91458,10 @@
         <v>6.05</v>
       </c>
       <c r="M1784">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1784">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1784">
         <v>1</v>
@@ -91484,7 +91484,7 @@
         <v>517</v>
       </c>
       <c r="E1785">
-        <v>1.667730730555679</v>
+        <v>1.730014208892582</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91493,10 +91493,10 @@
         <v>0.01071112753027587</v>
       </c>
       <c r="H1785">
-        <v>0.01065226926944432</v>
+        <v>0.01082998579110742</v>
       </c>
       <c r="I1785">
-        <v>0.001141739168451394</v>
+        <v>-0.06114173916845189</v>
       </c>
       <c r="J1785">
         <v>0.9619420277182702</v>
@@ -91508,10 +91508,10 @@
         <v>6.19</v>
       </c>
       <c r="M1785">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1785">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91534,7 +91534,7 @@
         <v>517</v>
       </c>
       <c r="E1786">
-        <v>1.667730730555679</v>
+        <v>1.730014208892582</v>
       </c>
       <c r="F1786">
         <v>-1</v>
@@ -91543,10 +91543,10 @@
         <v>0.01053417216805841</v>
       </c>
       <c r="H1786">
-        <v>0.01065226926944432</v>
+        <v>0.01082998579110742</v>
       </c>
       <c r="I1786">
-        <v>-0.02190289861408701</v>
+        <v>-0.08418637695099029</v>
       </c>
       <c r="J1786">
         <v>0.9619420277182702</v>
@@ -91558,10 +91558,10 @@
         <v>6.09</v>
       </c>
       <c r="M1786">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1786">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1786">
         <v>1</v>
@@ -91584,7 +91584,7 @@
         <v>517</v>
       </c>
       <c r="E1787">
-        <v>1.667730730555679</v>
+        <v>1.730014208892582</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91593,10 +91593,10 @@
         <v>0.009985208980020111</v>
       </c>
       <c r="H1787">
-        <v>0.01065226926944432</v>
+        <v>0.01082998579110742</v>
       </c>
       <c r="I1787">
-        <v>-0.01293971057578869</v>
+        <v>-0.07522318891269197</v>
       </c>
       <c r="J1787">
         <v>0.9619420277182702</v>
@@ -91608,10 +91608,10 @@
         <v>5.82</v>
       </c>
       <c r="M1787">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1787">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91634,7 +91634,7 @@
         <v>517</v>
       </c>
       <c r="E1788">
-        <v>1.667730730555679</v>
+        <v>1.730014208892582</v>
       </c>
       <c r="F1788">
         <v>-1</v>
@@ -91643,10 +91643,10 @@
         <v>0.01075150810999869</v>
       </c>
       <c r="H1788">
-        <v>0.01065226926944432</v>
+        <v>0.01082998579110742</v>
       </c>
       <c r="I1788">
-        <v>0.06076115944563387</v>
+        <v>-0.001522318891269414</v>
       </c>
       <c r="J1788">
         <v>0.9619420277182702</v>
@@ -91658,10 +91658,10 @@
         <v>6.24</v>
       </c>
       <c r="M1788">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1788">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91684,7 +91684,7 @@
         <v>517</v>
       </c>
       <c r="E1789">
-        <v>1.667730730555679</v>
+        <v>1.730014208892582</v>
       </c>
       <c r="F1789">
         <v>-1</v>
@@ -91693,10 +91693,10 @@
         <v>0.01107617999387924</v>
       </c>
       <c r="H1789">
-        <v>0.01065226926944432</v>
+        <v>0.01082998579110742</v>
       </c>
       <c r="I1789">
-        <v>0.1160892755650762</v>
+        <v>0.05380579722817291</v>
       </c>
       <c r="J1789">
         <v>0.9619420277182702</v>
@@ -91708,10 +91708,10 @@
         <v>6.43</v>
       </c>
       <c r="M1789">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1789">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1789">
         <v>1</v>
@@ -91734,7 +91734,7 @@
         <v>517</v>
       </c>
       <c r="E1790">
-        <v>1.667730730555679</v>
+        <v>1.730014208892582</v>
       </c>
       <c r="F1790">
         <v>-1</v>
@@ -91743,10 +91743,10 @@
         <v>0.01065303042888996</v>
       </c>
       <c r="H1790">
-        <v>0.01065226926944432</v>
+        <v>0.01082998579110742</v>
       </c>
       <c r="I1790">
-        <v>0.039238840554364</v>
+        <v>-0.02304463778253929</v>
       </c>
       <c r="J1790">
         <v>0.9619420277182702</v>
@@ -91758,10 +91758,10 @@
         <v>6.18</v>
       </c>
       <c r="M1790">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1790">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1790">
         <v>1</v>
@@ -91984,7 +91984,7 @@
         <v>517</v>
       </c>
       <c r="E1795">
-        <v>1.39931371241455</v>
+        <v>1.458148578098677</v>
       </c>
       <c r="F1795">
         <v>-1</v>
@@ -91993,10 +91993,10 @@
         <v>0.0106883560189537</v>
       </c>
       <c r="H1795">
-        <v>0.01092068628758545</v>
+        <v>0.01110185142190132</v>
       </c>
       <c r="I1795">
-        <v>0.01233026863174569</v>
+        <v>-0.04650459705238141</v>
       </c>
       <c r="J1795">
         <v>1.01941890526455</v>
@@ -92008,10 +92008,10 @@
         <v>6.05</v>
       </c>
       <c r="M1795">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1795">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -92034,7 +92034,7 @@
         <v>517</v>
       </c>
       <c r="E1796">
-        <v>1.39931371241455</v>
+        <v>1.458148578098677</v>
       </c>
       <c r="F1796">
         <v>-1</v>
@@ -92043,10 +92043,10 @@
         <v>0.01098126885474339</v>
       </c>
       <c r="H1796">
-        <v>0.01092068628758545</v>
+        <v>0.01110185142190132</v>
       </c>
       <c r="I1796">
-        <v>-0.0005825671579362535</v>
+        <v>-0.05941743284206336</v>
       </c>
       <c r="J1796">
         <v>1.01941890526455</v>
@@ -92058,10 +92058,10 @@
         <v>6.19</v>
       </c>
       <c r="M1796">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1796">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92084,7 +92084,7 @@
         <v>517</v>
       </c>
       <c r="E1797">
-        <v>1.39931371241455</v>
+        <v>1.458148578098677</v>
       </c>
       <c r="F1797">
         <v>-1</v>
@@ -92093,10 +92093,10 @@
         <v>0.0102340838597955</v>
       </c>
       <c r="H1797">
-        <v>0.01092068628758545</v>
+        <v>0.01110185142190132</v>
       </c>
       <c r="I1797">
-        <v>0.006602427789947463</v>
+        <v>-0.05223243789417964</v>
       </c>
       <c r="J1797">
         <v>1.01941890526455</v>
@@ -92108,10 +92108,10 @@
         <v>5.82</v>
       </c>
       <c r="M1797">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1797">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92134,7 +92134,7 @@
         <v>517</v>
       </c>
       <c r="E1798">
-        <v>1.39931371241455</v>
+        <v>1.458148578098677</v>
       </c>
       <c r="F1798">
         <v>-1</v>
@@ -92143,10 +92143,10 @@
         <v>0.01102107466569074</v>
       </c>
       <c r="H1798">
-        <v>0.01092068628758545</v>
+        <v>0.01110185142190132</v>
       </c>
       <c r="I1798">
-        <v>0.05961162189470848</v>
+        <v>0.0007767562105813752</v>
       </c>
       <c r="J1798">
         <v>1.01941890526455</v>
@@ -92158,10 +92158,10 @@
         <v>6.24</v>
       </c>
       <c r="M1798">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1798">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92184,7 +92184,7 @@
         <v>517</v>
       </c>
       <c r="E1799">
-        <v>1.39931371241455</v>
+        <v>1.458148578098677</v>
       </c>
       <c r="F1799">
         <v>-1</v>
@@ -92193,10 +92193,10 @@
         <v>0.01135379331242778</v>
       </c>
       <c r="H1799">
-        <v>0.01092068628758545</v>
+        <v>0.01110185142190132</v>
       </c>
       <c r="I1799">
-        <v>0.1068929751576713</v>
+        <v>0.04805810947354416</v>
       </c>
       <c r="J1799">
         <v>1.01941890526455</v>
@@ -92208,10 +92208,10 @@
         <v>6.43</v>
       </c>
       <c r="M1799">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1799">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1799">
         <v>1</v>
@@ -92234,7 +92234,7 @@
         <v>517</v>
       </c>
       <c r="E1800">
-        <v>1.39931371241455</v>
+        <v>1.458148578098677</v>
       </c>
       <c r="F1800">
         <v>-1</v>
@@ -92243,10 +92243,10 @@
         <v>0.01092029790948016</v>
       </c>
       <c r="H1800">
-        <v>0.01092068628758545</v>
+        <v>0.01110185142190132</v>
       </c>
       <c r="I1800">
-        <v>0.04038837810529028</v>
+        <v>-0.01844648757883682</v>
       </c>
       <c r="J1800">
         <v>1.01941890526455</v>
@@ -92258,10 +92258,10 @@
         <v>6.18</v>
       </c>
       <c r="M1800">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1800">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1800">
         <v>1</v>
@@ -92434,7 +92434,7 @@
         <v>517</v>
       </c>
       <c r="E1804">
-        <v>1.136772783582265</v>
+        <v>1.192234532407733</v>
       </c>
       <c r="F1804">
         <v>-1</v>
@@ -92443,10 +92443,10 @@
         <v>0.01094415071406867</v>
       </c>
       <c r="H1804">
-        <v>0.01118322721641773</v>
+        <v>0.01136776546759227</v>
       </c>
       <c r="I1804">
-        <v>0.01907650234906377</v>
+        <v>-0.03638524647640384</v>
       </c>
       <c r="J1804">
         <v>1.075637519575532</v>
@@ -92458,10 +92458,10 @@
         <v>6.05</v>
       </c>
       <c r="M1804">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1804">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1804">
         <v>1</v>
@@ -92484,7 +92484,7 @@
         <v>517</v>
       </c>
       <c r="E1805">
-        <v>1.136772783582265</v>
+        <v>1.192234532407733</v>
       </c>
       <c r="F1805">
         <v>-1</v>
@@ -92493,10 +92493,10 @@
         <v>0.01047751045976206</v>
       </c>
       <c r="H1805">
-        <v>0.01118322721641773</v>
+        <v>0.01136776546759227</v>
       </c>
       <c r="I1805">
-        <v>0.02571675665568041</v>
+        <v>-0.02974499216978721</v>
       </c>
       <c r="J1805">
         <v>1.075637519575532</v>
@@ -92508,10 +92508,10 @@
         <v>5.82</v>
       </c>
       <c r="M1805">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1805">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1805">
         <v>1</v>
@@ -92534,7 +92534,7 @@
         <v>517</v>
       </c>
       <c r="E1806">
-        <v>1.136772783582265</v>
+        <v>1.192234532407733</v>
       </c>
       <c r="F1806">
         <v>-1</v>
@@ -92543,10 +92543,10 @@
         <v>0.01128473996680925</v>
       </c>
       <c r="H1806">
-        <v>0.01118322721641773</v>
+        <v>0.01136776546759227</v>
       </c>
       <c r="I1806">
-        <v>0.05848724960848894</v>
+        <v>0.003025500783021329</v>
       </c>
       <c r="J1806">
         <v>1.075637519575532</v>
@@ -92558,10 +92558,10 @@
         <v>6.24</v>
       </c>
       <c r="M1806">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1806">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92584,7 +92584,7 @@
         <v>517</v>
       </c>
       <c r="E1807">
-        <v>1.136772783582265</v>
+        <v>1.192234532407733</v>
       </c>
       <c r="F1807">
         <v>-1</v>
@@ -92593,10 +92593,10 @@
         <v>0.01162532921954982</v>
       </c>
       <c r="H1807">
-        <v>0.01118322721641773</v>
+        <v>0.01136776546759227</v>
       </c>
       <c r="I1807">
-        <v>0.09789799686791412</v>
+        <v>0.0424362480424465</v>
       </c>
       <c r="J1807">
         <v>1.075637519575532</v>
@@ -92608,10 +92608,10 @@
         <v>6.43</v>
       </c>
       <c r="M1807">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1807">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1807">
         <v>1</v>
@@ -92634,7 +92634,7 @@
         <v>517</v>
       </c>
       <c r="E1808">
-        <v>1.136772783582265</v>
+        <v>1.192234532407733</v>
       </c>
       <c r="F1808">
         <v>-1</v>
@@ -92643,10 +92643,10 @@
         <v>0.01157684196994133</v>
       </c>
       <c r="H1808">
-        <v>0.01118322721641773</v>
+        <v>0.01136776546759227</v>
       </c>
       <c r="I1808">
-        <v>0.006385246476404483</v>
+        <v>-0.04907650234906313</v>
       </c>
       <c r="J1808">
         <v>1.075637519575532</v>
@@ -92658,10 +92658,10 @@
         <v>6.36</v>
       </c>
       <c r="M1808">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1808">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1808">
         <v>1</v>
@@ -92684,7 +92684,7 @@
         <v>517</v>
       </c>
       <c r="E1809">
-        <v>1.136772783582265</v>
+        <v>1.192234532407733</v>
       </c>
       <c r="F1809">
         <v>-1</v>
@@ -92693,10 +92693,10 @@
         <v>0.01118171446602623</v>
       </c>
       <c r="H1809">
-        <v>0.01118322721641773</v>
+        <v>0.01136776546759227</v>
       </c>
       <c r="I1809">
-        <v>0.04151275039150981</v>
+        <v>-0.0139489984339578</v>
       </c>
       <c r="J1809">
         <v>1.075637519575532</v>
@@ -92708,10 +92708,10 @@
         <v>6.18</v>
       </c>
       <c r="M1809">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1809">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1809">
         <v>1</v>
@@ -92834,7 +92834,7 @@
         <v>517</v>
       </c>
       <c r="E1812">
-        <v>1.073282812133617</v>
+        <v>1.127928843981158</v>
       </c>
       <c r="F1812">
         <v>-1</v>
@@ -92843,10 +92843,10 @@
         <v>0.01100600925156146</v>
       </c>
       <c r="H1812">
-        <v>0.01124671718786638</v>
+        <v>0.01143207115601884</v>
       </c>
       <c r="I1812">
-        <v>0.02070793630491785</v>
+        <v>-0.03393809554262273</v>
       </c>
       <c r="J1812">
         <v>1.089232802540981</v>
@@ -92858,10 +92858,10 @@
         <v>6.05</v>
       </c>
       <c r="M1812">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1812">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1812">
         <v>1</v>
@@ -92884,7 +92884,7 @@
         <v>517</v>
       </c>
       <c r="E1813">
-        <v>1.073282812133617</v>
+        <v>1.127928843981158</v>
       </c>
       <c r="F1813">
         <v>-1</v>
@@ -92893,10 +92893,10 @@
         <v>0.01053637803500245</v>
       </c>
       <c r="H1813">
-        <v>0.01124671718786638</v>
+        <v>0.01143207115601884</v>
       </c>
       <c r="I1813">
-        <v>0.03033915286393363</v>
+        <v>-0.02430687898360695</v>
       </c>
       <c r="J1813">
         <v>1.089232802540981</v>
@@ -92908,10 +92908,10 @@
         <v>5.82</v>
       </c>
       <c r="M1813">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1813">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1813">
         <v>1</v>
@@ -92934,7 +92934,7 @@
         <v>517</v>
       </c>
       <c r="E1814">
-        <v>1.073282812133617</v>
+        <v>1.127928843981158</v>
       </c>
       <c r="F1814">
         <v>-1</v>
@@ -92943,10 +92943,10 @@
         <v>0.0113485018439172</v>
       </c>
       <c r="H1814">
-        <v>0.01124671718786638</v>
+        <v>0.01143207115601884</v>
       </c>
       <c r="I1814">
-        <v>0.05821534394917993</v>
+        <v>0.003569312101639355</v>
       </c>
       <c r="J1814">
         <v>1.089232802540981</v>
@@ -92958,10 +92958,10 @@
         <v>6.24</v>
       </c>
       <c r="M1814">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1814">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1814">
         <v>1</v>
@@ -92984,7 +92984,7 @@
         <v>517</v>
       </c>
       <c r="E1815">
-        <v>1.073282812133617</v>
+        <v>1.127928843981158</v>
       </c>
       <c r="F1815">
         <v>-1</v>
@@ -92993,10 +92993,10 @@
         <v>0.01169099443627294</v>
       </c>
       <c r="H1815">
-        <v>0.01124671718786638</v>
+        <v>0.01143207115601884</v>
       </c>
       <c r="I1815">
-        <v>0.09572275159344201</v>
+        <v>0.04107671974590144</v>
       </c>
       <c r="J1815">
         <v>1.089232802540981</v>
@@ -93008,10 +93008,10 @@
         <v>6.43</v>
       </c>
       <c r="M1815">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1815">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1815">
         <v>1</v>
@@ -93034,7 +93034,7 @@
         <v>517</v>
       </c>
       <c r="E1816">
-        <v>1.073282812133617</v>
+        <v>1.127928843981158</v>
       </c>
       <c r="F1816">
         <v>-1</v>
@@ -93043,10 +93043,10 @@
         <v>0.01124493253181556</v>
       </c>
       <c r="H1816">
-        <v>0.01124671718786638</v>
+        <v>0.01143207115601884</v>
       </c>
       <c r="I1816">
-        <v>0.04178465605081882</v>
+        <v>-0.01286137579672175</v>
       </c>
       <c r="J1816">
         <v>1.089232802540981</v>
@@ -93058,10 +93058,10 @@
         <v>6.18</v>
       </c>
       <c r="M1816">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="N1816">
-        <v>6.16</v>
+        <v>6.28</v>
       </c>
       <c r="O1816">
         <v>1</v>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5481" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5472" uniqueCount="632">
   <si>
     <t>trade_time</t>
   </si>
@@ -1060,9 +1060,6 @@
     <t>2021-06-25</t>
   </si>
   <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
     <t>2021-07-27</t>
   </si>
   <si>
@@ -1075,16 +1072,19 @@
     <t>2021-10-15</t>
   </si>
   <si>
+    <t>2021-10-20</t>
+  </si>
+  <si>
     <t>2021-10-25</t>
   </si>
   <si>
     <t>2021-10-28</t>
   </si>
   <si>
-    <t>2021-09-16</t>
+    <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-05-27</t>
+    <t>2021-09-16</t>
   </si>
   <si>
     <t>2021-09-08</t>
@@ -1567,7 +1567,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-11-02</t>
+    <t>2021-11-03</t>
   </si>
   <si>
     <t>2016-03-09</t>
@@ -2267,7 +2267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1823"/>
+  <dimension ref="A1:P1820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91325,40 +91325,40 @@
         <v>348</v>
       </c>
       <c r="C1782">
-        <v>1.302297687229486</v>
+        <v>1.787560005246361</v>
       </c>
       <c r="D1782" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E1782">
-        <v>1.515827831941592</v>
+        <v>1.415657106632275</v>
       </c>
       <c r="F1782">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1782">
-        <v>0.01051770231277051</v>
+        <v>0.009752439994753639</v>
       </c>
       <c r="H1782">
-        <v>0.01040417216805841</v>
+        <v>0.009284342893367726</v>
       </c>
       <c r="I1782">
-        <v>0.2135301447121059</v>
+        <v>0.3719028986140867</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1782">
-        <v>4.79</v>
+        <v>4.14</v>
       </c>
       <c r="L1782">
-        <v>5.91</v>
+        <v>5.77</v>
       </c>
       <c r="M1782">
-        <v>4.62</v>
+        <v>4.09</v>
       </c>
       <c r="N1782">
-        <v>5.96</v>
+        <v>5.35</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91375,40 +91375,40 @@
         <v>349</v>
       </c>
       <c r="C1783">
-        <v>1.787560005246361</v>
+        <v>1.730985222751716</v>
       </c>
       <c r="D1783" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E1783">
-        <v>1.415657106632275</v>
+        <v>2.001641454990602</v>
       </c>
       <c r="F1783">
         <v>-1</v>
       </c>
       <c r="G1783">
-        <v>0.009752439994753639</v>
+        <v>0.009869014777248284</v>
       </c>
       <c r="H1783">
-        <v>0.009284342893367726</v>
+        <v>0.0106783585450094</v>
       </c>
       <c r="I1783">
-        <v>0.3719028986140867</v>
+        <v>-0.2706562322388857</v>
       </c>
       <c r="J1783">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1783">
-        <v>4.14</v>
+        <v>4.23</v>
       </c>
       <c r="L1783">
-        <v>5.77</v>
+        <v>5.8</v>
       </c>
       <c r="M1783">
-        <v>4.09</v>
+        <v>4.51</v>
       </c>
       <c r="N1783">
-        <v>5.35</v>
+        <v>6.34</v>
       </c>
       <c r="O1783">
         <v>1</v>
@@ -91425,40 +91425,40 @@
         <v>350</v>
       </c>
       <c r="C1784">
-        <v>1.730985222751716</v>
+        <v>1.728491890001313</v>
       </c>
       <c r="D1784" t="s">
         <v>517</v>
       </c>
       <c r="E1784">
-        <v>2.043544353604688</v>
+        <v>2.001641454990602</v>
       </c>
       <c r="F1784">
         <v>-1</v>
       </c>
       <c r="G1784">
-        <v>0.009869014777248284</v>
+        <v>0.01075150810999869</v>
       </c>
       <c r="H1784">
-        <v>0.01081645564639531</v>
+        <v>0.0106783585450094</v>
       </c>
       <c r="I1784">
-        <v>-0.3125591308529714</v>
+        <v>-0.2731495649892892</v>
       </c>
       <c r="J1784">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1784">
-        <v>4.23</v>
+        <v>4.69</v>
       </c>
       <c r="L1784">
-        <v>5.8</v>
+        <v>6.24</v>
       </c>
       <c r="M1784">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1784">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1784">
         <v>1</v>
@@ -91475,40 +91475,40 @@
         <v>351</v>
       </c>
       <c r="C1785">
-        <v>1.728491890001313</v>
+        <v>1.783820006120755</v>
       </c>
       <c r="D1785" t="s">
         <v>517</v>
       </c>
       <c r="E1785">
-        <v>2.043544353604688</v>
+        <v>2.001641454990602</v>
       </c>
       <c r="F1785">
         <v>-1</v>
       </c>
       <c r="G1785">
-        <v>0.01075150810999869</v>
+        <v>0.01107617999387924</v>
       </c>
       <c r="H1785">
-        <v>0.01081645564639531</v>
+        <v>0.0106783585450094</v>
       </c>
       <c r="I1785">
-        <v>-0.3150524636033749</v>
+        <v>-0.2178214488698469</v>
       </c>
       <c r="J1785">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1785">
-        <v>4.69</v>
+        <v>4.83</v>
       </c>
       <c r="L1785">
-        <v>6.24</v>
+        <v>6.43</v>
       </c>
       <c r="M1785">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1785">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91525,40 +91525,40 @@
         <v>352</v>
       </c>
       <c r="C1786">
-        <v>1.783820006120755</v>
+        <v>1.69458116556639</v>
       </c>
       <c r="D1786" t="s">
         <v>517</v>
       </c>
       <c r="E1786">
-        <v>2.043544353604688</v>
+        <v>2.001641454990602</v>
       </c>
       <c r="F1786">
         <v>-1</v>
       </c>
       <c r="G1786">
-        <v>0.01107617999387924</v>
+        <v>0.01102541883443361</v>
       </c>
       <c r="H1786">
-        <v>0.01081645564639531</v>
+        <v>0.0106783585450094</v>
       </c>
       <c r="I1786">
-        <v>-0.2597243474839326</v>
+        <v>-0.3070602894242116</v>
       </c>
       <c r="J1786">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1786">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="L1786">
-        <v>6.43</v>
+        <v>6.36</v>
       </c>
       <c r="M1786">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1786">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1786">
         <v>1</v>
@@ -91581,7 +91581,7 @@
         <v>517</v>
       </c>
       <c r="E1787">
-        <v>2.043544353604688</v>
+        <v>2.001641454990602</v>
       </c>
       <c r="F1787">
         <v>-1</v>
@@ -91590,10 +91590,10 @@
         <v>0.01065303042888996</v>
       </c>
       <c r="H1787">
-        <v>0.01081645564639531</v>
+        <v>0.0106783585450094</v>
       </c>
       <c r="I1787">
-        <v>-0.3365747824946448</v>
+        <v>-0.2946718838805591</v>
       </c>
       <c r="J1787">
         <v>0.9619420277182702</v>
@@ -91605,10 +91605,10 @@
         <v>6.18</v>
       </c>
       <c r="M1787">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1787">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91631,7 +91631,7 @@
         <v>517</v>
       </c>
       <c r="E1788">
-        <v>2.043544353604688</v>
+        <v>2.001641454990602</v>
       </c>
       <c r="F1788">
         <v>-1</v>
@@ -91640,10 +91640,10 @@
         <v>0.01082998579110742</v>
       </c>
       <c r="H1788">
-        <v>0.01081645564639531</v>
+        <v>0.0106783585450094</v>
       </c>
       <c r="I1788">
-        <v>-0.3135301447121055</v>
+        <v>-0.2716272460980198</v>
       </c>
       <c r="J1788">
         <v>0.9619420277182702</v>
@@ -91655,10 +91655,10 @@
         <v>6.28</v>
       </c>
       <c r="M1788">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1788">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91772,7 +91772,7 @@
         <v>2</v>
       </c>
       <c r="B1791" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C1791">
         <v>1.549605732204761</v>
@@ -91822,43 +91822,43 @@
         <v>3</v>
       </c>
       <c r="B1792" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C1792">
-        <v>1.428246408836243</v>
+        <v>1.487858030730951</v>
       </c>
       <c r="D1792" t="s">
         <v>517</v>
       </c>
       <c r="E1792">
-        <v>1.78144979199365</v>
+        <v>1.742420737256878</v>
       </c>
       <c r="F1792">
         <v>-1</v>
       </c>
       <c r="G1792">
-        <v>0.01001175359116376</v>
+        <v>0.01011214196926905</v>
       </c>
       <c r="H1792">
-        <v>0.01107855020800635</v>
+        <v>0.01093757926274312</v>
       </c>
       <c r="I1792">
-        <v>-0.3532033831574077</v>
+        <v>-0.2545627065259266</v>
       </c>
       <c r="J1792">
         <v>1.01941890526455</v>
       </c>
       <c r="K1792">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="L1792">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="M1792">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1792">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91872,7 +91872,7 @@
         <v>4</v>
       </c>
       <c r="B1793" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C1793">
         <v>1.458925334309258</v>
@@ -91881,7 +91881,7 @@
         <v>517</v>
       </c>
       <c r="E1793">
-        <v>1.78144979199365</v>
+        <v>1.742420737256878</v>
       </c>
       <c r="F1793">
         <v>-1</v>
@@ -91890,10 +91890,10 @@
         <v>0.01102107466569074</v>
       </c>
       <c r="H1793">
-        <v>0.01107855020800635</v>
+        <v>0.01093757926274312</v>
       </c>
       <c r="I1793">
-        <v>-0.3225244576843922</v>
+        <v>-0.2834954029476195</v>
       </c>
       <c r="J1793">
         <v>1.01941890526455</v>
@@ -91905,10 +91905,10 @@
         <v>6.24</v>
       </c>
       <c r="M1793">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1793">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -91922,7 +91922,7 @@
         <v>5</v>
       </c>
       <c r="B1794" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C1794">
         <v>1.506206687572221</v>
@@ -91931,7 +91931,7 @@
         <v>517</v>
       </c>
       <c r="E1794">
-        <v>1.78144979199365</v>
+        <v>1.742420737256878</v>
       </c>
       <c r="F1794">
         <v>-1</v>
@@ -91940,10 +91940,10 @@
         <v>0.01135379331242778</v>
       </c>
       <c r="H1794">
-        <v>0.01107855020800635</v>
+        <v>0.01093757926274312</v>
       </c>
       <c r="I1794">
-        <v>-0.2752431044214294</v>
+        <v>-0.2362140496846568</v>
       </c>
       <c r="J1794">
         <v>1.01941890526455</v>
@@ -91955,10 +91955,10 @@
         <v>6.43</v>
       </c>
       <c r="M1794">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1794">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1794">
         <v>1</v>
@@ -91981,7 +91981,7 @@
         <v>517</v>
       </c>
       <c r="E1795">
-        <v>1.78144979199365</v>
+        <v>1.742420737256878</v>
       </c>
       <c r="F1795">
         <v>-1</v>
@@ -91990,10 +91990,10 @@
         <v>0.01092029790948016</v>
       </c>
       <c r="H1795">
-        <v>0.01107855020800635</v>
+        <v>0.01093757926274312</v>
       </c>
       <c r="I1795">
-        <v>-0.3417477014738104</v>
+        <v>-0.3027186467370377</v>
       </c>
       <c r="J1795">
         <v>1.01941890526455</v>
@@ -92005,10 +92005,10 @@
         <v>6.18</v>
       </c>
       <c r="M1795">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1795">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -92031,7 +92031,7 @@
         <v>517</v>
       </c>
       <c r="E1796">
-        <v>1.78144979199365</v>
+        <v>1.742420737256878</v>
       </c>
       <c r="F1796">
         <v>-1</v>
@@ -92040,10 +92040,10 @@
         <v>0.01110185142190132</v>
       </c>
       <c r="H1796">
-        <v>0.01107855020800635</v>
+        <v>0.01093757926274312</v>
       </c>
       <c r="I1796">
-        <v>-0.3233012138949736</v>
+        <v>-0.2842721591582009</v>
       </c>
       <c r="J1796">
         <v>1.01941890526455</v>
@@ -92055,10 +92055,10 @@
         <v>6.28</v>
       </c>
       <c r="M1796">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1796">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92072,7 +92072,7 @@
         <v>0</v>
       </c>
       <c r="B1797" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C1797">
         <v>0.7149171399855092</v>
@@ -92122,7 +92122,7 @@
         <v>1</v>
       </c>
       <c r="B1798" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C1798">
         <v>1.316860668957297</v>
@@ -92172,7 +92172,7 @@
         <v>2</v>
       </c>
       <c r="B1799" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C1799">
         <v>1.191566042587009</v>
@@ -92181,7 +92181,7 @@
         <v>517</v>
       </c>
       <c r="E1799">
-        <v>1.525092910735574</v>
+        <v>1.488874786714351</v>
       </c>
       <c r="F1799">
         <v>-1</v>
@@ -92190,10 +92190,10 @@
         <v>0.01024843395741299</v>
       </c>
       <c r="H1799">
-        <v>0.01133490708926443</v>
+        <v>0.01119112521328565</v>
       </c>
       <c r="I1799">
-        <v>-0.3335268681485646</v>
+        <v>-0.2973087441273412</v>
       </c>
       <c r="J1799">
         <v>1.075637519575532</v>
@@ -92205,10 +92205,10 @@
         <v>5.72</v>
       </c>
       <c r="M1799">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1799">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1799">
         <v>1</v>
@@ -92222,7 +92222,7 @@
         <v>3</v>
       </c>
       <c r="B1800" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C1800">
         <v>1.195260033190754</v>
@@ -92231,7 +92231,7 @@
         <v>517</v>
       </c>
       <c r="E1800">
-        <v>1.525092910735574</v>
+        <v>1.488874786714351</v>
       </c>
       <c r="F1800">
         <v>-1</v>
@@ -92240,10 +92240,10 @@
         <v>0.01128473996680925</v>
       </c>
       <c r="H1800">
-        <v>0.01133490708926443</v>
+        <v>0.01119112521328565</v>
       </c>
       <c r="I1800">
-        <v>-0.3298328775448196</v>
+        <v>-0.2936147535235962</v>
       </c>
       <c r="J1800">
         <v>1.075637519575532</v>
@@ -92255,10 +92255,10 @@
         <v>6.24</v>
       </c>
       <c r="M1800">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1800">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1800">
         <v>1</v>
@@ -92272,7 +92272,7 @@
         <v>4</v>
       </c>
       <c r="B1801" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C1801">
         <v>1.23467078045018</v>
@@ -92281,7 +92281,7 @@
         <v>517</v>
       </c>
       <c r="E1801">
-        <v>1.525092910735574</v>
+        <v>1.488874786714351</v>
       </c>
       <c r="F1801">
         <v>-1</v>
@@ -92290,10 +92290,10 @@
         <v>0.01162532921954982</v>
       </c>
       <c r="H1801">
-        <v>0.01133490708926443</v>
+        <v>0.01119112521328565</v>
       </c>
       <c r="I1801">
-        <v>-0.2904221302853944</v>
+        <v>-0.2542040062641711</v>
       </c>
       <c r="J1801">
         <v>1.075637519575532</v>
@@ -92305,10 +92305,10 @@
         <v>6.43</v>
       </c>
       <c r="M1801">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1801">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1801">
         <v>1</v>
@@ -92322,43 +92322,43 @@
         <v>5</v>
       </c>
       <c r="B1802" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C1802">
-        <v>1.178285533973775</v>
+        <v>1.192234532407733</v>
       </c>
       <c r="D1802" t="s">
         <v>517</v>
       </c>
       <c r="E1802">
-        <v>1.525092910735574</v>
+        <v>1.488874786714351</v>
       </c>
       <c r="F1802">
         <v>-1</v>
       </c>
       <c r="G1802">
-        <v>0.01118171446602623</v>
+        <v>0.01136776546759227</v>
       </c>
       <c r="H1802">
-        <v>0.01133490708926443</v>
+        <v>0.01119112521328565</v>
       </c>
       <c r="I1802">
-        <v>-0.3468073767617987</v>
+        <v>-0.2966402543066176</v>
       </c>
       <c r="J1802">
         <v>1.075637519575532</v>
       </c>
       <c r="K1802">
-        <v>4.65</v>
+        <v>4.73</v>
       </c>
       <c r="L1802">
-        <v>6.18</v>
+        <v>6.28</v>
       </c>
       <c r="M1802">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1802">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1802">
         <v>1</v>
@@ -92369,346 +92369,346 @@
     </row>
     <row r="1803" spans="1:16">
       <c r="A1803" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1803" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C1803">
-        <v>1.192234532407733</v>
+        <v>1.260576197480336</v>
       </c>
       <c r="D1803" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E1803">
-        <v>1.525092910735574</v>
+        <v>0.8950378376073855</v>
       </c>
       <c r="F1803">
         <v>-1</v>
       </c>
       <c r="G1803">
-        <v>0.01136776546759227</v>
+        <v>0.01027942380251966</v>
       </c>
       <c r="H1803">
-        <v>0.01133490708926443</v>
+        <v>0.009804962162392614</v>
       </c>
       <c r="I1803">
-        <v>-0.3328583783278409</v>
+        <v>0.3655383598729509</v>
       </c>
       <c r="J1803">
-        <v>1.075637519575532</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1803">
-        <v>4.73</v>
+        <v>4.14</v>
       </c>
       <c r="L1803">
-        <v>6.28</v>
+        <v>5.77</v>
       </c>
       <c r="M1803">
-        <v>4.56</v>
+        <v>4.09</v>
       </c>
       <c r="N1803">
-        <v>6.43</v>
+        <v>5.35</v>
       </c>
       <c r="O1803">
         <v>1</v>
       </c>
       <c r="P1803" t="s">
-        <v>628</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1804" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C1804">
-        <v>1.260576197480336</v>
+        <v>1.134329901302468</v>
       </c>
       <c r="D1804" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E1804">
-        <v>0.8950378376073855</v>
+        <v>1.427560060540173</v>
       </c>
       <c r="F1804">
         <v>-1</v>
       </c>
       <c r="G1804">
-        <v>0.01027942380251966</v>
+        <v>0.01030567009869753</v>
       </c>
       <c r="H1804">
-        <v>0.009804962162392614</v>
+        <v>0.01125243993945983</v>
       </c>
       <c r="I1804">
-        <v>0.3655383598729509</v>
+        <v>-0.2932301592377051</v>
       </c>
       <c r="J1804">
         <v>1.089232802540981</v>
       </c>
       <c r="K1804">
-        <v>4.14</v>
+        <v>4.21</v>
       </c>
       <c r="L1804">
-        <v>5.77</v>
+        <v>5.72</v>
       </c>
       <c r="M1804">
-        <v>4.09</v>
+        <v>4.51</v>
       </c>
       <c r="N1804">
-        <v>5.35</v>
+        <v>6.34</v>
       </c>
       <c r="O1804">
         <v>1</v>
       </c>
       <c r="P1804" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1805" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C1805">
-        <v>1.134329901302468</v>
+        <v>1.131498156082797</v>
       </c>
       <c r="D1805" t="s">
         <v>517</v>
       </c>
       <c r="E1805">
-        <v>1.463098420413125</v>
+        <v>1.427560060540173</v>
       </c>
       <c r="F1805">
         <v>-1</v>
       </c>
       <c r="G1805">
-        <v>0.01030567009869753</v>
+        <v>0.0113485018439172</v>
       </c>
       <c r="H1805">
-        <v>0.01139690157958687</v>
+        <v>0.01125243993945983</v>
       </c>
       <c r="I1805">
-        <v>-0.3287685191106569</v>
+        <v>-0.2960619044573765</v>
       </c>
       <c r="J1805">
         <v>1.089232802540981</v>
       </c>
       <c r="K1805">
-        <v>4.21</v>
+        <v>4.69</v>
       </c>
       <c r="L1805">
-        <v>5.72</v>
+        <v>6.24</v>
       </c>
       <c r="M1805">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1805">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1805">
         <v>1</v>
       </c>
       <c r="P1805" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1806" t="s">
         <v>351</v>
       </c>
       <c r="C1806">
-        <v>1.131498156082797</v>
+        <v>1.169005563727059</v>
       </c>
       <c r="D1806" t="s">
         <v>517</v>
       </c>
       <c r="E1806">
-        <v>1.463098420413125</v>
+        <v>1.427560060540173</v>
       </c>
       <c r="F1806">
         <v>-1</v>
       </c>
       <c r="G1806">
-        <v>0.0113485018439172</v>
+        <v>0.01169099443627294</v>
       </c>
       <c r="H1806">
-        <v>0.01139690157958687</v>
+        <v>0.01125243993945983</v>
       </c>
       <c r="I1806">
-        <v>-0.3316002643303282</v>
+        <v>-0.2585544968131144</v>
       </c>
       <c r="J1806">
         <v>1.089232802540981</v>
       </c>
       <c r="K1806">
-        <v>4.69</v>
+        <v>4.83</v>
       </c>
       <c r="L1806">
-        <v>6.24</v>
+        <v>6.43</v>
       </c>
       <c r="M1806">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1806">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1806">
         <v>1</v>
       </c>
       <c r="P1806" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1807" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C1807">
-        <v>1.169005563727059</v>
+        <v>1.127928843981158</v>
       </c>
       <c r="D1807" t="s">
         <v>517</v>
       </c>
       <c r="E1807">
-        <v>1.463098420413125</v>
+        <v>1.427560060540173</v>
       </c>
       <c r="F1807">
         <v>-1</v>
       </c>
       <c r="G1807">
-        <v>0.01169099443627294</v>
+        <v>0.01143207115601884</v>
       </c>
       <c r="H1807">
-        <v>0.01139690157958687</v>
+        <v>0.01125243993945983</v>
       </c>
       <c r="I1807">
-        <v>-0.2940928566860661</v>
+        <v>-0.2996312165590158</v>
       </c>
       <c r="J1807">
         <v>1.089232802540981</v>
       </c>
       <c r="K1807">
-        <v>4.83</v>
+        <v>4.73</v>
       </c>
       <c r="L1807">
-        <v>6.43</v>
+        <v>6.28</v>
       </c>
       <c r="M1807">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="N1807">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="O1807">
         <v>1</v>
       </c>
       <c r="P1807" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1808" spans="1:16">
       <c r="A1808" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1808" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C1808">
-        <v>1.127928843981158</v>
+        <v>1.427808430496056</v>
       </c>
       <c r="D1808" t="s">
-        <v>517</v>
+        <v>349</v>
       </c>
       <c r="E1808">
-        <v>1.463098420413125</v>
+        <v>1.595242416523244</v>
       </c>
       <c r="F1808">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1808">
-        <v>0.01143207115601884</v>
+        <v>0.01069219156950394</v>
       </c>
       <c r="H1808">
-        <v>0.01139690157958687</v>
+        <v>0.01000475758347676</v>
       </c>
       <c r="I1808">
-        <v>-0.3351695764319675</v>
+        <v>0.1674339860271878</v>
       </c>
       <c r="J1808">
-        <v>1.089232802540981</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1808">
-        <v>4.73</v>
+        <v>4.66</v>
       </c>
       <c r="L1808">
-        <v>6.28</v>
+        <v>6.06</v>
       </c>
       <c r="M1808">
-        <v>4.56</v>
+        <v>4.23</v>
       </c>
       <c r="N1808">
-        <v>6.43</v>
+        <v>5.8</v>
       </c>
       <c r="O1808">
         <v>1</v>
       </c>
       <c r="P1808" t="s">
-        <v>356</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1809" spans="1:16">
       <c r="A1809" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1809" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C1809">
-        <v>1.427808430496056</v>
+        <v>1.415719814471675</v>
       </c>
       <c r="D1809" t="s">
         <v>350</v>
       </c>
       <c r="E1809">
-        <v>1.595242416523244</v>
+        <v>1.577987454726718</v>
       </c>
       <c r="F1809">
         <v>1</v>
       </c>
       <c r="G1809">
-        <v>0.01069219156950394</v>
+        <v>0.009984280185528325</v>
       </c>
       <c r="H1809">
-        <v>0.01000475758347676</v>
+        <v>0.01090201254527328</v>
       </c>
       <c r="I1809">
-        <v>0.1674339860271878</v>
+        <v>0.1622676402550427</v>
       </c>
       <c r="J1809">
         <v>0.994032525644623</v>
       </c>
       <c r="K1809">
-        <v>4.66</v>
+        <v>4.31</v>
       </c>
       <c r="L1809">
-        <v>6.06</v>
+        <v>5.7</v>
       </c>
       <c r="M1809">
-        <v>4.23</v>
+        <v>4.69</v>
       </c>
       <c r="N1809">
-        <v>5.8</v>
+        <v>6.24</v>
       </c>
       <c r="O1809">
         <v>1</v>
@@ -92719,46 +92719,46 @@
     </row>
     <row r="1810" spans="1:16">
       <c r="A1810" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1810" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C1810">
-        <v>1.415719814471675</v>
+        <v>1.848285828444487</v>
       </c>
       <c r="D1810" t="s">
-        <v>351</v>
+        <v>517</v>
       </c>
       <c r="E1810">
-        <v>1.577987454726718</v>
+        <v>1.85691330934275</v>
       </c>
       <c r="F1810">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1810">
-        <v>0.009984280185528325</v>
+        <v>0.01127171417155551</v>
       </c>
       <c r="H1810">
-        <v>0.01090201254527328</v>
+        <v>0.01082308669065725</v>
       </c>
       <c r="I1810">
-        <v>0.1622676402550427</v>
+        <v>-0.008627480898263151</v>
       </c>
       <c r="J1810">
         <v>0.994032525644623</v>
       </c>
       <c r="K1810">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="L1810">
-        <v>5.7</v>
+        <v>6.56</v>
       </c>
       <c r="M1810">
-        <v>4.69</v>
+        <v>4.51</v>
       </c>
       <c r="N1810">
-        <v>6.24</v>
+        <v>6.34</v>
       </c>
       <c r="O1810">
         <v>1</v>
@@ -92769,96 +92769,96 @@
     </row>
     <row r="1811" spans="1:16">
       <c r="A1811" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1811" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C1811">
-        <v>1.848285828444487</v>
+        <v>1.091573753380461</v>
       </c>
       <c r="D1811" t="s">
-        <v>517</v>
+        <v>356</v>
       </c>
       <c r="E1811">
-        <v>1.89721168306052</v>
+        <v>1.231357403805094</v>
       </c>
       <c r="F1811">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1811">
-        <v>0.01127171417155551</v>
+        <v>0.01102842624661954</v>
       </c>
       <c r="H1811">
-        <v>0.01096278831693948</v>
+        <v>0.01020864259619491</v>
       </c>
       <c r="I1811">
-        <v>-0.04892585461603272</v>
+        <v>0.1397836504246337</v>
       </c>
       <c r="J1811">
-        <v>0.994032525644623</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1811">
-        <v>4.74</v>
+        <v>4.66</v>
       </c>
       <c r="L1811">
-        <v>6.56</v>
+        <v>6.06</v>
       </c>
       <c r="M1811">
-        <v>4.56</v>
+        <v>4.21</v>
       </c>
       <c r="N1811">
-        <v>6.43</v>
+        <v>5.72</v>
       </c>
       <c r="O1811">
         <v>1</v>
       </c>
       <c r="P1811" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1812" spans="1:16">
       <c r="A1812" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1812" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C1812">
-        <v>1.091573753380461</v>
+        <v>1.088782084736915</v>
       </c>
       <c r="D1812" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E1812">
-        <v>1.231357403805094</v>
+        <v>1.239588176685485</v>
       </c>
       <c r="F1812">
         <v>1</v>
       </c>
       <c r="G1812">
-        <v>0.01102842624661954</v>
+        <v>0.01047121791526309</v>
       </c>
       <c r="H1812">
-        <v>0.01020864259619491</v>
+        <v>0.01124041182331452</v>
       </c>
       <c r="I1812">
-        <v>0.1397836504246337</v>
+        <v>0.1508060919485699</v>
       </c>
       <c r="J1812">
         <v>1.066185889832519</v>
       </c>
       <c r="K1812">
-        <v>4.66</v>
+        <v>4.4</v>
       </c>
       <c r="L1812">
-        <v>6.06</v>
+        <v>5.78</v>
       </c>
       <c r="M1812">
-        <v>4.21</v>
+        <v>4.69</v>
       </c>
       <c r="N1812">
-        <v>5.72</v>
+        <v>6.24</v>
       </c>
       <c r="O1812">
         <v>1</v>
@@ -92869,46 +92869,46 @@
     </row>
     <row r="1813" spans="1:16">
       <c r="A1813" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1813" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1813">
-        <v>1.088782084736915</v>
+        <v>1.093631446600559</v>
       </c>
       <c r="D1813" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E1813">
-        <v>1.239588176685485</v>
+        <v>1.236940741092184</v>
       </c>
       <c r="F1813">
         <v>1</v>
       </c>
       <c r="G1813">
-        <v>0.01047121791526309</v>
+        <v>0.01128636855339944</v>
       </c>
       <c r="H1813">
-        <v>0.01124041182331452</v>
+        <v>0.01132305925890782</v>
       </c>
       <c r="I1813">
-        <v>0.1508060919485699</v>
+        <v>0.1433092944916252</v>
       </c>
       <c r="J1813">
         <v>1.066185889832519</v>
       </c>
       <c r="K1813">
-        <v>4.4</v>
+        <v>4.78</v>
       </c>
       <c r="L1813">
-        <v>5.78</v>
+        <v>6.19</v>
       </c>
       <c r="M1813">
-        <v>4.69</v>
+        <v>4.73</v>
       </c>
       <c r="N1813">
-        <v>6.24</v>
+        <v>6.28</v>
       </c>
       <c r="O1813">
         <v>1</v>
@@ -92919,46 +92919,46 @@
     </row>
     <row r="1814" spans="1:16">
       <c r="A1814" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1814" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C1814">
-        <v>1.093631446600559</v>
+        <v>1.506278882193858</v>
       </c>
       <c r="D1814" t="s">
-        <v>353</v>
+        <v>517</v>
       </c>
       <c r="E1814">
-        <v>1.222235612278785</v>
+        <v>1.531501636855339</v>
       </c>
       <c r="F1814">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1814">
-        <v>0.01128636855339944</v>
+        <v>0.01161372111780614</v>
       </c>
       <c r="H1814">
-        <v>0.01113776438772121</v>
+        <v>0.01114849836314466</v>
       </c>
       <c r="I1814">
-        <v>0.1286041656782269</v>
+        <v>-0.02522275466148027</v>
       </c>
       <c r="J1814">
         <v>1.066185889832519</v>
       </c>
       <c r="K1814">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="L1814">
-        <v>6.19</v>
+        <v>6.56</v>
       </c>
       <c r="M1814">
-        <v>4.65</v>
+        <v>4.51</v>
       </c>
       <c r="N1814">
-        <v>6.18</v>
+        <v>6.34</v>
       </c>
       <c r="O1814">
         <v>1</v>
@@ -92969,96 +92969,96 @@
     </row>
     <row r="1815" spans="1:16">
       <c r="A1815" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1815" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C1815">
-        <v>1.506278882193858</v>
+        <v>0.9462796035341885</v>
       </c>
       <c r="D1815" t="s">
-        <v>517</v>
+        <v>350</v>
       </c>
       <c r="E1815">
-        <v>1.568192342363713</v>
+        <v>1.087693486494396</v>
       </c>
       <c r="F1815">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1815">
-        <v>0.01161372111780614</v>
+        <v>0.01061372039646581</v>
       </c>
       <c r="H1815">
-        <v>0.01129180765763629</v>
+        <v>0.01139230651350561</v>
       </c>
       <c r="I1815">
-        <v>-0.06191346016985477</v>
+        <v>0.1414138829602072</v>
       </c>
       <c r="J1815">
-        <v>1.066185889832519</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1815">
-        <v>4.74</v>
+        <v>4.4</v>
       </c>
       <c r="L1815">
-        <v>6.56</v>
+        <v>5.78</v>
       </c>
       <c r="M1815">
-        <v>4.56</v>
+        <v>4.69</v>
       </c>
       <c r="N1815">
-        <v>6.43</v>
+        <v>6.24</v>
       </c>
       <c r="O1815">
         <v>1</v>
       </c>
       <c r="P1815" t="s">
-        <v>630</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1816" spans="1:16">
       <c r="A1816" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1816" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C1816">
-        <v>0.9527648456254667</v>
+        <v>0.9388219329303231</v>
       </c>
       <c r="D1816" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E1816">
-        <v>1.095008438836121</v>
+        <v>1.083750573799252</v>
       </c>
       <c r="F1816">
         <v>1</v>
       </c>
       <c r="G1816">
-        <v>0.01136723515437453</v>
+        <v>0.01144117806706968</v>
       </c>
       <c r="H1816">
-        <v>0.01034499156116388</v>
+        <v>0.01147624942620075</v>
       </c>
       <c r="I1816">
-        <v>0.1422435932106545</v>
+        <v>0.1449286408689288</v>
       </c>
       <c r="J1816">
         <v>1.098572817378594</v>
       </c>
       <c r="K1816">
-        <v>4.74</v>
+        <v>4.78</v>
       </c>
       <c r="L1816">
-        <v>6.16</v>
+        <v>6.19</v>
       </c>
       <c r="M1816">
-        <v>4.21</v>
+        <v>4.73</v>
       </c>
       <c r="N1816">
-        <v>5.72</v>
+        <v>6.28</v>
       </c>
       <c r="O1816">
         <v>1</v>
@@ -93069,46 +93069,46 @@
     </row>
     <row r="1817" spans="1:16">
       <c r="A1817" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1817" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C1817">
-        <v>0.9462796035341885</v>
+        <v>1.352764845625466</v>
       </c>
       <c r="D1817" t="s">
-        <v>351</v>
+        <v>517</v>
       </c>
       <c r="E1817">
-        <v>1.087693486494396</v>
+        <v>1.385436593622543</v>
       </c>
       <c r="F1817">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1817">
-        <v>0.01061372039646581</v>
+        <v>0.01176723515437453</v>
       </c>
       <c r="H1817">
-        <v>0.01139230651350561</v>
+        <v>0.01129456340637746</v>
       </c>
       <c r="I1817">
-        <v>0.1414138829602072</v>
+        <v>-0.03267174799707728</v>
       </c>
       <c r="J1817">
         <v>1.098572817378594</v>
       </c>
       <c r="K1817">
-        <v>4.4</v>
+        <v>4.74</v>
       </c>
       <c r="L1817">
-        <v>5.78</v>
+        <v>6.56</v>
       </c>
       <c r="M1817">
-        <v>4.69</v>
+        <v>4.51</v>
       </c>
       <c r="N1817">
-        <v>6.24</v>
+        <v>6.34</v>
       </c>
       <c r="O1817">
         <v>1</v>
@@ -93119,301 +93119,151 @@
     </row>
     <row r="1818" spans="1:16">
       <c r="A1818" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1818" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C1818">
-        <v>0.9388219329303231</v>
+        <v>0.8652138986958411</v>
       </c>
       <c r="D1818" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E1818">
-        <v>1.071636399189539</v>
+        <v>1.017246943778374</v>
       </c>
       <c r="F1818">
         <v>1</v>
       </c>
       <c r="G1818">
-        <v>0.01144117806706968</v>
+        <v>0.01145478610130416</v>
       </c>
       <c r="H1818">
-        <v>0.01128836360081046</v>
+        <v>0.01042275305622163</v>
       </c>
       <c r="I1818">
-        <v>0.1328144662592159</v>
+        <v>0.1520330450825327</v>
       </c>
       <c r="J1818">
-        <v>1.098572817378594</v>
+        <v>1.117043481287797</v>
       </c>
       <c r="K1818">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="L1818">
-        <v>6.19</v>
+        <v>6.16</v>
       </c>
       <c r="M1818">
-        <v>4.65</v>
+        <v>4.21</v>
       </c>
       <c r="N1818">
-        <v>6.18</v>
+        <v>5.72</v>
       </c>
       <c r="O1818">
         <v>1</v>
       </c>
       <c r="P1818" t="s">
-        <v>357</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1819" spans="1:16">
       <c r="A1819" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1819" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C1819">
-        <v>1.352764845625466</v>
+        <v>0.8650086823336922</v>
       </c>
       <c r="D1819" t="s">
-        <v>517</v>
+        <v>350</v>
       </c>
       <c r="E1819">
-        <v>1.420507952753614</v>
+        <v>1.001066072760231</v>
       </c>
       <c r="F1819">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1819">
-        <v>0.01176723515437453</v>
+        <v>0.01069499131766631</v>
       </c>
       <c r="H1819">
-        <v>0.01143949204724639</v>
+        <v>0.01147893392723977</v>
       </c>
       <c r="I1819">
-        <v>-0.06774310712814735</v>
+        <v>0.1360573904265392</v>
       </c>
       <c r="J1819">
-        <v>1.098572817378594</v>
+        <v>1.117043481287797</v>
       </c>
       <c r="K1819">
-        <v>4.74</v>
+        <v>4.4</v>
       </c>
       <c r="L1819">
-        <v>6.56</v>
+        <v>5.78</v>
       </c>
       <c r="M1819">
-        <v>4.56</v>
+        <v>4.69</v>
       </c>
       <c r="N1819">
-        <v>6.43</v>
+        <v>6.24</v>
       </c>
       <c r="O1819">
         <v>1</v>
       </c>
       <c r="P1819" t="s">
-        <v>357</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1820" spans="1:16">
       <c r="A1820" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1820" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C1820">
-        <v>0.8652138986958411</v>
+        <v>0.85053215944433</v>
       </c>
       <c r="D1820" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E1820">
-        <v>1.017246943778374</v>
+        <v>1.265213898695841</v>
       </c>
       <c r="F1820">
         <v>1</v>
       </c>
       <c r="G1820">
-        <v>0.01145478610130416</v>
+        <v>0.01152946784055567</v>
       </c>
       <c r="H1820">
-        <v>0.01042275305622163</v>
+        <v>0.01185478610130416</v>
       </c>
       <c r="I1820">
-        <v>0.1520330450825327</v>
+        <v>0.4146817392515105</v>
       </c>
       <c r="J1820">
         <v>1.117043481287797</v>
       </c>
       <c r="K1820">
+        <v>4.78</v>
+      </c>
+      <c r="L1820">
+        <v>6.19</v>
+      </c>
+      <c r="M1820">
         <v>4.74</v>
       </c>
-      <c r="L1820">
-        <v>6.16</v>
-      </c>
-      <c r="M1820">
-        <v>4.21</v>
-      </c>
       <c r="N1820">
-        <v>5.72</v>
+        <v>6.56</v>
       </c>
       <c r="O1820">
         <v>1</v>
       </c>
       <c r="P1820" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="1821" spans="1:16">
-      <c r="A1821" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1821" t="s">
-        <v>360</v>
-      </c>
-      <c r="C1821">
-        <v>0.8650086823336922</v>
-      </c>
-      <c r="D1821" t="s">
-        <v>351</v>
-      </c>
-      <c r="E1821">
-        <v>1.001066072760231</v>
-      </c>
-      <c r="F1821">
-        <v>1</v>
-      </c>
-      <c r="G1821">
-        <v>0.01069499131766631</v>
-      </c>
-      <c r="H1821">
-        <v>0.01147893392723977</v>
-      </c>
-      <c r="I1821">
-        <v>0.1360573904265392</v>
-      </c>
-      <c r="J1821">
-        <v>1.117043481287797</v>
-      </c>
-      <c r="K1821">
-        <v>4.4</v>
-      </c>
-      <c r="L1821">
-        <v>5.78</v>
-      </c>
-      <c r="M1821">
-        <v>4.69</v>
-      </c>
-      <c r="N1821">
-        <v>6.24</v>
-      </c>
-      <c r="O1821">
-        <v>1</v>
-      </c>
-      <c r="P1821" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="1822" spans="1:16">
-      <c r="A1822" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1822" t="s">
-        <v>361</v>
-      </c>
-      <c r="C1822">
-        <v>0.85053215944433</v>
-      </c>
-      <c r="D1822" t="s">
-        <v>354</v>
-      </c>
-      <c r="E1822">
-        <v>0.9963843335087192</v>
-      </c>
-      <c r="F1822">
-        <v>1</v>
-      </c>
-      <c r="G1822">
-        <v>0.01152946784055567</v>
-      </c>
-      <c r="H1822">
-        <v>0.01156361566649128</v>
-      </c>
-      <c r="I1822">
-        <v>0.1458521740643892</v>
-      </c>
-      <c r="J1822">
-        <v>1.117043481287797</v>
-      </c>
-      <c r="K1822">
-        <v>4.78</v>
-      </c>
-      <c r="L1822">
-        <v>6.19</v>
-      </c>
-      <c r="M1822">
-        <v>4.73</v>
-      </c>
-      <c r="N1822">
-        <v>6.28</v>
-      </c>
-      <c r="O1822">
-        <v>1</v>
-      </c>
-      <c r="P1822" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="1823" spans="1:16">
-      <c r="A1823" s="1">
-        <v>3</v>
-      </c>
-      <c r="B1823" t="s">
-        <v>359</v>
-      </c>
-      <c r="C1823">
-        <v>1.265213898695841</v>
-      </c>
-      <c r="D1823" t="s">
-        <v>517</v>
-      </c>
-      <c r="E1823">
-        <v>1.336281725327645</v>
-      </c>
-      <c r="F1823">
-        <v>-1</v>
-      </c>
-      <c r="G1823">
-        <v>0.01185478610130416</v>
-      </c>
-      <c r="H1823">
-        <v>0.01152371827467235</v>
-      </c>
-      <c r="I1823">
-        <v>-0.07106782663180411</v>
-      </c>
-      <c r="J1823">
-        <v>1.117043481287797</v>
-      </c>
-      <c r="K1823">
-        <v>4.74</v>
-      </c>
-      <c r="L1823">
-        <v>6.56</v>
-      </c>
-      <c r="M1823">
-        <v>4.56</v>
-      </c>
-      <c r="N1823">
-        <v>6.43</v>
-      </c>
-      <c r="O1823">
-        <v>1</v>
-      </c>
-      <c r="P1823" t="s">
         <v>631</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -1063,13 +1063,13 @@
     <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-09-23</t>
-  </si>
-  <si>
     <t>2021-10-15</t>
   </si>
   <si>
     <t>2021-10-29</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2021-05-27</t>
@@ -1558,7 +1558,7 @@
     <t>2021-11-08</t>
   </si>
   <si>
-    <t>2021-11-10</t>
+    <t>2021-11-11</t>
   </si>
   <si>
     <t>2016-03-09</t>
@@ -91366,7 +91366,7 @@
         <v>349</v>
       </c>
       <c r="C1783">
-        <v>1.751746382197352</v>
+        <v>1.783820006120755</v>
       </c>
       <c r="D1783" t="s">
         <v>513</v>
@@ -91378,22 +91378,22 @@
         <v>-1</v>
       </c>
       <c r="G1783">
-        <v>0.009928253617802647</v>
+        <v>0.01107617999387924</v>
       </c>
       <c r="H1783">
         <v>0.01145884405193897</v>
       </c>
       <c r="I1783">
-        <v>-0.5494095658636819</v>
+        <v>-0.5173359419402788</v>
       </c>
       <c r="J1783">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1783">
-        <v>4.25</v>
+        <v>4.83</v>
       </c>
       <c r="L1783">
-        <v>5.84</v>
+        <v>6.43</v>
       </c>
       <c r="M1783">
         <v>4.76</v>
@@ -91416,7 +91416,7 @@
         <v>350</v>
       </c>
       <c r="C1784">
-        <v>1.783820006120755</v>
+        <v>2.000394788615399</v>
       </c>
       <c r="D1784" t="s">
         <v>513</v>
@@ -91428,22 +91428,22 @@
         <v>-1</v>
       </c>
       <c r="G1784">
-        <v>0.01107617999387924</v>
+        <v>0.0111196052113846</v>
       </c>
       <c r="H1784">
         <v>0.01145884405193897</v>
       </c>
       <c r="I1784">
-        <v>-0.5173359419402788</v>
+        <v>-0.300761159445635</v>
       </c>
       <c r="J1784">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1784">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="L1784">
-        <v>6.43</v>
+        <v>6.56</v>
       </c>
       <c r="M1784">
         <v>4.76</v>
@@ -91460,63 +91460,63 @@
     </row>
     <row r="1785" spans="1:16">
       <c r="A1785" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1785" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C1785">
-        <v>2.000394788615399</v>
+        <v>0.9728076429396824</v>
       </c>
       <c r="D1785" t="s">
-        <v>513</v>
+        <v>341</v>
       </c>
       <c r="E1785">
-        <v>2.301155948061034</v>
+        <v>1.329119523361904</v>
       </c>
       <c r="F1785">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1785">
-        <v>0.0111196052113846</v>
+        <v>0.01222719235706032</v>
       </c>
       <c r="H1785">
-        <v>0.01145884405193897</v>
+        <v>0.0108708804766381</v>
       </c>
       <c r="I1785">
-        <v>-0.300761159445635</v>
+        <v>0.3563118804222221</v>
       </c>
       <c r="J1785">
-        <v>0.9619420277182702</v>
+        <v>1.01941890526455</v>
       </c>
       <c r="K1785">
-        <v>4.74</v>
+        <v>5.52</v>
       </c>
       <c r="L1785">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="M1785">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="N1785">
-        <v>6.88</v>
+        <v>6.1</v>
       </c>
       <c r="O1785">
         <v>1</v>
       </c>
       <c r="P1785" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1786" spans="1:16">
       <c r="A1786" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1786" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C1786">
-        <v>0.9728076429396824</v>
+        <v>0.9472739911505288</v>
       </c>
       <c r="D1786" t="s">
         <v>341</v>
@@ -91528,22 +91528,22 @@
         <v>1</v>
       </c>
       <c r="G1786">
-        <v>0.01222719235706032</v>
+        <v>0.01173272600884947</v>
       </c>
       <c r="H1786">
         <v>0.0108708804766381</v>
       </c>
       <c r="I1786">
-        <v>0.3563118804222221</v>
+        <v>0.3818455322113756</v>
       </c>
       <c r="J1786">
         <v>1.01941890526455</v>
       </c>
       <c r="K1786">
-        <v>5.52</v>
+        <v>5.29</v>
       </c>
       <c r="L1786">
-        <v>6.6</v>
+        <v>6.34</v>
       </c>
       <c r="M1786">
         <v>4.68</v>
@@ -91560,46 +91560,46 @@
     </row>
     <row r="1787" spans="1:16">
       <c r="A1787" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1787" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C1787">
-        <v>0.9472739911505288</v>
+        <v>1.549605732204761</v>
       </c>
       <c r="D1787" t="s">
-        <v>341</v>
+        <v>512</v>
       </c>
       <c r="E1787">
-        <v>1.329119523361904</v>
+        <v>1.180576677467989</v>
       </c>
       <c r="F1787">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1787">
-        <v>0.01173272600884947</v>
+        <v>0.009990394267795239</v>
       </c>
       <c r="H1787">
-        <v>0.0108708804766381</v>
+        <v>0.009519423322532011</v>
       </c>
       <c r="I1787">
-        <v>0.3818455322113756</v>
+        <v>0.3690290547367727</v>
       </c>
       <c r="J1787">
         <v>1.01941890526455</v>
       </c>
       <c r="K1787">
-        <v>5.29</v>
+        <v>4.14</v>
       </c>
       <c r="L1787">
-        <v>6.34</v>
+        <v>5.77</v>
       </c>
       <c r="M1787">
-        <v>4.68</v>
+        <v>4.09</v>
       </c>
       <c r="N1787">
-        <v>6.1</v>
+        <v>5.35</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91610,46 +91610,46 @@
     </row>
     <row r="1788" spans="1:16">
       <c r="A1788" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1788" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C1788">
-        <v>1.549605732204761</v>
+        <v>1.507469652625661</v>
       </c>
       <c r="D1788" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E1788">
-        <v>1.180576677467989</v>
+        <v>2.02756601094074</v>
       </c>
       <c r="F1788">
         <v>-1</v>
       </c>
       <c r="G1788">
-        <v>0.009990394267795239</v>
+        <v>0.01017253034737434</v>
       </c>
       <c r="H1788">
-        <v>0.009519423322532011</v>
+        <v>0.01173243398905926</v>
       </c>
       <c r="I1788">
-        <v>0.3690290547367727</v>
+        <v>-0.5200963583150795</v>
       </c>
       <c r="J1788">
         <v>1.01941890526455</v>
       </c>
       <c r="K1788">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="L1788">
-        <v>5.77</v>
+        <v>5.84</v>
       </c>
       <c r="M1788">
-        <v>4.09</v>
+        <v>4.76</v>
       </c>
       <c r="N1788">
-        <v>5.35</v>
+        <v>6.88</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91660,13 +91660,13 @@
     </row>
     <row r="1789" spans="1:16">
       <c r="A1789" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1789" t="s">
         <v>349</v>
       </c>
       <c r="C1789">
-        <v>1.507469652625661</v>
+        <v>1.506206687572221</v>
       </c>
       <c r="D1789" t="s">
         <v>513</v>
@@ -91678,22 +91678,22 @@
         <v>-1</v>
       </c>
       <c r="G1789">
-        <v>0.01017253034737434</v>
+        <v>0.01135379331242778</v>
       </c>
       <c r="H1789">
         <v>0.01173243398905926</v>
       </c>
       <c r="I1789">
-        <v>-0.5200963583150795</v>
+        <v>-0.521359323368519</v>
       </c>
       <c r="J1789">
         <v>1.01941890526455</v>
       </c>
       <c r="K1789">
-        <v>4.25</v>
+        <v>4.83</v>
       </c>
       <c r="L1789">
-        <v>5.84</v>
+        <v>6.43</v>
       </c>
       <c r="M1789">
         <v>4.76</v>
@@ -91710,13 +91710,13 @@
     </row>
     <row r="1790" spans="1:16">
       <c r="A1790" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1790" t="s">
         <v>350</v>
       </c>
       <c r="C1790">
-        <v>1.506206687572221</v>
+        <v>1.72795438904603</v>
       </c>
       <c r="D1790" t="s">
         <v>513</v>
@@ -91728,22 +91728,22 @@
         <v>-1</v>
       </c>
       <c r="G1790">
-        <v>0.01135379331242778</v>
+        <v>0.01139204561095397</v>
       </c>
       <c r="H1790">
         <v>0.01173243398905926</v>
       </c>
       <c r="I1790">
-        <v>-0.521359323368519</v>
+        <v>-0.2996116218947096</v>
       </c>
       <c r="J1790">
         <v>1.01941890526455</v>
       </c>
       <c r="K1790">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="L1790">
-        <v>6.43</v>
+        <v>6.56</v>
       </c>
       <c r="M1790">
         <v>4.76</v>
@@ -91760,96 +91760,96 @@
     </row>
     <row r="1791" spans="1:16">
       <c r="A1791" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1791" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C1791">
-        <v>1.72795438904603</v>
+        <v>0.7149171399855092</v>
       </c>
       <c r="D1791" t="s">
-        <v>513</v>
+        <v>341</v>
       </c>
       <c r="E1791">
-        <v>2.02756601094074</v>
+        <v>1.06601640838651</v>
       </c>
       <c r="F1791">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1791">
-        <v>0.01139204561095397</v>
+        <v>0.01280508286001449</v>
       </c>
       <c r="H1791">
-        <v>0.01173243398905926</v>
+        <v>0.01113398359161349</v>
       </c>
       <c r="I1791">
-        <v>-0.2996116218947096</v>
+        <v>0.3510992684010006</v>
       </c>
       <c r="J1791">
-        <v>1.01941890526455</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1791">
-        <v>4.74</v>
+        <v>5.62</v>
       </c>
       <c r="L1791">
-        <v>6.56</v>
+        <v>6.76</v>
       </c>
       <c r="M1791">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="N1791">
-        <v>6.88</v>
+        <v>6.1</v>
       </c>
       <c r="O1791">
         <v>1</v>
       </c>
       <c r="P1791" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1792" spans="1:16">
       <c r="A1792" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1792" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C1792">
-        <v>0.7149171399855092</v>
+        <v>1.316860668957297</v>
       </c>
       <c r="D1792" t="s">
-        <v>341</v>
+        <v>512</v>
       </c>
       <c r="E1792">
-        <v>1.06601640838651</v>
+        <v>0.9506425449360734</v>
       </c>
       <c r="F1792">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1792">
-        <v>0.01280508286001449</v>
+        <v>0.0102231393310427</v>
       </c>
       <c r="H1792">
-        <v>0.01113398359161349</v>
+        <v>0.009749357455063926</v>
       </c>
       <c r="I1792">
-        <v>0.3510992684010006</v>
+        <v>0.3662181240212234</v>
       </c>
       <c r="J1792">
         <v>1.075637519575532</v>
       </c>
       <c r="K1792">
-        <v>5.62</v>
+        <v>4.14</v>
       </c>
       <c r="L1792">
-        <v>6.76</v>
+        <v>5.77</v>
       </c>
       <c r="M1792">
-        <v>4.68</v>
+        <v>4.09</v>
       </c>
       <c r="N1792">
-        <v>6.1</v>
+        <v>5.35</v>
       </c>
       <c r="O1792">
         <v>1</v>
@@ -91860,46 +91860,46 @@
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1793" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C1793">
-        <v>1.316860668957297</v>
+        <v>1.268540541803988</v>
       </c>
       <c r="D1793" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E1793">
-        <v>0.9506425449360734</v>
+        <v>1.759965406820467</v>
       </c>
       <c r="F1793">
         <v>-1</v>
       </c>
       <c r="G1793">
-        <v>0.0102231393310427</v>
+        <v>0.01041145945819601</v>
       </c>
       <c r="H1793">
-        <v>0.009749357455063926</v>
+        <v>0.01200003459317953</v>
       </c>
       <c r="I1793">
-        <v>0.3662181240212234</v>
+        <v>-0.4914248650164792</v>
       </c>
       <c r="J1793">
         <v>1.075637519575532</v>
       </c>
       <c r="K1793">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="L1793">
-        <v>5.77</v>
+        <v>5.84</v>
       </c>
       <c r="M1793">
-        <v>4.09</v>
+        <v>4.76</v>
       </c>
       <c r="N1793">
-        <v>5.35</v>
+        <v>6.88</v>
       </c>
       <c r="O1793">
         <v>1</v>
@@ -91910,13 +91910,13 @@
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1794" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C1794">
-        <v>1.250053292195498</v>
+        <v>1.461478157211977</v>
       </c>
       <c r="D1794" t="s">
         <v>513</v>
@@ -91928,22 +91928,22 @@
         <v>-1</v>
       </c>
       <c r="G1794">
-        <v>0.0103499467078045</v>
+        <v>0.01165852184278802</v>
       </c>
       <c r="H1794">
         <v>0.01200003459317953</v>
       </c>
       <c r="I1794">
-        <v>-0.509912114624969</v>
+        <v>-0.29848724960849</v>
       </c>
       <c r="J1794">
         <v>1.075637519575532</v>
       </c>
       <c r="K1794">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="L1794">
-        <v>5.8</v>
+        <v>6.56</v>
       </c>
       <c r="M1794">
         <v>4.76</v>
@@ -91960,96 +91960,96 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1795" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C1795">
-        <v>1.461478157211977</v>
+        <v>1.260576197480336</v>
       </c>
       <c r="D1795" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E1795">
-        <v>1.759965406820467</v>
+        <v>0.8950378376073855</v>
       </c>
       <c r="F1795">
         <v>-1</v>
       </c>
       <c r="G1795">
-        <v>0.01165852184278802</v>
+        <v>0.01027942380251966</v>
       </c>
       <c r="H1795">
-        <v>0.01200003459317953</v>
+        <v>0.009804962162392614</v>
       </c>
       <c r="I1795">
-        <v>-0.29848724960849</v>
+        <v>0.3655383598729509</v>
       </c>
       <c r="J1795">
-        <v>1.075637519575532</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1795">
-        <v>4.74</v>
+        <v>4.14</v>
       </c>
       <c r="L1795">
-        <v>6.56</v>
+        <v>5.77</v>
       </c>
       <c r="M1795">
-        <v>4.76</v>
+        <v>4.09</v>
       </c>
       <c r="N1795">
-        <v>6.88</v>
+        <v>5.35</v>
       </c>
       <c r="O1795">
         <v>1</v>
       </c>
       <c r="P1795" t="s">
-        <v>625</v>
+        <v>352</v>
       </c>
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1796" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C1796">
-        <v>1.260576197480336</v>
+        <v>1.192545245251648</v>
       </c>
       <c r="D1796" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E1796">
-        <v>0.8950378376073855</v>
+        <v>1.384543923600011</v>
       </c>
       <c r="F1796">
         <v>-1</v>
       </c>
       <c r="G1796">
-        <v>0.01027942380251966</v>
+        <v>0.01040745475474835</v>
       </c>
       <c r="H1796">
-        <v>0.009804962162392614</v>
+        <v>0.01201545607639999</v>
       </c>
       <c r="I1796">
-        <v>0.3655383598729509</v>
+        <v>-0.1919986783483623</v>
       </c>
       <c r="J1796">
         <v>1.089232802540981</v>
       </c>
       <c r="K1796">
-        <v>4.14</v>
+        <v>4.23</v>
       </c>
       <c r="L1796">
-        <v>5.77</v>
+        <v>5.8</v>
       </c>
       <c r="M1796">
-        <v>4.09</v>
+        <v>4.88</v>
       </c>
       <c r="N1796">
-        <v>5.35</v>
+        <v>6.7</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92060,46 +92060,46 @@
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1797" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C1797">
-        <v>1.192545245251648</v>
+        <v>1.397036515955747</v>
       </c>
       <c r="D1797" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E1797">
-        <v>1.695251859904928</v>
+        <v>1.384543923600011</v>
       </c>
       <c r="F1797">
         <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.01040745475474835</v>
+        <v>0.01172296348404425</v>
       </c>
       <c r="H1797">
-        <v>0.01206474814009507</v>
+        <v>0.01201545607639999</v>
       </c>
       <c r="I1797">
-        <v>-0.5027066146532801</v>
+        <v>0.01249259235573685</v>
       </c>
       <c r="J1797">
         <v>1.089232802540981</v>
       </c>
       <c r="K1797">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="L1797">
-        <v>5.8</v>
+        <v>6.56</v>
       </c>
       <c r="M1797">
-        <v>4.76</v>
+        <v>4.88</v>
       </c>
       <c r="N1797">
-        <v>6.88</v>
+        <v>6.7</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92110,96 +92110,96 @@
     </row>
     <row r="1798" spans="1:16">
       <c r="A1798" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1798" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C1798">
-        <v>1.397036515955747</v>
+        <v>1.415719814471675</v>
       </c>
       <c r="D1798" t="s">
-        <v>513</v>
+        <v>349</v>
       </c>
       <c r="E1798">
-        <v>1.695251859904928</v>
+        <v>1.628822901136471</v>
       </c>
       <c r="F1798">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1798">
-        <v>0.01172296348404425</v>
+        <v>0.009984280185528325</v>
       </c>
       <c r="H1798">
-        <v>0.01206474814009507</v>
+        <v>0.01123117709886353</v>
       </c>
       <c r="I1798">
-        <v>-0.298215343949181</v>
+        <v>0.2131030866647956</v>
       </c>
       <c r="J1798">
-        <v>1.089232802540981</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1798">
-        <v>4.74</v>
+        <v>4.31</v>
       </c>
       <c r="L1798">
-        <v>6.56</v>
+        <v>5.7</v>
       </c>
       <c r="M1798">
-        <v>4.76</v>
+        <v>4.83</v>
       </c>
       <c r="N1798">
-        <v>6.88</v>
+        <v>6.43</v>
       </c>
       <c r="O1798">
         <v>1</v>
       </c>
       <c r="P1798" t="s">
-        <v>352</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1799" spans="1:16">
       <c r="A1799" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1799" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C1799">
-        <v>1.415719814471675</v>
+        <v>1.89721168306052</v>
       </c>
       <c r="D1799" t="s">
-        <v>350</v>
+        <v>514</v>
       </c>
       <c r="E1799">
-        <v>1.628822901136471</v>
+        <v>1.84912127485424</v>
       </c>
       <c r="F1799">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1799">
-        <v>0.009984280185528325</v>
+        <v>0.01096278831693948</v>
       </c>
       <c r="H1799">
-        <v>0.01123117709886353</v>
+        <v>0.01155087872514576</v>
       </c>
       <c r="I1799">
-        <v>0.2131030866647956</v>
+        <v>0.04809040820627963</v>
       </c>
       <c r="J1799">
         <v>0.994032525644623</v>
       </c>
       <c r="K1799">
-        <v>4.31</v>
+        <v>4.56</v>
       </c>
       <c r="L1799">
-        <v>5.7</v>
+        <v>6.43</v>
       </c>
       <c r="M1799">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="N1799">
-        <v>6.43</v>
+        <v>6.7</v>
       </c>
       <c r="O1799">
         <v>1</v>
@@ -92210,96 +92210,96 @@
     </row>
     <row r="1800" spans="1:16">
       <c r="A1800" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1800" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C1800">
-        <v>1.89721168306052</v>
+        <v>1.091573753380461</v>
       </c>
       <c r="D1800" t="s">
-        <v>514</v>
+        <v>353</v>
       </c>
       <c r="E1800">
-        <v>1.819001925367132</v>
+        <v>1.290033686008443</v>
       </c>
       <c r="F1800">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1800">
-        <v>0.01096278831693948</v>
+        <v>0.01102842624661954</v>
       </c>
       <c r="H1800">
-        <v>0.01148099807463287</v>
+        <v>0.01030996631399156</v>
       </c>
       <c r="I1800">
-        <v>0.07820975769338734</v>
+        <v>0.1984599326279826</v>
       </c>
       <c r="J1800">
-        <v>0.994032525644623</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1800">
-        <v>4.56</v>
+        <v>4.66</v>
       </c>
       <c r="L1800">
-        <v>6.43</v>
+        <v>6.06</v>
       </c>
       <c r="M1800">
-        <v>4.86</v>
+        <v>4.23</v>
       </c>
       <c r="N1800">
-        <v>6.65</v>
+        <v>5.8</v>
       </c>
       <c r="O1800">
         <v>1</v>
       </c>
       <c r="P1800" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1801" spans="1:16">
       <c r="A1801" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1801" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1801">
-        <v>1.091573753380461</v>
+        <v>1.088782084736915</v>
       </c>
       <c r="D1801" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E1801">
-        <v>1.290033686008443</v>
+        <v>1.506278882193858</v>
       </c>
       <c r="F1801">
         <v>1</v>
       </c>
       <c r="G1801">
-        <v>0.01102842624661954</v>
+        <v>0.01047121791526309</v>
       </c>
       <c r="H1801">
-        <v>0.01030996631399156</v>
+        <v>0.01161372111780614</v>
       </c>
       <c r="I1801">
-        <v>0.1984599326279826</v>
+        <v>0.417496797456943</v>
       </c>
       <c r="J1801">
         <v>1.066185889832519</v>
       </c>
       <c r="K1801">
-        <v>4.66</v>
+        <v>4.4</v>
       </c>
       <c r="L1801">
-        <v>6.06</v>
+        <v>5.78</v>
       </c>
       <c r="M1801">
-        <v>4.23</v>
+        <v>4.74</v>
       </c>
       <c r="N1801">
-        <v>5.8</v>
+        <v>6.56</v>
       </c>
       <c r="O1801">
         <v>1</v>
@@ -92310,16 +92310,16 @@
     </row>
     <row r="1802" spans="1:16">
       <c r="A1802" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1802" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C1802">
-        <v>1.088782084736915</v>
+        <v>1.093631446600559</v>
       </c>
       <c r="D1802" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1802">
         <v>1.506278882193858</v>
@@ -92328,22 +92328,22 @@
         <v>1</v>
       </c>
       <c r="G1802">
-        <v>0.01047121791526309</v>
+        <v>0.01128636855339944</v>
       </c>
       <c r="H1802">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1802">
-        <v>0.417496797456943</v>
+        <v>0.4126474355932999</v>
       </c>
       <c r="J1802">
         <v>1.066185889832519</v>
       </c>
       <c r="K1802">
-        <v>4.4</v>
+        <v>4.78</v>
       </c>
       <c r="L1802">
-        <v>5.78</v>
+        <v>6.19</v>
       </c>
       <c r="M1802">
         <v>4.74</v>
@@ -92360,46 +92360,46 @@
     </row>
     <row r="1803" spans="1:16">
       <c r="A1803" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1803" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C1803">
-        <v>1.093631446600559</v>
+        <v>1.568192342363713</v>
       </c>
       <c r="D1803" t="s">
-        <v>351</v>
+        <v>514</v>
       </c>
       <c r="E1803">
-        <v>1.506278882193858</v>
+        <v>1.497012857617307</v>
       </c>
       <c r="F1803">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1803">
-        <v>0.01128636855339944</v>
+        <v>0.01129180765763629</v>
       </c>
       <c r="H1803">
-        <v>0.01161372111780614</v>
+        <v>0.01190298714238269</v>
       </c>
       <c r="I1803">
-        <v>0.4126474355932999</v>
+        <v>0.07117948474640645</v>
       </c>
       <c r="J1803">
         <v>1.066185889832519</v>
       </c>
       <c r="K1803">
-        <v>4.78</v>
+        <v>4.56</v>
       </c>
       <c r="L1803">
-        <v>6.19</v>
+        <v>6.43</v>
       </c>
       <c r="M1803">
-        <v>4.74</v>
+        <v>4.88</v>
       </c>
       <c r="N1803">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="O1803">
         <v>1</v>
@@ -92410,57 +92410,57 @@
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1804" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C1804">
-        <v>1.568192342363713</v>
+        <v>0.9527648456254667</v>
       </c>
       <c r="D1804" t="s">
-        <v>514</v>
+        <v>353</v>
       </c>
       <c r="E1804">
-        <v>1.468336575413957</v>
+        <v>1.153036982488548</v>
       </c>
       <c r="F1804">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1804">
-        <v>0.01129180765763629</v>
+        <v>0.01136723515437453</v>
       </c>
       <c r="H1804">
-        <v>0.01183166342458604</v>
+        <v>0.01044696301751145</v>
       </c>
       <c r="I1804">
-        <v>0.09985576694975595</v>
+        <v>0.2002721368630818</v>
       </c>
       <c r="J1804">
-        <v>1.066185889832519</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1804">
-        <v>4.56</v>
+        <v>4.74</v>
       </c>
       <c r="L1804">
-        <v>6.43</v>
+        <v>6.16</v>
       </c>
       <c r="M1804">
-        <v>4.86</v>
+        <v>4.23</v>
       </c>
       <c r="N1804">
-        <v>6.65</v>
+        <v>5.8</v>
       </c>
       <c r="O1804">
         <v>1</v>
       </c>
       <c r="P1804" t="s">
-        <v>627</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1805" t="s">
         <v>357</v>
@@ -92469,7 +92469,7 @@
         <v>0.9462796035341885</v>
       </c>
       <c r="D1805" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1805">
         <v>1.352764845625466</v>
@@ -92510,7 +92510,7 @@
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1806" t="s">
         <v>358</v>
@@ -92519,7 +92519,7 @@
         <v>0.9388219329303231</v>
       </c>
       <c r="D1806" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1806">
         <v>1.352764845625466</v>
@@ -92560,7 +92560,7 @@
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1807" t="s">
         <v>355</v>
@@ -92572,7 +92572,7 @@
         <v>514</v>
       </c>
       <c r="E1807">
-        <v>1.310936107540035</v>
+        <v>1.338964651192463</v>
       </c>
       <c r="F1807">
         <v>-1</v>
@@ -92581,10 +92581,10 @@
         <v>0.01143949204724639</v>
       </c>
       <c r="H1807">
-        <v>0.01198906389245996</v>
+        <v>0.01206103534880754</v>
       </c>
       <c r="I1807">
-        <v>0.1095718452135781</v>
+        <v>0.08154330156115019</v>
       </c>
       <c r="J1807">
         <v>1.098572817378594</v>
@@ -92596,10 +92596,10 @@
         <v>6.43</v>
       </c>
       <c r="M1807">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="N1807">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="O1807">
         <v>1</v>
@@ -92669,7 +92669,7 @@
         <v>0.8650086823336922</v>
       </c>
       <c r="D1809" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1809">
         <v>1.265213898695841</v>
@@ -92719,7 +92719,7 @@
         <v>0.85053215944433</v>
       </c>
       <c r="D1810" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1810">
         <v>1.265213898695841</v>
@@ -92772,7 +92772,7 @@
         <v>514</v>
       </c>
       <c r="E1811">
-        <v>1.221168680941306</v>
+        <v>1.24882781131555</v>
       </c>
       <c r="F1811">
         <v>-1</v>
@@ -92781,10 +92781,10 @@
         <v>0.01152371827467235</v>
       </c>
       <c r="H1811">
-        <v>0.0120788313190587</v>
+        <v>0.01215117218868445</v>
       </c>
       <c r="I1811">
-        <v>0.1151130443863391</v>
+        <v>0.08745391401209446</v>
       </c>
       <c r="J1811">
         <v>1.117043481287797</v>
@@ -92796,10 +92796,10 @@
         <v>6.43</v>
       </c>
       <c r="M1811">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="N1811">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="O1811">
         <v>1</v>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5481" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5484" uniqueCount="628">
   <si>
     <t>trade_time</t>
   </si>
@@ -1063,10 +1063,10 @@
     <t>2021-10-29</t>
   </si>
   <si>
-    <t>2021-05-27</t>
+    <t>2021-07-06</t>
   </si>
   <si>
-    <t>2021-07-06</t>
+    <t>2021-05-27</t>
   </si>
   <si>
     <t>2021-09-06</t>
@@ -1555,7 +1555,7 @@
     <t>2021-08-11</t>
   </si>
   <si>
-    <t>2021-11-24</t>
+    <t>2021-11-25</t>
   </si>
   <si>
     <t>2016-03-09</t>
@@ -2255,7 +2255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1823"/>
+  <dimension ref="A1:P1824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91319,7 +91319,7 @@
         <v>513</v>
       </c>
       <c r="E1782">
-        <v>2.050014208892581</v>
+        <v>1.980014208892582</v>
       </c>
       <c r="F1782">
         <v>-1</v>
@@ -91328,10 +91328,10 @@
         <v>0.0111196052113846</v>
       </c>
       <c r="H1782">
-        <v>0.01114998579110742</v>
+        <v>0.01107998579110742</v>
       </c>
       <c r="I1782">
-        <v>-0.04961942027718269</v>
+        <v>0.02038057972281671</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
@@ -91346,7 +91346,7 @@
         <v>4.73</v>
       </c>
       <c r="N1782">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91410,10 +91410,10 @@
         <v>1</v>
       </c>
       <c r="B1784" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C1784">
-        <v>0.9472739911505288</v>
+        <v>1.026983443782804</v>
       </c>
       <c r="D1784" t="s">
         <v>341</v>
@@ -91425,22 +91425,22 @@
         <v>1</v>
       </c>
       <c r="G1784">
-        <v>0.01173272600884947</v>
+        <v>0.0107930165562172</v>
       </c>
       <c r="H1784">
         <v>0.0108708804766381</v>
       </c>
       <c r="I1784">
-        <v>0.3818455322113756</v>
+        <v>0.3021360795791006</v>
       </c>
       <c r="J1784">
         <v>1.01941890526455</v>
       </c>
       <c r="K1784">
-        <v>5.29</v>
+        <v>4.79</v>
       </c>
       <c r="L1784">
-        <v>6.34</v>
+        <v>5.91</v>
       </c>
       <c r="M1784">
         <v>4.68</v>
@@ -91469,7 +91469,7 @@
         <v>513</v>
       </c>
       <c r="E1785">
-        <v>1.778148578098676</v>
+        <v>1.708148578098677</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91478,10 +91478,10 @@
         <v>0.01139204561095397</v>
       </c>
       <c r="H1785">
-        <v>0.01142185142190132</v>
+        <v>0.01135185142190132</v>
       </c>
       <c r="I1785">
-        <v>-0.05019418905264583</v>
+        <v>0.01980581094735356</v>
       </c>
       <c r="J1785">
         <v>1.01941890526455</v>
@@ -91496,7 +91496,7 @@
         <v>4.73</v>
       </c>
       <c r="N1785">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91510,7 +91510,7 @@
         <v>0</v>
       </c>
       <c r="B1786" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C1786">
         <v>0.7149171399855092</v>
@@ -91560,43 +91560,43 @@
         <v>1</v>
       </c>
       <c r="B1787" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C1787">
-        <v>1.461478157211977</v>
+        <v>0.7576962812332013</v>
       </c>
       <c r="D1787" t="s">
-        <v>513</v>
+        <v>341</v>
       </c>
       <c r="E1787">
-        <v>1.512234532407732</v>
+        <v>1.06601640838651</v>
       </c>
       <c r="F1787">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1787">
-        <v>0.01165852184278802</v>
+        <v>0.0110623037187668</v>
       </c>
       <c r="H1787">
-        <v>0.01168776546759227</v>
+        <v>0.01113398359161349</v>
       </c>
       <c r="I1787">
-        <v>-0.05075637519575515</v>
+        <v>0.3083201271533085</v>
       </c>
       <c r="J1787">
         <v>1.075637519575532</v>
       </c>
       <c r="K1787">
-        <v>4.74</v>
+        <v>4.79</v>
       </c>
       <c r="L1787">
-        <v>6.56</v>
+        <v>5.91</v>
       </c>
       <c r="M1787">
-        <v>4.73</v>
+        <v>4.68</v>
       </c>
       <c r="N1787">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91607,163 +91607,163 @@
     </row>
     <row r="1788" spans="1:16">
       <c r="A1788" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1788" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C1788">
-        <v>0.6925748758286989</v>
+        <v>1.461478157211977</v>
       </c>
       <c r="D1788" t="s">
-        <v>341</v>
+        <v>513</v>
       </c>
       <c r="E1788">
-        <v>1.002390484108207</v>
+        <v>1.442234532407733</v>
       </c>
       <c r="F1788">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1788">
-        <v>0.0111274251241713</v>
+        <v>0.01165852184278802</v>
       </c>
       <c r="H1788">
-        <v>0.01119760951589179</v>
+        <v>0.01161776546759227</v>
       </c>
       <c r="I1788">
-        <v>0.309815608279508</v>
+        <v>0.01924362480424424</v>
       </c>
       <c r="J1788">
-        <v>1.089232802540981</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1788">
-        <v>4.79</v>
+        <v>4.74</v>
       </c>
       <c r="L1788">
-        <v>5.91</v>
+        <v>6.56</v>
       </c>
       <c r="M1788">
-        <v>4.68</v>
+        <v>4.73</v>
       </c>
       <c r="N1788">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="O1788">
         <v>1</v>
       </c>
       <c r="P1788" t="s">
-        <v>349</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1789" spans="1:16">
       <c r="A1789" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1789" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C1789">
-        <v>1.397036515955747</v>
+        <v>0.6925748758286989</v>
       </c>
       <c r="D1789" t="s">
-        <v>513</v>
+        <v>341</v>
       </c>
       <c r="E1789">
-        <v>1.447928843981157</v>
+        <v>1.002390484108207</v>
       </c>
       <c r="F1789">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1789">
-        <v>0.01172296348404425</v>
+        <v>0.0111274251241713</v>
       </c>
       <c r="H1789">
-        <v>0.01175207115601884</v>
+        <v>0.01119760951589179</v>
       </c>
       <c r="I1789">
-        <v>-0.05089232802540966</v>
+        <v>0.309815608279508</v>
       </c>
       <c r="J1789">
         <v>1.089232802540981</v>
       </c>
       <c r="K1789">
-        <v>4.74</v>
+        <v>4.79</v>
       </c>
       <c r="L1789">
-        <v>6.56</v>
+        <v>5.91</v>
       </c>
       <c r="M1789">
-        <v>4.73</v>
+        <v>4.68</v>
       </c>
       <c r="N1789">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="O1789">
         <v>1</v>
       </c>
       <c r="P1789" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1790" spans="1:16">
       <c r="A1790" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1790" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C1790">
-        <v>1.437331032547627</v>
+        <v>1.397036515955747</v>
       </c>
       <c r="D1790" t="s">
-        <v>348</v>
+        <v>513</v>
       </c>
       <c r="E1790">
-        <v>1.848285828444487</v>
+        <v>1.377928843981158</v>
       </c>
       <c r="F1790">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1790">
-        <v>0.01054266896745237</v>
+        <v>0.01172296348404425</v>
       </c>
       <c r="H1790">
-        <v>0.01127171417155551</v>
+        <v>0.01168207115601884</v>
       </c>
       <c r="I1790">
-        <v>0.4109547958968598</v>
+        <v>0.01910767197458973</v>
       </c>
       <c r="J1790">
-        <v>0.994032525644623</v>
+        <v>1.089232802540981</v>
       </c>
       <c r="K1790">
-        <v>4.58</v>
+        <v>4.74</v>
       </c>
       <c r="L1790">
-        <v>5.99</v>
+        <v>6.56</v>
       </c>
       <c r="M1790">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="N1790">
-        <v>6.56</v>
+        <v>6.53</v>
       </c>
       <c r="O1790">
         <v>1</v>
       </c>
       <c r="P1790" t="s">
-        <v>625</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1791" spans="1:16">
       <c r="A1791" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1791" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C1791">
-        <v>1.427808430496056</v>
+        <v>1.437331032547627</v>
       </c>
       <c r="D1791" t="s">
         <v>348</v>
@@ -91775,22 +91775,22 @@
         <v>1</v>
       </c>
       <c r="G1791">
-        <v>0.01069219156950394</v>
+        <v>0.01054266896745237</v>
       </c>
       <c r="H1791">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1791">
-        <v>0.4204773979484306</v>
+        <v>0.4109547958968598</v>
       </c>
       <c r="J1791">
         <v>0.994032525644623</v>
       </c>
       <c r="K1791">
-        <v>4.66</v>
+        <v>4.58</v>
       </c>
       <c r="L1791">
-        <v>6.06</v>
+        <v>5.99</v>
       </c>
       <c r="M1791">
         <v>4.74</v>
@@ -91807,13 +91807,13 @@
     </row>
     <row r="1792" spans="1:16">
       <c r="A1792" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1792" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C1792">
-        <v>1.448285828444487</v>
+        <v>1.427808430496056</v>
       </c>
       <c r="D1792" t="s">
         <v>348</v>
@@ -91825,22 +91825,22 @@
         <v>1</v>
       </c>
       <c r="G1792">
-        <v>0.01087171417155551</v>
+        <v>0.01069219156950394</v>
       </c>
       <c r="H1792">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1792">
-        <v>0.3999999999999995</v>
+        <v>0.4204773979484306</v>
       </c>
       <c r="J1792">
         <v>0.994032525644623</v>
       </c>
       <c r="K1792">
-        <v>4.74</v>
+        <v>4.66</v>
       </c>
       <c r="L1792">
-        <v>6.16</v>
+        <v>6.06</v>
       </c>
       <c r="M1792">
         <v>4.74</v>
@@ -91857,13 +91857,13 @@
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1793" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C1793">
-        <v>1.415719814471675</v>
+        <v>1.448285828444487</v>
       </c>
       <c r="D1793" t="s">
         <v>348</v>
@@ -91875,22 +91875,22 @@
         <v>1</v>
       </c>
       <c r="G1793">
-        <v>0.009984280185528325</v>
+        <v>0.01087171417155551</v>
       </c>
       <c r="H1793">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1793">
-        <v>0.4325660139728118</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1793">
         <v>0.994032525644623</v>
       </c>
       <c r="K1793">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="L1793">
-        <v>5.7</v>
+        <v>6.16</v>
       </c>
       <c r="M1793">
         <v>4.74</v>
@@ -91907,13 +91907,13 @@
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1794" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C1794">
-        <v>1.438524527418703</v>
+        <v>1.415719814471675</v>
       </c>
       <c r="D1794" t="s">
         <v>348</v>
@@ -91925,22 +91925,22 @@
         <v>1</v>
       </c>
       <c r="G1794">
-        <v>0.0109414754725813</v>
+        <v>0.009984280185528325</v>
       </c>
       <c r="H1794">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1794">
-        <v>0.4097613010257843</v>
+        <v>0.4325660139728118</v>
       </c>
       <c r="J1794">
         <v>0.994032525644623</v>
       </c>
       <c r="K1794">
-        <v>4.78</v>
+        <v>4.31</v>
       </c>
       <c r="L1794">
-        <v>6.19</v>
+        <v>5.7</v>
       </c>
       <c r="M1794">
         <v>4.74</v>
@@ -91957,46 +91957,46 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1795" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C1795">
-        <v>1.89721168306052</v>
+        <v>1.438524527418703</v>
       </c>
       <c r="D1795" t="s">
-        <v>513</v>
+        <v>348</v>
       </c>
       <c r="E1795">
-        <v>1.898226153700932</v>
+        <v>1.848285828444487</v>
       </c>
       <c r="F1795">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1795">
-        <v>0.01096278831693948</v>
+        <v>0.0109414754725813</v>
       </c>
       <c r="H1795">
-        <v>0.01130177384629907</v>
+        <v>0.01127171417155551</v>
       </c>
       <c r="I1795">
-        <v>-0.00101447064041249</v>
+        <v>0.4097613010257843</v>
       </c>
       <c r="J1795">
         <v>0.994032525644623</v>
       </c>
       <c r="K1795">
-        <v>4.56</v>
+        <v>4.78</v>
       </c>
       <c r="L1795">
-        <v>6.43</v>
+        <v>6.19</v>
       </c>
       <c r="M1795">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="N1795">
-        <v>6.6</v>
+        <v>6.56</v>
       </c>
       <c r="O1795">
         <v>1</v>
@@ -92007,46 +92007,46 @@
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1796" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1796">
-        <v>1.906853634599196</v>
+        <v>1.89721168306052</v>
       </c>
       <c r="D1796" t="s">
         <v>513</v>
       </c>
       <c r="E1796">
-        <v>1.898226153700932</v>
+        <v>1.828226153700933</v>
       </c>
       <c r="F1796">
         <v>-1</v>
       </c>
       <c r="G1796">
-        <v>0.0108531463654008</v>
+        <v>0.01096278831693948</v>
       </c>
       <c r="H1796">
-        <v>0.01130177384629907</v>
+        <v>0.01123177384629907</v>
       </c>
       <c r="I1796">
-        <v>0.008627480898264039</v>
+        <v>0.06898552935958691</v>
       </c>
       <c r="J1796">
         <v>0.994032525644623</v>
       </c>
       <c r="K1796">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="L1796">
-        <v>6.38</v>
+        <v>6.43</v>
       </c>
       <c r="M1796">
         <v>4.73</v>
       </c>
       <c r="N1796">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92057,46 +92057,46 @@
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1797" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C1797">
-        <v>2.029061600110686</v>
+        <v>1.906853634599196</v>
       </c>
       <c r="D1797" t="s">
         <v>513</v>
       </c>
       <c r="E1797">
-        <v>1.898226153700932</v>
+        <v>1.828226153700933</v>
       </c>
       <c r="F1797">
         <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.01171093839988931</v>
+        <v>0.0108531463654008</v>
       </c>
       <c r="H1797">
-        <v>0.01130177384629907</v>
+        <v>0.01123177384629907</v>
       </c>
       <c r="I1797">
-        <v>0.1308354464097539</v>
+        <v>0.07862748089826344</v>
       </c>
       <c r="J1797">
         <v>0.994032525644623</v>
       </c>
       <c r="K1797">
-        <v>4.87</v>
+        <v>4.5</v>
       </c>
       <c r="L1797">
-        <v>6.87</v>
+        <v>6.38</v>
       </c>
       <c r="M1797">
         <v>4.73</v>
       </c>
       <c r="N1797">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92107,46 +92107,46 @@
     </row>
     <row r="1798" spans="1:16">
       <c r="A1798" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1798" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1798">
-        <v>2.03816647895738</v>
+        <v>2.029061600110686</v>
       </c>
       <c r="D1798" t="s">
         <v>513</v>
       </c>
       <c r="E1798">
-        <v>1.898226153700932</v>
+        <v>1.828226153700933</v>
       </c>
       <c r="F1798">
         <v>-1</v>
       </c>
       <c r="G1798">
-        <v>0.01142183352104262</v>
+        <v>0.01171093839988931</v>
       </c>
       <c r="H1798">
-        <v>0.01130177384629907</v>
+        <v>0.01123177384629907</v>
       </c>
       <c r="I1798">
-        <v>0.1399403252564477</v>
+        <v>0.2008354464097533</v>
       </c>
       <c r="J1798">
         <v>0.994032525644623</v>
       </c>
       <c r="K1798">
-        <v>4.72</v>
+        <v>4.87</v>
       </c>
       <c r="L1798">
-        <v>6.73</v>
+        <v>6.87</v>
       </c>
       <c r="M1798">
         <v>4.73</v>
       </c>
       <c r="N1798">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92157,63 +92157,63 @@
     </row>
     <row r="1799" spans="1:16">
       <c r="A1799" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1799" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C1799">
-        <v>1.091573753380461</v>
+        <v>2.03816647895738</v>
       </c>
       <c r="D1799" t="s">
-        <v>348</v>
+        <v>513</v>
       </c>
       <c r="E1799">
-        <v>1.506278882193858</v>
+        <v>1.828226153700933</v>
       </c>
       <c r="F1799">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1799">
-        <v>0.01102842624661954</v>
+        <v>0.01142183352104262</v>
       </c>
       <c r="H1799">
-        <v>0.01161372111780614</v>
+        <v>0.01123177384629907</v>
       </c>
       <c r="I1799">
-        <v>0.4147051288133978</v>
+        <v>0.2099403252564471</v>
       </c>
       <c r="J1799">
-        <v>1.066185889832519</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1799">
-        <v>4.66</v>
+        <v>4.72</v>
       </c>
       <c r="L1799">
-        <v>6.06</v>
+        <v>6.73</v>
       </c>
       <c r="M1799">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="N1799">
-        <v>6.56</v>
+        <v>6.53</v>
       </c>
       <c r="O1799">
         <v>1</v>
       </c>
       <c r="P1799" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1800" spans="1:16">
       <c r="A1800" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1800" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C1800">
-        <v>1.106278882193859</v>
+        <v>1.091573753380461</v>
       </c>
       <c r="D1800" t="s">
         <v>348</v>
@@ -92225,22 +92225,22 @@
         <v>1</v>
       </c>
       <c r="G1800">
-        <v>0.01121372111780614</v>
+        <v>0.01102842624661954</v>
       </c>
       <c r="H1800">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1800">
-        <v>0.3999999999999995</v>
+        <v>0.4147051288133978</v>
       </c>
       <c r="J1800">
         <v>1.066185889832519</v>
       </c>
       <c r="K1800">
-        <v>4.74</v>
+        <v>4.66</v>
       </c>
       <c r="L1800">
-        <v>6.16</v>
+        <v>6.06</v>
       </c>
       <c r="M1800">
         <v>4.74</v>
@@ -92257,13 +92257,13 @@
     </row>
     <row r="1801" spans="1:16">
       <c r="A1801" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1801" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C1801">
-        <v>1.104738814821843</v>
+        <v>1.106278882193859</v>
       </c>
       <c r="D1801" t="s">
         <v>348</v>
@@ -92275,22 +92275,22 @@
         <v>1</v>
       </c>
       <c r="G1801">
-        <v>0.01029526118517816</v>
+        <v>0.01121372111780614</v>
       </c>
       <c r="H1801">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1801">
-        <v>0.4015400673720153</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1801">
         <v>1.066185889832519</v>
       </c>
       <c r="K1801">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="L1801">
-        <v>5.7</v>
+        <v>6.16</v>
       </c>
       <c r="M1801">
         <v>4.74</v>
@@ -92307,13 +92307,13 @@
     </row>
     <row r="1802" spans="1:16">
       <c r="A1802" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1802" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C1802">
-        <v>1.132969587702234</v>
+        <v>1.104738814821843</v>
       </c>
       <c r="D1802" t="s">
         <v>348</v>
@@ -92325,22 +92325,22 @@
         <v>1</v>
       </c>
       <c r="G1802">
-        <v>0.01134703041229777</v>
+        <v>0.01029526118517816</v>
       </c>
       <c r="H1802">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1802">
-        <v>0.3733092944916248</v>
+        <v>0.4015400673720153</v>
       </c>
       <c r="J1802">
         <v>1.066185889832519</v>
       </c>
       <c r="K1802">
-        <v>4.79</v>
+        <v>4.31</v>
       </c>
       <c r="L1802">
-        <v>6.24</v>
+        <v>5.7</v>
       </c>
       <c r="M1802">
         <v>4.74</v>
@@ -92357,13 +92357,13 @@
     </row>
     <row r="1803" spans="1:16">
       <c r="A1803" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1803" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C1803">
-        <v>1.093631446600559</v>
+        <v>1.132969587702234</v>
       </c>
       <c r="D1803" t="s">
         <v>348</v>
@@ -92375,22 +92375,22 @@
         <v>1</v>
       </c>
       <c r="G1803">
-        <v>0.01128636855339944</v>
+        <v>0.01134703041229777</v>
       </c>
       <c r="H1803">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1803">
-        <v>0.4126474355932999</v>
+        <v>0.3733092944916248</v>
       </c>
       <c r="J1803">
         <v>1.066185889832519</v>
       </c>
       <c r="K1803">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="L1803">
-        <v>6.19</v>
+        <v>6.24</v>
       </c>
       <c r="M1803">
         <v>4.74</v>
@@ -92407,46 +92407,46 @@
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1804" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C1804">
-        <v>1.568192342363713</v>
+        <v>1.093631446600559</v>
       </c>
       <c r="D1804" t="s">
-        <v>513</v>
+        <v>348</v>
       </c>
       <c r="E1804">
-        <v>1.556940741092183</v>
+        <v>1.506278882193858</v>
       </c>
       <c r="F1804">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1804">
-        <v>0.01129180765763629</v>
+        <v>0.01128636855339944</v>
       </c>
       <c r="H1804">
-        <v>0.01164305925890782</v>
+        <v>0.01161372111780614</v>
       </c>
       <c r="I1804">
-        <v>0.01125160127153002</v>
+        <v>0.4126474355932999</v>
       </c>
       <c r="J1804">
         <v>1.066185889832519</v>
       </c>
       <c r="K1804">
-        <v>4.56</v>
+        <v>4.78</v>
       </c>
       <c r="L1804">
-        <v>6.43</v>
+        <v>6.19</v>
       </c>
       <c r="M1804">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="N1804">
-        <v>6.6</v>
+        <v>6.56</v>
       </c>
       <c r="O1804">
         <v>1</v>
@@ -92457,46 +92457,46 @@
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1805" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1805">
-        <v>1.582163495753663</v>
+        <v>1.568192342363713</v>
       </c>
       <c r="D1805" t="s">
         <v>513</v>
       </c>
       <c r="E1805">
-        <v>1.556940741092183</v>
+        <v>1.486940741092184</v>
       </c>
       <c r="F1805">
         <v>-1</v>
       </c>
       <c r="G1805">
-        <v>0.01117783650424634</v>
+        <v>0.01129180765763629</v>
       </c>
       <c r="H1805">
-        <v>0.01164305925890782</v>
+        <v>0.01157305925890782</v>
       </c>
       <c r="I1805">
-        <v>0.02522275466148027</v>
+        <v>0.08125160127152942</v>
       </c>
       <c r="J1805">
         <v>1.066185889832519</v>
       </c>
       <c r="K1805">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="L1805">
-        <v>6.38</v>
+        <v>6.43</v>
       </c>
       <c r="M1805">
         <v>4.73</v>
       </c>
       <c r="N1805">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1805">
         <v>1</v>
@@ -92507,46 +92507,46 @@
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1806" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C1806">
-        <v>1.677674716515631</v>
+        <v>1.582163495753663</v>
       </c>
       <c r="D1806" t="s">
         <v>513</v>
       </c>
       <c r="E1806">
-        <v>1.556940741092183</v>
+        <v>1.486940741092184</v>
       </c>
       <c r="F1806">
         <v>-1</v>
       </c>
       <c r="G1806">
-        <v>0.01206232528348437</v>
+        <v>0.01117783650424634</v>
       </c>
       <c r="H1806">
-        <v>0.01164305925890782</v>
+        <v>0.01157305925890782</v>
       </c>
       <c r="I1806">
-        <v>0.1207339754234482</v>
+        <v>0.09522275466147967</v>
       </c>
       <c r="J1806">
         <v>1.066185889832519</v>
       </c>
       <c r="K1806">
-        <v>4.87</v>
+        <v>4.5</v>
       </c>
       <c r="L1806">
-        <v>6.87</v>
+        <v>6.38</v>
       </c>
       <c r="M1806">
         <v>4.73</v>
       </c>
       <c r="N1806">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92557,46 +92557,46 @@
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1807" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1807">
-        <v>1.69760259999051</v>
+        <v>1.677674716515631</v>
       </c>
       <c r="D1807" t="s">
         <v>513</v>
       </c>
       <c r="E1807">
-        <v>1.556940741092183</v>
+        <v>1.486940741092184</v>
       </c>
       <c r="F1807">
         <v>-1</v>
       </c>
       <c r="G1807">
-        <v>0.01176239740000949</v>
+        <v>0.01206232528348437</v>
       </c>
       <c r="H1807">
-        <v>0.01164305925890782</v>
+        <v>0.01157305925890782</v>
       </c>
       <c r="I1807">
-        <v>0.1406618588983273</v>
+        <v>0.1907339754234476</v>
       </c>
       <c r="J1807">
         <v>1.066185889832519</v>
       </c>
       <c r="K1807">
-        <v>4.72</v>
+        <v>4.87</v>
       </c>
       <c r="L1807">
-        <v>6.73</v>
+        <v>6.87</v>
       </c>
       <c r="M1807">
         <v>4.73</v>
       </c>
       <c r="N1807">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1807">
         <v>1</v>
@@ -92607,63 +92607,63 @@
     </row>
     <row r="1808" spans="1:16">
       <c r="A1808" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1808" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C1808">
-        <v>0.9527648456254667</v>
+        <v>1.69760259999051</v>
       </c>
       <c r="D1808" t="s">
-        <v>348</v>
+        <v>513</v>
       </c>
       <c r="E1808">
-        <v>1.352764845625466</v>
+        <v>1.486940741092184</v>
       </c>
       <c r="F1808">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1808">
-        <v>0.01136723515437453</v>
+        <v>0.01176239740000949</v>
       </c>
       <c r="H1808">
-        <v>0.01176723515437453</v>
+        <v>0.01157305925890782</v>
       </c>
       <c r="I1808">
-        <v>0.3999999999999995</v>
+        <v>0.2106618588983267</v>
       </c>
       <c r="J1808">
-        <v>1.098572817378594</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1808">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="L1808">
-        <v>6.16</v>
+        <v>6.73</v>
       </c>
       <c r="M1808">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="N1808">
-        <v>6.56</v>
+        <v>6.53</v>
       </c>
       <c r="O1808">
         <v>1</v>
       </c>
       <c r="P1808" t="s">
-        <v>352</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1809" spans="1:16">
       <c r="A1809" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1809" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C1809">
-        <v>0.965151157098262</v>
+        <v>0.9527648456254667</v>
       </c>
       <c r="D1809" t="s">
         <v>348</v>
@@ -92675,22 +92675,22 @@
         <v>1</v>
       </c>
       <c r="G1809">
-        <v>0.01043484884290174</v>
+        <v>0.01136723515437453</v>
       </c>
       <c r="H1809">
         <v>0.01176723515437453</v>
       </c>
       <c r="I1809">
-        <v>0.3876136885272041</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1809">
         <v>1.098572817378594</v>
       </c>
       <c r="K1809">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="L1809">
-        <v>5.7</v>
+        <v>6.16</v>
       </c>
       <c r="M1809">
         <v>4.74</v>
@@ -92707,13 +92707,13 @@
     </row>
     <row r="1810" spans="1:16">
       <c r="A1810" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1810" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C1810">
-        <v>0.977836204756537</v>
+        <v>0.965151157098262</v>
       </c>
       <c r="D1810" t="s">
         <v>348</v>
@@ -92725,22 +92725,22 @@
         <v>1</v>
       </c>
       <c r="G1810">
-        <v>0.01150216379524346</v>
+        <v>0.01043484884290174</v>
       </c>
       <c r="H1810">
         <v>0.01176723515437453</v>
       </c>
       <c r="I1810">
-        <v>0.3749286408689292</v>
+        <v>0.3876136885272041</v>
       </c>
       <c r="J1810">
         <v>1.098572817378594</v>
       </c>
       <c r="K1810">
-        <v>4.79</v>
+        <v>4.31</v>
       </c>
       <c r="L1810">
-        <v>6.24</v>
+        <v>5.7</v>
       </c>
       <c r="M1810">
         <v>4.74</v>
@@ -92757,13 +92757,13 @@
     </row>
     <row r="1811" spans="1:16">
       <c r="A1811" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1811" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C1811">
-        <v>0.9388219329303231</v>
+        <v>0.977836204756537</v>
       </c>
       <c r="D1811" t="s">
         <v>348</v>
@@ -92775,22 +92775,22 @@
         <v>1</v>
       </c>
       <c r="G1811">
-        <v>0.01144117806706968</v>
+        <v>0.01150216379524346</v>
       </c>
       <c r="H1811">
         <v>0.01176723515437453</v>
       </c>
       <c r="I1811">
-        <v>0.4139429126951431</v>
+        <v>0.3749286408689292</v>
       </c>
       <c r="J1811">
         <v>1.098572817378594</v>
       </c>
       <c r="K1811">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="L1811">
-        <v>6.19</v>
+        <v>6.24</v>
       </c>
       <c r="M1811">
         <v>4.74</v>
@@ -92807,46 +92807,46 @@
     </row>
     <row r="1812" spans="1:16">
       <c r="A1812" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1812" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C1812">
-        <v>1.420507952753614</v>
+        <v>0.9388219329303231</v>
       </c>
       <c r="D1812" t="s">
-        <v>513</v>
+        <v>348</v>
       </c>
       <c r="E1812">
-        <v>1.403750573799251</v>
+        <v>1.352764845625466</v>
       </c>
       <c r="F1812">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1812">
-        <v>0.01143949204724639</v>
+        <v>0.01144117806706968</v>
       </c>
       <c r="H1812">
-        <v>0.01179624942620075</v>
+        <v>0.01176723515437453</v>
       </c>
       <c r="I1812">
-        <v>0.01675737895436225</v>
+        <v>0.4139429126951431</v>
       </c>
       <c r="J1812">
         <v>1.098572817378594</v>
       </c>
       <c r="K1812">
-        <v>4.56</v>
+        <v>4.78</v>
       </c>
       <c r="L1812">
-        <v>6.43</v>
+        <v>6.19</v>
       </c>
       <c r="M1812">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="N1812">
-        <v>6.6</v>
+        <v>6.56</v>
       </c>
       <c r="O1812">
         <v>1</v>
@@ -92857,46 +92857,46 @@
     </row>
     <row r="1813" spans="1:16">
       <c r="A1813" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1813" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1813">
-        <v>1.436422321796329</v>
+        <v>1.420507952753614</v>
       </c>
       <c r="D1813" t="s">
         <v>513</v>
       </c>
       <c r="E1813">
-        <v>1.403750573799251</v>
+        <v>1.333750573799252</v>
       </c>
       <c r="F1813">
         <v>-1</v>
       </c>
       <c r="G1813">
-        <v>0.01132357767820367</v>
+        <v>0.01143949204724639</v>
       </c>
       <c r="H1813">
-        <v>0.01179624942620075</v>
+        <v>0.01172624942620075</v>
       </c>
       <c r="I1813">
-        <v>0.03267174799707728</v>
+        <v>0.08675737895436164</v>
       </c>
       <c r="J1813">
         <v>1.098572817378594</v>
       </c>
       <c r="K1813">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="L1813">
-        <v>6.38</v>
+        <v>6.43</v>
       </c>
       <c r="M1813">
         <v>4.73</v>
       </c>
       <c r="N1813">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1813">
         <v>1</v>
@@ -92907,46 +92907,46 @@
     </row>
     <row r="1814" spans="1:16">
       <c r="A1814" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1814" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C1814">
-        <v>1.519950379366249</v>
+        <v>1.436422321796329</v>
       </c>
       <c r="D1814" t="s">
         <v>513</v>
       </c>
       <c r="E1814">
-        <v>1.403750573799251</v>
+        <v>1.333750573799252</v>
       </c>
       <c r="F1814">
         <v>-1</v>
       </c>
       <c r="G1814">
-        <v>0.01222004962063375</v>
+        <v>0.01132357767820367</v>
       </c>
       <c r="H1814">
-        <v>0.01179624942620075</v>
+        <v>0.01172624942620075</v>
       </c>
       <c r="I1814">
-        <v>0.1161998055669979</v>
+        <v>0.1026717479970767</v>
       </c>
       <c r="J1814">
         <v>1.098572817378594</v>
       </c>
       <c r="K1814">
-        <v>4.87</v>
+        <v>4.5</v>
       </c>
       <c r="L1814">
-        <v>6.87</v>
+        <v>6.38</v>
       </c>
       <c r="M1814">
         <v>4.73</v>
       </c>
       <c r="N1814">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1814">
         <v>1</v>
@@ -92957,46 +92957,46 @@
     </row>
     <row r="1815" spans="1:16">
       <c r="A1815" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1815" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1815">
-        <v>1.544736301973039</v>
+        <v>1.519950379366249</v>
       </c>
       <c r="D1815" t="s">
         <v>513</v>
       </c>
       <c r="E1815">
-        <v>1.403750573799251</v>
+        <v>1.333750573799252</v>
       </c>
       <c r="F1815">
         <v>-1</v>
       </c>
       <c r="G1815">
-        <v>0.01191526369802696</v>
+        <v>0.01222004962063375</v>
       </c>
       <c r="H1815">
-        <v>0.01179624942620075</v>
+        <v>0.01172624942620075</v>
       </c>
       <c r="I1815">
-        <v>0.1409857281737876</v>
+        <v>0.1861998055669973</v>
       </c>
       <c r="J1815">
         <v>1.098572817378594</v>
       </c>
       <c r="K1815">
-        <v>4.72</v>
+        <v>4.87</v>
       </c>
       <c r="L1815">
-        <v>6.73</v>
+        <v>6.87</v>
       </c>
       <c r="M1815">
         <v>4.73</v>
       </c>
       <c r="N1815">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1815">
         <v>1</v>
@@ -93007,63 +93007,63 @@
     </row>
     <row r="1816" spans="1:16">
       <c r="A1816" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1816" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C1816">
-        <v>0.8652138986958411</v>
+        <v>1.544736301973039</v>
       </c>
       <c r="D1816" t="s">
-        <v>348</v>
+        <v>513</v>
       </c>
       <c r="E1816">
-        <v>1.265213898695841</v>
+        <v>1.333750573799252</v>
       </c>
       <c r="F1816">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1816">
-        <v>0.01145478610130416</v>
+        <v>0.01191526369802696</v>
       </c>
       <c r="H1816">
-        <v>0.01185478610130416</v>
+        <v>0.01172624942620075</v>
       </c>
       <c r="I1816">
-        <v>0.3999999999999995</v>
+        <v>0.210985728173787</v>
       </c>
       <c r="J1816">
-        <v>1.117043481287797</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1816">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="L1816">
-        <v>6.16</v>
+        <v>6.73</v>
       </c>
       <c r="M1816">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="N1816">
-        <v>6.56</v>
+        <v>6.53</v>
       </c>
       <c r="O1816">
         <v>1</v>
       </c>
       <c r="P1816" t="s">
-        <v>627</v>
+        <v>352</v>
       </c>
     </row>
     <row r="1817" spans="1:16">
       <c r="A1817" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1817" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C1817">
-        <v>0.8855425956495946</v>
+        <v>0.8652138986958411</v>
       </c>
       <c r="D1817" t="s">
         <v>348</v>
@@ -93075,22 +93075,22 @@
         <v>1</v>
       </c>
       <c r="G1817">
-        <v>0.01051445740435041</v>
+        <v>0.01145478610130416</v>
       </c>
       <c r="H1817">
         <v>0.01185478610130416</v>
       </c>
       <c r="I1817">
-        <v>0.379671303046246</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1817">
         <v>1.117043481287797</v>
       </c>
       <c r="K1817">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="L1817">
-        <v>5.7</v>
+        <v>6.16</v>
       </c>
       <c r="M1817">
         <v>4.74</v>
@@ -93107,13 +93107,13 @@
     </row>
     <row r="1818" spans="1:16">
       <c r="A1818" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1818" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C1818">
-        <v>0.8893617246314518</v>
+        <v>0.8855425956495946</v>
       </c>
       <c r="D1818" t="s">
         <v>348</v>
@@ -93125,22 +93125,22 @@
         <v>1</v>
       </c>
       <c r="G1818">
-        <v>0.01159063827536855</v>
+        <v>0.01051445740435041</v>
       </c>
       <c r="H1818">
         <v>0.01185478610130416</v>
       </c>
       <c r="I1818">
-        <v>0.3758521740643888</v>
+        <v>0.379671303046246</v>
       </c>
       <c r="J1818">
         <v>1.117043481287797</v>
       </c>
       <c r="K1818">
-        <v>4.79</v>
+        <v>4.31</v>
       </c>
       <c r="L1818">
-        <v>6.24</v>
+        <v>5.7</v>
       </c>
       <c r="M1818">
         <v>4.74</v>
@@ -93157,13 +93157,13 @@
     </row>
     <row r="1819" spans="1:16">
       <c r="A1819" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1819" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C1819">
-        <v>0.85053215944433</v>
+        <v>0.8893617246314518</v>
       </c>
       <c r="D1819" t="s">
         <v>348</v>
@@ -93175,22 +93175,22 @@
         <v>1</v>
       </c>
       <c r="G1819">
-        <v>0.01152946784055567</v>
+        <v>0.01159063827536855</v>
       </c>
       <c r="H1819">
         <v>0.01185478610130416</v>
       </c>
       <c r="I1819">
-        <v>0.4146817392515105</v>
+        <v>0.3758521740643888</v>
       </c>
       <c r="J1819">
         <v>1.117043481287797</v>
       </c>
       <c r="K1819">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="L1819">
-        <v>6.19</v>
+        <v>6.24</v>
       </c>
       <c r="M1819">
         <v>4.74</v>
@@ -93207,46 +93207,46 @@
     </row>
     <row r="1820" spans="1:16">
       <c r="A1820" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1820" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C1820">
-        <v>1.336281725327645</v>
+        <v>0.85053215944433</v>
       </c>
       <c r="D1820" t="s">
-        <v>513</v>
+        <v>348</v>
       </c>
       <c r="E1820">
-        <v>1.316384333508719</v>
+        <v>1.265213898695841</v>
       </c>
       <c r="F1820">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1820">
-        <v>0.01152371827467235</v>
+        <v>0.01152946784055567</v>
       </c>
       <c r="H1820">
-        <v>0.01188361566649128</v>
+        <v>0.01185478610130416</v>
       </c>
       <c r="I1820">
-        <v>0.01989739181892602</v>
+        <v>0.4146817392515105</v>
       </c>
       <c r="J1820">
         <v>1.117043481287797</v>
       </c>
       <c r="K1820">
-        <v>4.56</v>
+        <v>4.78</v>
       </c>
       <c r="L1820">
-        <v>6.43</v>
+        <v>6.19</v>
       </c>
       <c r="M1820">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="N1820">
-        <v>6.6</v>
+        <v>6.56</v>
       </c>
       <c r="O1820">
         <v>1</v>
@@ -93257,46 +93257,46 @@
     </row>
     <row r="1821" spans="1:16">
       <c r="A1821" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1821" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1821">
-        <v>1.353304334204912</v>
+        <v>1.336281725327645</v>
       </c>
       <c r="D1821" t="s">
         <v>513</v>
       </c>
       <c r="E1821">
-        <v>1.316384333508719</v>
+        <v>1.246384333508719</v>
       </c>
       <c r="F1821">
         <v>-1</v>
       </c>
       <c r="G1821">
-        <v>0.01140669566579509</v>
+        <v>0.01152371827467235</v>
       </c>
       <c r="H1821">
-        <v>0.01188361566649128</v>
+        <v>0.01181361566649128</v>
       </c>
       <c r="I1821">
-        <v>0.03692000069619361</v>
+        <v>0.08989739181892542</v>
       </c>
       <c r="J1821">
         <v>1.117043481287797</v>
       </c>
       <c r="K1821">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="L1821">
-        <v>6.38</v>
+        <v>6.43</v>
       </c>
       <c r="M1821">
         <v>4.73</v>
       </c>
       <c r="N1821">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1821">
         <v>1</v>
@@ -93307,46 +93307,46 @@
     </row>
     <row r="1822" spans="1:16">
       <c r="A1822" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1822" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C1822">
-        <v>1.429998246128427</v>
+        <v>1.353304334204912</v>
       </c>
       <c r="D1822" t="s">
         <v>513</v>
       </c>
       <c r="E1822">
-        <v>1.316384333508719</v>
+        <v>1.246384333508719</v>
       </c>
       <c r="F1822">
         <v>-1</v>
       </c>
       <c r="G1822">
-        <v>0.01231000175387157</v>
+        <v>0.01140669566579509</v>
       </c>
       <c r="H1822">
-        <v>0.01188361566649128</v>
+        <v>0.01181361566649128</v>
       </c>
       <c r="I1822">
-        <v>0.1136139126197087</v>
+        <v>0.106920000696193</v>
       </c>
       <c r="J1822">
         <v>1.117043481287797</v>
       </c>
       <c r="K1822">
-        <v>4.87</v>
+        <v>4.5</v>
       </c>
       <c r="L1822">
-        <v>6.87</v>
+        <v>6.38</v>
       </c>
       <c r="M1822">
         <v>4.73</v>
       </c>
       <c r="N1822">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1822">
         <v>1</v>
@@ -93357,51 +93357,101 @@
     </row>
     <row r="1823" spans="1:16">
       <c r="A1823" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1823" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1823">
-        <v>1.457554768321598</v>
+        <v>1.429998246128427</v>
       </c>
       <c r="D1823" t="s">
         <v>513</v>
       </c>
       <c r="E1823">
-        <v>1.316384333508719</v>
+        <v>1.246384333508719</v>
       </c>
       <c r="F1823">
         <v>-1</v>
       </c>
       <c r="G1823">
-        <v>0.0120024452316784</v>
+        <v>0.01231000175387157</v>
       </c>
       <c r="H1823">
-        <v>0.01188361566649128</v>
+        <v>0.01181361566649128</v>
       </c>
       <c r="I1823">
-        <v>0.1411704348128797</v>
+        <v>0.1836139126197081</v>
       </c>
       <c r="J1823">
         <v>1.117043481287797</v>
       </c>
       <c r="K1823">
-        <v>4.72</v>
+        <v>4.87</v>
       </c>
       <c r="L1823">
-        <v>6.73</v>
+        <v>6.87</v>
       </c>
       <c r="M1823">
         <v>4.73</v>
       </c>
       <c r="N1823">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
       <c r="O1823">
         <v>1</v>
       </c>
       <c r="P1823" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:16">
+      <c r="A1824" s="1">
+        <v>7</v>
+      </c>
+      <c r="B1824" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1824">
+        <v>1.457554768321598</v>
+      </c>
+      <c r="D1824" t="s">
+        <v>513</v>
+      </c>
+      <c r="E1824">
+        <v>1.246384333508719</v>
+      </c>
+      <c r="F1824">
+        <v>-1</v>
+      </c>
+      <c r="G1824">
+        <v>0.0120024452316784</v>
+      </c>
+      <c r="H1824">
+        <v>0.01181361566649128</v>
+      </c>
+      <c r="I1824">
+        <v>0.2111704348128791</v>
+      </c>
+      <c r="J1824">
+        <v>1.117043481287797</v>
+      </c>
+      <c r="K1824">
+        <v>4.72</v>
+      </c>
+      <c r="L1824">
+        <v>6.73</v>
+      </c>
+      <c r="M1824">
+        <v>4.73</v>
+      </c>
+      <c r="N1824">
+        <v>6.53</v>
+      </c>
+      <c r="O1824">
+        <v>1</v>
+      </c>
+      <c r="P1824" t="s">
         <v>627</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -1552,7 +1552,7 @@
     <t>2021-08-11</t>
   </si>
   <si>
-    <t>2021-11-29</t>
+    <t>2021-11-30</t>
   </si>
   <si>
     <t>2016-03-09</t>
@@ -91316,7 +91316,7 @@
         <v>512</v>
       </c>
       <c r="E1782">
-        <v>1.92897739693088</v>
+        <v>1.974029860534256</v>
       </c>
       <c r="F1782">
         <v>-1</v>
@@ -91325,10 +91325,10 @@
         <v>0.0111196052113846</v>
       </c>
       <c r="H1782">
-        <v>0.01047102260306912</v>
+        <v>0.01026597013946574</v>
       </c>
       <c r="I1782">
-        <v>0.07141739168451888</v>
+        <v>0.02636492808114266</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
@@ -91340,10 +91340,10 @@
         <v>6.56</v>
       </c>
       <c r="M1782">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1782">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91466,7 +91466,7 @@
         <v>512</v>
       </c>
       <c r="E1785">
-        <v>1.673780060625396</v>
+        <v>1.726304518309789</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91475,10 +91475,10 @@
         <v>0.01139204561095397</v>
       </c>
       <c r="H1785">
-        <v>0.0107262199393746</v>
+        <v>0.01051369548169021</v>
       </c>
       <c r="I1785">
-        <v>0.05417432842063441</v>
+        <v>0.001649870736241787</v>
       </c>
       <c r="J1785">
         <v>1.01941890526455</v>
@@ -91490,10 +91490,10 @@
         <v>6.56</v>
       </c>
       <c r="M1785">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1785">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91616,7 +91616,7 @@
         <v>512</v>
       </c>
       <c r="E1788">
-        <v>1.424169413084638</v>
+        <v>1.484002290629457</v>
       </c>
       <c r="F1788">
         <v>-1</v>
@@ -91625,10 +91625,10 @@
         <v>0.01165852184278802</v>
       </c>
       <c r="H1788">
-        <v>0.01097583058691536</v>
+        <v>0.01075599770937054</v>
       </c>
       <c r="I1788">
-        <v>0.03730874412733964</v>
+        <v>-0.0225241334174795</v>
       </c>
       <c r="J1788">
         <v>1.075637519575532</v>
@@ -91640,10 +91640,10 @@
         <v>6.56</v>
       </c>
       <c r="M1788">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1788">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91716,7 +91716,7 @@
         <v>512</v>
       </c>
       <c r="E1790">
-        <v>1.363806356718042</v>
+        <v>1.425406621048371</v>
       </c>
       <c r="F1790">
         <v>-1</v>
@@ -91725,10 +91725,10 @@
         <v>0.01172296348404425</v>
       </c>
       <c r="H1790">
-        <v>0.01103619364328196</v>
+        <v>0.01081459337895163</v>
       </c>
       <c r="I1790">
-        <v>0.03323015923770534</v>
+        <v>-0.02837010509262328</v>
       </c>
       <c r="J1790">
         <v>1.089232802540981</v>
@@ -91740,10 +91740,10 @@
         <v>6.56</v>
       </c>
       <c r="M1790">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1790">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1790">
         <v>1</v>
@@ -92016,7 +92016,7 @@
         <v>512</v>
       </c>
       <c r="E1796">
-        <v>1.786495586137874</v>
+        <v>1.835719814471675</v>
       </c>
       <c r="F1796">
         <v>-1</v>
@@ -92025,10 +92025,10 @@
         <v>0.01096278831693948</v>
       </c>
       <c r="H1796">
-        <v>0.01061350441386213</v>
+        <v>0.01040428018552833</v>
       </c>
       <c r="I1796">
-        <v>0.1107160969226459</v>
+        <v>0.06149186858884459</v>
       </c>
       <c r="J1796">
         <v>0.994032525644623</v>
@@ -92040,10 +92040,10 @@
         <v>6.43</v>
       </c>
       <c r="M1796">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1796">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92066,7 +92066,7 @@
         <v>512</v>
       </c>
       <c r="E1797">
-        <v>1.786495586137874</v>
+        <v>1.835719814471675</v>
       </c>
       <c r="F1797">
         <v>-1</v>
@@ -92075,10 +92075,10 @@
         <v>0.0108531463654008</v>
       </c>
       <c r="H1797">
-        <v>0.01061350441386213</v>
+        <v>0.01040428018552833</v>
       </c>
       <c r="I1797">
-        <v>0.1203580484613225</v>
+        <v>0.07113382012752112</v>
       </c>
       <c r="J1797">
         <v>0.994032525644623</v>
@@ -92090,10 +92090,10 @@
         <v>6.38</v>
       </c>
       <c r="M1797">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1797">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92116,7 +92116,7 @@
         <v>512</v>
       </c>
       <c r="E1798">
-        <v>1.786495586137874</v>
+        <v>1.835719814471675</v>
       </c>
       <c r="F1798">
         <v>-1</v>
@@ -92125,10 +92125,10 @@
         <v>0.01171093839988931</v>
       </c>
       <c r="H1798">
-        <v>0.01061350441386213</v>
+        <v>0.01040428018552833</v>
       </c>
       <c r="I1798">
-        <v>0.2425660139728123</v>
+        <v>0.1933417856390109</v>
       </c>
       <c r="J1798">
         <v>0.994032525644623</v>
@@ -92140,10 +92140,10 @@
         <v>6.87</v>
       </c>
       <c r="M1798">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1798">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92166,7 +92166,7 @@
         <v>512</v>
       </c>
       <c r="E1799">
-        <v>1.786495586137874</v>
+        <v>1.835719814471675</v>
       </c>
       <c r="F1799">
         <v>-1</v>
@@ -92175,10 +92175,10 @@
         <v>0.01142183352104262</v>
       </c>
       <c r="H1799">
-        <v>0.01061350441386213</v>
+        <v>0.01040428018552833</v>
       </c>
       <c r="I1799">
-        <v>0.2516708928195062</v>
+        <v>0.2024466644857048</v>
       </c>
       <c r="J1799">
         <v>0.994032525644623</v>
@@ -92190,10 +92190,10 @@
         <v>6.73</v>
       </c>
       <c r="M1799">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1799">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1799">
         <v>1</v>
@@ -92466,7 +92466,7 @@
         <v>512</v>
       </c>
       <c r="E1805">
-        <v>1.466134649143615</v>
+        <v>1.524738814821843</v>
       </c>
       <c r="F1805">
         <v>-1</v>
@@ -92475,10 +92475,10 @@
         <v>0.01129180765763629</v>
       </c>
       <c r="H1805">
-        <v>0.01093386535085639</v>
+        <v>0.01071526118517816</v>
       </c>
       <c r="I1805">
-        <v>0.1020576932200985</v>
+        <v>0.04345352754187015</v>
       </c>
       <c r="J1805">
         <v>1.066185889832519</v>
@@ -92490,10 +92490,10 @@
         <v>6.43</v>
       </c>
       <c r="M1805">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1805">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1805">
         <v>1</v>
@@ -92516,7 +92516,7 @@
         <v>512</v>
       </c>
       <c r="E1806">
-        <v>1.466134649143615</v>
+        <v>1.524738814821843</v>
       </c>
       <c r="F1806">
         <v>-1</v>
@@ -92525,10 +92525,10 @@
         <v>0.01117783650424634</v>
       </c>
       <c r="H1806">
-        <v>0.01093386535085639</v>
+        <v>0.01071526118517816</v>
       </c>
       <c r="I1806">
-        <v>0.1160288466100488</v>
+        <v>0.0574246809318204</v>
       </c>
       <c r="J1806">
         <v>1.066185889832519</v>
@@ -92540,10 +92540,10 @@
         <v>6.38</v>
       </c>
       <c r="M1806">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1806">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92566,7 +92566,7 @@
         <v>512</v>
       </c>
       <c r="E1807">
-        <v>1.466134649143615</v>
+        <v>1.524738814821843</v>
       </c>
       <c r="F1807">
         <v>-1</v>
@@ -92575,10 +92575,10 @@
         <v>0.01206232528348437</v>
       </c>
       <c r="H1807">
-        <v>0.01093386535085639</v>
+        <v>0.01071526118517816</v>
       </c>
       <c r="I1807">
-        <v>0.2115400673720167</v>
+        <v>0.1529359016937883</v>
       </c>
       <c r="J1807">
         <v>1.066185889832519</v>
@@ -92590,10 +92590,10 @@
         <v>6.87</v>
       </c>
       <c r="M1807">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1807">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1807">
         <v>1</v>
@@ -92616,7 +92616,7 @@
         <v>512</v>
       </c>
       <c r="E1808">
-        <v>1.466134649143615</v>
+        <v>1.524738814821843</v>
       </c>
       <c r="F1808">
         <v>-1</v>
@@ -92625,10 +92625,10 @@
         <v>0.01176239740000949</v>
       </c>
       <c r="H1808">
-        <v>0.01093386535085639</v>
+        <v>0.01071526118517816</v>
       </c>
       <c r="I1808">
-        <v>0.2314679508468958</v>
+        <v>0.1728637851686674</v>
       </c>
       <c r="J1808">
         <v>1.066185889832519</v>
@@ -92640,10 +92640,10 @@
         <v>6.73</v>
       </c>
       <c r="M1808">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1808">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1808">
         <v>1</v>
@@ -92866,7 +92866,7 @@
         <v>512</v>
       </c>
       <c r="E1813">
-        <v>1.322336690839045</v>
+        <v>1.385151157098262</v>
       </c>
       <c r="F1813">
         <v>-1</v>
@@ -92875,10 +92875,10 @@
         <v>0.01143949204724639</v>
       </c>
       <c r="H1813">
-        <v>0.01107766330916096</v>
+        <v>0.01085484884290174</v>
       </c>
       <c r="I1813">
-        <v>0.09817126191456893</v>
+        <v>0.03535679565535155</v>
       </c>
       <c r="J1813">
         <v>1.098572817378594</v>
@@ -92890,10 +92890,10 @@
         <v>6.43</v>
       </c>
       <c r="M1813">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1813">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1813">
         <v>1</v>
@@ -92916,7 +92916,7 @@
         <v>512</v>
       </c>
       <c r="E1814">
-        <v>1.322336690839045</v>
+        <v>1.385151157098262</v>
       </c>
       <c r="F1814">
         <v>-1</v>
@@ -92925,10 +92925,10 @@
         <v>0.01132357767820367</v>
       </c>
       <c r="H1814">
-        <v>0.01107766330916096</v>
+        <v>0.01085484884290174</v>
       </c>
       <c r="I1814">
-        <v>0.114085630957284</v>
+        <v>0.05127116469806658</v>
       </c>
       <c r="J1814">
         <v>1.098572817378594</v>
@@ -92940,10 +92940,10 @@
         <v>6.38</v>
       </c>
       <c r="M1814">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1814">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1814">
         <v>1</v>
@@ -92966,7 +92966,7 @@
         <v>512</v>
       </c>
       <c r="E1815">
-        <v>1.322336690839045</v>
+        <v>1.385151157098262</v>
       </c>
       <c r="F1815">
         <v>-1</v>
@@ -92975,10 +92975,10 @@
         <v>0.01222004962063375</v>
       </c>
       <c r="H1815">
-        <v>0.01107766330916096</v>
+        <v>0.01085484884290174</v>
       </c>
       <c r="I1815">
-        <v>0.1976136885272046</v>
+        <v>0.1347992222679872</v>
       </c>
       <c r="J1815">
         <v>1.098572817378594</v>
@@ -92990,10 +92990,10 @@
         <v>6.87</v>
       </c>
       <c r="M1815">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1815">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1815">
         <v>1</v>
@@ -93016,7 +93016,7 @@
         <v>512</v>
       </c>
       <c r="E1816">
-        <v>1.322336690839045</v>
+        <v>1.385151157098262</v>
       </c>
       <c r="F1816">
         <v>-1</v>
@@ -93025,10 +93025,10 @@
         <v>0.01191526369802696</v>
       </c>
       <c r="H1816">
-        <v>0.01107766330916096</v>
+        <v>0.01085484884290174</v>
       </c>
       <c r="I1816">
-        <v>0.2223996111339943</v>
+        <v>0.1595851448747769</v>
       </c>
       <c r="J1816">
         <v>1.098572817378594</v>
@@ -93040,10 +93040,10 @@
         <v>6.73</v>
       </c>
       <c r="M1816">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1816">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1816">
         <v>1</v>
@@ -93266,7 +93266,7 @@
         <v>512</v>
       </c>
       <c r="E1821">
-        <v>1.24032694308218</v>
+        <v>1.305542595649595</v>
       </c>
       <c r="F1821">
         <v>-1</v>
@@ -93275,10 +93275,10 @@
         <v>0.01152371827467235</v>
       </c>
       <c r="H1821">
-        <v>0.01115967305691782</v>
+        <v>0.01093445740435041</v>
       </c>
       <c r="I1821">
-        <v>0.09595478224546472</v>
+        <v>0.03073912967805015</v>
       </c>
       <c r="J1821">
         <v>1.117043481287797</v>
@@ -93290,10 +93290,10 @@
         <v>6.43</v>
       </c>
       <c r="M1821">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1821">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1821">
         <v>1</v>
@@ -93316,7 +93316,7 @@
         <v>512</v>
       </c>
       <c r="E1822">
-        <v>1.24032694308218</v>
+        <v>1.305542595649595</v>
       </c>
       <c r="F1822">
         <v>-1</v>
@@ -93325,10 +93325,10 @@
         <v>0.01140669566579509</v>
       </c>
       <c r="H1822">
-        <v>0.01115967305691782</v>
+        <v>0.01093445740435041</v>
       </c>
       <c r="I1822">
-        <v>0.1129773911227323</v>
+        <v>0.04776173855531773</v>
       </c>
       <c r="J1822">
         <v>1.117043481287797</v>
@@ -93340,10 +93340,10 @@
         <v>6.38</v>
       </c>
       <c r="M1822">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1822">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1822">
         <v>1</v>
@@ -93366,7 +93366,7 @@
         <v>512</v>
       </c>
       <c r="E1823">
-        <v>1.24032694308218</v>
+        <v>1.305542595649595</v>
       </c>
       <c r="F1823">
         <v>-1</v>
@@ -93375,10 +93375,10 @@
         <v>0.01231000175387157</v>
       </c>
       <c r="H1823">
-        <v>0.01115967305691782</v>
+        <v>0.01093445740435041</v>
       </c>
       <c r="I1823">
-        <v>0.1896713030462474</v>
+        <v>0.1244556504788328</v>
       </c>
       <c r="J1823">
         <v>1.117043481287797</v>
@@ -93390,10 +93390,10 @@
         <v>6.87</v>
       </c>
       <c r="M1823">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1823">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1823">
         <v>1</v>
@@ -93416,7 +93416,7 @@
         <v>512</v>
       </c>
       <c r="E1824">
-        <v>1.24032694308218</v>
+        <v>1.305542595649595</v>
       </c>
       <c r="F1824">
         <v>-1</v>
@@ -93425,10 +93425,10 @@
         <v>0.0120024452316784</v>
       </c>
       <c r="H1824">
-        <v>0.01115967305691782</v>
+        <v>0.01093445740435041</v>
       </c>
       <c r="I1824">
-        <v>0.2172278252394184</v>
+        <v>0.1520121726720038</v>
       </c>
       <c r="J1824">
         <v>1.117043481287797</v>
@@ -93440,10 +93440,10 @@
         <v>6.73</v>
       </c>
       <c r="M1824">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="N1824">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="O1824">
         <v>1</v>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5484" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5493" uniqueCount="627">
   <si>
     <t>trade_time</t>
   </si>
@@ -1066,16 +1066,19 @@
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
     <t>2021-09-08</t>
   </si>
   <si>
     <t>2021-09-10</t>
   </si>
   <si>
+    <t>2021-09-14</t>
+  </si>
+  <si>
     <t>2021-09-29</t>
+  </si>
+  <si>
+    <t>2021-10-12</t>
   </si>
   <si>
     <t>2021-10-22</t>
@@ -1091,9 +1094,6 @@
   </si>
   <si>
     <t>2021-11-19</t>
-  </si>
-  <si>
-    <t>2021-10-12</t>
   </si>
   <si>
     <t>2016-05-11</t>
@@ -1552,7 +1552,7 @@
     <t>2021-08-11</t>
   </si>
   <si>
-    <t>2021-11-30</t>
+    <t>2021-12-01</t>
   </si>
   <si>
     <t>2016-03-09</t>
@@ -2252,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1824"/>
+  <dimension ref="A1:P1827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91316,7 +91316,7 @@
         <v>512</v>
       </c>
       <c r="E1782">
-        <v>1.974029860534256</v>
+        <v>2.03479101997989</v>
       </c>
       <c r="F1782">
         <v>-1</v>
@@ -91325,10 +91325,10 @@
         <v>0.0111196052113846</v>
       </c>
       <c r="H1782">
-        <v>0.01026597013946574</v>
+        <v>0.01036520898002011</v>
       </c>
       <c r="I1782">
-        <v>0.02636492808114266</v>
+        <v>-0.03439623136449121</v>
       </c>
       <c r="J1782">
         <v>0.9619420277182702</v>
@@ -91340,10 +91340,10 @@
         <v>6.56</v>
       </c>
       <c r="M1782">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1782">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1782">
         <v>1</v>
@@ -91466,7 +91466,7 @@
         <v>512</v>
       </c>
       <c r="E1785">
-        <v>1.726304518309789</v>
+        <v>1.785916140204497</v>
       </c>
       <c r="F1785">
         <v>-1</v>
@@ -91475,10 +91475,10 @@
         <v>0.01139204561095397</v>
       </c>
       <c r="H1785">
-        <v>0.01051369548169021</v>
+        <v>0.0106140838597955</v>
       </c>
       <c r="I1785">
-        <v>0.001649870736241787</v>
+        <v>-0.05796175115846669</v>
       </c>
       <c r="J1785">
         <v>1.01941890526455</v>
@@ -91490,10 +91490,10 @@
         <v>6.56</v>
       </c>
       <c r="M1785">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1785">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1785">
         <v>1</v>
@@ -91616,7 +91616,7 @@
         <v>512</v>
       </c>
       <c r="E1788">
-        <v>1.484002290629457</v>
+        <v>1.542489540237946</v>
       </c>
       <c r="F1788">
         <v>-1</v>
@@ -91625,10 +91625,10 @@
         <v>0.01165852184278802</v>
       </c>
       <c r="H1788">
-        <v>0.01075599770937054</v>
+        <v>0.01085751045976205</v>
       </c>
       <c r="I1788">
-        <v>-0.0225241334174795</v>
+        <v>-0.08101138302596844</v>
       </c>
       <c r="J1788">
         <v>1.075637519575532</v>
@@ -91640,10 +91640,10 @@
         <v>6.56</v>
       </c>
       <c r="M1788">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1788">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1788">
         <v>1</v>
@@ -91716,7 +91716,7 @@
         <v>512</v>
       </c>
       <c r="E1790">
-        <v>1.425406621048371</v>
+        <v>1.483621964997551</v>
       </c>
       <c r="F1790">
         <v>-1</v>
@@ -91725,10 +91725,10 @@
         <v>0.01172296348404425</v>
       </c>
       <c r="H1790">
-        <v>0.01081459337895163</v>
+        <v>0.01091637803500245</v>
       </c>
       <c r="I1790">
-        <v>-0.02837010509262328</v>
+        <v>-0.08658544904180321</v>
       </c>
       <c r="J1790">
         <v>1.089232802540981</v>
@@ -91740,10 +91740,10 @@
         <v>6.56</v>
       </c>
       <c r="M1790">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1790">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1790">
         <v>1</v>
@@ -91760,7 +91760,7 @@
         <v>350</v>
       </c>
       <c r="C1791">
-        <v>1.437331032547627</v>
+        <v>1.427808430496056</v>
       </c>
       <c r="D1791" t="s">
         <v>348</v>
@@ -91772,22 +91772,22 @@
         <v>1</v>
       </c>
       <c r="G1791">
-        <v>0.01054266896745237</v>
+        <v>0.01069219156950394</v>
       </c>
       <c r="H1791">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1791">
-        <v>0.4109547958968598</v>
+        <v>0.4204773979484306</v>
       </c>
       <c r="J1791">
         <v>0.994032525644623</v>
       </c>
       <c r="K1791">
-        <v>4.58</v>
+        <v>4.66</v>
       </c>
       <c r="L1791">
-        <v>5.99</v>
+        <v>6.06</v>
       </c>
       <c r="M1791">
         <v>4.74</v>
@@ -91810,7 +91810,7 @@
         <v>351</v>
       </c>
       <c r="C1792">
-        <v>1.427808430496056</v>
+        <v>1.448285828444487</v>
       </c>
       <c r="D1792" t="s">
         <v>348</v>
@@ -91822,22 +91822,22 @@
         <v>1</v>
       </c>
       <c r="G1792">
-        <v>0.01069219156950394</v>
+        <v>0.01087171417155551</v>
       </c>
       <c r="H1792">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1792">
-        <v>0.4204773979484306</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1792">
         <v>0.994032525644623</v>
       </c>
       <c r="K1792">
-        <v>4.66</v>
+        <v>4.74</v>
       </c>
       <c r="L1792">
-        <v>6.06</v>
+        <v>6.16</v>
       </c>
       <c r="M1792">
         <v>4.74</v>
@@ -91860,7 +91860,7 @@
         <v>352</v>
       </c>
       <c r="C1793">
-        <v>1.448285828444487</v>
+        <v>1.476614935624982</v>
       </c>
       <c r="D1793" t="s">
         <v>348</v>
@@ -91872,22 +91872,22 @@
         <v>1</v>
       </c>
       <c r="G1793">
-        <v>0.01087171417155551</v>
+        <v>0.01034338506437502</v>
       </c>
       <c r="H1793">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1793">
-        <v>0.3999999999999995</v>
+        <v>0.3716708928195054</v>
       </c>
       <c r="J1793">
         <v>0.994032525644623</v>
       </c>
       <c r="K1793">
-        <v>4.74</v>
+        <v>4.46</v>
       </c>
       <c r="L1793">
-        <v>6.16</v>
+        <v>5.91</v>
       </c>
       <c r="M1793">
         <v>4.74</v>
@@ -91960,7 +91960,7 @@
         <v>354</v>
       </c>
       <c r="C1795">
-        <v>1.438524527418703</v>
+        <v>1.478584202162256</v>
       </c>
       <c r="D1795" t="s">
         <v>348</v>
@@ -91972,22 +91972,22 @@
         <v>1</v>
       </c>
       <c r="G1795">
-        <v>0.0109414754725813</v>
+        <v>0.01100141579783774</v>
       </c>
       <c r="H1795">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1795">
-        <v>0.4097613010257843</v>
+        <v>0.3697016262822306</v>
       </c>
       <c r="J1795">
         <v>0.994032525644623</v>
       </c>
       <c r="K1795">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="L1795">
-        <v>6.19</v>
+        <v>6.24</v>
       </c>
       <c r="M1795">
         <v>4.74</v>
@@ -92010,40 +92010,40 @@
         <v>355</v>
       </c>
       <c r="C1796">
-        <v>1.89721168306052</v>
+        <v>1.438524527418703</v>
       </c>
       <c r="D1796" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="E1796">
-        <v>1.835719814471675</v>
+        <v>1.848285828444487</v>
       </c>
       <c r="F1796">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1796">
-        <v>0.01096278831693948</v>
+        <v>0.0109414754725813</v>
       </c>
       <c r="H1796">
-        <v>0.01040428018552833</v>
+        <v>0.01127171417155551</v>
       </c>
       <c r="I1796">
-        <v>0.06149186858884459</v>
+        <v>0.4097613010257843</v>
       </c>
       <c r="J1796">
         <v>0.994032525644623</v>
       </c>
       <c r="K1796">
-        <v>4.56</v>
+        <v>4.78</v>
       </c>
       <c r="L1796">
-        <v>6.43</v>
+        <v>6.19</v>
       </c>
       <c r="M1796">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="N1796">
-        <v>6.12</v>
+        <v>6.56</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92060,40 +92060,40 @@
         <v>356</v>
       </c>
       <c r="C1797">
-        <v>1.906853634599196</v>
+        <v>1.89721168306052</v>
       </c>
       <c r="D1797" t="s">
         <v>512</v>
       </c>
       <c r="E1797">
-        <v>1.835719814471675</v>
+        <v>1.895839163958783</v>
       </c>
       <c r="F1797">
         <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.0108531463654008</v>
+        <v>0.01096278831693948</v>
       </c>
       <c r="H1797">
-        <v>0.01040428018552833</v>
+        <v>0.01050416083604122</v>
       </c>
       <c r="I1797">
-        <v>0.07113382012752112</v>
+        <v>0.001372519101736636</v>
       </c>
       <c r="J1797">
         <v>0.994032525644623</v>
       </c>
       <c r="K1797">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="L1797">
-        <v>6.38</v>
+        <v>6.43</v>
       </c>
       <c r="M1797">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1797">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92110,40 +92110,40 @@
         <v>357</v>
       </c>
       <c r="C1798">
-        <v>2.029061600110686</v>
+        <v>1.906853634599196</v>
       </c>
       <c r="D1798" t="s">
         <v>512</v>
       </c>
       <c r="E1798">
-        <v>1.835719814471675</v>
+        <v>1.895839163958783</v>
       </c>
       <c r="F1798">
         <v>-1</v>
       </c>
       <c r="G1798">
-        <v>0.01171093839988931</v>
+        <v>0.0108531463654008</v>
       </c>
       <c r="H1798">
-        <v>0.01040428018552833</v>
+        <v>0.01050416083604122</v>
       </c>
       <c r="I1798">
-        <v>0.1933417856390109</v>
+        <v>0.01101447064041317</v>
       </c>
       <c r="J1798">
         <v>0.994032525644623</v>
       </c>
       <c r="K1798">
-        <v>4.87</v>
+        <v>4.5</v>
       </c>
       <c r="L1798">
-        <v>6.87</v>
+        <v>6.38</v>
       </c>
       <c r="M1798">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1798">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92160,40 +92160,40 @@
         <v>358</v>
       </c>
       <c r="C1799">
-        <v>2.03816647895738</v>
+        <v>2.029061600110686</v>
       </c>
       <c r="D1799" t="s">
         <v>512</v>
       </c>
       <c r="E1799">
-        <v>1.835719814471675</v>
+        <v>1.895839163958783</v>
       </c>
       <c r="F1799">
         <v>-1</v>
       </c>
       <c r="G1799">
-        <v>0.01142183352104262</v>
+        <v>0.01171093839988931</v>
       </c>
       <c r="H1799">
-        <v>0.01040428018552833</v>
+        <v>0.01050416083604122</v>
       </c>
       <c r="I1799">
-        <v>0.2024466644857048</v>
+        <v>0.133222436151903</v>
       </c>
       <c r="J1799">
         <v>0.994032525644623</v>
       </c>
       <c r="K1799">
-        <v>4.72</v>
+        <v>4.87</v>
       </c>
       <c r="L1799">
-        <v>6.73</v>
+        <v>6.87</v>
       </c>
       <c r="M1799">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1799">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1799">
         <v>1</v>
@@ -92204,63 +92204,63 @@
     </row>
     <row r="1800" spans="1:16">
       <c r="A1800" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1800" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C1800">
-        <v>1.091573753380461</v>
+        <v>2.03816647895738</v>
       </c>
       <c r="D1800" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1800">
-        <v>1.506278882193858</v>
+        <v>1.895839163958783</v>
       </c>
       <c r="F1800">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1800">
-        <v>0.01102842624661954</v>
+        <v>0.01142183352104262</v>
       </c>
       <c r="H1800">
-        <v>0.01161372111780614</v>
+        <v>0.01050416083604122</v>
       </c>
       <c r="I1800">
-        <v>0.4147051288133978</v>
+        <v>0.1423273149985969</v>
       </c>
       <c r="J1800">
-        <v>1.066185889832519</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1800">
-        <v>4.66</v>
+        <v>4.72</v>
       </c>
       <c r="L1800">
-        <v>6.06</v>
+        <v>6.73</v>
       </c>
       <c r="M1800">
-        <v>4.74</v>
+        <v>4.33</v>
       </c>
       <c r="N1800">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="O1800">
         <v>1</v>
       </c>
       <c r="P1800" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1801" spans="1:16">
       <c r="A1801" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1801" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C1801">
-        <v>1.106278882193859</v>
+        <v>1.091573753380461</v>
       </c>
       <c r="D1801" t="s">
         <v>348</v>
@@ -92272,22 +92272,22 @@
         <v>1</v>
       </c>
       <c r="G1801">
-        <v>0.01121372111780614</v>
+        <v>0.01102842624661954</v>
       </c>
       <c r="H1801">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1801">
-        <v>0.3999999999999995</v>
+        <v>0.4147051288133978</v>
       </c>
       <c r="J1801">
         <v>1.066185889832519</v>
       </c>
       <c r="K1801">
-        <v>4.74</v>
+        <v>4.66</v>
       </c>
       <c r="L1801">
-        <v>6.16</v>
+        <v>6.06</v>
       </c>
       <c r="M1801">
         <v>4.74</v>
@@ -92304,13 +92304,13 @@
     </row>
     <row r="1802" spans="1:16">
       <c r="A1802" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1802" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C1802">
-        <v>1.104738814821843</v>
+        <v>1.106278882193859</v>
       </c>
       <c r="D1802" t="s">
         <v>348</v>
@@ -92322,22 +92322,22 @@
         <v>1</v>
       </c>
       <c r="G1802">
-        <v>0.01029526118517816</v>
+        <v>0.01121372111780614</v>
       </c>
       <c r="H1802">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1802">
-        <v>0.4015400673720153</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1802">
         <v>1.066185889832519</v>
       </c>
       <c r="K1802">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="L1802">
-        <v>5.7</v>
+        <v>6.16</v>
       </c>
       <c r="M1802">
         <v>4.74</v>
@@ -92354,13 +92354,13 @@
     </row>
     <row r="1803" spans="1:16">
       <c r="A1803" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1803" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C1803">
-        <v>1.132969587702234</v>
+        <v>1.154810931346964</v>
       </c>
       <c r="D1803" t="s">
         <v>348</v>
@@ -92372,22 +92372,22 @@
         <v>1</v>
       </c>
       <c r="G1803">
-        <v>0.01134703041229777</v>
+        <v>0.01066518906865303</v>
       </c>
       <c r="H1803">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1803">
-        <v>0.3733092944916248</v>
+        <v>0.3514679508468941</v>
       </c>
       <c r="J1803">
         <v>1.066185889832519</v>
       </c>
       <c r="K1803">
-        <v>4.79</v>
+        <v>4.46</v>
       </c>
       <c r="L1803">
-        <v>6.24</v>
+        <v>5.91</v>
       </c>
       <c r="M1803">
         <v>4.74</v>
@@ -92404,13 +92404,13 @@
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1804" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C1804">
-        <v>1.093631446600559</v>
+        <v>1.104738814821843</v>
       </c>
       <c r="D1804" t="s">
         <v>348</v>
@@ -92422,22 +92422,22 @@
         <v>1</v>
       </c>
       <c r="G1804">
-        <v>0.01128636855339944</v>
+        <v>0.01029526118517816</v>
       </c>
       <c r="H1804">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1804">
-        <v>0.4126474355932999</v>
+        <v>0.4015400673720153</v>
       </c>
       <c r="J1804">
         <v>1.066185889832519</v>
       </c>
       <c r="K1804">
-        <v>4.78</v>
+        <v>4.31</v>
       </c>
       <c r="L1804">
-        <v>6.19</v>
+        <v>5.7</v>
       </c>
       <c r="M1804">
         <v>4.74</v>
@@ -92454,46 +92454,46 @@
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1805" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C1805">
-        <v>1.568192342363713</v>
+        <v>1.132969587702234</v>
       </c>
       <c r="D1805" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="E1805">
-        <v>1.524738814821843</v>
+        <v>1.506278882193858</v>
       </c>
       <c r="F1805">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1805">
-        <v>0.01129180765763629</v>
+        <v>0.01134703041229777</v>
       </c>
       <c r="H1805">
-        <v>0.01071526118517816</v>
+        <v>0.01161372111780614</v>
       </c>
       <c r="I1805">
-        <v>0.04345352754187015</v>
+        <v>0.3733092944916248</v>
       </c>
       <c r="J1805">
         <v>1.066185889832519</v>
       </c>
       <c r="K1805">
-        <v>4.56</v>
+        <v>4.79</v>
       </c>
       <c r="L1805">
-        <v>6.43</v>
+        <v>6.24</v>
       </c>
       <c r="M1805">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="N1805">
-        <v>6.12</v>
+        <v>6.56</v>
       </c>
       <c r="O1805">
         <v>1</v>
@@ -92504,46 +92504,46 @@
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1806" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C1806">
-        <v>1.582163495753663</v>
+        <v>1.093631446600559</v>
       </c>
       <c r="D1806" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="E1806">
-        <v>1.524738814821843</v>
+        <v>1.506278882193858</v>
       </c>
       <c r="F1806">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1806">
-        <v>0.01117783650424634</v>
+        <v>0.01128636855339944</v>
       </c>
       <c r="H1806">
-        <v>0.01071526118517816</v>
+        <v>0.01161372111780614</v>
       </c>
       <c r="I1806">
-        <v>0.0574246809318204</v>
+        <v>0.4126474355932999</v>
       </c>
       <c r="J1806">
         <v>1.066185889832519</v>
       </c>
       <c r="K1806">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="L1806">
-        <v>6.38</v>
+        <v>6.19</v>
       </c>
       <c r="M1806">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="N1806">
-        <v>6.12</v>
+        <v>6.56</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92554,46 +92554,46 @@
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1807" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1807">
-        <v>1.677674716515631</v>
+        <v>1.568192342363713</v>
       </c>
       <c r="D1807" t="s">
         <v>512</v>
       </c>
       <c r="E1807">
-        <v>1.524738814821843</v>
+        <v>1.583415097025192</v>
       </c>
       <c r="F1807">
         <v>-1</v>
       </c>
       <c r="G1807">
-        <v>0.01206232528348437</v>
+        <v>0.01129180765763629</v>
       </c>
       <c r="H1807">
-        <v>0.01071526118517816</v>
+        <v>0.01081658490297481</v>
       </c>
       <c r="I1807">
-        <v>0.1529359016937883</v>
+        <v>-0.01522275466147871</v>
       </c>
       <c r="J1807">
         <v>1.066185889832519</v>
       </c>
       <c r="K1807">
-        <v>4.87</v>
+        <v>4.56</v>
       </c>
       <c r="L1807">
-        <v>6.87</v>
+        <v>6.43</v>
       </c>
       <c r="M1807">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1807">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1807">
         <v>1</v>
@@ -92604,46 +92604,46 @@
     </row>
     <row r="1808" spans="1:16">
       <c r="A1808" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1808" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C1808">
-        <v>1.69760259999051</v>
+        <v>1.582163495753663</v>
       </c>
       <c r="D1808" t="s">
         <v>512</v>
       </c>
       <c r="E1808">
-        <v>1.524738814821843</v>
+        <v>1.583415097025192</v>
       </c>
       <c r="F1808">
         <v>-1</v>
       </c>
       <c r="G1808">
-        <v>0.01176239740000949</v>
+        <v>0.01117783650424634</v>
       </c>
       <c r="H1808">
-        <v>0.01071526118517816</v>
+        <v>0.01081658490297481</v>
       </c>
       <c r="I1808">
-        <v>0.1728637851686674</v>
+        <v>-0.001251601271528457</v>
       </c>
       <c r="J1808">
         <v>1.066185889832519</v>
       </c>
       <c r="K1808">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="L1808">
-        <v>6.73</v>
+        <v>6.38</v>
       </c>
       <c r="M1808">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1808">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1808">
         <v>1</v>
@@ -92654,113 +92654,113 @@
     </row>
     <row r="1809" spans="1:16">
       <c r="A1809" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1809" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C1809">
-        <v>0.9527648456254667</v>
+        <v>1.677674716515631</v>
       </c>
       <c r="D1809" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1809">
-        <v>1.352764845625466</v>
+        <v>1.583415097025192</v>
       </c>
       <c r="F1809">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1809">
-        <v>0.01136723515437453</v>
+        <v>0.01206232528348437</v>
       </c>
       <c r="H1809">
-        <v>0.01176723515437453</v>
+        <v>0.01081658490297481</v>
       </c>
       <c r="I1809">
-        <v>0.3999999999999995</v>
+        <v>0.09425961949043948</v>
       </c>
       <c r="J1809">
-        <v>1.098572817378594</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1809">
-        <v>4.74</v>
+        <v>4.87</v>
       </c>
       <c r="L1809">
-        <v>6.16</v>
+        <v>6.87</v>
       </c>
       <c r="M1809">
-        <v>4.74</v>
+        <v>4.33</v>
       </c>
       <c r="N1809">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="O1809">
         <v>1</v>
       </c>
       <c r="P1809" t="s">
-        <v>351</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1810" spans="1:16">
       <c r="A1810" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B1810" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C1810">
-        <v>0.965151157098262</v>
+        <v>1.69760259999051</v>
       </c>
       <c r="D1810" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1810">
-        <v>1.352764845625466</v>
+        <v>1.583415097025192</v>
       </c>
       <c r="F1810">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1810">
-        <v>0.01043484884290174</v>
+        <v>0.01176239740000949</v>
       </c>
       <c r="H1810">
-        <v>0.01176723515437453</v>
+        <v>0.01081658490297481</v>
       </c>
       <c r="I1810">
-        <v>0.3876136885272041</v>
+        <v>0.1141875029653185</v>
       </c>
       <c r="J1810">
-        <v>1.098572817378594</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1810">
-        <v>4.31</v>
+        <v>4.72</v>
       </c>
       <c r="L1810">
-        <v>5.7</v>
+        <v>6.73</v>
       </c>
       <c r="M1810">
-        <v>4.74</v>
+        <v>4.33</v>
       </c>
       <c r="N1810">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="O1810">
         <v>1</v>
       </c>
       <c r="P1810" t="s">
-        <v>351</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1811" spans="1:16">
       <c r="A1811" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1811" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C1811">
-        <v>0.977836204756537</v>
+        <v>0.9527648456254667</v>
       </c>
       <c r="D1811" t="s">
         <v>348</v>
@@ -92772,22 +92772,22 @@
         <v>1</v>
       </c>
       <c r="G1811">
-        <v>0.01150216379524346</v>
+        <v>0.01136723515437453</v>
       </c>
       <c r="H1811">
         <v>0.01176723515437453</v>
       </c>
       <c r="I1811">
-        <v>0.3749286408689292</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1811">
         <v>1.098572817378594</v>
       </c>
       <c r="K1811">
-        <v>4.79</v>
+        <v>4.74</v>
       </c>
       <c r="L1811">
-        <v>6.24</v>
+        <v>6.16</v>
       </c>
       <c r="M1811">
         <v>4.74</v>
@@ -92799,18 +92799,18 @@
         <v>1</v>
       </c>
       <c r="P1811" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1812" spans="1:16">
       <c r="A1812" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1812" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C1812">
-        <v>0.9388219329303231</v>
+        <v>1.010365234491473</v>
       </c>
       <c r="D1812" t="s">
         <v>348</v>
@@ -92822,22 +92822,22 @@
         <v>1</v>
       </c>
       <c r="G1812">
-        <v>0.01144117806706968</v>
+        <v>0.01080963476550853</v>
       </c>
       <c r="H1812">
         <v>0.01176723515437453</v>
       </c>
       <c r="I1812">
-        <v>0.4139429126951431</v>
+        <v>0.3423996111339935</v>
       </c>
       <c r="J1812">
         <v>1.098572817378594</v>
       </c>
       <c r="K1812">
-        <v>4.78</v>
+        <v>4.46</v>
       </c>
       <c r="L1812">
-        <v>6.19</v>
+        <v>5.91</v>
       </c>
       <c r="M1812">
         <v>4.74</v>
@@ -92849,368 +92849,368 @@
         <v>1</v>
       </c>
       <c r="P1812" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1813" spans="1:16">
       <c r="A1813" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1813" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C1813">
-        <v>1.420507952753614</v>
+        <v>0.965151157098262</v>
       </c>
       <c r="D1813" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="E1813">
-        <v>1.385151157098262</v>
+        <v>1.352764845625466</v>
       </c>
       <c r="F1813">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1813">
-        <v>0.01143949204724639</v>
+        <v>0.01043484884290174</v>
       </c>
       <c r="H1813">
-        <v>0.01085484884290174</v>
+        <v>0.01176723515437453</v>
       </c>
       <c r="I1813">
-        <v>0.03535679565535155</v>
+        <v>0.3876136885272041</v>
       </c>
       <c r="J1813">
         <v>1.098572817378594</v>
       </c>
       <c r="K1813">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="L1813">
-        <v>6.43</v>
+        <v>5.7</v>
       </c>
       <c r="M1813">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="N1813">
-        <v>6.12</v>
+        <v>6.56</v>
       </c>
       <c r="O1813">
         <v>1</v>
       </c>
       <c r="P1813" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1814" spans="1:16">
       <c r="A1814" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1814" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C1814">
-        <v>1.436422321796329</v>
+        <v>0.977836204756537</v>
       </c>
       <c r="D1814" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="E1814">
-        <v>1.385151157098262</v>
+        <v>1.352764845625466</v>
       </c>
       <c r="F1814">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1814">
-        <v>0.01132357767820367</v>
+        <v>0.01150216379524346</v>
       </c>
       <c r="H1814">
-        <v>0.01085484884290174</v>
+        <v>0.01176723515437453</v>
       </c>
       <c r="I1814">
-        <v>0.05127116469806658</v>
+        <v>0.3749286408689292</v>
       </c>
       <c r="J1814">
         <v>1.098572817378594</v>
       </c>
       <c r="K1814">
-        <v>4.5</v>
+        <v>4.79</v>
       </c>
       <c r="L1814">
-        <v>6.38</v>
+        <v>6.24</v>
       </c>
       <c r="M1814">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="N1814">
-        <v>6.12</v>
+        <v>6.56</v>
       </c>
       <c r="O1814">
         <v>1</v>
       </c>
       <c r="P1814" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1815" spans="1:16">
       <c r="A1815" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1815" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C1815">
-        <v>1.519950379366249</v>
+        <v>0.9388219329303231</v>
       </c>
       <c r="D1815" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="E1815">
-        <v>1.385151157098262</v>
+        <v>1.352764845625466</v>
       </c>
       <c r="F1815">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1815">
-        <v>0.01222004962063375</v>
+        <v>0.01144117806706968</v>
       </c>
       <c r="H1815">
-        <v>0.01085484884290174</v>
+        <v>0.01176723515437453</v>
       </c>
       <c r="I1815">
-        <v>0.1347992222679872</v>
+        <v>0.4139429126951431</v>
       </c>
       <c r="J1815">
         <v>1.098572817378594</v>
       </c>
       <c r="K1815">
-        <v>4.87</v>
+        <v>4.78</v>
       </c>
       <c r="L1815">
-        <v>6.87</v>
+        <v>6.19</v>
       </c>
       <c r="M1815">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="N1815">
-        <v>6.12</v>
+        <v>6.56</v>
       </c>
       <c r="O1815">
         <v>1</v>
       </c>
       <c r="P1815" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1816" spans="1:16">
       <c r="A1816" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1816" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C1816">
-        <v>1.544736301973039</v>
+        <v>1.420507952753614</v>
       </c>
       <c r="D1816" t="s">
         <v>512</v>
       </c>
       <c r="E1816">
-        <v>1.385151157098262</v>
+        <v>1.44317970075069</v>
       </c>
       <c r="F1816">
         <v>-1</v>
       </c>
       <c r="G1816">
-        <v>0.01191526369802696</v>
+        <v>0.01143949204724639</v>
       </c>
       <c r="H1816">
-        <v>0.01085484884290174</v>
+        <v>0.01095682029924931</v>
       </c>
       <c r="I1816">
-        <v>0.1595851448747769</v>
+        <v>-0.02267174799707661</v>
       </c>
       <c r="J1816">
         <v>1.098572817378594</v>
       </c>
       <c r="K1816">
-        <v>4.72</v>
+        <v>4.56</v>
       </c>
       <c r="L1816">
-        <v>6.73</v>
+        <v>6.43</v>
       </c>
       <c r="M1816">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="N1816">
-        <v>6.12</v>
+        <v>6.2</v>
       </c>
       <c r="O1816">
         <v>1</v>
       </c>
       <c r="P1816" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1817" spans="1:16">
       <c r="A1817" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1817" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C1817">
-        <v>0.8652138986958411</v>
+        <v>1.436422321796329</v>
       </c>
       <c r="D1817" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1817">
-        <v>1.265213898695841</v>
+        <v>1.44317970075069</v>
       </c>
       <c r="F1817">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1817">
-        <v>0.01145478610130416</v>
+        <v>0.01132357767820367</v>
       </c>
       <c r="H1817">
-        <v>0.01185478610130416</v>
+        <v>0.01095682029924931</v>
       </c>
       <c r="I1817">
-        <v>0.3999999999999995</v>
+        <v>-0.00675737895436157</v>
       </c>
       <c r="J1817">
-        <v>1.117043481287797</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1817">
-        <v>4.74</v>
+        <v>4.5</v>
       </c>
       <c r="L1817">
-        <v>6.16</v>
+        <v>6.38</v>
       </c>
       <c r="M1817">
-        <v>4.74</v>
+        <v>4.33</v>
       </c>
       <c r="N1817">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="O1817">
         <v>1</v>
       </c>
       <c r="P1817" t="s">
-        <v>626</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1818" spans="1:16">
       <c r="A1818" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B1818" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C1818">
-        <v>0.8855425956495946</v>
+        <v>1.519950379366249</v>
       </c>
       <c r="D1818" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1818">
-        <v>1.265213898695841</v>
+        <v>1.44317970075069</v>
       </c>
       <c r="F1818">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1818">
-        <v>0.01051445740435041</v>
+        <v>0.01222004962063375</v>
       </c>
       <c r="H1818">
-        <v>0.01185478610130416</v>
+        <v>0.01095682029924931</v>
       </c>
       <c r="I1818">
-        <v>0.379671303046246</v>
+        <v>0.07677067861555908</v>
       </c>
       <c r="J1818">
-        <v>1.117043481287797</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1818">
-        <v>4.31</v>
+        <v>4.87</v>
       </c>
       <c r="L1818">
-        <v>5.7</v>
+        <v>6.87</v>
       </c>
       <c r="M1818">
-        <v>4.74</v>
+        <v>4.33</v>
       </c>
       <c r="N1818">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="O1818">
         <v>1</v>
       </c>
       <c r="P1818" t="s">
-        <v>626</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1819" spans="1:16">
       <c r="A1819" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B1819" t="s">
         <v>359</v>
       </c>
       <c r="C1819">
-        <v>0.8893617246314518</v>
+        <v>1.544736301973039</v>
       </c>
       <c r="D1819" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1819">
-        <v>1.265213898695841</v>
+        <v>1.44317970075069</v>
       </c>
       <c r="F1819">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1819">
-        <v>0.01159063827536855</v>
+        <v>0.01191526369802696</v>
       </c>
       <c r="H1819">
-        <v>0.01185478610130416</v>
+        <v>0.01095682029924931</v>
       </c>
       <c r="I1819">
-        <v>0.3758521740643888</v>
+        <v>0.1015566012223488</v>
       </c>
       <c r="J1819">
-        <v>1.117043481287797</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1819">
-        <v>4.79</v>
+        <v>4.72</v>
       </c>
       <c r="L1819">
-        <v>6.24</v>
+        <v>6.73</v>
       </c>
       <c r="M1819">
-        <v>4.74</v>
+        <v>4.33</v>
       </c>
       <c r="N1819">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="O1819">
         <v>1</v>
       </c>
       <c r="P1819" t="s">
-        <v>626</v>
+        <v>350</v>
       </c>
     </row>
     <row r="1820" spans="1:16">
       <c r="A1820" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1820" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C1820">
-        <v>0.85053215944433</v>
+        <v>0.8652138986958411</v>
       </c>
       <c r="D1820" t="s">
         <v>348</v>
@@ -93222,22 +93222,22 @@
         <v>1</v>
       </c>
       <c r="G1820">
-        <v>0.01152946784055567</v>
+        <v>0.01145478610130416</v>
       </c>
       <c r="H1820">
         <v>0.01185478610130416</v>
       </c>
       <c r="I1820">
-        <v>0.4146817392515105</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1820">
         <v>1.117043481287797</v>
       </c>
       <c r="K1820">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="L1820">
-        <v>6.19</v>
+        <v>6.16</v>
       </c>
       <c r="M1820">
         <v>4.74</v>
@@ -93254,46 +93254,46 @@
     </row>
     <row r="1821" spans="1:16">
       <c r="A1821" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1821" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C1821">
-        <v>1.336281725327645</v>
+        <v>0.8855425956495946</v>
       </c>
       <c r="D1821" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="E1821">
-        <v>1.305542595649595</v>
+        <v>1.265213898695841</v>
       </c>
       <c r="F1821">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1821">
-        <v>0.01152371827467235</v>
+        <v>0.01051445740435041</v>
       </c>
       <c r="H1821">
-        <v>0.01093445740435041</v>
+        <v>0.01185478610130416</v>
       </c>
       <c r="I1821">
-        <v>0.03073912967805015</v>
+        <v>0.379671303046246</v>
       </c>
       <c r="J1821">
         <v>1.117043481287797</v>
       </c>
       <c r="K1821">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="L1821">
-        <v>6.43</v>
+        <v>5.7</v>
       </c>
       <c r="M1821">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="N1821">
-        <v>6.12</v>
+        <v>6.56</v>
       </c>
       <c r="O1821">
         <v>1</v>
@@ -93304,46 +93304,46 @@
     </row>
     <row r="1822" spans="1:16">
       <c r="A1822" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1822" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C1822">
-        <v>1.353304334204912</v>
+        <v>0.8893617246314518</v>
       </c>
       <c r="D1822" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="E1822">
-        <v>1.305542595649595</v>
+        <v>1.265213898695841</v>
       </c>
       <c r="F1822">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1822">
-        <v>0.01140669566579509</v>
+        <v>0.01159063827536855</v>
       </c>
       <c r="H1822">
-        <v>0.01093445740435041</v>
+        <v>0.01185478610130416</v>
       </c>
       <c r="I1822">
-        <v>0.04776173855531773</v>
+        <v>0.3758521740643888</v>
       </c>
       <c r="J1822">
         <v>1.117043481287797</v>
       </c>
       <c r="K1822">
-        <v>4.5</v>
+        <v>4.79</v>
       </c>
       <c r="L1822">
-        <v>6.38</v>
+        <v>6.24</v>
       </c>
       <c r="M1822">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="N1822">
-        <v>6.12</v>
+        <v>6.56</v>
       </c>
       <c r="O1822">
         <v>1</v>
@@ -93354,46 +93354,46 @@
     </row>
     <row r="1823" spans="1:16">
       <c r="A1823" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1823" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C1823">
-        <v>1.429998246128427</v>
+        <v>0.85053215944433</v>
       </c>
       <c r="D1823" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="E1823">
-        <v>1.305542595649595</v>
+        <v>1.265213898695841</v>
       </c>
       <c r="F1823">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1823">
-        <v>0.01231000175387157</v>
+        <v>0.01152946784055567</v>
       </c>
       <c r="H1823">
-        <v>0.01093445740435041</v>
+        <v>0.01185478610130416</v>
       </c>
       <c r="I1823">
-        <v>0.1244556504788328</v>
+        <v>0.4146817392515105</v>
       </c>
       <c r="J1823">
         <v>1.117043481287797</v>
       </c>
       <c r="K1823">
-        <v>4.87</v>
+        <v>4.78</v>
       </c>
       <c r="L1823">
-        <v>6.87</v>
+        <v>6.19</v>
       </c>
       <c r="M1823">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="N1823">
-        <v>6.12</v>
+        <v>6.56</v>
       </c>
       <c r="O1823">
         <v>1</v>
@@ -93404,51 +93404,201 @@
     </row>
     <row r="1824" spans="1:16">
       <c r="A1824" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1824" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C1824">
-        <v>1.457554768321598</v>
+        <v>1.336281725327645</v>
       </c>
       <c r="D1824" t="s">
         <v>512</v>
       </c>
       <c r="E1824">
-        <v>1.305542595649595</v>
+        <v>1.363201726023838</v>
       </c>
       <c r="F1824">
         <v>-1</v>
       </c>
       <c r="G1824">
-        <v>0.0120024452316784</v>
+        <v>0.01152371827467235</v>
       </c>
       <c r="H1824">
-        <v>0.01093445740435041</v>
+        <v>0.01103679827397616</v>
       </c>
       <c r="I1824">
-        <v>0.1520121726720038</v>
+        <v>-0.02692000069619382</v>
       </c>
       <c r="J1824">
         <v>1.117043481287797</v>
       </c>
       <c r="K1824">
+        <v>4.56</v>
+      </c>
+      <c r="L1824">
+        <v>6.43</v>
+      </c>
+      <c r="M1824">
+        <v>4.33</v>
+      </c>
+      <c r="N1824">
+        <v>6.2</v>
+      </c>
+      <c r="O1824">
+        <v>1</v>
+      </c>
+      <c r="P1824" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:16">
+      <c r="A1825" s="1">
+        <v>5</v>
+      </c>
+      <c r="B1825" t="s">
+        <v>357</v>
+      </c>
+      <c r="C1825">
+        <v>1.353304334204912</v>
+      </c>
+      <c r="D1825" t="s">
+        <v>512</v>
+      </c>
+      <c r="E1825">
+        <v>1.363201726023838</v>
+      </c>
+      <c r="F1825">
+        <v>-1</v>
+      </c>
+      <c r="G1825">
+        <v>0.01140669566579509</v>
+      </c>
+      <c r="H1825">
+        <v>0.01103679827397616</v>
+      </c>
+      <c r="I1825">
+        <v>-0.009897391818926238</v>
+      </c>
+      <c r="J1825">
+        <v>1.117043481287797</v>
+      </c>
+      <c r="K1825">
+        <v>4.5</v>
+      </c>
+      <c r="L1825">
+        <v>6.38</v>
+      </c>
+      <c r="M1825">
+        <v>4.33</v>
+      </c>
+      <c r="N1825">
+        <v>6.2</v>
+      </c>
+      <c r="O1825">
+        <v>1</v>
+      </c>
+      <c r="P1825" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:16">
+      <c r="A1826" s="1">
+        <v>6</v>
+      </c>
+      <c r="B1826" t="s">
+        <v>358</v>
+      </c>
+      <c r="C1826">
+        <v>1.429998246128427</v>
+      </c>
+      <c r="D1826" t="s">
+        <v>512</v>
+      </c>
+      <c r="E1826">
+        <v>1.363201726023838</v>
+      </c>
+      <c r="F1826">
+        <v>-1</v>
+      </c>
+      <c r="G1826">
+        <v>0.01231000175387157</v>
+      </c>
+      <c r="H1826">
+        <v>0.01103679827397616</v>
+      </c>
+      <c r="I1826">
+        <v>0.06679652010458881</v>
+      </c>
+      <c r="J1826">
+        <v>1.117043481287797</v>
+      </c>
+      <c r="K1826">
+        <v>4.87</v>
+      </c>
+      <c r="L1826">
+        <v>6.87</v>
+      </c>
+      <c r="M1826">
+        <v>4.33</v>
+      </c>
+      <c r="N1826">
+        <v>6.2</v>
+      </c>
+      <c r="O1826">
+        <v>1</v>
+      </c>
+      <c r="P1826" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:16">
+      <c r="A1827" s="1">
+        <v>7</v>
+      </c>
+      <c r="B1827" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1827">
+        <v>1.457554768321598</v>
+      </c>
+      <c r="D1827" t="s">
+        <v>512</v>
+      </c>
+      <c r="E1827">
+        <v>1.363201726023838</v>
+      </c>
+      <c r="F1827">
+        <v>-1</v>
+      </c>
+      <c r="G1827">
+        <v>0.0120024452316784</v>
+      </c>
+      <c r="H1827">
+        <v>0.01103679827397616</v>
+      </c>
+      <c r="I1827">
+        <v>0.09435304229775987</v>
+      </c>
+      <c r="J1827">
+        <v>1.117043481287797</v>
+      </c>
+      <c r="K1827">
         <v>4.72</v>
       </c>
-      <c r="L1824">
+      <c r="L1827">
         <v>6.73</v>
       </c>
-      <c r="M1824">
-        <v>4.31</v>
-      </c>
-      <c r="N1824">
-        <v>6.12</v>
-      </c>
-      <c r="O1824">
-        <v>1</v>
-      </c>
-      <c r="P1824" t="s">
+      <c r="M1827">
+        <v>4.33</v>
+      </c>
+      <c r="N1827">
+        <v>6.2</v>
+      </c>
+      <c r="O1827">
+        <v>1</v>
+      </c>
+      <c r="P1827" t="s">
         <v>626</v>
       </c>
     </row>

--- a/s60_signal/position-01055-600029.xlsx
+++ b/s60_signal/position-01055-600029.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5493" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5487" uniqueCount="627">
   <si>
     <t>trade_time</t>
   </si>
@@ -1051,9 +1051,6 @@
     <t>2021-05-28</t>
   </si>
   <si>
-    <t>2021-06-01</t>
-  </si>
-  <si>
     <t>2021-06-07</t>
   </si>
   <si>
@@ -1084,9 +1081,6 @@
     <t>2021-10-22</t>
   </si>
   <si>
-    <t>2021-11-02</t>
-  </si>
-  <si>
     <t>2021-11-04</t>
   </si>
   <si>
@@ -1094,6 +1088,12 @@
   </si>
   <si>
     <t>2021-11-19</t>
+  </si>
+  <si>
+    <t>2021-12-01</t>
+  </si>
+  <si>
+    <t>2021-10-19</t>
   </si>
   <si>
     <t>2016-05-11</t>
@@ -1552,7 +1552,7 @@
     <t>2021-08-11</t>
   </si>
   <si>
-    <t>2021-12-01</t>
+    <t>2021-12-02</t>
   </si>
   <si>
     <t>2016-03-09</t>
@@ -2252,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1827"/>
+  <dimension ref="A1:P1825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -91160,7 +91160,7 @@
         <v>345</v>
       </c>
       <c r="C1779">
-        <v>1.233610151707254</v>
+        <v>1.25132667337035</v>
       </c>
       <c r="D1779" t="s">
         <v>341</v>
@@ -91172,22 +91172,22 @@
         <v>1</v>
       </c>
       <c r="G1779">
-        <v>0.01152638984829274</v>
+        <v>0.01142867332662965</v>
       </c>
       <c r="H1779">
         <v>0.0106018886897215</v>
       </c>
       <c r="I1779">
-        <v>0.3645011585712412</v>
+        <v>0.3467846369081453</v>
       </c>
       <c r="J1779">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1779">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="L1779">
-        <v>6.38</v>
+        <v>6.34</v>
       </c>
       <c r="M1779">
         <v>4.68</v>
@@ -91210,7 +91210,7 @@
         <v>346</v>
       </c>
       <c r="C1780">
-        <v>1.25132667337035</v>
+        <v>1.302297687229486</v>
       </c>
       <c r="D1780" t="s">
         <v>341</v>
@@ -91222,22 +91222,22 @@
         <v>1</v>
       </c>
       <c r="G1780">
-        <v>0.01142867332662965</v>
+        <v>0.01051770231277051</v>
       </c>
       <c r="H1780">
         <v>0.0106018886897215</v>
       </c>
       <c r="I1780">
-        <v>0.3467846369081453</v>
+        <v>0.2958136230490096</v>
       </c>
       <c r="J1780">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1780">
-        <v>5.29</v>
+        <v>4.79</v>
       </c>
       <c r="L1780">
-        <v>6.34</v>
+        <v>5.91</v>
       </c>
       <c r="M1780">
         <v>4.68</v>
@@ -91260,40 +91260,40 @@
         <v>347</v>
       </c>
       <c r="C1781">
-        <v>1.302297687229486</v>
+        <v>2.000394788615399</v>
       </c>
       <c r="D1781" t="s">
-        <v>341</v>
+        <v>512</v>
       </c>
       <c r="E1781">
-        <v>1.598111310278496</v>
+        <v>2.082507541642987</v>
       </c>
       <c r="F1781">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1781">
-        <v>0.01051770231277051</v>
+        <v>0.0111196052113846</v>
       </c>
       <c r="H1781">
-        <v>0.0106018886897215</v>
+        <v>0.01029749245835701</v>
       </c>
       <c r="I1781">
-        <v>0.2958136230490096</v>
+        <v>-0.08211275302758825</v>
       </c>
       <c r="J1781">
         <v>0.9619420277182702</v>
       </c>
       <c r="K1781">
-        <v>4.79</v>
+        <v>4.74</v>
       </c>
       <c r="L1781">
-        <v>5.91</v>
+        <v>6.56</v>
       </c>
       <c r="M1781">
-        <v>4.68</v>
+        <v>4.27</v>
       </c>
       <c r="N1781">
-        <v>6.1</v>
+        <v>6.19</v>
       </c>
       <c r="O1781">
         <v>1</v>
@@ -91304,63 +91304,63 @@
     </row>
     <row r="1782" spans="1:16">
       <c r="A1782" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1782" t="s">
         <v>348</v>
       </c>
       <c r="C1782">
-        <v>2.000394788615399</v>
+        <v>1.030865752413226</v>
       </c>
       <c r="D1782" t="s">
-        <v>512</v>
+        <v>341</v>
       </c>
       <c r="E1782">
-        <v>2.03479101997989</v>
+        <v>1.329119523361904</v>
       </c>
       <c r="F1782">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1782">
-        <v>0.0111196052113846</v>
+        <v>0.01248913424758677</v>
       </c>
       <c r="H1782">
-        <v>0.01036520898002011</v>
+        <v>0.0108708804766381</v>
       </c>
       <c r="I1782">
-        <v>-0.03439623136449121</v>
+        <v>0.2982537709486781</v>
       </c>
       <c r="J1782">
-        <v>0.9619420277182702</v>
+        <v>1.01941890526455</v>
       </c>
       <c r="K1782">
-        <v>4.74</v>
+        <v>5.62</v>
       </c>
       <c r="L1782">
-        <v>6.56</v>
+        <v>6.76</v>
       </c>
       <c r="M1782">
-        <v>4.33</v>
+        <v>4.68</v>
       </c>
       <c r="N1782">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="O1782">
         <v>1</v>
       </c>
       <c r="P1782" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="1783" spans="1:16">
       <c r="A1783" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1783" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C1783">
-        <v>1.030865752413226</v>
+        <v>1.026983443782804</v>
       </c>
       <c r="D1783" t="s">
         <v>341</v>
@@ -91372,22 +91372,22 @@
         <v>1</v>
       </c>
       <c r="G1783">
-        <v>0.01248913424758677</v>
+        <v>0.0107930165562172</v>
       </c>
       <c r="H1783">
         <v>0.0108708804766381</v>
       </c>
       <c r="I1783">
-        <v>0.2982537709486781</v>
+        <v>0.3021360795791006</v>
       </c>
       <c r="J1783">
         <v>1.01941890526455</v>
       </c>
       <c r="K1783">
-        <v>5.62</v>
+        <v>4.79</v>
       </c>
       <c r="L1783">
-        <v>6.76</v>
+        <v>5.91</v>
       </c>
       <c r="M1783">
         <v>4.68</v>
@@ -91404,46 +91404,46 @@
     </row>
     <row r="1784" spans="1:16">
       <c r="A1784" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1784" t="s">
         <v>347</v>
       </c>
       <c r="C1784">
-        <v>1.026983443782804</v>
+        <v>1.72795438904603</v>
       </c>
       <c r="D1784" t="s">
-        <v>341</v>
+        <v>512</v>
       </c>
       <c r="E1784">
-        <v>1.329119523361904</v>
+        <v>1.83708127452037</v>
       </c>
       <c r="F1784">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1784">
-        <v>0.0107930165562172</v>
+        <v>0.01139204561095397</v>
       </c>
       <c r="H1784">
-        <v>0.0108708804766381</v>
+        <v>0.01054291872547963</v>
       </c>
       <c r="I1784">
-        <v>0.3021360795791006</v>
+        <v>-0.1091268854743399</v>
       </c>
       <c r="J1784">
         <v>1.01941890526455</v>
       </c>
       <c r="K1784">
-        <v>4.79</v>
+        <v>4.74</v>
       </c>
       <c r="L1784">
-        <v>5.91</v>
+        <v>6.56</v>
       </c>
       <c r="M1784">
-        <v>4.68</v>
+        <v>4.27</v>
       </c>
       <c r="N1784">
-        <v>6.1</v>
+        <v>6.19</v>
       </c>
       <c r="O1784">
         <v>1</v>
@@ -91454,63 +91454,63 @@
     </row>
     <row r="1785" spans="1:16">
       <c r="A1785" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1785" t="s">
         <v>348</v>
       </c>
       <c r="C1785">
-        <v>1.72795438904603</v>
+        <v>0.7149171399855092</v>
       </c>
       <c r="D1785" t="s">
-        <v>512</v>
+        <v>341</v>
       </c>
       <c r="E1785">
-        <v>1.785916140204497</v>
+        <v>1.06601640838651</v>
       </c>
       <c r="F1785">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1785">
-        <v>0.01139204561095397</v>
+        <v>0.01280508286001449</v>
       </c>
       <c r="H1785">
-        <v>0.0106140838597955</v>
+        <v>0.01113398359161349</v>
       </c>
       <c r="I1785">
-        <v>-0.05796175115846669</v>
+        <v>0.3510992684010006</v>
       </c>
       <c r="J1785">
-        <v>1.01941890526455</v>
+        <v>1.075637519575532</v>
       </c>
       <c r="K1785">
-        <v>4.74</v>
+        <v>5.62</v>
       </c>
       <c r="L1785">
-        <v>6.56</v>
+        <v>6.76</v>
       </c>
       <c r="M1785">
-        <v>4.33</v>
+        <v>4.68</v>
       </c>
       <c r="N1785">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="O1785">
         <v>1</v>
       </c>
       <c r="P1785" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="1786" spans="1:16">
       <c r="A1786" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1786" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C1786">
-        <v>0.7149171399855092</v>
+        <v>0.7576962812332013</v>
       </c>
       <c r="D1786" t="s">
         <v>341</v>
@@ -91522,22 +91522,22 @@
         <v>1</v>
       </c>
       <c r="G1786">
-        <v>0.01280508286001449</v>
+        <v>0.0110623037187668</v>
       </c>
       <c r="H1786">
         <v>0.01113398359161349</v>
       </c>
       <c r="I1786">
-        <v>0.3510992684010006</v>
+        <v>0.3083201271533085</v>
       </c>
       <c r="J1786">
         <v>1.075637519575532</v>
       </c>
       <c r="K1786">
-        <v>5.62</v>
+        <v>4.79</v>
       </c>
       <c r="L1786">
-        <v>6.76</v>
+        <v>5.91</v>
       </c>
       <c r="M1786">
         <v>4.68</v>
@@ -91554,46 +91554,46 @@
     </row>
     <row r="1787" spans="1:16">
       <c r="A1787" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1787" t="s">
         <v>347</v>
       </c>
       <c r="C1787">
-        <v>0.7576962812332013</v>
+        <v>1.461478157211977</v>
       </c>
       <c r="D1787" t="s">
-        <v>341</v>
+        <v>512</v>
       </c>
       <c r="E1787">
-        <v>1.06601640838651</v>
+        <v>1.597027791412478</v>
       </c>
       <c r="F1787">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1787">
-        <v>0.0110623037187668</v>
+        <v>0.01165852184278802</v>
       </c>
       <c r="H1787">
-        <v>0.01113398359161349</v>
+        <v>0.01078297220858752</v>
       </c>
       <c r="I1787">
-        <v>0.3083201271533085</v>
+        <v>-0.1355496342005011</v>
       </c>
       <c r="J1787">
         <v>1.075637519575532</v>
       </c>
       <c r="K1787">
-        <v>4.79</v>
+        <v>4.74</v>
       </c>
       <c r="L1787">
-        <v>5.91</v>
+        <v>6.56</v>
       </c>
       <c r="M1787">
-        <v>4.68</v>
+        <v>4.27</v>
       </c>
       <c r="N1787">
-        <v>6.1</v>
+        <v>6.19</v>
       </c>
       <c r="O1787">
         <v>1</v>
@@ -91604,166 +91604,166 @@
     </row>
     <row r="1788" spans="1:16">
       <c r="A1788" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1788" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1788">
+        <v>0.6925748758286989</v>
+      </c>
+      <c r="D1788" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1788">
+        <v>1.002390484108207</v>
+      </c>
+      <c r="F1788">
+        <v>1</v>
+      </c>
+      <c r="G1788">
+        <v>0.0111274251241713</v>
+      </c>
+      <c r="H1788">
+        <v>0.01119760951589179</v>
+      </c>
+      <c r="I1788">
+        <v>0.309815608279508</v>
+      </c>
+      <c r="J1788">
+        <v>1.089232802540981</v>
+      </c>
+      <c r="K1788">
+        <v>4.79</v>
+      </c>
+      <c r="L1788">
+        <v>5.91</v>
+      </c>
+      <c r="M1788">
+        <v>4.68</v>
+      </c>
+      <c r="N1788">
+        <v>6.1</v>
+      </c>
+      <c r="O1788">
+        <v>1</v>
+      </c>
+      <c r="P1788" t="s">
         <v>348</v>
-      </c>
-      <c r="C1788">
-        <v>1.461478157211977</v>
-      </c>
-      <c r="D1788" t="s">
-        <v>512</v>
-      </c>
-      <c r="E1788">
-        <v>1.542489540237946</v>
-      </c>
-      <c r="F1788">
-        <v>-1</v>
-      </c>
-      <c r="G1788">
-        <v>0.01165852184278802</v>
-      </c>
-      <c r="H1788">
-        <v>0.01085751045976205</v>
-      </c>
-      <c r="I1788">
-        <v>-0.08101138302596844</v>
-      </c>
-      <c r="J1788">
-        <v>1.075637519575532</v>
-      </c>
-      <c r="K1788">
-        <v>4.74</v>
-      </c>
-      <c r="L1788">
-        <v>6.56</v>
-      </c>
-      <c r="M1788">
-        <v>4.33</v>
-      </c>
-      <c r="N1788">
-        <v>6.2</v>
-      </c>
-      <c r="O1788">
-        <v>1</v>
-      </c>
-      <c r="P1788" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="1789" spans="1:16">
       <c r="A1789" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1789" t="s">
         <v>347</v>
       </c>
       <c r="C1789">
-        <v>0.6925748758286989</v>
+        <v>1.397036515955747</v>
       </c>
       <c r="D1789" t="s">
-        <v>341</v>
+        <v>512</v>
       </c>
       <c r="E1789">
-        <v>1.002390484108207</v>
+        <v>1.53897593315001</v>
       </c>
       <c r="F1789">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1789">
-        <v>0.0111274251241713</v>
+        <v>0.01172296348404425</v>
       </c>
       <c r="H1789">
-        <v>0.01119760951589179</v>
+        <v>0.01084102406684999</v>
       </c>
       <c r="I1789">
-        <v>0.309815608279508</v>
+        <v>-0.141939417194263</v>
       </c>
       <c r="J1789">
         <v>1.089232802540981</v>
       </c>
       <c r="K1789">
-        <v>4.79</v>
+        <v>4.74</v>
       </c>
       <c r="L1789">
-        <v>5.91</v>
+        <v>6.56</v>
       </c>
       <c r="M1789">
-        <v>4.68</v>
+        <v>4.27</v>
       </c>
       <c r="N1789">
-        <v>6.1</v>
+        <v>6.19</v>
       </c>
       <c r="O1789">
         <v>1</v>
       </c>
       <c r="P1789" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1790" spans="1:16">
       <c r="A1790" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1790" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C1790">
-        <v>1.397036515955747</v>
+        <v>1.427808430496056</v>
       </c>
       <c r="D1790" t="s">
-        <v>512</v>
+        <v>347</v>
       </c>
       <c r="E1790">
-        <v>1.483621964997551</v>
+        <v>1.848285828444487</v>
       </c>
       <c r="F1790">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1790">
-        <v>0.01172296348404425</v>
+        <v>0.01069219156950394</v>
       </c>
       <c r="H1790">
-        <v>0.01091637803500245</v>
+        <v>0.01127171417155551</v>
       </c>
       <c r="I1790">
-        <v>-0.08658544904180321</v>
+        <v>0.4204773979484306</v>
       </c>
       <c r="J1790">
-        <v>1.089232802540981</v>
+        <v>0.994032525644623</v>
       </c>
       <c r="K1790">
+        <v>4.66</v>
+      </c>
+      <c r="L1790">
+        <v>6.06</v>
+      </c>
+      <c r="M1790">
         <v>4.74</v>
       </c>
-      <c r="L1790">
+      <c r="N1790">
         <v>6.56</v>
       </c>
-      <c r="M1790">
-        <v>4.33</v>
-      </c>
-      <c r="N1790">
-        <v>6.2</v>
-      </c>
       <c r="O1790">
         <v>1</v>
       </c>
       <c r="P1790" t="s">
-        <v>349</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1791" spans="1:16">
       <c r="A1791" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1791" t="s">
         <v>350</v>
       </c>
       <c r="C1791">
-        <v>1.427808430496056</v>
+        <v>1.448285828444487</v>
       </c>
       <c r="D1791" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1791">
         <v>1.848285828444487</v>
@@ -91772,22 +91772,22 @@
         <v>1</v>
       </c>
       <c r="G1791">
-        <v>0.01069219156950394</v>
+        <v>0.01087171417155551</v>
       </c>
       <c r="H1791">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1791">
-        <v>0.4204773979484306</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1791">
         <v>0.994032525644623</v>
       </c>
       <c r="K1791">
-        <v>4.66</v>
+        <v>4.74</v>
       </c>
       <c r="L1791">
-        <v>6.06</v>
+        <v>6.16</v>
       </c>
       <c r="M1791">
         <v>4.74</v>
@@ -91804,16 +91804,16 @@
     </row>
     <row r="1792" spans="1:16">
       <c r="A1792" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1792" t="s">
         <v>351</v>
       </c>
       <c r="C1792">
-        <v>1.448285828444487</v>
+        <v>1.476614935624982</v>
       </c>
       <c r="D1792" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1792">
         <v>1.848285828444487</v>
@@ -91822,22 +91822,22 @@
         <v>1</v>
       </c>
       <c r="G1792">
-        <v>0.01087171417155551</v>
+        <v>0.01034338506437502</v>
       </c>
       <c r="H1792">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1792">
-        <v>0.3999999999999995</v>
+        <v>0.3716708928195054</v>
       </c>
       <c r="J1792">
         <v>0.994032525644623</v>
       </c>
       <c r="K1792">
-        <v>4.74</v>
+        <v>4.46</v>
       </c>
       <c r="L1792">
-        <v>6.16</v>
+        <v>5.91</v>
       </c>
       <c r="M1792">
         <v>4.74</v>
@@ -91854,16 +91854,16 @@
     </row>
     <row r="1793" spans="1:16">
       <c r="A1793" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1793" t="s">
         <v>352</v>
       </c>
       <c r="C1793">
-        <v>1.476614935624982</v>
+        <v>1.415719814471675</v>
       </c>
       <c r="D1793" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1793">
         <v>1.848285828444487</v>
@@ -91872,22 +91872,22 @@
         <v>1</v>
       </c>
       <c r="G1793">
-        <v>0.01034338506437502</v>
+        <v>0.009984280185528325</v>
       </c>
       <c r="H1793">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1793">
-        <v>0.3716708928195054</v>
+        <v>0.4325660139728118</v>
       </c>
       <c r="J1793">
         <v>0.994032525644623</v>
       </c>
       <c r="K1793">
-        <v>4.46</v>
+        <v>4.31</v>
       </c>
       <c r="L1793">
-        <v>5.91</v>
+        <v>5.7</v>
       </c>
       <c r="M1793">
         <v>4.74</v>
@@ -91904,16 +91904,16 @@
     </row>
     <row r="1794" spans="1:16">
       <c r="A1794" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1794" t="s">
         <v>353</v>
       </c>
       <c r="C1794">
-        <v>1.415719814471675</v>
+        <v>1.478584202162256</v>
       </c>
       <c r="D1794" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1794">
         <v>1.848285828444487</v>
@@ -91922,22 +91922,22 @@
         <v>1</v>
       </c>
       <c r="G1794">
-        <v>0.009984280185528325</v>
+        <v>0.01100141579783774</v>
       </c>
       <c r="H1794">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1794">
-        <v>0.4325660139728118</v>
+        <v>0.3697016262822306</v>
       </c>
       <c r="J1794">
         <v>0.994032525644623</v>
       </c>
       <c r="K1794">
-        <v>4.31</v>
+        <v>4.79</v>
       </c>
       <c r="L1794">
-        <v>5.7</v>
+        <v>6.24</v>
       </c>
       <c r="M1794">
         <v>4.74</v>
@@ -91954,16 +91954,16 @@
     </row>
     <row r="1795" spans="1:16">
       <c r="A1795" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1795" t="s">
         <v>354</v>
       </c>
       <c r="C1795">
-        <v>1.478584202162256</v>
+        <v>1.438524527418703</v>
       </c>
       <c r="D1795" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1795">
         <v>1.848285828444487</v>
@@ -91972,22 +91972,22 @@
         <v>1</v>
       </c>
       <c r="G1795">
-        <v>0.01100141579783774</v>
+        <v>0.0109414754725813</v>
       </c>
       <c r="H1795">
         <v>0.01127171417155551</v>
       </c>
       <c r="I1795">
-        <v>0.3697016262822306</v>
+        <v>0.4097613010257843</v>
       </c>
       <c r="J1795">
         <v>0.994032525644623</v>
       </c>
       <c r="K1795">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="L1795">
-        <v>6.24</v>
+        <v>6.19</v>
       </c>
       <c r="M1795">
         <v>4.74</v>
@@ -92004,46 +92004,46 @@
     </row>
     <row r="1796" spans="1:16">
       <c r="A1796" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1796" t="s">
         <v>355</v>
       </c>
       <c r="C1796">
-        <v>1.438524527418703</v>
+        <v>1.906853634599196</v>
       </c>
       <c r="D1796" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1796">
-        <v>1.848285828444487</v>
+        <v>1.945481115497461</v>
       </c>
       <c r="F1796">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1796">
-        <v>0.0109414754725813</v>
+        <v>0.0108531463654008</v>
       </c>
       <c r="H1796">
-        <v>0.01127171417155551</v>
+        <v>0.01043451888450254</v>
       </c>
       <c r="I1796">
-        <v>0.4097613010257843</v>
+        <v>-0.03862748089826429</v>
       </c>
       <c r="J1796">
         <v>0.994032525644623</v>
       </c>
       <c r="K1796">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="L1796">
+        <v>6.38</v>
+      </c>
+      <c r="M1796">
+        <v>4.27</v>
+      </c>
+      <c r="N1796">
         <v>6.19</v>
-      </c>
-      <c r="M1796">
-        <v>4.74</v>
-      </c>
-      <c r="N1796">
-        <v>6.56</v>
       </c>
       <c r="O1796">
         <v>1</v>
@@ -92054,46 +92054,46 @@
     </row>
     <row r="1797" spans="1:16">
       <c r="A1797" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1797" t="s">
         <v>356</v>
       </c>
       <c r="C1797">
-        <v>1.89721168306052</v>
+        <v>2.029061600110686</v>
       </c>
       <c r="D1797" t="s">
         <v>512</v>
       </c>
       <c r="E1797">
-        <v>1.895839163958783</v>
+        <v>1.945481115497461</v>
       </c>
       <c r="F1797">
         <v>-1</v>
       </c>
       <c r="G1797">
-        <v>0.01096278831693948</v>
+        <v>0.01171093839988931</v>
       </c>
       <c r="H1797">
-        <v>0.01050416083604122</v>
+        <v>0.01043451888450254</v>
       </c>
       <c r="I1797">
-        <v>0.001372519101736636</v>
+        <v>0.08358048461322554</v>
       </c>
       <c r="J1797">
         <v>0.994032525644623</v>
       </c>
       <c r="K1797">
-        <v>4.56</v>
+        <v>4.87</v>
       </c>
       <c r="L1797">
-        <v>6.43</v>
+        <v>6.87</v>
       </c>
       <c r="M1797">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="N1797">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="O1797">
         <v>1</v>
@@ -92104,46 +92104,46 @@
     </row>
     <row r="1798" spans="1:16">
       <c r="A1798" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1798" t="s">
         <v>357</v>
       </c>
       <c r="C1798">
-        <v>1.906853634599196</v>
+        <v>2.03816647895738</v>
       </c>
       <c r="D1798" t="s">
         <v>512</v>
       </c>
       <c r="E1798">
-        <v>1.895839163958783</v>
+        <v>1.945481115497461</v>
       </c>
       <c r="F1798">
         <v>-1</v>
       </c>
       <c r="G1798">
-        <v>0.0108531463654008</v>
+        <v>0.01142183352104262</v>
       </c>
       <c r="H1798">
-        <v>0.01050416083604122</v>
+        <v>0.01043451888450254</v>
       </c>
       <c r="I1798">
-        <v>0.01101447064041317</v>
+        <v>0.0926853634599194</v>
       </c>
       <c r="J1798">
         <v>0.994032525644623</v>
       </c>
       <c r="K1798">
-        <v>4.5</v>
+        <v>4.72</v>
       </c>
       <c r="L1798">
-        <v>6.38</v>
+        <v>6.73</v>
       </c>
       <c r="M1798">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="N1798">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="O1798">
         <v>1</v>
@@ -92154,116 +92154,116 @@
     </row>
     <row r="1799" spans="1:16">
       <c r="A1799" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1799" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C1799">
-        <v>2.029061600110686</v>
+        <v>1.091573753380461</v>
       </c>
       <c r="D1799" t="s">
-        <v>512</v>
+        <v>347</v>
       </c>
       <c r="E1799">
-        <v>1.895839163958783</v>
+        <v>1.506278882193858</v>
       </c>
       <c r="F1799">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1799">
-        <v>0.01171093839988931</v>
+        <v>0.01102842624661954</v>
       </c>
       <c r="H1799">
-        <v>0.01050416083604122</v>
+        <v>0.01161372111780614</v>
       </c>
       <c r="I1799">
-        <v>0.133222436151903</v>
+        <v>0.4147051288133978</v>
       </c>
       <c r="J1799">
-        <v>0.994032525644623</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1799">
-        <v>4.87</v>
+        <v>4.66</v>
       </c>
       <c r="L1799">
-        <v>6.87</v>
+        <v>6.06</v>
       </c>
       <c r="M1799">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1799">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
       <c r="O1799">
         <v>1</v>
       </c>
       <c r="P1799" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1800" spans="1:16">
       <c r="A1800" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B1800" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C1800">
-        <v>2.03816647895738</v>
+        <v>1.106278882193859</v>
       </c>
       <c r="D1800" t="s">
-        <v>512</v>
+        <v>347</v>
       </c>
       <c r="E1800">
-        <v>1.895839163958783</v>
+        <v>1.506278882193858</v>
       </c>
       <c r="F1800">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1800">
-        <v>0.01142183352104262</v>
+        <v>0.01121372111780614</v>
       </c>
       <c r="H1800">
-        <v>0.01050416083604122</v>
+        <v>0.01161372111780614</v>
       </c>
       <c r="I1800">
-        <v>0.1423273149985969</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1800">
-        <v>0.994032525644623</v>
+        <v>1.066185889832519</v>
       </c>
       <c r="K1800">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="L1800">
-        <v>6.73</v>
+        <v>6.16</v>
       </c>
       <c r="M1800">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1800">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
       <c r="O1800">
         <v>1</v>
       </c>
       <c r="P1800" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="1801" spans="1:16">
       <c r="A1801" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1801" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C1801">
-        <v>1.091573753380461</v>
+        <v>1.154810931346964</v>
       </c>
       <c r="D1801" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1801">
         <v>1.506278882193858</v>
@@ -92272,22 +92272,22 @@
         <v>1</v>
       </c>
       <c r="G1801">
-        <v>0.01102842624661954</v>
+        <v>0.01066518906865303</v>
       </c>
       <c r="H1801">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1801">
-        <v>0.4147051288133978</v>
+        <v>0.3514679508468941</v>
       </c>
       <c r="J1801">
         <v>1.066185889832519</v>
       </c>
       <c r="K1801">
-        <v>4.66</v>
+        <v>4.46</v>
       </c>
       <c r="L1801">
-        <v>6.06</v>
+        <v>5.91</v>
       </c>
       <c r="M1801">
         <v>4.74</v>
@@ -92304,16 +92304,16 @@
     </row>
     <row r="1802" spans="1:16">
       <c r="A1802" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1802" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C1802">
-        <v>1.106278882193859</v>
+        <v>1.104738814821843</v>
       </c>
       <c r="D1802" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1802">
         <v>1.506278882193858</v>
@@ -92322,22 +92322,22 @@
         <v>1</v>
       </c>
       <c r="G1802">
-        <v>0.01121372111780614</v>
+        <v>0.01029526118517816</v>
       </c>
       <c r="H1802">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1802">
-        <v>0.3999999999999995</v>
+        <v>0.4015400673720153</v>
       </c>
       <c r="J1802">
         <v>1.066185889832519</v>
       </c>
       <c r="K1802">
-        <v>4.74</v>
+        <v>4.31</v>
       </c>
       <c r="L1802">
-        <v>6.16</v>
+        <v>5.7</v>
       </c>
       <c r="M1802">
         <v>4.74</v>
@@ -92354,16 +92354,16 @@
     </row>
     <row r="1803" spans="1:16">
       <c r="A1803" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1803" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C1803">
-        <v>1.154810931346964</v>
+        <v>1.132969587702234</v>
       </c>
       <c r="D1803" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1803">
         <v>1.506278882193858</v>
@@ -92372,22 +92372,22 @@
         <v>1</v>
       </c>
       <c r="G1803">
-        <v>0.01066518906865303</v>
+        <v>0.01134703041229777</v>
       </c>
       <c r="H1803">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1803">
-        <v>0.3514679508468941</v>
+        <v>0.3733092944916248</v>
       </c>
       <c r="J1803">
         <v>1.066185889832519</v>
       </c>
       <c r="K1803">
-        <v>4.46</v>
+        <v>4.79</v>
       </c>
       <c r="L1803">
-        <v>5.91</v>
+        <v>6.24</v>
       </c>
       <c r="M1803">
         <v>4.74</v>
@@ -92404,16 +92404,16 @@
     </row>
     <row r="1804" spans="1:16">
       <c r="A1804" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1804" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C1804">
-        <v>1.104738814821843</v>
+        <v>1.093631446600559</v>
       </c>
       <c r="D1804" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1804">
         <v>1.506278882193858</v>
@@ -92422,22 +92422,22 @@
         <v>1</v>
       </c>
       <c r="G1804">
-        <v>0.01029526118517816</v>
+        <v>0.01128636855339944</v>
       </c>
       <c r="H1804">
         <v>0.01161372111780614</v>
       </c>
       <c r="I1804">
-        <v>0.4015400673720153</v>
+        <v>0.4126474355932999</v>
       </c>
       <c r="J1804">
         <v>1.066185889832519</v>
       </c>
       <c r="K1804">
-        <v>4.31</v>
+        <v>4.78</v>
       </c>
       <c r="L1804">
-        <v>5.7</v>
+        <v>6.19</v>
       </c>
       <c r="M1804">
         <v>4.74</v>
@@ -92454,46 +92454,46 @@
     </row>
     <row r="1805" spans="1:16">
       <c r="A1805" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1805" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C1805">
-        <v>1.132969587702234</v>
+        <v>1.582163495753663</v>
       </c>
       <c r="D1805" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1805">
-        <v>1.506278882193858</v>
+        <v>1.637386250415144</v>
       </c>
       <c r="F1805">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1805">
-        <v>0.01134703041229777</v>
+        <v>0.01117783650424634</v>
       </c>
       <c r="H1805">
-        <v>0.01161372111780614</v>
+        <v>0.01074261374958486</v>
       </c>
       <c r="I1805">
-        <v>0.3733092944916248</v>
+        <v>-0.05522275466148052</v>
       </c>
       <c r="J1805">
         <v>1.066185889832519</v>
       </c>
       <c r="K1805">
-        <v>4.79</v>
+        <v>4.5</v>
       </c>
       <c r="L1805">
-        <v>6.24</v>
+        <v>6.38</v>
       </c>
       <c r="M1805">
-        <v>4.74</v>
+        <v>4.27</v>
       </c>
       <c r="N1805">
-        <v>6.56</v>
+        <v>6.19</v>
       </c>
       <c r="O1805">
         <v>1</v>
@@ -92504,46 +92504,46 @@
     </row>
     <row r="1806" spans="1:16">
       <c r="A1806" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1806" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C1806">
-        <v>1.093631446600559</v>
+        <v>1.677674716515631</v>
       </c>
       <c r="D1806" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1806">
-        <v>1.506278882193858</v>
+        <v>1.637386250415144</v>
       </c>
       <c r="F1806">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1806">
-        <v>0.01128636855339944</v>
+        <v>0.01206232528348437</v>
       </c>
       <c r="H1806">
-        <v>0.01161372111780614</v>
+        <v>0.01074261374958486</v>
       </c>
       <c r="I1806">
-        <v>0.4126474355932999</v>
+        <v>0.04028846610048742</v>
       </c>
       <c r="J1806">
         <v>1.066185889832519</v>
       </c>
       <c r="K1806">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="L1806">
+        <v>6.87</v>
+      </c>
+      <c r="M1806">
+        <v>4.27</v>
+      </c>
+      <c r="N1806">
         <v>6.19</v>
-      </c>
-      <c r="M1806">
-        <v>4.74</v>
-      </c>
-      <c r="N1806">
-        <v>6.56</v>
       </c>
       <c r="O1806">
         <v>1</v>
@@ -92554,46 +92554,46 @@
     </row>
     <row r="1807" spans="1:16">
       <c r="A1807" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1807" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1807">
-        <v>1.568192342363713</v>
+        <v>1.69760259999051</v>
       </c>
       <c r="D1807" t="s">
         <v>512</v>
       </c>
       <c r="E1807">
-        <v>1.583415097025192</v>
+        <v>1.637386250415144</v>
       </c>
       <c r="F1807">
         <v>-1</v>
       </c>
       <c r="G1807">
-        <v>0.01129180765763629</v>
+        <v>0.01176239740000949</v>
       </c>
       <c r="H1807">
-        <v>0.01081658490297481</v>
+        <v>0.01074261374958486</v>
       </c>
       <c r="I1807">
-        <v>-0.01522275466147871</v>
+        <v>0.06021634957536648</v>
       </c>
       <c r="J1807">
         <v>1.066185889832519</v>
       </c>
       <c r="K1807">
-        <v>4.56</v>
+        <v>4.72</v>
       </c>
       <c r="L1807">
-        <v>6.43</v>
+        <v>6.73</v>
       </c>
       <c r="M1807">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="N1807">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="O1807">
         <v>1</v>
@@ -92604,46 +92604,46 @@
     </row>
     <row r="1808" spans="1:16">
       <c r="A1808" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B1808" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C1808">
-        <v>1.582163495753663</v>
+        <v>1.583415097025192</v>
       </c>
       <c r="D1808" t="s">
         <v>512</v>
       </c>
       <c r="E1808">
-        <v>1.583415097025192</v>
+        <v>1.637386250415144</v>
       </c>
       <c r="F1808">
         <v>-1</v>
       </c>
       <c r="G1808">
-        <v>0.01117783650424634</v>
+        <v>0.01081658490297481</v>
       </c>
       <c r="H1808">
-        <v>0.01081658490297481</v>
+        <v>0.01074261374958486</v>
       </c>
       <c r="I1808">
-        <v>-0.001251601271528457</v>
+        <v>-0.05397115338995206</v>
       </c>
       <c r="J1808">
         <v>1.066185889832519</v>
       </c>
       <c r="K1808">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L1808">
-        <v>6.38</v>
+        <v>6.2</v>
       </c>
       <c r="M1808">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="N1808">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="O1808">
         <v>1</v>
@@ -92654,116 +92654,116 @@
     </row>
     <row r="1809" spans="1:16">
       <c r="A1809" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1809" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C1809">
-        <v>1.677674716515631</v>
+        <v>0.9527648456254667</v>
       </c>
       <c r="D1809" t="s">
-        <v>512</v>
+        <v>347</v>
       </c>
       <c r="E1809">
-        <v>1.583415097025192</v>
+        <v>1.352764845625466</v>
       </c>
       <c r="F1809">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1809">
-        <v>0.01206232528348437</v>
+        <v>0.01136723515437453</v>
       </c>
       <c r="H1809">
-        <v>0.01081658490297481</v>
+        <v>0.01176723515437453</v>
       </c>
       <c r="I1809">
-        <v>0.09425961949043948</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1809">
-        <v>1.066185889832519</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1809">
-        <v>4.87</v>
+        <v>4.74</v>
       </c>
       <c r="L1809">
-        <v>6.87</v>
+        <v>6.16</v>
       </c>
       <c r="M1809">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1809">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
       <c r="O1809">
         <v>1</v>
       </c>
       <c r="P1809" t="s">
-        <v>625</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1810" spans="1:16">
       <c r="A1810" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B1810" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C1810">
-        <v>1.69760259999051</v>
+        <v>0.965151157098262</v>
       </c>
       <c r="D1810" t="s">
-        <v>512</v>
+        <v>347</v>
       </c>
       <c r="E1810">
-        <v>1.583415097025192</v>
+        <v>1.352764845625466</v>
       </c>
       <c r="F1810">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1810">
-        <v>0.01176239740000949</v>
+        <v>0.01043484884290174</v>
       </c>
       <c r="H1810">
-        <v>0.01081658490297481</v>
+        <v>0.01176723515437453</v>
       </c>
       <c r="I1810">
-        <v>0.1141875029653185</v>
+        <v>0.3876136885272041</v>
       </c>
       <c r="J1810">
-        <v>1.066185889832519</v>
+        <v>1.098572817378594</v>
       </c>
       <c r="K1810">
-        <v>4.72</v>
+        <v>4.31</v>
       </c>
       <c r="L1810">
-        <v>6.73</v>
+        <v>5.7</v>
       </c>
       <c r="M1810">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1810">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
       <c r="O1810">
         <v>1</v>
       </c>
       <c r="P1810" t="s">
-        <v>625</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1811" spans="1:16">
       <c r="A1811" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1811" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C1811">
-        <v>0.9527648456254667</v>
+        <v>0.977836204756537</v>
       </c>
       <c r="D1811" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1811">
         <v>1.352764845625466</v>
@@ -92772,22 +92772,22 @@
         <v>1</v>
       </c>
       <c r="G1811">
-        <v>0.01136723515437453</v>
+        <v>0.01150216379524346</v>
       </c>
       <c r="H1811">
         <v>0.01176723515437453</v>
       </c>
       <c r="I1811">
-        <v>0.3999999999999995</v>
+        <v>0.3749286408689292</v>
       </c>
       <c r="J1811">
         <v>1.098572817378594</v>
       </c>
       <c r="K1811">
-        <v>4.74</v>
+        <v>4.79</v>
       </c>
       <c r="L1811">
-        <v>6.16</v>
+        <v>6.24</v>
       </c>
       <c r="M1811">
         <v>4.74</v>
@@ -92799,21 +92799,21 @@
         <v>1</v>
       </c>
       <c r="P1811" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1812" spans="1:16">
       <c r="A1812" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1812" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C1812">
-        <v>1.010365234491473</v>
+        <v>0.9388219329303231</v>
       </c>
       <c r="D1812" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1812">
         <v>1.352764845625466</v>
@@ -92822,22 +92822,22 @@
         <v>1</v>
       </c>
       <c r="G1812">
-        <v>0.01080963476550853</v>
+        <v>0.01144117806706968</v>
       </c>
       <c r="H1812">
         <v>0.01176723515437453</v>
       </c>
       <c r="I1812">
-        <v>0.3423996111339935</v>
+        <v>0.4139429126951431</v>
       </c>
       <c r="J1812">
         <v>1.098572817378594</v>
       </c>
       <c r="K1812">
-        <v>4.46</v>
+        <v>4.78</v>
       </c>
       <c r="L1812">
-        <v>5.91</v>
+        <v>6.19</v>
       </c>
       <c r="M1812">
         <v>4.74</v>
@@ -92849,371 +92849,371 @@
         <v>1</v>
       </c>
       <c r="P1812" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1813" spans="1:16">
       <c r="A1813" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1813" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C1813">
-        <v>0.965151157098262</v>
+        <v>1.436422321796329</v>
       </c>
       <c r="D1813" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1813">
-        <v>1.352764845625466</v>
+        <v>1.499094069793406</v>
       </c>
       <c r="F1813">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1813">
-        <v>0.01043484884290174</v>
+        <v>0.01132357767820367</v>
       </c>
       <c r="H1813">
-        <v>0.01176723515437453</v>
+        <v>0.0108809059302066</v>
       </c>
       <c r="I1813">
-        <v>0.3876136885272041</v>
+        <v>-0.06267174799707753</v>
       </c>
       <c r="J1813">
         <v>1.098572817378594</v>
       </c>
       <c r="K1813">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="L1813">
-        <v>5.7</v>
+        <v>6.38</v>
       </c>
       <c r="M1813">
-        <v>4.74</v>
+        <v>4.27</v>
       </c>
       <c r="N1813">
-        <v>6.56</v>
+        <v>6.19</v>
       </c>
       <c r="O1813">
         <v>1</v>
       </c>
       <c r="P1813" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1814" spans="1:16">
       <c r="A1814" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1814" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C1814">
-        <v>0.977836204756537</v>
+        <v>1.519950379366249</v>
       </c>
       <c r="D1814" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1814">
-        <v>1.352764845625466</v>
+        <v>1.499094069793406</v>
       </c>
       <c r="F1814">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1814">
-        <v>0.01150216379524346</v>
+        <v>0.01222004962063375</v>
       </c>
       <c r="H1814">
-        <v>0.01176723515437453</v>
+        <v>0.0108809059302066</v>
       </c>
       <c r="I1814">
-        <v>0.3749286408689292</v>
+        <v>0.02085630957284312</v>
       </c>
       <c r="J1814">
         <v>1.098572817378594</v>
       </c>
       <c r="K1814">
-        <v>4.79</v>
+        <v>4.87</v>
       </c>
       <c r="L1814">
-        <v>6.24</v>
+        <v>6.87</v>
       </c>
       <c r="M1814">
-        <v>4.74</v>
+        <v>4.27</v>
       </c>
       <c r="N1814">
-        <v>6.56</v>
+        <v>6.19</v>
       </c>
       <c r="O1814">
         <v>1</v>
       </c>
       <c r="P1814" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1815" spans="1:16">
       <c r="A1815" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1815" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C1815">
-        <v>0.9388219329303231</v>
+        <v>1.544736301973039</v>
       </c>
       <c r="D1815" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1815">
-        <v>1.352764845625466</v>
+        <v>1.499094069793406</v>
       </c>
       <c r="F1815">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1815">
-        <v>0.01144117806706968</v>
+        <v>0.01191526369802696</v>
       </c>
       <c r="H1815">
-        <v>0.01176723515437453</v>
+        <v>0.0108809059302066</v>
       </c>
       <c r="I1815">
-        <v>0.4139429126951431</v>
+        <v>0.04564223217963281</v>
       </c>
       <c r="J1815">
         <v>1.098572817378594</v>
       </c>
       <c r="K1815">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="L1815">
+        <v>6.73</v>
+      </c>
+      <c r="M1815">
+        <v>4.27</v>
+      </c>
+      <c r="N1815">
         <v>6.19</v>
       </c>
-      <c r="M1815">
-        <v>4.74</v>
-      </c>
-      <c r="N1815">
-        <v>6.56</v>
-      </c>
       <c r="O1815">
         <v>1</v>
       </c>
       <c r="P1815" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1816" spans="1:16">
       <c r="A1816" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1816" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C1816">
-        <v>1.420507952753614</v>
+        <v>1.44317970075069</v>
       </c>
       <c r="D1816" t="s">
         <v>512</v>
       </c>
       <c r="E1816">
-        <v>1.44317970075069</v>
+        <v>1.499094069793406</v>
       </c>
       <c r="F1816">
         <v>-1</v>
       </c>
       <c r="G1816">
-        <v>0.01143949204724639</v>
+        <v>0.01095682029924931</v>
       </c>
       <c r="H1816">
-        <v>0.01095682029924931</v>
+        <v>0.0108809059302066</v>
       </c>
       <c r="I1816">
-        <v>-0.02267174799707661</v>
+        <v>-0.05591436904271596</v>
       </c>
       <c r="J1816">
         <v>1.098572817378594</v>
       </c>
       <c r="K1816">
-        <v>4.56</v>
+        <v>4.33</v>
       </c>
       <c r="L1816">
-        <v>6.43</v>
+        <v>6.2</v>
       </c>
       <c r="M1816">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="N1816">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="O1816">
         <v>1</v>
       </c>
       <c r="P1816" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1817" spans="1:16">
       <c r="A1817" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1817" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C1817">
-        <v>1.436422321796329</v>
+        <v>0.8652138986958411</v>
       </c>
       <c r="D1817" t="s">
-        <v>512</v>
+        <v>347</v>
       </c>
       <c r="E1817">
-        <v>1.44317970075069</v>
+        <v>1.265213898695841</v>
       </c>
       <c r="F1817">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1817">
-        <v>0.01132357767820367</v>
+        <v>0.01145478610130416</v>
       </c>
       <c r="H1817">
-        <v>0.01095682029924931</v>
+        <v>0.01185478610130416</v>
       </c>
       <c r="I1817">
-        <v>-0.00675737895436157</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="J1817">
-        <v>1.098572817378594</v>
+        <v>1.117043481287797</v>
       </c>
       <c r="K1817">
-        <v>4.5</v>
+        <v>4.74</v>
       </c>
       <c r="L1817">
-        <v>6.38</v>
+        <v>6.16</v>
       </c>
       <c r="M1817">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1817">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
       <c r="O1817">
         <v>1</v>
       </c>
       <c r="P1817" t="s">
-        <v>350</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1818" spans="1:16">
       <c r="A1818" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B1818" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C1818">
-        <v>1.519950379366249</v>
+        <v>0.8855425956495946</v>
       </c>
       <c r="D1818" t="s">
-        <v>512</v>
+        <v>347</v>
       </c>
       <c r="E1818">
-        <v>1.44317970075069</v>
+        <v>1.265213898695841</v>
       </c>
       <c r="F1818">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1818">
-        <v>0.01222004962063375</v>
+        <v>0.01051445740435041</v>
       </c>
       <c r="H1818">
-        <v>0.01095682029924931</v>
+        <v>0.01185478610130416</v>
       </c>
       <c r="I1818">
-        <v>0.07677067861555908</v>
+        <v>0.379671303046246</v>
       </c>
       <c r="J1818">
-        <v>1.098572817378594</v>
+        <v>1.117043481287797</v>
       </c>
       <c r="K1818">
-        <v>4.87</v>
+        <v>4.31</v>
       </c>
       <c r="L1818">
-        <v>6.87</v>
+        <v>5.7</v>
       </c>
       <c r="M1818">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1818">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
       <c r="O1818">
         <v>1</v>
       </c>
       <c r="P1818" t="s">
-        <v>350</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1819" spans="1:16">
       <c r="A1819" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B1819" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C1819">
-        <v>1.544736301973039</v>
+        <v>0.8893617246314518</v>
       </c>
       <c r="D1819" t="s">
-        <v>512</v>
+        <v>347</v>
       </c>
       <c r="E1819">
-        <v>1.44317970075069</v>
+        <v>1.265213898695841</v>
       </c>
       <c r="F1819">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1819">
-        <v>0.01191526369802696</v>
+        <v>0.01159063827536855</v>
       </c>
       <c r="H1819">
-        <v>0.01095682029924931</v>
+        <v>0.01185478610130416</v>
       </c>
       <c r="I1819">
-        <v>0.1015566012223488</v>
+        <v>0.3758521740643888</v>
       </c>
       <c r="J1819">
-        <v>1.098572817378594</v>
+        <v>1.117043481287797</v>
       </c>
       <c r="K1819">
-        <v>4.72</v>
+        <v>4.79</v>
       </c>
       <c r="L1819">
-        <v>6.73</v>
+        <v>6.24</v>
       </c>
       <c r="M1819">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="N1819">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
       <c r="O1819">
         <v>1</v>
       </c>
       <c r="P1819" t="s">
-        <v>350</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1820" spans="1:16">
       <c r="A1820" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1820" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C1820">
-        <v>0.8652138986958411</v>
+        <v>0.9346799853799395</v>
       </c>
       <c r="D1820" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1820">
         <v>1.265213898695841</v>
@@ -93222,22 +93222,22 @@
         <v>1</v>
       </c>
       <c r="G1820">
-        <v>0.01145478610130416</v>
+        <v>0.01172532001462006</v>
       </c>
       <c r="H1820">
         <v>0.01185478610130416</v>
       </c>
       <c r="I1820">
-        <v>0.3999999999999995</v>
+        <v>0.3305339133159011</v>
       </c>
       <c r="J1820">
         <v>1.117043481287797</v>
       </c>
       <c r="K1820">
-        <v>4.74</v>
+        <v>4.83</v>
       </c>
       <c r="L1820">
-        <v>6.16</v>
+        <v>6.33</v>
       </c>
       <c r="M1820">
         <v>4.74</v>
@@ -93254,16 +93254,16 @@
     </row>
     <row r="1821" spans="1:16">
       <c r="A1821" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1821" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C1821">
-        <v>0.8855425956495946</v>
+        <v>0.85053215944433</v>
       </c>
       <c r="D1821" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1821">
         <v>1.265213898695841</v>
@@ -93272,22 +93272,22 @@
         <v>1</v>
       </c>
       <c r="G1821">
-        <v>0.01051445740435041</v>
+        <v>0.01152946784055567</v>
       </c>
       <c r="H1821">
         <v>0.01185478610130416</v>
       </c>
       <c r="I1821">
-        <v>0.379671303046246</v>
+        <v>0.4146817392515105</v>
       </c>
       <c r="J1821">
         <v>1.117043481287797</v>
       </c>
       <c r="K1821">
-        <v>4.31</v>
+        <v>4.78</v>
       </c>
       <c r="L1821">
-        <v>5.7</v>
+        <v>6.19</v>
       </c>
       <c r="M1821">
         <v>4.74</v>
@@ -93304,46 +93304,46 @@
     </row>
     <row r="1822" spans="1:16">
       <c r="A1822" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1822" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C1822">
-        <v>0.8893617246314518</v>
+        <v>1.353304334204912</v>
       </c>
       <c r="D1822" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1822">
-        <v>1.265213898695841</v>
+        <v>1.420224334901107</v>
       </c>
       <c r="F1822">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1822">
-        <v>0.01159063827536855</v>
+        <v>0.01140669566579509</v>
       </c>
       <c r="H1822">
-        <v>0.01185478610130416</v>
+        <v>0.01095977566509889</v>
       </c>
       <c r="I1822">
-        <v>0.3758521740643888</v>
+        <v>-0.06692000069619475</v>
       </c>
       <c r="J1822">
         <v>1.117043481287797</v>
       </c>
       <c r="K1822">
-        <v>4.79</v>
+        <v>4.5</v>
       </c>
       <c r="L1822">
-        <v>6.24</v>
+        <v>6.38</v>
       </c>
       <c r="M1822">
-        <v>4.74</v>
+        <v>4.27</v>
       </c>
       <c r="N1822">
-        <v>6.56</v>
+        <v>6.19</v>
       </c>
       <c r="O1822">
         <v>1</v>
@@ -93354,46 +93354,46 @@
     </row>
     <row r="1823" spans="1:16">
       <c r="A1823" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B1823" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C1823">
-        <v>0.85053215944433</v>
+        <v>1.429998246128427</v>
       </c>
       <c r="D1823" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="E1823">
-        <v>1.265213898695841</v>
+        <v>1.420224334901107</v>
       </c>
       <c r="F1823">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1823">
-        <v>0.01152946784055567</v>
+        <v>0.01231000175387157</v>
       </c>
       <c r="H1823">
-        <v>0.01185478610130416</v>
+        <v>0.01095977566509889</v>
       </c>
       <c r="I1823">
-        <v>0.4146817392515105</v>
+        <v>0.009773911227320298</v>
       </c>
       <c r="J1823">
         <v>1.117043481287797</v>
       </c>
       <c r="K1823">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="L1823">
+        <v>6.87</v>
+      </c>
+      <c r="M1823">
+        <v>4.27</v>
+      </c>
+      <c r="N1823">
         <v>6.19</v>
-      </c>
-      <c r="M1823">
-        <v>4.74</v>
-      </c>
-      <c r="N1823">
-        <v>6.56</v>
       </c>
       <c r="O1823">
         <v>1</v>
@@ -93404,46 +93404,46 @@
     </row>
     <row r="1824" spans="1:16">
       <c r="A1824" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B1824" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1824">
-        <v>1.336281725327645</v>
+        <v>1.457554768321598</v>
       </c>
       <c r="D1824" t="s">
         <v>512</v>
       </c>
       <c r="E1824">
-        <v>1.363201726023838</v>
+        <v>1.420224334901107</v>
       </c>
       <c r="F1824">
         <v>-1</v>
       </c>
       <c r="G1824">
-        <v>0.01152371827467235</v>
+        <v>0.0120024452316784</v>
       </c>
       <c r="H1824">
-        <v>0.01103679827397616</v>
+        <v>0.01095977566509889</v>
       </c>
       <c r="I1824">
-        <v>-0.02692000069619382</v>
+        <v>0.03733043342049136</v>
       </c>
       <c r="J1824">
         <v>1.117043481287797</v>
       </c>
       <c r="K1824">
-        <v>4.56</v>
+        <v>4.72</v>
       </c>
       <c r="L1824">
-        <v>6.43</v>
+        <v>6.73</v>
       </c>
       <c r="M1824">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="N1824">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="O1824">
         <v>1</v>
@@ -93454,151 +93454,51 @@
     </row>
     <row r="1825" spans="1:16">
       <c r="A1825" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B1825" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C1825">
-        <v>1.353304334204912</v>
+        <v>1.363201726023838</v>
       </c>
       <c r="D1825" t="s">
         <v>512</v>
       </c>
       <c r="E1825">
-        <v>1.363201726023838</v>
+        <v>1.420224334901107</v>
       </c>
       <c r="F1825">
         <v>-1</v>
       </c>
       <c r="G1825">
-        <v>0.01140669566579509</v>
+        <v>0.01103679827397616</v>
       </c>
       <c r="H1825">
-        <v>0.01103679827397616</v>
+        <v>0.01095977566509889</v>
       </c>
       <c r="I1825">
-        <v>-0.009897391818926238</v>
+        <v>-0.05702260887726851</v>
       </c>
       <c r="J1825">
         <v>1.117043481287797</v>
       </c>
       <c r="K1825">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L1825">
-        <v>6.38</v>
+        <v>6.2</v>
       </c>
       <c r="M1825">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="N1825">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="O1825">
         <v>1</v>
       </c>
       <c r="P1825" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="1826" spans="1:16">
-      <c r="A1826" s="1">
-        <v>6</v>
-      </c>
-      <c r="B1826" t="s">
-        <v>358</v>
-      </c>
-      <c r="C1826">
-        <v>1.429998246128427</v>
-      </c>
-      <c r="D1826" t="s">
-        <v>512</v>
-      </c>
-      <c r="E1826">
-        <v>1.363201726023838</v>
-      </c>
-      <c r="F1826">
-        <v>-1</v>
-      </c>
-      <c r="G1826">
-        <v>0.01231000175387157</v>
-      </c>
-      <c r="H1826">
-        <v>0.01103679827397616</v>
-      </c>
-      <c r="I1826">
-        <v>0.06679652010458881</v>
-      </c>
-      <c r="J1826">
-        <v>1.117043481287797</v>
-      </c>
-      <c r="K1826">
-        <v>4.87</v>
-      </c>
-      <c r="L1826">
-        <v>6.87</v>
-      </c>
-      <c r="M1826">
-        <v>4.33</v>
-      </c>
-      <c r="N1826">
-        <v>6.2</v>
-      </c>
-      <c r="O1826">
-        <v>1</v>
-      </c>
-      <c r="P1826" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="1827" spans="1:16">
-      <c r="A1827" s="1">
-        <v>7</v>
-      </c>
-      <c r="B1827" t="s">
-        <v>359</v>
-      </c>
-      <c r="C1827">
-        <v>1.457554768321598</v>
-      </c>
-      <c r="D1827" t="s">
-        <v>512</v>
-      </c>
-      <c r="E1827">
-        <v>1.363201726023838</v>
-      </c>
-      <c r="F1827">
-        <v>-1</v>
-      </c>
-      <c r="G1827">
-        <v>0.0120024452316784</v>
-      </c>
-      <c r="H1827">
-        <v>0.01103679827397616</v>
-      </c>
-      <c r="I1827">
-        <v>0.09435304229775987</v>
-      </c>
-      <c r="J1827">
-        <v>1.117043481287797</v>
-      </c>
-      <c r="K1827">
-        <v>4.72</v>
-      </c>
-      <c r="L1827">
-        <v>6.73</v>
-      </c>
-      <c r="M1827">
-        <v>4.33</v>
-      </c>
-      <c r="N1827">
-        <v>6.2</v>
-      </c>
-      <c r="O1827">
-        <v>1</v>
-      </c>
-      <c r="P1827" t="s">
         <v>626</v>
       </c>
     </row>
